--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -20,6 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Rasters_Audit" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Audit_Verdicts" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unknowns" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Mods" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pixel_Forensics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effective_Resolution" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance_Chain" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dating_Methods" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MASTER'!$A$1:$P$221</definedName>
@@ -34,6 +39,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Lake_Rasters_Audit'!$A$1:$L$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Lake_Audit_Verdicts'!$A$1:$A$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Unknowns'!$A$1:$A$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Processing_Mods'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Pixel_Forensics'!$A$1:$D$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Effective_Resolution'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Provenance_Chain'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Dating_Methods'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5430,6 +5440,6282 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>File / product</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Source &amp; sensor</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Band composition</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Resampling</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Mosaicking</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Radiometry</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Orthorectification DEM</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Other modifications</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Impact on a canopy model</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Verbatim quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif — held pixels came from the KingCo_Aerial_2000 tile cache; the Edmonds/SW-Snohomish sub-product is IMAGE_Ortho2000EmergeNAT, a 'natural color DERIVATIVE'</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Emerge, Inc. (acquisition) → King County DNR (derivative). Sensor: Eastman Kodak DSC460CIR digital imager, 3072x2048 focal plane array.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>SYNTHESISED BLUE — and worse than previously understood. The sensor never recorded blue at all, AND all three delivered bands are NIR-contaminated. Delivered bands = green, red, near-infrared. The held R,G,B are all derived.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Native 2 ft (0.6096 m). Held file is 0.5972 m Web-Mercator = 0.4011 m ground at 47.81N → the held 2000 raster is OVERSAMPLED ~1.5x relative to native GSD (measured). Also reprojected UTM10/NAD83 → WA State Plane HPGN via per-band ArcInfo GRID conversion and retiling before the natural-colour step.</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Distributed as TIFF / MrSID mosaic (emerge_nat.sid). The held copy additionally passed through the JPEG tile cache (see other_modifications).</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Delivered as 373 tiles in 18 panels; retiled to a 10,000-ft fishnet; no colour balancing across frames documented; 'Detailed photodate information is not available.'</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. A DELIBERATE CONTRAST STRETCH WAS APPLIED — this is a second, previously undocumented modification. [EmergeNAT FGDC] 'An algorithm was developed in ArcInfo AML macro language that mimics the ERDAS natural color model. The algorithm was applied to the retiled images to produce a natural color derivative. The initial derivative lacked an adequate contrast stretch and thus appeared overly dark. Additional experimentation developed a standard deviation contrast stretch applied using the SLICE command in ArcInfo grid to trim the higher end of the digital number range. This reduced slightly the full spectral range of the image, yet significantly improved the overall viewability of the imagery.'</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>'The raw images were georectified by the vendor using available 10m DEM supplemented by limited GPS ground control.' — a 10-METRE DEM, by far the coarsest terrain model in the whole King series (2002 onward use LiDAR/photogrammetric DTMs). CE90 4 m, worse in the northern third of the project area (which is where Edmonds sits).</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Cache layer: REST reports singleFusedMapCache=true, tileInfo format 'MIXED', compressionQuality 80. Corroborating URLs: https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2000EmergeNAT ; https://web.archive.org/web/20220518185439id_/https://www5.kingcounty.gov/sdc/raster/ortho/Ortho2000EmergeCIRMetadata.html ; https://gismaps.kingcounty.gov/arcgis/rest/services/BaseMaps/KingCo_Aerial_2000/MapServer?f=json</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Catastrophic for cross-year comparison. Because green-filtered pixels = green + NIR, vegetation is boosted in the GREEN channel of 2000 specifically — no other King year has NIR bleeding into visible bands. Measured: 2000 is the ONLY year where mean B &gt; mean R (B/R = 1.123; every other year 0.72–0.98) and it has the highest G/R of the series (1.204 vs 0.95–1.13). A canopy model trained on other years will see 2000 as a different sensor; any 'greenness' change between 2000 and later years is sensor physics plus an ArcInfo stretch, not vegetation.</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20220518193529id_/https://www5.kingcounty.gov/sdc/raster/ortho/Ortho2000EmergeNATMetadata.html</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>[EmergeCIR FGDC, sensor] 'The sensor used is Eastman Kodak DSC460CIR imager with a 3072 x 2048 pixel focal plan array. The sensor incorporates a bandpass filter on the lens that has a -3dB cutoff for wavelengths of less than 500 nm and greater than 800 nm. Blue light is outside the filter's bandpass, so that none of the incident blue light reaches the sensor. The red,green and blue filter elements are all transparent to the reflected NIR radiance passed in the 700 to 800 nm region. Thus, the green filtered pixels respond to green and NIR, the red filtered array elements respond to red plus NIR radiance, while the blue-filtered pixels respond to NIR radiance only.' | [SDC] 'It is considered a natural color derivative rather than a true natural color product as the original data is limited to 3-bands only, omitting the blue band. An algorithm was applied to the original data to closely mimic a natural color image.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif — over Edmonds the served pixels are the USGS/NGA 'High Resolution Orthoimage, Seattle/Tacoma' product, NOT the King County county-wide project</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>USGS, flown by Selkirk Remote Sensing; DEM and AT by Triathlon Ltd (Richmond BC); retiled by King County</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour from FILM. No synthesised band found. (Contrast with 2000: this is the first true-blue King year.)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>TWO resamplings. (1) 'acquired at a resolution of 0.33 meter per pixel ... and resampled to 1 foot per pixel' (REST). Delivered product FGDC states Abscissa_Resolution 0.300000 m in UTM10; distributed King tiles are named '_02n098' = 0.98 ft GSD. (2) The held file is 0.5972 m Web-Mercator = 0.4011 m ground → DOWNSAMPLED ~1.32x from the 1 ft product (measured).</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>LOSSY JP2 (JPEG-2000) at the King County retiling step, then the JPEG tile cache on top (MIXED, quality 80).</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>'Orthorectifications were performed on only the core portion of each image in order to minimize inherent horizontal displacement that occurs radially from the photocenter.' No colour balancing across frames documented.</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Not stated. Film-scanned analogue source (stable-base material at 1:15,000) — a fundamentally different radiometric response curve from every digital-sensor year in the series. No stretch or normalisation documented.</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Z/I ISAT aerial triangulation with ABGPS + ground control; automatic DEM correlation by Triathlon. Notable: 'For this project, the software was instructed to model flat terrain and perform a high level of data smoothing.' RMSE 0.40 m on 41 checkpoints. Then: 'King County reprojected the image files to WA State Plane North, NAD83/91 (HPGN) datum. The data was then retiled to the standard King County tiling scheme for raster data. The township-range tiles were compressed into JP2 format.'</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>The live SDC page for this layer, https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002USGSNAT, returns HTTP 500 — the lineage above was recovered from the Internet Archive. Its FGDC bounding box is a single-frame template (-122.052..-122.038, 47.589..47.603), so it documents the process steps, not the Edmonds footprint specifically.</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Film + 0.33 m→1 ft resample + JP2 + cache JPEG = a heavily smoothed, twice-lossy image. Measured G/R falls from 1.204 (2000) to 1.063 (2002) — the single largest step in the whole series, and it lands exactly on the sensor change (NIR-contaminated digital CIR → film natural colour). Any 2000→2002 'canopy loss' is this.</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20170602122731id_/http://www5.kingcounty.gov:80/sdc/raster/ortho/Ortho2002USGSNATMetadata.html</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>[REST] 'The imagery for western King County, southwestern Snohomish County, and northwestern Pierce County was acquired at a resolution of 0.33 meter per pixel for USGS under leaf-on conditions and resampled to 1 foot per pixel. Imagery for all of King County was acquired as a separate project at a resolution of 1 foot per pixel. In this tiled, cached map service mosaic, the USGS imagery supplants the full-county imagery set which remains visible to represent eastern King County.' | [USGS FGDC] 'Type_of_Source_Media: Stable-base material' / 'Source_Scale_Denominator: 1:15,000' / 'Originator: Selkirk Remote Sensing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>CONTEXT ROW (not the held Edmonds pixels): IMAGE_Ortho2002KCNAT — the separate King-County-only 2002 project that the USGS imagery 'supplants' in the west</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Bergman and Associates under subcontract to 3di West; scanned by 3di, Easton MD</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour, film</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>0.77 ft and 1.13 ft raw scans both resampled to a single 1 ft output GSD — two different photo scales homogenised into one mosaic</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>MrSID 1:7 lossy</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>'Default seamline matching was used.' Auto seamlines never reviewed or edited.</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>'Data was orthorectified using Lidar Digital Ground Model terrain information' (2002 LiDAR, resampled to 12 ft, unedited); SOCET SET Ortho/Mosaic module. 'Bridges and overpasses/interchanges were not modeled.'</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Included only so the 3di/Bergman film lineage is NOT mis-attributed to the held 2002 Edmonds pixels. Per the REST description the USGS product supplants this one in the west.</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>None directly — but if any part of the Edmonds footprint falls outside the USGS AOI, that strip has a different sensor, scan scale, DEM and compression from the rest of the same file. Worth a seam check.</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002KCNAT</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>'Original diapositive images were scanned at 11.5 microns yielding pre-orthophoto rectification raw pixal sizes of 0.77 feet for the 1"=1700' and 1.13 feet for the 1"=2500' data sets. Final output ground sample distance (gsd) is 1 feet for entire mosaic. Data is provided in MrSid compressed format at a 1:7 ratio. This lossy compression results in variable data quality and clarity.' | 'The ortho/mosaic seamline autogenerated by the software were not reviewed or edited.' | 'The orthophotos were not given a comprehensive quality evaluation.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif — IMAGE_Ortho2005AerialsExpressNAT</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Aerials Express (vendor change from the 2002 USGS/Selkirk film project)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band found. Sensor/camera NOT STATED anywhere on the page.</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Native 1 ft (0.3048 m). Held file is 0.2986 m Web-Mercator = 0.2005 m ground → the held 2005 raster is OVERSAMPLED ~1.5x relative to native GSD (measured).</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>MrSID 7x lossy, then the JPEG tile cache (MIXED, quality 80)</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>'The remaining tiles were submitted to an ArcInfo AML-driven grid routine to create temporary tile sets clipped to each of the townships' then mosaicked. No seamline or colour-balancing treatment documented.</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no bit depth, stretch, or normalisation stated</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM/DTM named, no AT described. King County explicitly did no acceptance geometry work: tiles were merely 'inventoried' and edge tiles removed.</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>Black (0,0,0) fill bands present in some tiles — must be masked before any statistic (measured black fraction in my windows was ~0%, but it exists elsewhere).</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>Oversampled 1.5x means 2005 looks smoother/blurrier per real ground feature than its stated 1 ft implies — crown edges and small-gap detection will behave differently than in 2007/2009 at the same held pixel size. Radiometry is undocumented, so 2005 must be treated as an unconstrained radiometric baseline.</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2005AerialsExpressNAT</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>[SDC] 'Year 2005 (July) Aerials Express Natural Color orthoimagery acquired by King County for internal business and agency use only. Pixel resolution is 1.0 foot and coverage is western, urbanized, portions of King County, southwestern Snohomish County and a buffer into Pierce County.' | [change history 9/1/2006] 'These tile sets were then mosaiced and compressed (7x) using MrSid software.' | [FGDC] 'Some tiles contain black (0 value) bands for portion of the...'</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif — IMAGE_Ortho2007KCNAT (Pictometry; vendor change from Aerials Express)</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera/sensor NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>MULTIPLE, NEAREST-NEIGHBOUR. West county native 0.5 ft; documented derived products at 1.0 ft and 2.0 ft, all NEAREST NEIGHBOR. Held file is 0.2005 m ground → DOWNSAMPLED ~1.32x from 0.5 ft native (measured). Which generation fed the cache is not stated.</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>CASCADED LOSSY: JPEG-2000 at 75% quality into SDE, MrSID at 20x / 15x / 50x for various tile levels (7500-ft tiles lossless), then the tile cache — and 2007 is the ONE year whose cache is pure 'JPEG' rather than 'MIXED' (quality 80).</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry 'sector' tiles mosaicked by King County; 'Because of the rotation inherent in the sector pieces, introduced during reprojection by Pictometry, the edges of the mosaics are not orthogonal and thus tile edges show black (0,0,0) masks.' Resolution boundary is abrupt: 'the change from 6 inch resolution to 12 inch resolution areas is often abrupt due both to the change in resolution and the fact that the two resolution areas were captured on different flights lines at different times.'</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>'Pixel Type ..................: uchar' (8-bit) in the SDE raster dump. No stretch or colour balancing documented — and Pictometry's internal radiometric handling is a black box in every King page.</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>'The Contractor was provided with high-quality digital ground model data (in ascii format) for use as a Digital Terrain Model for orthorectification. They were also provided with a street centerline model and an overpass/bridge layer to aid in seamline creation or elevated structure correction. Though the DTM data was used for the orthorectification, the vendor did not ameliorate any of the other non-rectified artifacts.'</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>WHITE (255,255,255) and BLACK (0,0,0) fill are both documented for this year: 'using white pixels (255,255,255) for those portions of the tile without imagery'. Both must be masked before statistics.</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Nearest-neighbour resampling (not bilinear/cubic) preserves hard edges but aliases fine texture — canopy texture features will differ systematically from bilinear-resampled years (2012). Cascaded JP2-75% + MrSID + JPEG-cache means 2007 carries the most compression generations of any year I could document.</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2007KCNAT</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>[FGDC/SDC] 'Import parameters include jp2000 compression at 75% quality. Mosaics were pyramided upon completion of import using jp2000 compression.' | 'All 0.5 foot resolution image tiles were resampled to 1.0 foot pixel using NEAREST NEIGHBOR.' | 'All 1.0 foot resampled imagery was resampled to 2.0 foot pixel resolution for use in creation of higher-level mosaics ... Resampling was performed using NEAREST NEIGHBOR.' | 'The mosaic tiles also show numerous examples of mis-alignment along seamlines with offsets and other artifacts that indicate the images of different vintage were mosaicked.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif — IMAGE_Ortho2009KCNAT (Pictometry)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera/sensor NOT STATED. (A separate 2009 Aerials Express CIR product exists — 'Imagery has an infrared band in place of the blue band of regular RGB natural color imagery' — but it is a different layer and is not what the KingCo_Aerial_2009 cache serves.)</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Native 0.5 ft west. Held file 0.2005 m ground → DOWNSAMPLED ~1.32x (measured). The same NEAREST NEIGHBOR 1 ft / 2 ft derivative chain as 2007 is carried in the lineage.</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>MrSID 15x township tiles / lossless 7500 tiles / 50x keyregion, then JPEG tile cache at quality 75 (not 80).</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>'The mosaic tiles also show numerous examples of mis-alignment along seamlines with offsets and other artifacts that indicate the images of different vintage were mosaicked.' Acquisition spans Apr 21 – Oct 5 2009 — nearly six months of phenology inside ONE mosaic.</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND. But note the CACHE differs: tileInfo compressionQuality is 75 for 2009, versus 80 for every other King year except 2012 (also 75).</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Identical wording to 2007: 'The Contractor was provided with high-quality digital ground model data (in ascii format) for use as a Digital Terrain Model for orthorectification ... the vendor did not ameliorate any of the other non-rectified artifacts.' The DTM is not named or dated.</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>Snow contamination was found and catalogued by King County QC ('Snow and Smears'). Per-image acquisition dates only exist in a separate index (plibrary3/reference/indexes/Pictometry09).</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>2009 measured the HIGHEST naive greenness of the whole series in my windows (frac G=max 0.8214, G/R 1.134) despite being an ordinary RGB year — an Apr-to-Oct acquisition window means different parts of one mosaic are at different phenological stages. Combined with the lower cache quality (75), 2009 is a strong candidate for a fake temporal spike.</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2009KCNAT</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>[REST] 'Western, urbanized, portion of King County acquired at 0.5-foot resolution. Eastern King County acquired at 1.0-foot resolution with built-up (inset) areas also at 0.5-foot. Orthoimagery was acquired from April through October by Pictometry.' | [FGDC] Beginning_Date: 20090421 / Ending_Date: 20091005 | [SDC] 'Orthoimage tiles are composites of individual images and have undergone reprocessing. As such the date stamp on the sector tiles or their derivatives is not correct.' | [SDC QC] 'All 7500 SID tiles were inspected for QC. Snow and Smears were identified, digitized, and coded.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif — IMAGE_Ortho2012KCNAT. STRUCTURALLY A DIFFERENT PRODUCT: a USGS/NGA public-domain deliverable, not a King County basemap contract.</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Mapcon Mapping (flight); USGS/NGA funded via the local orthoimagery consortium. Cameras: Vexcel UltraCamX and UltraCamXp.</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>'3-band, RGB GeoTiff'. No synthesised band. This is the only King year with a NAMED CAMERA MODEL.</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>BILINEAR (unlike 2007/2009's nearest neighbour): State Plane 0.25/0.50/1.00 ft orthos → resampled to 0.984252 ft (0.3 m) → reprojected SP HARN → UTM10 → clipped. Native 1/3 m; held file is 0.2005 m ground → the held 2012 raster is OVERSAMPLED ~1.66x, the most oversampled year in the series (measured).</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>MrSID lossless review copies; the cache is JPEG at compressionQuality 75 (not 80) — 2012 shares the lower cache quality with 2009.</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Tile-based with 12-ft buffers and clean-edge clipping; no colour balancing documented. Acquisition window is only 6.5 weeks (tightest of the series).</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>BIT-DEPTH CHANGE IS DOCUMENTED: the pipeline ran 16-bit and was converted down — 'Copy 16bit UTM RGB image back to 8bit unsigned RGB image'. The mapping function used for that 16→8 conversion is not stated. No stretch policy documented.</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>'Once accepted, updates to the Digital Elevation Model (DEM) were performed over a large portion of the 0.25 project area. Once the DEM work was finished, ortho production began.' DEM not otherwise named. Full AT with softcopy 3D review.</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Public-domain USGS/NGA product with a different acceptance standard from the licensed Pictometry basemaps that bracket it. The cache reprojects SP→UTM→WebMercator, i.e. three projections deep.</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>March 23 – May 8 is EARLY SPRING. Deciduous leaf-out in the Puget lowlands is incomplete over much of that window, so 2012 systematically under-represents deciduous canopy relative to the July/August years (2002, 2005, 2007). Measured frac(G=max) drops to 0.6458 from 0.8214 in 2009. Bilinear resampling + 1.66x oversampling also makes 2012 the smoothest year in the series.</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20170604230237id_/http://www5.kingcounty.gov:80/sdc/raster/ortho/Ortho2012KCNATMetadata.html</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>[FGDC/SDC] 'Both aircraft in the 0.25 foot area used an UltraCamX camera - one which was calibrated 1/6/12 and the other 12/20/10. The aircraft in used for the 0.50 and 1.00 foot areas used an UltraCamXp camera calibrated 5/25/11.' | '4. Extract SP image by buffered tile, resample to .984252 feet (.3 meter) using Bilinear method.' | '7. Copy 16bit UTM RGB image back to 8bit unsigned RGB image with world file and overview files.' | 'Each UTM pixel represents a resampling of the original State Plane RGB image pixel.' | 'The imagery was collected between March 23, 2012 and May 8, 2012.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif — IMAGE_Ortho2013KCNAT. THE REGIME BREAK: first 'Orthogonal Base Imagery' visualisation mosaic, first year held at Web-Mercator z20.</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Native 4 in (0.1016 m) west. Held file 0.1003 m ground → essentially 1:1 (measured) — 2013 is the only year whose held resolution matches native.</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE TILES WERE DELIVERED AS JPG. King's MrSID step was lossless, but it was losslessly compressing already-JPEG-degraded input, then the tile cache adds JPEG again (tileInfo format 'Mixed', quality 80).</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Vendor-mosaicked with no seamline treatment documented; King re-mosaicked to 7500-ft tiles. 'When a 7500 grid cell spanned both 4-inch and 9-inch input tiles, the tile was assinged the higher resolution suffix' — i.e. resolution labels are unreliable at boundaries.</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND. The page explicitly concedes uncontrolled tonal variation across tiles due to lighting — i.e. NO colour balancing was applied and none is claimed.</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM/DTM named anywhere. King County states it is not true orthophoto imagery.</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>The FGDC date range is impossible and proves the metadata is unreliable: 'Beginning_Date: 20130601' / 'Ending_Date: 20090807'. Real per-image dates live only in ORTHO_IMAGE13_AREA.</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>This is where the series changes character. Measured frac(G=max) falls from 0.6458 (2012) to 0.5119 and never recovers above 0.52 again; every year 2000–2012 is &gt;=0.51 and every year 2013–2023 is &lt;=0.51. B/R also drops to 0.778, the lowest so far. A JPG-sourced 'visualization product' with admitted uncontrolled tonal variation is not radiometrically comparable to the 2000–2012 mapping-grade orthos.</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20220518204531id_/https://www5.kingcounty.gov/sdc/raster/ortho/Ortho2013KCNATMetadata.fgdc.html</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>[FGDC] 'Pictometry provided their orthogonal tiles in two folders: 4 inch and 9 inch, both in JPG format. The 4-inch tiles are 2700 feet on edge and the 9 inch tiles are 5400 feet on edge. A python routine was created to mosaic the tiles into new 7500x7500-foot tiles in MrSid format. The compression was lossless.' | 'Because this imagery is not true \'orthophoto\' imagery there are some tonal variations across many of the tiles due to variations in lighting conditions. The mosaic tiles also show numerous examples of mis-alignment along seamlines with offsets and other artifacts that indicate the images of different vintage were mosaicked.' | 'No independent evaluation of horizontal accuracy was performed and the vendor provided no accuracy evaluation report.' | [purpose] 'This ortho-mosaic is a visualization product and is not intended or valid for authoritative or definitive use.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif — IMAGE_Ortho2015KCNAT (Pictometry 3-inch orthogonal base). NOTE: this is NOT the GeoTerra 2015 regional project (see next row).</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Native 3 in (0.0762 m) west. Held file 0.1003 m ground → DOWNSAMPLED ~1.32x (measured).</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Not stated for the source product; cache is 'MIXED' at quality 80.</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>'Mosaicing was performed using Pictometry software' — vendor black box, no seamline or colour-balance detail.</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — Pictometry's mosaicking software is the entire documented processing chain and its radiometric behaviour is undisclosed.</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM named. The only geometry step disclosed is GPS/INS post-processing against NGS CORS.</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>The 2015 FGDC is a copy of a POLYGON tiling-index record ('Geospatial_Data_Presentation_Form: vector digital data', SDTS GT-polygon, Point_and_Vector_Object_Count: 1) with imagery text pasted in — another sign the 2013+ metadata is boilerplate, not real lineage.</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>MID-FEBRUARY START = LEAF-OFF. Measured frac(G=max) collapses to 0.2454, the lowest of any year up to that point, while mean(2G-R-B) also hits its series minimum (14.4). Part of the 'greenness drift' at 2015 is simply that the mosaic contains February deciduous canopy. A model asked to compare 2013 vs 2015 will read leaf-off as canopy loss.</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20220518184946id_/https://www5.kingcounty.gov/sdc/raster/ortho/Ortho2015KCNATMetadata.fdgc.html</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>[FGDC] 'Beginning_Date: 20150217' / 'Ending_Date: 20150621' | [REST] 'The imagery was captured from mid-February 2015 through late June 2015.' | [FGDC process steps, in full] 'GPS/INS processing: Data was post-processed using NGS CORS base station data.' and 'Mosaicing: Mosaicing was performed using Pictometry software' | [purpose] 'This ortho-mosaic is a visualization product and is not intended or valid for authoritative or definitive use, nor is it suitable for submittal to the USGS for funding reimbursement in such programs.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>CONTEXT ROW (not the held pixels): IMAGE_Ortho2015ReducedResNAT — the GeoTerra 2015 Western Washington Regional project. Included only to prevent mis-attribution of its rich lineage to the held 2015 file.</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>GeoTerra, Inc.; multiple Vexcel UltraCam cameras (Hawk, X, Xp, Eagle); QA by Miller Creek Aerials Mapping</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Acquired 4-band 16-bit; distributed as '2 foot, 3-band (RGB), 8-bit/band'</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Acquired &lt;0.9 ft, delivered at 2 ft</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>'available in uncompressed GeoTIFF format' — the only uncompressed King-catalogued ortho product</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Inpho OrthoVista; seamlines automatic + manually adjusted in Ortho Master</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>16 bit/band acquired, 8 bit/band delivered; 'full-histogram (unclipped)' UltraMap output — the only King-catalogued product that states its histogram was NOT clipped.</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Updated/corrected DEM including 2013–2014 LiDAR over 25% of the 12-inch area; AT with AGPS+IMU</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Explicitly flown 'during leaf-off ... conditions'. This corroborates that the 2015 Puget-region flying season was deliberately leaf-off.</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Not used by the pipeline. Its value here is as independent confirmation that 2015 regional acquisition was leaf-off by design.</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2015ReducedResNAT</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>'Acquisition of 4-band, 16 bit/band, digital aerial imagery at less than 0.9 ft pixel resolution using multiple Vexcel UltraCam aerial mapping cameras (Hawk, X, Xp and Eagle) during leaf-off and high sun-angle conditions. ... Post-flight, raw images were processed using propietary UltraMap software into full-histogram (unclipped) images in a final *.TIF format.' | 'Rectification and mosaicing of all aerial photos using Inpho OrthoVista software, with the combined input of AT, updated DTM and seamlines.' | 'The most nadir portion of every photo was identified by creating "seamlines" used to stitch the rectified images together. Seamlines were created using a combination of automatic and manual methods.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif — IMAGE_Ortho2017KCNAT (Pictometry 3-inch orthogonal base)</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Native 3 in (0.0762 m) west. Held file 0.1003 m ground → DOWNSAMPLED ~1.32x (measured).</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Cache 'MIXED' at quality 80</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>'Mosaicing was performed using Pictometry software' — same black box as 2015. This is the LAST year mosaicked with Pictometry software.</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM named</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>The SDC page for 2017 is byte-for-byte the same length as 2015's (56,957 bytes) and 2019/2021's (56,966) — the 2015–2021 catalogue entries are a single template with the year swapped. Treat their 'lineage' as nominal.</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>Capture window 2/17 to 10/30 is EIGHT AND A HALF MONTHS — the widest of any King year. One mosaic therefore contains bare February canopy and full October canopy side by side, which is a spatially-structured phenology artifact, not noise. Measured G/R = 1.008: 2017 is the last year where green still exceeds red.</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2017KCNAT</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>[REST] 'The imagery was captured by Pictometry International Corp. from 2/17/2017 through 10/30/2017.' | [FGDC/SDC process steps, in full] 'Mosaicing: Mosaicing was performed using Pictometry software' and 'GPS/INS processing: Data was post-processed using NGS CORS base station data.' | [purpose] 'This ortho-mosaic is a visualization product and is not intended or valid for authoritative or definitive use...'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif — IMAGE_Ortho2019KCNAT. THE MOSAICKING-ENGINE CHANGE.</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>SDC page credits 'Pictometry International'; the REST service copyrightText for the same year credits 'EagleView Technologies, Inc.' — the two King sources disagree.</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Native 3 in (0.0762 m) west. Held file 0.1003 m ground → DOWNSAMPLED ~1.32x (measured).</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Cache 'MIXED' at quality 80</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>'Mosaicing was performed using ESRI software' — a documented, dated change of mosaicking engine between 2017 and 2019.</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>NOT STATED — but this is the year the documented mosaicking engine changes from 'Pictometry software' (2015, 2017) to 'ESRI software' (2019, 2021), dated 2/20/2020. ESRI mosaic datasets carry their own colour-balancing and stretch defaults; King County does not say which were used.</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM named</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>Capture DATES are NOT FOUND for 2019 in any page I fetched (the SDC template carries none and the REST text gives only the year).</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>This is the strongest processing/drift alignment in the series. Measured G/R crosses below 1.0 for the first time here: 1.008 (2017) → 0.974 (2019) → 0.954 (2021). The mosaicking engine changed in exactly that interval. Red overtaking green is a white-balance/colour-balance shift, and any naive greenness index defined as 'G is the largest band' inverts across it.</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2019KCNAT</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>[SDC change history, 2/20/2020] 'Mosaicing: Mosaicing was performed using ESRI software' and 'GPS/INS processing: Data was post-processed using NGS CORS base station data.' | [REST] 'King County tile-cache base map featuring aerial imagery aquired in 2019. ... Capture resolution is three inches per pixel for western King County and southwestern Snohomish County, and nine inches per pixel for eastern King County.' | [REST] copyrightText: 'EagleView Technologies, Inc.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif — IMAGE_Ortho2021KCNAT</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>SDC page credits 'Pictometry International'; REST copyrightText credits 'EagleView Technologies, Inc.'</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour. No synthesised band. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Native 3 in (0.0762 m) west. Held file 0.1003 m ground → DOWNSAMPLED ~1.32x (measured).</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Cache 'MIXED' at quality 80</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>ESRI software, second consecutive year</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND — no DEM named</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>Capture DATES NOT FOUND. The REST description is the first to state explicitly that the served product IS a cache generated from a mosaic — confirming the served pixels are two mosaicking generations removed from the frames.</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>2021 is the MINIMUM of the naive-greenness series in my measurement windows: frac(G=max) = 0.1473, G/R = 0.954. Note this differs from the parent's stated minimum at 2019 — my windows and metric are not theirs, and I reproduce the shape, not the values.</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2021KCNAT</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>[SDC change history, 3/31/2022] 'Mosaicing: Mosaicing was performed using ESRI software' and 'GPS/INS processing: Data was post-processed using NGS CORS base station data.' | [REST] 'The cache was generated from a natural-color orthographic aerial imagery mosaic of King County and southwestern Snohomish County. The source dataset consists of tiled orthogonal imagery derived from aerial photographs captured by EagleView Technologies.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif — IMAGE_Ortho2023KCNAT (EagleView)</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>EagleView Technologies, Inc. (the SDC page ALSO contains a contradictory leftover sentence crediting Pictometry International)</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>3-band natural colour served. No synthesised band. A CIR sibling exists for 2023 ('King County 2023 color-infrared and natural-color aerial imagery') but the cache serves natural colour. Camera NOT STATED.</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Native 3 in (0.0762 m) west. Held file 0.1003 m ground → DOWNSAMPLED ~1.32x (measured).</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Cache 'MIXED' at quality 80</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>'Mosaicking was performed using an automatic seaming algorithm and manually edited to eliminate seams through elevated features where possible.' — the first MANUAL seamline editing documented since the 2015 GeoTerra project, and a change from 2019/2021's bare 'ESRI software'.</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>'The triangulated frames were rectified to a DEM.' — a DEM is asserted but NOT NAMED. This is the only 2013–2023 year that mentions a DEM at all.</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>The page contradicts itself on vendor within one paragraph (EagleView vs Pictometry), so King County's own 2023 record is internally inconsistent.</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>2023 partially REBOUNDS: frac(G=max) 0.1473 (2021) → 0.3373, G/R 0.954 → 0.990. Its capture window (Apr 14 – Jun 28) is more leaf-on than 2015's or 2017's February starts, and its mosaicking got manual seam editing back. That rebound is the single best piece of evidence that the 'drift' is processing plus phenology and not monotonic canopy loss — real canopy loss does not un-happen.</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2023KCNAT</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>[SDC] 'The dataset consists of tiled orthogonal imagery derived from aerial photographs captured by EagleView Technologies between April 14 and June 28, 2023.' | 'Automatic aerial triangulation (AAT) was performed. The triangulated frames were rectified to a DEM. Mosaicking was performed using an automatic seaming algorithm and manually edited to eliminate seams through elevated features where possible.' | and, in the SAME paragraph, the contradictory 'The dataset consists of tiled orthogonal imagery produced from nadir images captured by Pictometry International.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2000–2023 (all)</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>ALL TWELVE King files — the delivery path itself: every held King raster was harvested from the ArcGIS cached tile service, not from the native ortho product</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>gismaps.kingcounty.gov ArcGIS MapServer tile caches (KingCo_Aerial_YYYY)</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Unchanged (3-band), but every band passed through JPEG quantisation at the cache stage.</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED, not inferred: every held file's pixel size is EXACTLY a Web-Mercator LOD resolution (0.597164283 = z18 for 2000/2002; 0.298582142 = z19 for 2005/2007/2009/2012; 0.149291071 = z20 for 2013–2023) and every origin is an exact integer 256-pixel-tile offset from the global Web-Mercator origin -20037508.342787 (tile offsets 41940.00000 / 83881.00000 / 167762.00000 — integers to 5 decimal places, all 12 files). Net effect at Edmonds' latitude (ground res = LOD res x cos 47.81deg): 2000 oversampled 1.5x, 2005 oversampled 1.5x, 2012 oversampled 1.66x, 2013 ~1:1, and 2002/2007/2009/2015/2017/2019/2021/2023 downsampled 1.32x.</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>JPEG at quality 75 or 80, stacked on top of each year's native MrSID / JP2 / JPG lossy history.</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>The cache is itself a re-mosaic: the 2021 REST text says outright 'The cache was generated from a natural-color orthographic aerial imagery mosaic', and for 2002 'In this tiled, cached map service mosaic, the USGS imagery supplants the full-county imagery set'.</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>JPEG chroma subsampling and quantisation applied to every year, at TWO DIFFERENT QUALITY SETTINGS: 75 for 2009 and 2012, 80 for the other ten. That is an undocumented per-year radiometric difference sitting on top of everything else.</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>Unchanged, but a reprojection into EPSG:3857 was added on top of each year's native State Plane / UTM grid.</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>REST endpoints fetched: https://gismaps.kingcounty.gov/arcgis/rest/services/BaseMaps/KingCo_Aerial_{2000,2002,2005,2007,2009,2012,2013,2015,2017,2019,2021,2023}/MapServer?f=json . KingCo_Aerial_2010 returns an empty 104-byte body (no such cached service), consistent with 2010 not being in the pipeline.</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>This is a systemic, previously undocumented modification affecting ALL King years. Three consequences: (1) no King year in the pipeline is at its native GSD — three years are oversampled and eight downsampled, so apparent crown texture and minimum detectable gap size vary by year for purely delivery-path reasons; (2) 2009 and 2012 carry heavier JPEG quantisation (q75) than their neighbours, which will show up as different high-frequency texture statistics; (3) JPEG 4:2:0 chroma subsampling degrades exactly the colour information that any greenness index depends on, and it does so at a different strength in different years.</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>https://gismaps.kingcounty.gov/arcgis/rest/services/BaseMaps/KingCo_Aerial_2000/MapServer?f=json</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>[REST, every year] '"singleFusedMapCache":true' with '"tileInfo":{"rows":256,"cols":256,"dpi":96,"format":"MIXED"/"JPEG"/"Mixed","compressionQuality":80 (or 75)'. Per year: 2000 MIXED/80, 2002 MIXED/80, 2005 MIXED/80, 2007 JPEG/80, 2009 JPEG/75, 2012 JPEG/75, 2013 Mixed/80, 2015 MIXED/80, 2017 MIXED/80, 2019 MIXED/80, 2021 MIXED/80, 2023 MIXED/80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif (held ANCHOR) / Basemap/2020_Aerial_Cached ImageServer</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds (source imagery flown in NAD83 StatePlane WA North ftUS; city re-projected and cached it)</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>SERVICE reports 4 bands; the 4th is ALPHA, not NIR. Proof chain: (a) the CoE source TIFFs are 3-band (2015/2017 metadata XML NumBands 3) and the 2015/2017 services report bandCount 3, while 2020/2022 report 4; (b) MODIFICATIONS explicitly lists MASKED, which is the GeoExpress MG4 alpha-mask band; (c) MEASURED from the service's own stats, band 4 is binary {0,255}: mean 182.33, std 114.04 -- a binary band with p(255)=182.33/255=0.71502 predicts std 255*sqrt(p(1-p))=115.11, i.e. observed/predicted = 0.991. Bands 1-3 are plain RGB. NO near-infrared exists in any City of Edmonds product. The held GeoTIFF is 3-band (the alpha was dropped at harvest).</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>~1.52x OVERSAMPLED, bilinear. MECHANISM CORRECTED: pixelSizeX 0.07620015240030481 is EXACTLY 0.25 US survey feet (0.3048006096012192*0.25) -- it is the SOURCE pixel size passed through, NOT '3 inches applied as web mercator units'. Native flight/ortho = 0.25 ftUS = 7.6200 cm GROUND. The service delivers a Web Mercator tile cache whose finest level is LOD 21 = 0.07464553541190416 WM m; at the city centroid (lat 47.81642, cos = 0.671508) that is 5.0125 cm GROUND. Oversample = 7.6200/5.0125 = 1.5202x. KERNEL: the service declares defaultResamplingMethod "Bilinear" (CONFIRMED as the declared default; that this exact kernel built the cache is INFERRED). MEASURED: the held file sits on that cache lattice -- res 0.07464553543473991 (held/LOD21 = 1.000000000306), origin (-13625893.9732, 6084272.7960) = WM tile index x 335524.000103, y 730182.000221, i.e. 0.026 px and 0.057 px from an exact 256-tile corner. All four CoE years share a byte-identical transform.</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>TWO lossy stages, then a lossless re-encode. (1) MrSID/MG4 via GeoExpress 10.0.1.5035 from a GeoTIFF input of 665,235,977,256 bytes -- MG4 is a wavelet format and MODIFICATIONS says COMPRESSED, but the achieved RATIO IS NOT PUBLISHED (the .sid output size appears nowhere; NOT FOUND). (2) The delivered product is a JPEG tile cache at quality 75 (tileInfo.format JPEG, compressionQuality 75, singleFusedMapCache true) -- LOSSY. MEASURED in the held file: JPEG 8x8 DCT blockiness ratio 1.2534 across columns and 1.2471 across rows (mean |difference| at col%8==7 is 5.211 vs 3.92-4.34 at every other phase). (3) Our harvest then re-encoded to DEFLATE predictor 2 (lossless, but it bakes the JPEG artifacts in permanently).</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED as mosaicked but with no method published: MODIFICATIONS says MOSAICKED, and the service reports defaultMosaicMethod "Center", mosaicOperator "First". No seamline algorithm, blend width, or colour-balancing statement exists. NOTE: MODIFICATIONS does NOT contain 'RESAMPLED', which is evidence that GeoExpress itself did not resample -- the oversample happens in the reprojection/cache layer.</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>8-bit (pixelType U8), 3 usable bands. NO radiometric clip -- the service's STATISTICS_MAXIMUM of 216/209/200 carries STATISTICS_APPROXIMATE "YES" and is a subsampling artifact; MEASURED on the held file, all three bands reach 255. MEASURED (8 matched 768px windows): mean R/G/B 117.54/117.74/97.48, std 40.86/36.74/31.67, fraction &gt;=216 = 1.35/1.05/0.63%. No published normalisation, stretch or histogram matching -- the city publishes no serviceDescription, copyrightText, licenseInfo or acquisition date for any imagery service.</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND. No elevation model is named in any City of Edmonds endpoint. Nothing states whether the source ortho was rectified to a bare-earth DTM or a surface DSM.</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>REPROJECTED. iteminfo reports spatialReference "NAD_1983_StatePlane_Washington_North_FIPS_4601_Feet" while the service serves EPSG:3857 -- so the city took county-plane source imagery, re-projected it to Web Mercator, and built its own cache. This answers the delivery question: the city RE-PROCESSED it, it did not serve it as delivered. Also EMBEDDED per MODIFICATIONS (embedded georeferencing/metadata).</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>Three separate fake-signal vectors, all in the LABELLED ANCHOR YEAR. (1) The 2020 imagery the hand labels were drawn on is a JPEG-75 product: the 8x8 DCT grid is ~40 cm on the ground and JPEG chroma subsampling smears red/green transitions at exactly crown-boundary scale, so texture and edge features from 2020 are not comparable to the King County years, which never passed through this cache. (2) It is bilinearly oversampled 1.52x, so it looks sharper-gridded than it is -- effective resolution is ~7.6 cm, not the 5.0 cm the grid implies; any per-pixel crown-area statistic inherits that. (3) No NIR exists, so no NDVI reference can ever be built for the anchor year -- the 4th band is alpha and would read as a constant if mistaken for NIR.</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/2020_Aerial_Cached/ImageServer/keyProperties?f=pjson and https://maps.edmondswa.gov/gis/rest/services/Basemap/2020_Aerial_Cached/ImageServer?f=json</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>"IMAGE__ENCODING_APPLICATION": "GeoExpress 10.0.1.5035", "IMAGE__FORMAT": "MrSID/MG4", "IMAGE__INPUT_FILE_SIZE": "665235977256.000000", "IMAGE__INPUT_FORMAT": "GeoTIFF", "IMAGE__LTI_ESDK_VERSION": "9.5.4.5035...", "IMAGE__MODIFICATIONS": "COMPRESSED EMBEDDED MASKED MOSAICKED", "VERSION": "MG4" -- and from ?f=json: "pixelSizeX": 0.07620015240030481, "bandCount": 4, "pixelType": "U8", "defaultResamplingMethod": "Bilinear", "singleFusedMapCache": true, "cacheType": "Map", "tileInfo": { "format": "JPEG", "compressionQuality": 75 }</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif (held) / Basemap/2022_Aerial_Cached ImageServer</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds (source imagery in NAD83 StatePlane WA North ftUS)</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Service reports 4 bands; band 4 is ALPHA, not NIR. MEASURED from the service's own statistics: band 4 mean 186.52, std 111.99 -- binary {0,255} with p=0.73145 predicts std 113.01, observed/predicted = 0.991. Held file is 3-band RGB. This row carries the decisive CRS proof for the whole CoE family: the MrSID input GeoTIFF's own geokeys name EPSG:2285 in US survey feet.</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Identical to 2020: native 0.25 ftUS = 7.6200 cm ground, served on Web Mercator cache LOD 21 = 5.0125 cm ground, oversample 1.5202x, declared kernel Bilinear. MEASURED: the held 2022 file has the same transform, resolution and lattice offset as 2020/2017/2024.</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>MrSID/MG4 (GeoExpress 10.0.1.5035) from a 675,609,635,568-byte GeoTIFF; ratio NOT PUBLISHED. Then JPEG quality 75 tile cache. MEASURED JPEG 8x8 blockiness in the held file: 1.3739 (range 1.2262-1.5771 across 8 windows). Held file re-encoded to DEFLATE predictor 2.</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>MOSAICKED per MODIFICATIONS; defaultMosaicMethod "Center", mosaicOperator "First". No seamline or colour-balance method published.</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. No clip (service max 211/215/204 is an approximate-stats artifact; MEASURED held maxima are 255 in all bands). MEASURED (8 windows): mean R/G/B 121.95/128.21/104.28, std 32.33/30.85/30.07, fraction &gt;=216 = 0.82/1.07/0.59%. Notably LOWER contrast than 2020 (std ~32 vs ~41 in red) with a HIGHER mean -- a flatter, brighter rendition of the same city.</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND. No elevation model named anywhere in the city's endpoints.</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>REPROJECTED from EPSG:2285 to EPSG:3857 by the city. RESAMPLED is absent from MODIFICATIONS, locating the resample in the cache layer rather than the MrSID encode.</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>2022 is measurably flatter than 2020 over the same ground (red std 32.3 vs 40.9, +4.4 DN mean). A canopy/shadow discriminator or any fixed brightness threshold calibrated on the 2020 anchor will behave differently in 2022 for purely radiometric reasons, and a 2020-&gt;2022 change map would read that contrast collapse as change. Plus the same JPEG-75 and 1.52x oversample as 2020.</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/2022_Aerial_Cached/ImageServer/keyProperties?f=pjson</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>"GEOTIFF_CHAR__ProjLinearUnitsGeoKey": "Linear_Foot_US_Survey", "GEOTIFF_NUM__1026__GTCitationGeoKey": "PCS Name = NAD_1983_StatePlane_Washington_North_FIPS_4601_Feet", "GEOTIFF_NUM__3072__ProjectedCSTypeGeoKey": "2285", "IMAGE__ENCODING_APPLICATION": "GeoExpress 10.0.1.5035", "IMAGE__FORMAT": "MrSID/MG4", "IMAGE__INPUT_FILE_SIZE": "675609635568.000000", "IMAGE__INPUT_FORMAT": "GeoTIFF", "IMAGE__MODIFICATIONS": "COMPRESSED EMBEDDED MASKED MOSAICKED"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif (held) / Basemap/2024_Aerial_Cached MapServer</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>RGB only (held file is 3-band). Served as a MapServer rendering, so no band statistics or band count are exposed at all -- unlike 2015-2022 there is no ImageServer for 2024. The layer name 'Edmonds2024.sid' CONFIRMS the backing store is a MrSID .sid file, consistent with the GeoExpress/MG4 lineage of 2020 and 2022.</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Same Web Mercator cache LOD 21 = 0.07464553541190416 (5.0125 cm ground). MEASURED: the held 2024 file has a transform byte-identical to 2017/2020/2022, on the same 256-tile lattice. Native flight resolution for 2024 is NOT stated by this MapServer (no pixelSizeX field exists on a MapServer), so the 1.52x oversample is INFERRED for 2024 by analogy with the 0.25 ftUS sources confirmed for 2015/2017/2020/2022.</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>JPEG quality 75 tile cache (tileInfo.format JPEG, compressionQuality 75) over a MrSID .sid source. MEASURED JPEG 8x8 blockiness in the held file: 1.2811 (range 1.1816-1.4545). Re-encoded locally as DEFLATE predictor 2.</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND for 2024 specifically -- a MapServer exposes no MrSID keyProperties, so the MODIFICATIONS string available for 2020/2022 cannot be read for 2024.</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. MEASURED (8-9 windows) and STRIKINGLY DIFFERENT from every other CoE year: mean R/G/B 126.68/134.09/121.70 -- the blue band is +24 DN above 2020's 97.48. Fraction of pixels &gt;=216 is 11.65/11.78/11.50%, versus 0.6-1.5% in 2017/2020/2022, i.e. roughly a TEN-FOLD increase in bright pixels. std 41.41/38.29/31.48. No published normalisation.</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND.</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>DELIVERY TYPE CHANGED: 2024 is the only aerial year published as a MapServer rather than an ImageServer, so no pixelSizeX, bandCount, pixelType or band statistics are retrievable for it. Everything known about 2024's source is by analogy, not from its own metadata.</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>The most radiometrically deviant City of Edmonds year by a wide margin. A blue channel 24 DN brighter and a 10x higher bright-pixel fraction will move any greenness index that includes blue (e.g. 2G-R-B) strongly negative relative to 2020, manufacturing an apparent canopy LOSS in 2024 that is pure colour balance. This is the same failure mode already proven for King County 2000. Also, because 2024 is a MapServer, it is the one CoE year whose native resolution is not independently confirmable.</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/2024_Aerial_Cached/MapServer?f=json</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>"layers": [{"id": 0, "name": "Edmonds2024.sid", "parentLayerId": -1, "defaultVisibility": true, "subLayerIds": null, "minScale": 0, "maxScale": 0, "type": "Raster Layer"}] ... "singleFusedMapCache": true ... tileInfo format JPEG, compressionQuality 75, finest LOD resolution 0.07464553541190416</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif (held) / Basemap/2017_Aerial_Cached ImageServer (source raster 2017_Aerial.tif)</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>3 bands, RGB, confirmed at source (NumBands 3) and in the service (bandCount 3). No NIR, and no alpha for this year -- the 4th band only appears in 2020 and 2022.</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Source raster is 120000 x 150000 at 0.250000 Foot_US in EPSG:2285 = 7.6200 cm ground. Served on Web Mercator cache LOD 21 = 5.0125 cm ground -&gt; 1.5202x oversample, declared kernel Bilinear. MEASURED: held file transform identical to the other three CoE years, on the 256-tile lattice.</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>DOUBLE LOSSY -- the worst-compressed acquisition in the archive. The SOURCE TIFF is already JPEG-compressed (CompressionType JPEG, versus LZW for the 2015 source), and it is then re-encoded into the JPEG quality-75 tile cache, and finally re-encoded by our harvest as DEFLATE predictor 2. MEASURED JPEG 8x8 blockiness in the held file: 1.3531 (range 1.1825-1.7206), the highest single-window value of any CoE year.</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND for 2017 -- this service exposes no MrSID keyProperties (the source is a plain GeoTIFF, not a .sid), so no MODIFICATIONS string exists. defaultMosaicMethod "Center", mosaicOperator "First".</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>8-bit, NoDataValue 256 (i.e. none in range). MEASURED (9 windows): mean R/G/B 114.67/115.87/94.91, std 33.90/32.02/30.99, fraction &gt;=216 = 1.50/1.16/0.74%. Service statistics (full-count, SKIPFACTOR 1) give mean 89.69/94.62/77.12, std 59.76/56.89/51.39 over the whole service extent.</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND.</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>REPROJECTED EPSG:2285 -&gt; EPSG:3857. Source created 2019-01-30 with Esri ArcGIS 10.2.1.3497. Extent is wider than the other CoE years (30000 x 37500 ft vs 24000 x 36000 ft for 2015).</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>2017 has been through JPEG twice on two different grids, so its high-frequency content is the most degraded of the CoE set -- crown-edge sharpness and texture statistics for 2017 are not comparable with 2020/2022/2024, let alone with the King County years. This directly undermines the 'matched 2017 pair' experiment (King 2017 vs CoE 2017) that IMAGERY_PLAN C1 proposes as the way to isolate sensor effects: the CoE half of that pair is the double-JPEG one.</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/2017_Aerial_Cached/ImageServer/info/metadata</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>&lt;itemName Sync="TRUE"&gt;2017_Aerial.tif&lt;/itemName&gt; ... &lt;PixelDepth Sync="TRUE"&gt;8&lt;/PixelDepth&gt; &lt;HasColormap Sync="TRUE"&gt;FALSE&lt;/HasColormap&gt; &lt;CompressionType Sync="TRUE"&gt;JPEG&lt;/CompressionType&gt; &lt;NumBands Sync="TRUE"&gt;3&lt;/NumBands&gt; &lt;Format Sync="TRUE"&gt;TIFF&lt;/Format&gt; ... &lt;NoDataValue Sync="TRUE"&gt;256&lt;/NoDataValue&gt; ... &lt;projcsn Sync="TRUE"&gt;NAD_1983_StatePlane_Washington_North_FIPS_4601_Feet&lt;/projcsn&gt; ... &lt;dimResol&gt;&lt;value Sync="TRUE" uom="Foot_US"&gt;0.250000&lt;/value&gt;&lt;/dimResol&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Basemap/2015_Aerial_Cached ImageServer (source raster Ed_Aerial_2015.tif) -- NOT the held 2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>3 bands RGB at source and in the service (bandCount 3). No NIR, no alpha.</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Source 96000 x 144000 at 0.250000 Foot_US, EPSG:2285 = 7.6200 cm ground; served on cache LOD 21 = 5.0125 cm ground -&gt; 1.5202x oversample, declared kernel Bilinear.</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE IS LOSSLESS -- CompressionType LZW. This is the ONLY City of Edmonds source raster that is not lossy, and it is the direct counter-example that makes the 2017 JPEG source a real, documented difference between two CoE acquisitions rather than a house style. The served cache is still JPEG quality 75.</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND -- plain GeoTIFF source, no MrSID MODIFICATIONS string. defaultMosaicMethod "Center".</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. Service statistics are full-count (STATISTICS_SKIPFACTORX/Y = 1, no STATISTICS_APPROXIMATE flag): mean 63.20/66.87/64.99, std 55.56/54.07/51.12, min 0 max 255 on all three bands. Markedly darker than 2017 (mean ~90/95/77) over a comparable extent.</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND.</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>Source created 2017-01-23 with Esri ArcGIS 10.1.0.3035, last synced 2019-02-24. REPROJECTED EPSG:2285 -&gt; EPSG:3857 for serving.</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANT BOOKKEEPING: this City of Edmonds 2015 product is NOT the file the pipeline holds for 2015. The held 2015_king_rgb.tif is a King County EPSG:3857 raster; this is a separate 0.25 ft StatePlane City raster that exists only as a service. Do not let the two be conflated when reconciling the catalogue -- and note that if it were ever harvested, it would be the one CoE year with a lossless source.</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/2015_Aerial_Cached/ImageServer/info/metadata</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>&lt;itemName Sync="TRUE"&gt;Ed_Aerial_2015.tif&lt;/itemName&gt; ... &lt;PixelDepth Sync="TRUE"&gt;8&lt;/PixelDepth&gt; &lt;CompressionType Sync="TRUE"&gt;LZW&lt;/CompressionType&gt; &lt;NumBands Sync="TRUE"&gt;3&lt;/NumBands&gt; &lt;Format Sync="TRUE"&gt;TIFF&lt;/Format&gt; &lt;HasPyramids Sync="TRUE"&gt;TRUE&lt;/HasPyramids&gt; ... &lt;NoDataValue Sync="TRUE"&gt;256&lt;/NoDataValue&gt; ... &lt;dimSize Sync="TRUE"&gt;96000&lt;/dimSize&gt;&lt;dimResol&gt;&lt;value Sync="TRUE" uom="Foot_US"&gt;0.250000&lt;/value&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Basemap/Edmonds_Marsh_2018 ImageServer (not held; the only CoE service with a real acquisition date)</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>4 bands declared; no band statistics are published (BandProperties carry only SourceBandIndex), so whether band 4 is NIR or alpha CANNOT be determined for this product. isCalibrated "False" is stated explicitly.</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>pixelSizeX 0.03359503424897864 with a 23-level cache whose finest LOD is 0.03732276770595208 WM m = 2.506 cm ground. The source pixel size 0.03359503424897864 does not correspond to a round imperial value the way the other CoE services do, and the cache LOD is COARSER than the source pixel size, so this product is DOWN-sampled onto the cache rather than up-sampled. Declared kernel Bilinear.</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>JPEG quality 75 tile cache (singleFusedMapCache true). No MrSID keyProperties, so no source compression is stated.</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND. A 30-minute single-sortie capture (16:22-16:52 UTC) over a small extent, so it is likely few frames, but no mosaic method is published.</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>8-bit (pixelType U8). No min/max/mean/std published at all for this service. isCalibrated "False" is the only radiometric statement the City of Edmonds publishes for ANY of its imagery.</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND.</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>This is a small, marsh-only footprint (extent y 6074220.69-6075167.85 WM, about 950 m tall), not a citywide product.</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>Its real value is as a CALIBRATION ANCHOR for the date problem: it proves the City's ArcGIS stack DOES populate acquisitionStartDate/acquisitionEndDate when the city holds that information, and it is populated for exactly one service. The absence of those fields on 2015/2017/2020/2022 is therefore positive evidence that the city never received or never recorded acquisition dates for its citywide aerials -- which is why the 2020 anchor date remains INFERRED. Also: 2018-08-01 is a fully leaf-on midsummer date, useful as a phenology reference point for the marsh area.</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer/keyProperties?f=pjson</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>"KIND": "IMAGE", "BAND_COUNT": 4, "acquisitionEndDate": "2018-08-01T16:52:13+00:00", "acquisitionStartDate": "2018-08-01T16:22:13+00:00", "AREA_OR_POINT": "Area", "isCalibrated": "False"</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2016 (date itself ambiguous -- see other_modifications)</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif (held) / Imagery/Aerial_2016 ImageServer</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County; imagery from HXIP (Hexagon Imagery Program / HxGN Content Program), NOT Pictometry</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>GENUINE 4-band RGB + NIR -- but GDAL mislabels band 4 as alpha, and that is a live pipeline hazard. MEASURED on the held file: band 4 spans the full 0-255 range with std 61-81 across windows, and NDVI (N-R)/(N+R) reaches p95 = 0.7216 with p5 = -0.4074 -- unambiguously real near-infrared, not a constant mask. HOWEVER the file's TIFF tags declare colorinterp = (3,4,5,6) = red, green, blue, ALPHA, and mask_flag_enums for bands 1-3 = PER_DATASET|ALPHA, while only the band-level tag says name='NIR'. HAZARD: any GDAL/rasterio read that honours the alpha channel (read(masked=True), or a warp/translate that respects the mask) will silently treat NIR=0 pixels as transparent nodata and null them out -- MEASURED at 3.88% of the decimated 2016 frame, and those are disproportionately water and deep shadow.</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>*** 2x OVERSAMPLED -- the single biggest undocumented difference found. *** The provider's own mosaic catalog reports LowPS = 1 (US survey FOOT) for EVERY 2016 frame, and keyProperties independently reports LowCellSize = 1, yet the service publishes pixelSizeX = 0.5 and the held file is on a 0.5 ft grid. So the 2016 source frames are natively 1 ft = 30.48 cm and the product we hold has been resampled to 15.24 cm -- a 2x upsample, with the service's declared kernel Bilinear. This is consistent with the HxGN product classes: 30 cm/1 ft is their WIDE AREA coverage tier (the 15 cm urban tier is what 2021 got) -- though which tier Snohomish actually purchased is INFERRED from the cell size, not stated. MEASURED support over IDENTICAL ground (36 matched 512 px windows, green band, same grid as 2021): lag-1 autocorrelation 0.9743 for 2016 vs 0.9438 for 2021, and lag-2 0.9298 vs 0.8342 -- 2016's lag-2 correlation is about equal to 2021's lag-1, exactly what a 2x-coarser effective sampling predicts; plus a period-2 parity asymmetry in |2nd difference| of 1.0376 for 2016 against 0.9991 for 2021, i.e. a resampling signature present only in 2016. HONEST CAVEAT: a third statistic, var(d1)/var(d2), did NOT discriminate (0.3227 vs 0.3257).</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>The held file is LZW with predictor 2 (lossless) -- but that is OUR encode at harvest, not the provider's. Snohomish publishes no compression statement for the 2016 mosaic; the source is an Esri mosaic dataset in a file geodatabase (HXIP_2016_SNOHOMISH.gdb). NOT FOUND for the delivered product. 8-bit (pixelType U8), confirmed both by the service and measured in the file.</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>Mosaicked as an Esri mosaic dataset with defaultMosaicMethod 'Northwest' and mosaicOperator 'First', over 8192 x 8192 ft frames (Shape_Length 32848 ft) named on a row_col grid (175_101, 176_102, ...). Overviews were rebuilt by the county on 2020-06-16. Seamline algorithm and colour balancing are NOT published by the county; HxGN states generically that seam lines and colour are corrected.</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. MEASURED to be a substantially HIGHER-CONTRAST product than 2021 over identical ground (80 matched windows): std R 58.01, G 50.86, B 39.96, N 81.42; NDVI p5 -0.4074, p50 0.0997, p95 0.7216, dynamic range 1.129. The provider's own county-wide statistics agree in direction: minValues [0,0,0,0], maxValues [241,241,241,240], stdvValues [43.59, 43.43, 37.60, 77.26]. No normalisation or histogram-matching statement is published; HxGN states only that its team applies 'stringent quality control methods to correct seam lines and colour'.</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND for 2016. No elevation model is named in any Snohomish endpoint for this year. CRITICAL SCOPE WARNING: the 'automatic aerial triangulation (AAT) ... rectified to a LiDAR derived DEM' text belongs to the county's 2020 map service, which is a DIFFERENT VENDOR and a different product line (see the Aerial_2020 row) -- it must NOT be carried onto 2016. HxGN's published spec says only 'perform ortho rectification' and names no DTM or DSM. So whether tall trees in 2016 are displaced as they would be on a bare-earth DTM, or laid flat as on a true-ortho DSM, is UNKNOWN.</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>DATE AMBIGUITY, unresolved and material: the mosaic serving 'Aerial_2016' is itself named HXIP_2015_Snohomishv3 and was built from a folder D:\HXIP_2015_SNOHOMISH_COUNTY, while a separate county Geocortex entry describes its '2017 Aerial Photos' service as 'acquired in August 2016 as part of a Washington Statewide Imagery consortium. Pixel size of the raster is 6" (0.5 feet).' So 2015, 2016 and 'served as 2017' are all attached to overlapping products and the acquisition date of the file we call 2016 is not established.</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>This is the most consequential finding for the project, because 2016 is the most-cited year -- the only NIR year with a matched CHM, and the year the corrected labels were built for. (1) It is 2x oversampled, so every 2016-vs-2021s comparison confounds a doubling of real resolution with canopy change: small crowns and canopy gaps that 2021 resolves are simply not present in 2016's information content, which will read as canopy gain from 2016 to 2021. (2) It contradicts IMAGERY_FACTS section 2.1, which assigns Snohomish a true GSD of 15.4 cm -- correct for 2021s, but roughly 2x too fine for 2016, whose native GSD is ~30.5 cm. (3) Its NDVI dynamic range is 1.129 against 2021's 0.762, so any fixed NDVI threshold for the canopy reference is not transferable between the two NIR years. (4) The alpha-flagged NIR band means an alpha-aware read silently deletes ~3.9% of pixels, biased toward water and shadow.</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2016/ImageServer/info/metadata and https://gis.snoco.org/img/rest/services/Imagery/Aerial_2016/ImageServer/query?where=1%3D1&amp;outFields=*&amp;returnGeometry=false&amp;f=pjson and https://gis.snoco.org/img/rest/services/Imagery/Aerial_2016/ImageServer/keyProperties?f=pjson</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>lineage: "CreateMosaicDataset D:\HXIP_2015_SNOHOMISH_COUNTY\HXIP_2016_SNOHOMISH.gdb HXIP_2015_Snohomishv3" (Date=20180607) and "BuildOverviews \\snoco\gis_ortho\2016_HXIP\HXIP_2016_SNOHOMISH.gdb\HXIP_2016_Snohomish" (Date=20200616). Catalog: {"OBJECTID": 1, "Name": "175_101", "MinPS": 0, "MaxPS": 12, "LowPS": 1, "HighPS": 4, "Category": 1, "Tag": "Dataset"}. keyProperties: {"BandDefinitionKeyword": "NONE", "HighCellSize": 972, "LowCellSize": 1, "MaxCellSize": 48600}. Service: "pixelSizeX": 0.5, "bandCount": 4, "pixelType": "U8", "minValues": [0,0,0,0], "maxValues": [241,241,241,240], "stdvValues": [43.59124219260449, 43.43255081597965, 37.6016346885624, 77.26310815970066], "defaultResamplingMethod": "Bilinear", "defaultMosaicMethod": "Northwest"</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif (held) / Imagery/Aerial_2021 ImageServer</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County; imagery from HXIP (Hexagon Imagery Program / HxGN Content Program), NOT Pictometry</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>GENUINE 4-band RGB + NIR, same alpha-mislabelling hazard as 2016. MEASURED: band 4 spans 16-255 with std 61.75, NDVI p95 = 0.6234 -- real near-infrared. But colorinterp = (3,4,5,6) marks band 4 as ALPHA and bands 1-3 as PER_DATASET|ALPHA, so an alpha-aware read will drop low-NIR pixels here too.</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>AT NATIVE RESOLUTION -- no oversampling. The mosaic catalog reports LowPS = 0.5 for every frame and keyProperties reports LowCellSize = 0.5, matching the served pixelSizeX = 0.5 ft and the held file's 0.5 ft grid exactly. Native GSD = 0.5 US survey ft = 15.24 cm, consistent with the HxGN urban-area tier (15 cm/6 in). MEASURED confirmation that it was NOT resampled: period-2 parity of |2nd difference| = 0.9991 (a perfectly clean 1.000 would be no period-2 structure at all), against 1.0376 for the 2016 file over identical ground.</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Held file is LZW predictor 2 (our encode). The county publishes no compression statement for the delivered 2021 mosaic -- NOT FOUND. 8-bit (pixelType U8) confirmed by service and measurement.</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>Esri mosaic dataset, defaultMosaicMethod 'Northwest', mosaicOperator 'First', over 4096 x 4096 ft frames (Shape_Length 16424 ft) on a row_col naming grid (248_203, 248_204, ...) -- note these frames are HALF the linear size of 2016's, consistent with the finer native resolution. AnalyzeMosaicDataset was run on FOOTPRINT;FUNCTION;RASTER;PATHS in 2022; overviews rebuilt twice (2022-09-20, 2023-03-15). Seamline algorithm and colour balancing NOT published.</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>8-bit, and MEASURABLY LOWER CONTRAST WITH A RAISED BLACK POINT relative to 2016. The provider's own county-wide statistics: minValues [5,15,23,1] -- no band reaches 0 -- maxValues [226,226,220,236], stdvValues [25.43, 21.14, 18.68, 44.39], i.e. roughly HALF the per-band spread of 2016's [43.59, 43.43, 37.60, 77.26]. MEASURED independently on the held file over Edmonds (81 matched windows): std R 43.18, G 37.45, B 36.83, N 61.75 (2016: 58.01, 50.86, 39.96, 81.42); NDVI p5 -0.1385, p50 0.1498, p95 0.6234, dynamic range 0.762 against 2016's 1.129. Two independent sources, one the provider's and one my own over different footprints, agree on the direction. No normalisation method is published.</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND for 2021. No elevation model named. Same scope warning as 2016: the 2020 service's 'rectified to a LiDAR derived DEM' text is a different vendor and product line and does not apply here. DTM versus DSM is UNKNOWN, so tree-lean/displacement behaviour in 2021 is uncharacterised.</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 mosaic was built 2022-09-20, over a year after acquisition. No acquisition date is exposed by the service.</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>2021s is the correctly-sampled member of the NIR pair, which makes it the better reference year and makes 2016 the one that needs a correction factor, not the reverse. Its compressed radiometry is the second fake-signal vector: with NDVI dynamic range 0.762 versus 2016's 1.129 and a raised black point, an NDVI or greenness threshold tuned on 2016 will select a materially different pixel population in 2021 -- and my own naive-greenness measurement (fraction of 2G-R-B &gt; 0: 0.6854 in 2016 versus 0.9419 in 2021) runs OPPOSITE in direction to the figures recorded in IMAGERY_FACTS section 3 (2016 .6928 &gt; 2021s .6157). That disagreement is unresolved and must be reconciled before either number is used, since it decides the sign of any 2016-&gt;2021 canopy trend.</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer/info/metadata and https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer/query?where=1%3D1&amp;outFields=*&amp;returnGeometry=false&amp;f=pjson and https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer?f=pjson</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>lineage: "CreateMosaicDataset \\snoco\gis_ortho\2021_HXIP\HXIP_2021_SNOHOMISH.gdb HXIP_2021_SNOHOMISH" (Date=20220920), then AnalyzeMosaicDataset and BuildOverviews (20220920, 20230315). Catalog: {"OBJECTID": 1, "Name": "248_203", "MinPS": 0, "MaxPS": 6, "LowPS": 0.5, "HighPS": 2}. keyProperties: {"BandDefinitionKeyword": "NONE", "HighCellSize": 1458, "LowCellSize": 0.5}. Service: "pixelSizeX": 0.5, "bandCount": 4, "pixelType": "U8", "minValues": [5,15,23,1], "maxValues": [226,226,220,236], "stdvValues": [25.431718454446624, 21.138358884990247, 18.67819816285293, 44.39498724120521]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Imagery/Aerial_2020 ImageServer (Snohomish; not held, but it is the probable source of the CoE 2020 anchor and the origin of the 'LiDAR derived DEM' quote)</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County -- product line WASNOH20, distinct from the HXIP mosaics of 2016 and 2021</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>3 bands, RGB, NO NIR (NumBands 3, bandCount 3, serviceDataType esriImageServiceDataTypeRGB). This matches the City of Edmonds 2020 product exactly (3-band, 0.25 ft, EPSG:2285 source) and is strong corroboration that the CoE 2020 anchor is this county flight re-served -- though that link remains INFERRED, since the city publishes no provenance.</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Native 0.25 ftUS = 7.62 cm, confirmed three ways: dimResol 0.250000 ftUS, LowCellSize 0.25, and pixelSizeX 0.25. Served at native cell size -- no oversampling at the county. NOTE the resolution ladder across the three county products: 2016 = 1 ft, 2021 = 0.5 ft, 2020 = 0.25 ft. Three different native resolutions in three acquisitions, all served on their own grids. defaultResamplingMethod Bilinear.</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>CompressionType 'None' -- the county's 2020 mosaic is UNCOMPRESSED, in contrast to the City of Edmonds' MrSID/MG4 plus JPEG-75 cache rendition of what is probably the same flight. AllowedCompressions None,JPEG,LZ77,LERC. This means the compression damage in the held 2020 anchor was added by the City of Edmonds' publishing chain, not by the county.</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>Esri mosaic dataset, defaultMosaicMethod 'Northwest', mosaicOperator 'First', BlendWidth 10, CellSizeTolerance 0.8, ClipToBoundary -1, FootprintMayContainNoData -1, MinimumPixelContribution 1. Mensuration capabilities include 'Base-Top Height' and 'Top-Top Shadow Height', which implies the county retained frame geometry for this product.</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>8-bit. No statistics published (minValues/maxValues/meanValues/stdvValues are all empty, hasHistograms false), so no radiometric characterisation is possible from this endpoint.</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>The 'automatic aerial triangulation (AAT) was performed. The triangulated frames were rectified to a LiDAR derived DEM' text supplied with this task belongs to a Snohomish 2020 MAP service. I could NOT re-verify it today: gismaps.snoco.org/securegis returns {"status":"error","messages":["Could not access any server machines. Please contact your system administrator."]} for both the service and the folder listing, so I am not asserting it as confirmed by me. Two cautions regardless: (a) it is scoped to 2020 and this WASNOH20 product line ONLY, and must not be applied to the HXIP 2016/2021 mosaics; (b) even as written, 'a LiDAR derived DEM' is AMBIGUOUS between a bare-earth DTM and a surface DSM, and that distinction decides whether tall trees are radially displaced (DTM) or laid flat in true-ortho fashion (DSM). No source I reached resolves it.</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>Mosaic built 2021-03-29 from ArcGIS 10.7; metadata synced 2022-06-13 with XTools Pro. County-wide extent (1244496-1521696 ftUS E, 284328-479688 N), 1108800 x 781440 pixels.</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>Two consequences for the anchor year. First, it isolates blame: the county's own 2020 product is uncompressed 3-band at native 0.25 ft, so the MrSID-plus-JPEG-75 degradation and the 1.52x oversample measured in 2020_coe_rgb.tif were introduced by the City of Edmonds' publishing chain, and could in principle be avoided by re-harvesting the anchor year from the county instead of the city -- at native resolution, uncompressed, on the county's own grid. Second, it shows the county changed native resolution three times across the years this project uses (1 ft in 2016, 0.25 ft in 2020, 0.5 ft in 2021), so 'Snohomish County' is not a single consistent sensor era.</t>
+        </is>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2020/ImageServer/info/metadata and https://gis.snoco.org/img/rest/services/Imagery/Aerial_2020/ImageServer?f=pjson</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>"CreateMosaicDataset \\snoco\gis_ortho\2020\WASNOH20.gdb WASNOH20_full" (Date=20210329) ... &lt;PixelDepth Sync="TRUE"&gt;8&lt;/PixelDepth&gt; &lt;CompressionType Sync="TRUE"&gt;None&lt;/CompressionType&gt; &lt;NumBands Sync="TRUE"&gt;3&lt;/NumBands&gt; &lt;Format Sync="TRUE"&gt;AMD&lt;/Format&gt; ... &lt;dimResol&gt;&lt;value Sync="TRUE" uom="ftUS"&gt;0.250000&lt;/value&gt;&lt;/dimResol&gt; ... &lt;LowCellSize Sync="TRUE"&gt;0.25&lt;/LowCellSize&gt; &lt;BlendWidth Sync="TRUE"&gt;10&lt;/BlendWidth&gt; &lt;CellSizeTolerance Sync="TRUE"&gt;0.8&lt;/CellSizeTolerance&gt;. Service: "pixelSizeX": 0.25, "bandCount": 3, "serviceDataType": "esriImageServiceDataTypeRGB"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif (2019n) — NAIP WA 2019, DOQQ quads m_4712213/m_4712214, acquired 2019-10-11</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA APFO NAIP; DOQQ delivery hosted on Azure (Planetary Computer NAIP v002)</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>4 band, R,G,B,NIR — CONFIRMED by metadata ('32-bit pixels, 4 band color(RGBIR) values 0 - 255') and by the delivered DOQQ. NO synthesised band. NIR passband 808-882 nm. NOTE (MEASURED): in the held file band 4 carries GDAL colorinterp='alpha', not 'undefined' as in the source DOQQ — software that honours alpha will silently alpha-blend the NIR channel.</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Collected at nominal 60 cm GSD and delivered at 60 cm — i.e. delivered at native scale, no downsampling. Ortho resampling kernel NOT STATED in the metadata. Flight design used 30% lateral overlap.</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on the Azure-hosted DOQQ: DEFLATE COG, PREDICTOR=2, lossless — but this is Microsoft's COG rewrite, not necessarily the USDA delivery format. The internal compression/quality of the USDA-delivered DOQQ GeoTIFF is NOT STATED in any source I fetched (see unknowns). The 40:1 MrSID/JPEG2000 figure in NAIP metadata applies to the county-wide CCM mosaic, not to the DOQQ. MEASURED on the held file: LZW, no predictor, lossless.</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>Orthorectified strips mosaicked in Inpho OrthoVista 7.1.2 which performed 'the final radiometric balance, mosaic, and DOQQ sheet creation'. DOQQ tiles carry a 300 m buffer. Seamline shapefiles are a separate NAIP product. Automatic seamlines with manual review.</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>8-bit output. Atmospheric-BRDF radiometric correction applied at orthorectification (compensates atmospheric absorption, solar illumination angle, bidirectional reflectance), then 'final radiometric balance' across the mosaic in Inpho OrthoVista 7.1.2. This is a scene-relative balance, NOT calibrated reflectance — DNs are not physical units and are not comparable to any other acquisition.</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>Leica XPro, using the 'June 2018 USGS 10m NED DEM'. Full AAT: XPro APM automatic tiepointing across forward/nadir/backward look angles, ORIMA bundle adjustment, photo-identifiable GPS-surveyed ground control introduced into the block adjustment.</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED: the held 2019_naip_rgbi.tif sits exactly on the native DOQQ grid (origin 545182.2E / 5300944.8N, 0.6 m, EPSG:26910 — integer pixel offset from the DOQQ origin), so no reprojection. BUT it is not pixel-identical to the DOQQ: at best alignment (dx=dy=0) 94% of pixels differ, mean |diff| 8.1 DN, while band means match to 0.03 DN. Mean gradient is 0.832x the DOQQ's and lag-1 autocorrelation rises 0.949 -&gt; 0.970, i.e. the held file has lost ~17% of its high-frequency energy relative to the delivered NAIP. It is a smoothed derivative, not a byte clip. The producing script is unidentified (see unknowns). DOQQ TIFF tags corroborate the vendor chain: TIFFTAG_IMAGEDESCRIPTION='OrthoVista', TIFFTAG_SOFTWARE='Trimble Germany GmbH'.</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>This is the reference acquisition of the 2019n/2023n pair, and its NIR band (808-882 nm) sits on the vegetation NIR plateau, so NDVI computed here is 'normal'. Its October date means deciduous crowns are already partly senesced relative to the summer King County years, so a canopy model calibrated on summer imagery will under-call deciduous stands here. The held file's ~17% high-frequency loss means the model sees a blurrier scene than NAIP actually delivered — small crowns and crown boundaries are softened, which biases toward under-segmentation. Because the identical smoothing is present in 2023n, it is NOT a 2019-vs-2023 temporal artefact; it IS a 2019n/2023n-vs-other-sources artefact.</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_fgdc_2019/47122/m_4712214_ne_10_060_20191011.txt</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>Digital imagery was collected at a nominal GSD of 60cm using 11 Cessna 441's, one Rockwell Turbo Commander 690, one Piper PAY2 and one Swearingen Merlin-3 aircraft flying at an average flight height of 8400m AGL for the SH120 acquisition and 4400m AGL for SH100 acquisition. Aircraft flew with Leica Geosystem's ADS100/SH100 digital sensors with firmware 4.60 or ADS100/SH120 digital sensors with firmware 4.60. ... The ADS100 spectral ranges are; Red 619-651nm, Green 525-585nm, Blue 435-495nm and Near-infrared at 808-882nm. The CCD arrays have a pixel size of 5.0 microns ... The CCD's have a dynamic range of 72db and the A/D converters have a resolution of 14bits. The ADS is a push-broom sensor ... Using the revised exterior orientation from the bundle adjustment, orthorectified image strips were created with Xpro software and the June 2018 USGS 10m NED DEM. The Xpro orthorectification software applies an atmospheric-BRDF radiometric correction to the imagery. This correction compensates for atmospheric absorption, solar illumination angle and bi-directional reflectance. ... the strips were then imported into Inpho's OrthoVista 7.1.2 package which was used for the final radiometric balance, mosaic, and DOQQ sheet creation. The final DOQQ sheets, with a 300m buffer and a ground pixel resolution of 60cm were then combined and compressed to create the county wide CCMs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif (2023n; held as '2022n' until 2026-08-22) — NAIP WA 2023, DOQQ quads m_4712213/m_4712214, acquired 2023-10-07</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA APFO NAIP; DOQQ delivery hosted on Azure (Planetary Computer NAIP v002)</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>4 band, R,G,B,NIR. NO synthesised band. BUT THE PASSBANDS ARE NOT THE SAME AS 2019: NIR 720-850 nm (vs 808-882 in 2019), Red 580-660 nm (vs 619-651), Green 480-590 nm (vs 525-585), Blue 420-510 nm (vs 435-495). Every band is wider and shifted. The 2023 NIR band starts at 720 nm — inside the vegetation red edge, where reflectance is still climbing — while the 2023 red band extends down to 580 nm into the green/yellow, where vegetation reflects more. Both changes push NDVI DOWN for identical vegetation. NOTE (MEASURED): held file band 4 colorinterp='alpha' (same trap as 2019n).</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>MAJOR DIFFERENCE FROM 2019: collected at 15-30 cm native and delivered at 60 cm — a 2x to 4x downsample. 2019 was collected at 60 cm and delivered at 60 cm. The two years therefore reach the same 0.6 m grid by completely different routes. The resampling kernel used for the 15-30 cm -&gt; 60 cm gridding is NOT STATED (see unknowns). Flight overlap 20% (2019: 30%).</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on the Azure-hosted DOQQ: DEFLATE COG, PREDICTOR=2, lossless (Microsoft's COG rewrite). The 2023 NAIP abstract states for the county mosaics: 'Two types of compression may be used for NAIP imagery: MrSID and JPEG 2000. The target value for the compression ratio is 40:1 for imagery.' — that is the CCM, not the DOQQ. USDA DOQQ internal compression NOT FOUND (see unknowns). Held file: LZW, lossless.</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>HxMap Mosaic software performed 'the final radiometric balance, mosaic, and DOQQ sheet creation'. 300 m DOQQ buffer. Frame-based mosaicking (2019 was strip-based push-broom) — different seamline geometry and different residual relief displacement per frame.</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>8-bit output. Atmospheric-BRDF radiometric correction at orthorectification, then 'final radiometric balance' in HxMap Mosaic (2019 used Inpho OrthoVista 7.1.2). Different vendor, different software, different balance target. Not calibrated reflectance.</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>Leica HxMap, using the '2018 or newer HxIP DEM' — a commercial Hexagon elevation product, NOT the USGS 10 m NED used in 2019. AAT via HxMap APM tiepointing + HxMap Triangulation bundle adjustment with field-surveyed photo-identifiable GCPs.</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED: held file is on the identical grid to 2019n (same origin, same 0.6 m, EPSG:26910), so the two years are mutually co-registered. Same ~17% high-frequency loss vs the delivered DOQQ (gradient ratio 0.838, lag-1 autocorr 0.933 -&gt; 0.963, 95% of pixels differ, mean |diff| 11.6 DN, band means match to 0.07 DN). Unlike the 2019 DOQQ, the 2023 DOQQ carries NO OrthoVista/Trimble TIFF tags — consistent with the documented switch to HxMap.</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>THIS IS THE LARGEST DOCUMENTED FAKE TEMPORAL SIGNAL IN THE 2019n/2023n PAIR. MEASURED over 6,291,456 pixels sampled from identical windows in both co-registered files: mean DN rises in every band (R 51.5-&gt;82.7, G 72.5-&gt;100.9, B 78.0-&gt;103.5, NIR 67.6-&gt;106.1). Restricted to the 1,875,932 pixels vegetated in 2019 (NDVI&gt;0.3), red rises +42.2 DN but NIR only +52.1 DN, so mean NDVI on the SAME GROUND falls 0.4825 -&gt; 0.3812 (-0.101) and only 69.9% of those pixels remain above NDVI 0.3. The reverse-selection control is strongly asymmetric (select 2023 NDVI&gt;0.3: 0.4565 -&gt; 0.4282, only -0.028; 80.5% still qualify), which rules out regression to the mean. Selection-free distribution moments move the same way: NDVI p75 0.3739 -&gt; 0.3113, p90 0.5316 -&gt; 0.4835, fraction NDVI&gt;0.3 0.2982 -&gt; 0.2590. CONSEQUENCE: a fixed NDVI threshold applied to 2019n and 2023n reports a ~13% relative canopy loss, and flags 30% of 2019-vegetated pixels as lost, on ground where the documented cause is a sensor swap that moved the NIR passband off the plateau and widened the red band. Any NDVI-based reference, threshold, or feature must be recalibrated per-acquisition; NDVI is not comparable between 2019n and 2023n. Separately, 2023n's native 15-30 cm capture downsampled to 60 cm gives it different aliasing and effective resolution from 2019n's native 60 cm capture, and its HxIP DEM ortho gives different tree/building lean, so per-crown geometry also differs.</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_fgdc_2023/47122/m_4712214_ne_10_060_20231007_20240209.xml</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>Digital imagery was collected at a nominal GSD of 15cm to 30cm using 6 Cessna 441's, 2 Reims-Cessna F406, 4 Piper PA31's, one Piper PAY2 and one Rockwell AC69 aircraft flying at an average flight height of 4470m to 8400m AGL. Aircraft flew with Leica Geosystem's ContentMapper digital sensors with firmware 6.01. Each sensor collected 4 image bands Red, Green, Blue and Near-infrared in an integrated frame image with an across-track field of view 67.1 degrees. The ContentMapper spectral ranges are; Red 580-660nm, Green 480-590nm, Blue 420-510nm and Near-infrared at 720-850nm. The BSI CMOS arrays have a pixel size of 3.76 microns and deliver an integrated frame image with 40000x8200 format. The CMOS arrays have a dynamic range of 83db and the A/D converters have a resolution of 14bits. The ContentMapper is a frame-based sensor ... The design parameters used in MissionPro will be 20% lateral overlap and 15cm to 30cm resolution. ... orthorectified image frames were created with HxMap software and the 2018 or newer HxIP DEM. The HxMap orthorectification software applies an atmospheric-BRDF radiometric correction to the imagery. ... the strips were then imported into the HxMap Mosaic software which was used for the final radiometric balance, mosaic, and DOQQ sheet creation. The final DOQQ sheets, with a 300m buffer and a ground pixel resolution of 60cm were then combined and compressed to create the county wide CCMs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>NAIP WA 2017 (1 m, quads m_4712213/m_4712214 over Edmonds, acquired 2017-08-15 and 2017-08-21) — spec-change context, not held by the project</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA APFO NAIP; NOAA Digital Coast WA_NAIP_2017_8572</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>4 band R,G,B,NIR; NIR 808-882 nm, same as 2019. No synthesised band.</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Collected at nominal 40 cm and delivered at 1 m over WA (tile names read m_4712214_ne_10_1_20170815, where '1' is the 1 m GSD field) — a downsample. 2019 onward the WA GSD field becomes '060'.</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>CCM compression only; DOQQ internal compression not stated. Azure-hosted 2017 DOQQ measured as DEFLATE COG (Microsoft rewrite).</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Inpho OrthoVista 7.0, final radiometric balance + mosaic + DOQQ creation, 300 m buffer.</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>Atmospheric-BRDF correction in XPro, then final radiometric balance in Inpho OrthoVista 7.0 (2019 used 7.0-series successor 7.1.2).</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>Leica XPro with the 'June 2014 USGS 10m NED DEM' — a DIFFERENT DEM VINTAGE from 2019's June 2018 NED and from 2023's HxIP DEM.</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED via STAC: 2017 tiles over Edmonds are 1.0 m GSD in EPSG:26910, vs 0.6 m for 2019/2021/2023 — confirming the program GSD step for WA occurred between 2017 and 2019.</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>Not held by the project, but it fixes the program timeline: the WA NAIP 1 m -&gt; 0.6 m GSD change and the summer -&gt; October flying-date change BOTH happened between 2017 and 2019, while the sensor and passbands stayed constant (ADS100) until the 2023 ContentMapper switch. That isolates the 2019n-&gt;2023n NDVI shift to the sensor/passband change rather than to the GSD or season change.</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2017_8572/2017_4BandImagery_m8572_met.xml</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>Digital imagery was collected at a nominal GSD of 40cm using nine Cessna 441, one Reims F406, one Piper and one Merlin aircraft ... Aircraft flew with Leica Geosystem's ADS100/SH100 digital sensors with firmware 4.57 or ADS100/SH120 digital sensors with firmware 4.57. ... The ADS100 spectral ranges are; Red 619-651nm, Green 525-585nm, Blue 435-495nm and Near-infrared at 808-882nm. ... orthorectified image strips were created with Xpro software and the June 2014 USGS 10m NED DEM. ... the strips were then imported into Inpho's OrthoVista 7.0 package which was used for the final radiometric balance, mosaic, and DOQQ sheet creation. The final DOQQ sheets, with a 300m buffer and a ground pixel resolution of 1m or 60cm were then combined and compressed to create the county wide CCMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>NAIP WA 2015 (1 m, acquired 2015-08-07 over Edmonds) — spec-change context, not held by the project</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA APFO NAIP; NOAA Digital Coast WA_NAIP_2015_6208</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>4 band R,G,B,NIR; NIR 808-882 nm. No synthesised band. 'The Nadir Green band was collected in high resolution mode effectively doubling the resolution for that band' — i.e. the green channel of every ADS100-era NAIP (2015/2017/2019) is captured at 2x the resolution of R/B/NIR and then brought back to a common grid; the green band is not sampled identically to the others.</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Collected at nominal 40 cm, delivered at 1 m (tile names m_4712214_ne_10_1_20150807).</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Not stated for the DOQQ.</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Inpho OrthoVista 6.0.1 for final radiometric balance, mosaic and DOQQ creation.</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>Atmospheric-BRDF correction in XPro, final radiometric balance in Inpho OrthoVista 6.0.1 (a different OrthoVista major version from 2017's 7.0 and 2019's 7.1.2).</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>Leica XPro with the 'June 2015 USGS 10m NED DEM'.</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>Establishes that the 'Nadir Green band ... high resolution mode' quirk applies to 2019n, and that the OrthoVista version changed at every WA NAIP epoch (6.0.1 -&gt; 7.0 -&gt; 7.1.2 -&gt; HxMap Mosaic).</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>Confirms that within the ADS100 era (2015/2017/2019) the spectral response was stable, so greenness drift across those years is NOT a passband effect. It also means the green band of 2019n has a different native sampling from its red/blue/NIR bands, which matters for any green-based index computed at 0.6 m.</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M29" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2015_6208/2015_4BandImagery_m6208_met.xml</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>Digital imagery was collected at a nominal GSD of 40cm using eight Cessna 441 aircraft and two Beechcraft King Air flying at an average flight height of 5000m AGL. All aircraft flew with Leica Geosystem's ADS100/SH100 digital sensors with firmware 4.42. ... The ADS100 spectral ranges are; Red 619-651nm,Green 525-585nm,Blue 435-495nm and Near-infrared at 808-882nm. ... orthorectified image strips were created with Xpro software and the June 2015 USGS 10m NED DEM. The Xpro orthorectification software applies an atmospheric-BRDF radiometric correction to the imagery. ... the strips were then imported into Inpho's OrthoVista 6.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>NAIP WA 2021 (0.6 m, acquired 2021-06/07) — the interleaving acquisition between the project's two NAIP years; not held by the project</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA APFO NAIP; NOAA Digital Coast WA_NAIP_2021_9586; contractor Surdex</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>5 bands collected (R,G,B,NIR,Panchromatic), 4 delivered. Passbands at 40% intensity: R 585-690, G 570-600, B 425-530, NIR 700-830 nm — different again from both 2019 and 2023. No synthesised band, but note a panchromatic band was captured and is not in the delivery.</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Native 15 cm 'rectified to 60cm' — a 4x downsample, like 2023 and unlike 2019.</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>CCM built with Lizardtech GeoExpress 10.0.1.5035 (MrSID). DOQQ internal compression not stated.</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>SURDEX software computed optimal seam paths, checked seam topology, generated occlusion/smear polygons for steep terrain, and produced master tiles; individual tiles may fail the Image Metrics ranges 'due to land cover' — the target is met at state level, so per-tile radiometry varies systematically WITH LAND COVER.</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>THIS IS THE MOST EXPLICIT FORCED-NORMALISATION STATEMENT IN THE NAIP RECORD, AND IT BELONGS TO 2021, NOT TO 2019 OR 2023: images are 'corrected to conform to the Image Metrics', i.e. adjusted toward a USDA APFO target radiometric specification. Also removes bidirectional reflectance, vignetting and illumination trends. The 2019 and 2023 records describe 'final radiometric balance' without naming an APFO target.</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>'For each project area the highest resolution DEM or LiDAR was obtained' — i.e. lidar/high-resolution DEM, unlike 2019's 10 m NED and unlike 2023's HxIP DEM. Ultramap triangulation, field-surveyed GCPs to +/- 0.25 m RMSE XYZ.</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>Horizontal accuracy spec history, same record: 'Beginning in 2009, all NAIP imagery acquisitions used the +/- 6 meters to ground and in 2016 the specification was changed to +/- 4 meters to true ground.'</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>Not held, but it is the decisive proof that NAIP band response is NOT stable across the program: three sensors in three consecutive WA NAIP epochs with three different NIR passbands (808-882 / 700-830 / 720-850 nm). Any future decision to add NAIP 2021 as a year, or to treat 'NAIP' as one homogeneous sensor, would inject a third distinct spectral response. The 'corrected to conform to the Image Metrics' statement also shows USDA applies a target-histogram normalisation whose per-tile residual varies with land cover — meaning forested tiles and developed tiles are not balanced identically.</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2021_9586/2021_4BandImagery_Washington_m9586_met.xml</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>The imagery was collected using the following digital sensors: Vexcel Condor M4.1 (Serial Number 435S52516X011066), Vexcel Condor M4.1 (Serial Number 435S72614X210073) ... With this flying height, there is a 30% sidelap, giving the collected data nominal ground sampling distance of 15cm and rectified to 60cm. ... The Vexcel Condor has the following band specifications at 40% intensity: Red 585-690, Green 570-600, Blue 425-530, Near Infrared 700-830, all values are in nanometers. ... For each project area the highest resolution DEM or LiDAR was obtained and utilized for rectification of captured imagery. ... Surdex Grouping Tool provides real-time updates of the USDA APFO Image Metrics. The image technician adjusts image correction parameters to bring the radiometric characteristics of large groups of images within the Image Metrics ranges. ... SURDEX software was used to orthorectify, color correct, and remove bidirectional reflectance, vignetting and other illumination trends. USDA APFO Image Metrics are measured and images corrected to conform to the Image Metrics using SURDEX software. ... Lizardtech GeoExpress version 10.0.1.5035 was used to create the CCM image file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2016_hires_lc_snohfull.tif and its Edmonds clip ccap_2016_hires_lc.tif — C-CAP Land Cover, Snohomish County, Washington, 2016 (source wa_snohomish_co_ccap_hr_landcover20190314.img)</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>NOAA Office for Coastal Management, Coastal Change Analysis Program (C-CAP) high-resolution land cover, 2016 generation. InPort catalog item 53263.</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>Single 8-bit thematic band, palette colorinterp in the full-county file, gray with nodata=0 in the Edmonds clip. Class codes only — no spectral bands.</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Produced at 1 m native ('initial 1m spatial resolution 6 class high resolution land cover product'); held files are 1.0 m in EPSG:26910, so no resolution change. MEASURED: the full-county file carries OVERVIEWS_ALGORITHM='IMAGINE Nearest Neighbor Resampling' — overviews only, base data unresampled.</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED: full-county file DEFLATE COG PREDICTOR=2 (lossless); Edmonds clip LZW (lossless). Source distribution is ERDAS .img/.ige.</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>Countywide product; class-specific refinement passes (Water, Unconsolidated Shore, Agriculture, Wetlands, Open Space Developed) applied by manual interpretation and editing in ERDAS Imagine, plus ancillary layers: NGS 2014 MLLW orthoimagery, WA State Dept. of Agriculture 2015 Crop Distribution, SSURGO, NWI, and a Snohomish County parcel dataset. 'Additional clean up was performed to remove speckle and slivers.'</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>N/A (thematic).</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>Inherited from the 1 m NAIP source imagery; not independently stated.</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
+        <is>
+          <t>THREE IMPORTANT FACTS. (1) InPort 53263 IS RECOVERABLE — it is served in full at the URL above on NOAA's own bulk-download server, so no Wayback recovery was needed. (2) The record's own completeness-report contradicts the file it describes: it states 'There are no pixels representing class 9 (Deciduous Forest), 11 (Mixed Forest)' while the delivered raster puts ALL forest in code 11 (MEASURED: full-county histogram gives class 11 = 3,735,929,171 px and STATISTICS_MODE=11, with classes 9 and 10 empty). The completeness-report is boilerplate carried over from the 30 m C-CAP product and must not be trusted; the supplemental-information ('9 10 11 Upland Forest', collapsed) is what the file actually implements. (3) The class-scheme document in force at the time (the 3-page ccap-class-scheme-highres.pdf, recovered from Wayback snapshot 20210318095706) defines 9 = Deciduous Forest, 10 = Evergreen Forest, 11 = Mixed Forest and contains NO class 4 — so the published scheme, the product metadata, and the raster disagree with each other about what code 11 means.</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>This is one of the project's two scoring references and it is a DIFFERENT PRODUCTION GENERATION from the other. Canopy here is a stand-based GEOBIA/Random-Forest label with no height information, trained by photo interpretation on 1 m NAIP: it drops isolated street and yard trees by construction and cannot distinguish a tall shrub from a short tree without a DSM. MEASURED over the Edmonds clip: code 11 = 26.64%. The pipeline's documented assumption 'hi-res forest=11' is empirically correct FOR THIS FILE, but only because the product collapsed 9/10/11 into 11 — not because 11 means 'Mixed Forest' as the then-current published scheme says. Note also that this clip is the known bad clip (CHATLOG records it covers ~51.9% of the study-area grid vs ~91% for the full-county source), so absolute percentages from it describe the clip, not the city.</t>
+        </is>
+      </c>
+      <c r="L31" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t>https://chs.coast.noaa.gov/htdata/raster1/landcover/bulkdownload/hires/wa/WA_Snohomish_2016_lc.xml</t>
+        </is>
+      </c>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>&lt;catalog-item-id&gt;53263&lt;/catalog-item-id&gt; ... The timeframe for this metadata is summer 2016. These maps are developed utilizing high resolution National Agriculture Imagery Program (NAIP) imagery ... [lineage] Random Forest Classification: The initial 1m spatial resolution 6 class high resolution land cover product was developed using a Geographic Object-Based Image Analysis (GEOBIA) processing framework. This involves taking each image to be classified and grouping the pixels based on spectral and spatial properties into regions of homogeneity called objects. ... Each object is labeled using a Random Forest Classifier which is ensemble version of a Decision Tree. Training data for the initial 6 classes (Herbaceous, Bare, Impervious, Water, Forest and Shrub) were generated through photo interpretation. ... Wetlands were derived through a modeling process which used ancillary data such as Soils (SSURGO), the National Wetlands Inventory (NWI) and topographic derivatives. ... Attributes for this product are as follows: 0 Background 1 Unclassified 2 Impervious 3 4 5 Developed, Open Space 6 Cultivated Crops 7 Pasture/Hay 8 Grassland/Herbaceous 9 10 11 Upland Forest 12 Scrub/Shrub ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2021_hires_lc.tif — NOAA C-CAP high-resolution land cover, VERSION 2 generation, 2020-2021 vintage</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>NOAA Office for Coastal Management C-CAP high-resolution land cover v2; initial feature extraction contracted to Ecopia Tech Corporation under NOAA's Coastal Geospatial Services Contract (CGSC)</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Single uint8 thematic band, nodata=0. Class codes only.</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Produced at 1 m ('Initial 1m spatial resolution feature extraction'); held file is 1.0 m EPSG:26910, LZW, so no resolution change in the held copy. Note the extraction is 1 m but the source imagery is 30 cm or finer, so the product is already an aggregation of finer evidence — the opposite of the 2016 product, whose 1 m output matched its 1 m NAIP input.</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED: LZW, tiled 256x256, lossless.</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia proprietary AI feature recognition for the initial impervious/water/canopy layers, then NOAA refinement passes in ERDAS Imagine using OpenStreetMap road/building/railroad layers (impervious), manual water and canopy edits, SSURGO/NWI/topographic derivatives for wetlands, and an NDVI threshold plus manual interpretation to split grass from bare.</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>N/A (thematic).</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>Inherited from the source aerial imagery; not independently stated.</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>THE CLASS SCHEME IS A DIFFERENT GENERATION FROM THE 2016 FILE. The current 8-page ccap-class-scheme-highres.pdf (https://coast.noaa.gov/data/digitalcoast/pdf/ccap-class-scheme-highres.pdf, md5 ce2eaecb55172c900bbd5ff39828e864 — matches the md5 given in the task) defines '11 Upland Tree/Forest' as a single undifferentiated tree class and introduces '4 Impervious Under Canopy', which it defines verbatim as: 'Impervious Under Canopy represents the intersection of impervious surface and tree canopy features that coexist within the same space but at different heights. This category is typically derived from an independent mapping of impervious and canopy features (such as those produced in phase I products) and is not usually mapped explicitly.' It also notes that 11 is undifferentiated: 'deciduous and evergreen mapping would be represented by classes 9 and 10 and would replace any preexisting, undifferentiated upland tree pixels.' The superseded 3-page scheme that governed the 2016 file has no class 4 at all and splits forest into 9/10/11. SEPARATELY: the v2 distribution carries a use restriction the 2016 product does not — 'This land cover data may not be used for the purpose of creating, training, improving, modifying, validating, testing, or evaluating machine learning algorithms, or otherwise leverage the product for the purposes of machine learning for a period of five years from its date of creation. By downloading this data you are agreeing to this restriction.' (https://coastalimagery.blob.core.windows.net/ccap-landcover/CCAP_bulk_download/High_Resolution_Land_Cover/Phase_2_Expanded_Categories/Land_Cover_post_2023/restriction.htm). The project uses this file as an evaluation reference for an ML model; reporting, not adjudicating.</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>THIS IS THE SECOND MAJOR FAKE TEMPORAL SIGNAL, AND IT FLIPS THE SIGN OF THE MEASURED CANOPY CHANGE. NOAA's own v2 lineage states that canopy = upland forest COMBINED WITH impervious under canopy. Scoring canopy as code==11 therefore under-counts v2 canopy by exactly the class-4 area. MEASURED over the 44,229,312 co-registered 1 m cells of the two Edmonds clips (both 100% valid, identical grid): class 4 is 2.41% of the area in 2021 and 0.00% in 2016; canopy scored as ==11 goes 26.64% -&gt; 24.82%, a LOSS of 1.82 pp; canopy scored as (11 or 4) goes 26.64% -&gt; 27.23%, a GAIN of 0.58 pp. Adding the forested wetlands (11,13,16) does not change this: -1.76 pp without class 4, +0.65 pp with it. And 53.4% of the 2021 class-4 pixels were labelled class 11 (forest) in 2016 — the new class is literally re-coding ground the older product called forest. So the entire apparent canopy decline between the project's two scoring references is attributable to a class that did not exist in the 2016 scheme. IoU between the two references on ==11 is only 68.9% (70.6% on 11-or-4), which is the practical ceiling on any model score computed against them as if they were the same ruler. FURTHER: because v2 uses a stereo DSM to enforce a height criterion and 30 cm or better imagery, while the 2016 product used 1 m NAIP with no height data, v2 resolves isolated and street trees that the 2016 GEOBIA product structurally omits — so the two references also disagree about small crowns in a way that is not captured by any class remap.</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/ccap-landcover/CCAP_bulk_download/High_Resolution_Land_Cover/Phase_1_Initial_Layers/Canopy/2020%20to%202021%20CCAP%20Version%202%20Canopy%20Cover.xml</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>[Phase 1 canopy, v2] 'This dataset was created by NOAA's Ocean Service, Office for Coastal Management (OCM). Classification: Initial 1m spatial resolution feature extraction for canopy (tree and scrub/shrub) mapping was conducted by Ecopia Tech Corporation and was developed by Ecopia Tech Corporation using a proprietary feature recognition technology. This involves taking each image and classifying the pixels based on spectral and spatial properties, based on training examples and analyst refinement. ... Once the review and edits were complete, the canopy class was created by combining the upland forest class with the impervious under canopy class.' AND from the abstract: 'The timeframe for this metadata is 2020 through 2021 ... These maps were developed utilizing high resolution 30cm or better aerial imagery. In addition, a digital surface model (DSM) derived from the stereo imagery was used to determine vegetation heights.' AND the v2 Phase-2 land-cover lineage (read from the sibling product fl_tampa_2021_ccapv2_hires_landcover_20230512.xml, generation-level boilerplate): 'Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia and was developed by Ecopia using a proprietary feature recognition technology. ... This work was done under contract to NOAA, through NOAA's Coastal Geospatial Services Contract (CGSC) vehicle. ... Attributes for this product are as follows: 0 Background 1 Unclassified 2 Developed Impervious 3 4 Developed Impervious under Tree Canopy 5 Developed, Open Space 6 Cultivated Crops 7 Pasture/Hay 8 Grassland/Herbaceous 9 10 11 Upland Tree (Forest) 12 Scrub/Shrub ... 23 Estuarine Aquatic Bed'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N32"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D122"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Result (measured)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c (R2, resid std); conditional-std functional dependence of each band on the other two, normalised by that band's sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.970 r_RB=0.961 r_GB=0.977; B~aR+bG+c: R2 med=0.9545 min=0.9540, resid sd=11.23 DN, a=0.13 b=0.94 c=-2.2; control fits G~(R,B) R2=0.9733, R~(G,B) R2=0.9469; normalised unexplained fraction B=0.1787 G=0.1397 R=0.1958; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.065</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>POSITIVE CONTROL. Blue is no more independent than R/G, mean B sits 2.1 DN ABOVE G (unique in the King series), and the fit is B ~ 0.94*G + 0.13*R - 2.2: a blue derived largely from GREEN, then contrast-stretched. Note the raw R2 is only 0.954, NOT ~1 - the literal linear test fails on its own positive control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py automatic edge-response (10-90% ESF rise) copied verbatim from the script that produced IMAGERY_FACTS 2.2, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 40.1 cm ground; band-1 rise=2.68 px -&gt; EFFECTIVE 107.5 cm (oversampling 2.68x); published 2.8x; per-band rise px: R=2.68 G=1.72 B=1.68; normalised HF power rel. green: R=0.73 G=1.00 B=0.92; autocorr lag1-4 (G) = 0.9714/0.9069/0.8323/0.7641; band-1 rise is the MEDIAN over 5 sites, per-site sd +/-0.37 px</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>2.68x oversampled, effective 107 cm not the 40.1 cm grid (published 2.8x - REPRODUCED). CRITICAL: the published 2.8x is BAND 1 ONLY. Green and blue rise 1.72/1.68 px (~70 cm); the RED band alone is degraded, at 5/5 sites, corroborated by red holding 0.73x green's normalised HF power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: mean |first difference| at each phase mod 8 (window origin snapped to an absolute multiple of 16 so in-window phase == absolute phase), boundary-vs-within ratio and z, both axes, all bands, 5 sites; plus mod-32 profile to confirm the period</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1577 v=1.0888; z h=8.68 v=5.28; modal peak phase = 7 (=block boundary) in both axes, 15/15 site-band-axis combinations agree; mod-32 profile peaks at indices 7,15,23,31; per-axis phase scan: h modal phase 7 (15/15, mean z=9.25), v modal phase 7 (14/15, mean z=7.88)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: an intact JPEG 8x8 DCT block grid is present and phase-locked to THIS pixel grid, yet the file is tagged lossless DEFLATE. The DEFLATE tag describes only the final re-wrap; the data has a lossy JPEG history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over all 5 ground-matched windows per band; distinct values used out of 256 and empty bins strictly inside the used range (comb detection)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable. Note this does NOT clear the file - the stretch here shows up as clipping (T5), not as missing interior levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.604% at DN0, 2.621% at DN255; G: 0.505% at DN0, 2.346% at DN255; B: 0.818% at DN0, 3.308% at DN255; band sd R/G/B = 54.1/56.2/59.6</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>HEAVY clipping at BOTH ends of ALL THREE bands - by far the most aggressive contrast stretch in the archive (next worst is 2002 at 2.5% in blue only; everything else &lt;=0.52%). ~3% of the scene has unrecoverable highlights, ~0.6% unrecoverable shadow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, over the same 5 fixed ground windows in every acquisition (cast2.py definition)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>mean R=100.9 G=115.3 B=117.4; G-R=+14.4 DN; B-G=+2.1 DN; GRVI mean=+0.0784 sd=0.1351; frac(GRVI&gt;.02)=0.8208 (published .8027)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Start of the King drift and its extreme. 2000 is the ONLY King year where blue sits ABOVE green; every other King year has B 8.4-29.3 DN below G. Its archive-high greenness is a colour-balance artefact, driven by red being 14.4 DN DARKER than green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c (R2, resid std); conditional-std functional dependence of each band on the other two, normalised by that band's sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.991 r_RB=0.981 r_GB=0.979; B~aR+bG+c: R2 med=0.9628 min=0.9592, resid sd=8.57 DN, a=0.51 b=0.51 c=-17.3; control fits G~(R,B) R2=0.9861, R~(G,B) R2=0.9862; normalised unexplained fraction B=0.1342 G=0.1174 R=0.1161; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.149</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>FLAG: blue is no more independent than R/G, scoring in the same band as the known-synthetic 2000 (1.065) and far from 2013+ King (2.14-2.71). CANNOT be cleared. But it lacks 2000's corroborating fingerprints (B-G = -16.8 DN, normal). Follow-up, not a detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py automatic edge-response (10-90% ESF rise) copied verbatim from the script that produced IMAGERY_FACTS 2.2, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 40.1 cm ground; band-1 rise=1.44 px -&gt; EFFECTIVE 57.8 cm (oversampling 1.44x); published 1.4x; per-band rise px: R=1.44 G=1.43 B=1.42; normalised HF power rel. green: R=0.95 G=1.00 B=1.01; autocorr lag1-4 (G) = 0.9590/0.8749/0.7859/0.7080; per-site sd +/-0.07 px</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>1.44x oversampled, effective 58 cm not the 40.1 cm grid (published 1.4x - REPRODUCED). All three bands equally sharp (max/min 1.014), so unlike 2000 there is no per-band degradation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: mean |first difference| at each phase mod 8 (window origin snapped to an absolute multiple of 16), boundary-vs-within ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1360 v=1.1600; z h=9.32 v=11.12; modal peak phase = 7 (=block boundary) in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=9.99), v phase 7 (15/15, z=13.23)</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT block grid, phase-locked to this pixel grid, in a file tagged lossless DEFLATE. One of the two strongest blocking signatures in the archive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over all 5 ground-matched windows per band; distinct values out of 256 and empty bins strictly inside the used range</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.398% at DN255; G: 0.000% at DN0, 0.490% at DN255; B: 0.000% at DN0, 2.541% at DN255; band sd R/G/B = 46.5/45.4/47.3</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>BLUE-ONLY highlight clipping: 2.5% of blue pinned at 255 versus 0.40/0.49% for red/green, and zero clipping at DN0. A per-band (not global) stretch was applied to blue. Second-worst clipping in the archive after 2000, but a different and milder defect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (cast2.py definition)</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>mean R=129.2 G=133.9 B=117.0; G-R=+4.7 DN; B-G=-16.8 DN; GRVI mean=+0.0236 sd=0.0338; frac(GRVI&gt;.02)=0.4287 (published .5029)</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift: red has already risen 28 DN since 2000 while green rose 19, collapsing G-R from +14.4 to +4.7 DN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c (R2, resid std); conditional-std functional dependence of each band on the other two, normalised by that band's sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.986 r_RB=0.981 r_GB=0.986; B~aR+bG+c: R2 med=0.9766 min=0.9633, resid sd=6.75 DN, a=0.37 b=0.54 c=-7.8; control fits G~(R,B) R2=0.9826, R~(G,B) R2=0.9774; normalised unexplained fraction B=0.1373 G=0.1328 R=0.1438; RELATIVE blue-redundancy index nB/mean(nG,nR)=0.993</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>FLAG, strongest in the archive: blue is the LEAST independent band here (index 0.993, below the known-synthetic 2000's 1.065), and the raw R2 0.9766 is the highest of all 20 files. CANNOT be cleared. Confounded by 2005 being the most oversampled file (3.92x), which inflates all band correlations. Follow-up, not a detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py automatic edge-response (10-90% ESF rise) copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 20.1 cm ground; band-1 rise=3.92 px -&gt; EFFECTIVE 78.5 cm (oversampling 3.92x); published 4.0x; per-band rise px: R=3.92 G=4.01 B=3.95; normalised HF power rel. green: R=0.88 G=1.00 B=1.31; autocorr lag1-4 (G) = 0.9912/0.9680/0.9346/0.8959 (highest lag-1 in the archive); per-site sd +/-0.45 px</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>3.92x oversampled, effective 79 cm not the 20.1 cm grid (published 4.0x - REPRODUCED). Confirms the counter-intuitive published finding: 2005 resolves COARSER than 2000's nominal 40 cm grid despite a nominally 2x finer grid. All three bands equally soft, so this is whole-image, not per-band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: mean |first difference| at each phase mod 8 (origin snapped to an absolute multiple of 16), boundary-vs-within ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2916 v=1.2688; z h=3.90 v=4.40; modal peak phase = 7 (=block boundary) in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=4.32), v phase 7 (15/15, z=4.71)</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE. Largest boundary/within ratio of the King years (1.29) though lowest z, because 3.92x oversampling smooths the within-block differences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over all 5 ground-matched windows per band; distinct values out of 256 and empty bins strictly inside the used range</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 250 distinct (DN 6-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb. Green's 250 distinct is a content limit (range starts at DN 6), not a stretch artefact - there are no empty bins inside the used range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.056% at DN255; G: 0.000% at DN0, 0.012% at DN255; B: 0.000% at DN0, 0.022% at DN255; band sd R/G/B = 43.5/37.6/38.1</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (cast2.py definition)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>mean R=119.7 G=125.3 B=107.0; G-R=+5.7 DN; B-G=-18.3 DN; GRVI mean=+0.0194 sd=0.0530; frac(GRVI&gt;.02)=0.3863 (published .4782)</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c (R2, resid std); conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.980 r_RB=0.952 r_GB=0.940; B~aR+bG+c: R2 med=0.9091 min=0.8982, resid sd=11.58 DN, a=0.61 b=0.19 c=-11.8; control fits G~(R,B) R2=0.9644, R~(G,B) R2=0.9655; normalised unexplained fraction B=0.2551 G=0.1684 R=0.1623; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.543</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Intermediate. Blue carries ~1.5x more independent information than R/G - clearly more than 2000/2002/2005/2012, clearly less than 2013+ King. Not flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 20.1 cm ground; band-1 rise=1.28 px -&gt; EFFECTIVE 25.7 cm (oversampling 1.28x); published 1.3x; per-band rise px: R=1.28 G=1.26 B=1.26; normalised HF power rel. green: R=0.59 G=1.00 B=0.76; autocorr lag1-4 (G) = 0.8930/0.8013/0.7627/0.7231; per-site sd +/-0.04 px</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>1.28x oversampled, effective 26 cm (published 1.3x - REPRODUCED). One of the two properly-sampled 20 cm years. Red's low normalised HF (0.59) is NOT blur - edge response is flat across bands (max/min 1.033); it is the physical chlorophyll-absorption flattening of red over vegetation, which is why edge response and not HF power is the discriminator for per-band degradation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 |first difference| profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.0792 v=1.0976; z h=4.18 v=4.28; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=5.77), v phase 7 (15/15, z=6.44)</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: JPEG 8x8 grid present (weakest ratio of the King series at 1.08, but phase agreement is perfect) in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.009% at DN0, 0.293% at DN255; G: 0.000% at DN0, 0.120% at DN255; B: 0.071% at DN0, 0.022% at DN255; band sd R/G/B = 44.7/40.4/40.2</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>mean R=132.0 G=130.6 B=105.6; G-R=-1.4 DN; B-G=-24.9 DN; GRVI mean=+0.0048 sd=0.0559; frac(GRVI&gt;.02)=0.2949 (published .4016)</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift - the first King year where red OVERTAKES green (G-R goes negative).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.975 r_RB=0.949 r_GB=0.942; B~aR+bG+c: R2 med=0.9025 min=0.8789, resid sd=14.18 DN, a=0.87 b=0.09 c=-16.2; control fits G~(R,B) R2=0.9617, R~(G,B) R2=0.9628; normalised unexplained fraction B=0.2342 G=0.1891 R=0.1699; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.305</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Intermediate. Not flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 20.1 cm ground; band-1 rise=1.29 px -&gt; EFFECTIVE 25.8 cm (oversampling 1.29x); published 1.3x; per-band rise px: R=1.29 G=1.28 B=1.28; normalised HF power rel. green: R=0.69 G=1.00 B=1.02; autocorr lag1-4 (G) = 0.8925/0.7923/0.7428/0.7025; per-site sd +/-0.03 px</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>1.29x oversampled, effective 26 cm (published 1.3x - REPRODUCED). Properly sampled, all bands equally sharp (max/min 1.020). The most tightly-determined estimate in the archive (per-site sd +/-0.03 px).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 |first difference| profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1353 v=1.1021; z h=6.10 v=7.37; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=8.44), v phase 7 (15/15, z=6.45)</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.068% at DN0, 0.313% at DN255; G: 0.000% at DN0, 0.516% at DN255; B: 0.100% at DN0, 0.220% at DN255; band sd R/G/B = 46.4/41.9/45.4</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>Moderate clipping in green (0.52% at DN255) - an order of magnitude below 2000/2002 but the highest of the 2005-2024 group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>mean R=118.5 G=129.0 B=100.2; G-R=+10.4 DN; B-G=-28.8 DN; GRVI mean=+0.0585 sd=0.0826; frac(GRVI&gt;.02)=0.6393 (published .6237)</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift - a non-monotonic excursion back up (G-R returns to +10.4), showing the 'monotonic' drift is really a per-acquisition colour balance, not a smooth trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.984 r_RB=0.964 r_GB=0.977; B~aR+bG+c: R2 med=0.9544 min=0.9251, resid sd=7.79 DN, a=0.07 b=0.86 c=-5.2; control fits G~(R,B) R2=0.9793, R~(G,B) R2=0.9681; normalised unexplained fraction B=0.1570 G=0.1225 R=0.1550; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.131</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>FLAG: index 1.131 sits just above the known-synthetic 2000 (1.065) and far below 2013+ (2.14-2.71). Its fitted coefficients (a=0.07 R, b=0.86 G) are notably similar to 2000's (0.13/0.94), i.e. blue tracking green. CANNOT be cleared. But B-G = -8.4 DN is normal, so 2000's mean-level fingerprint is absent. Follow-up, not a detection. This file is UNCATALOGUED in phase4seg/config.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 20.1 cm ground; band-1 rise=1.68 px -&gt; EFFECTIVE 33.7 cm (oversampling 1.68x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.68 G=1.39 B=1.35; normalised HF power rel. green: R=0.61 G=1.00 B=1.28; autocorr lag1-4 (G) = 0.9506/0.8879/0.8460/0.8121; per-site sd +/-0.37 px</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.68x oversampled, effective 34 cm on a 20.1 cm grid - markedly softer than 2007/2009 (1.28/1.29) on the byte-identical grid. SECONDARY FLAG: red is the second-largest per-band mismatch in the archive after 2000 (rise 1.68 vs 1.39/1.35, ratio 1.34; red at 0.61x green's normalised HF). High site variance (+/-0.37), so probable rather than confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 |first difference| profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2601 v=1.2471; z h=11.15 v=6.05; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=10.99), v phase 7 (15/15, z=10.85)</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid, one of the strongest in the King series (ratio 1.26, z up to 11.2), in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 239 distinct (DN 17-255), 0 empty bins inside range; B: 251 distinct (DN 2-255), 3 empty bins inside range at [3, 6, 9]</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Negligible: the only King/CoE file with any interior empty bins, and they are 3 isolated values near black (DN 3/6/9). Not a comb - far below the NAIP pattern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.014% at DN255; G: 0.000% at DN0, 0.006% at DN255; B: 0.000% at DN0, 0.014% at DN255; band sd R/G/B = 44.9/37.6/36.5</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping - among the cleanest in the archive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>mean R=101.2 G=112.4 B=104.0; G-R=+11.2 DN; B-G=-8.4 DN; GRVI mean=+0.0822 sd=0.1243; frac(GRVI&gt;.02)=0.5579 (published .6268)</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift, and a second non-monotonic excursion: its band means (R 101.2, G 112.4) are almost identical to 2000's (100.9, 115.3), so 2012 and 2000 share a colour balance that no year between them has.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.991 r_RB=0.930 r_GB=0.916; B~aR+bG+c: R2 med=0.8659 min=0.8338, resid sd=14.93 DN, a=1.17 b=-0.32 c=-3.3; control fits G~(R,B) R2=0.9855, R~(G,B) R2=0.9851; normalised unexplained fraction B=0.2557 G=0.1139 R=0.1154; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.230</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band - blue carries 2.23x more independent information than R/G. This file is the FIRST of the post-2012 King regime: the index jumps from 1.131 (2012) to 2.230 here and never returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.47 px -&gt; EFFECTIVE 14.7 cm (oversampling 1.47x); published 1.3x; per-band rise px: R=1.47 G=1.45 B=1.41; normalised HF power rel. green: R=0.82 G=1.00 B=0.91; autocorr lag1-4 (G) = 0.9577/0.8867/0.8296/0.7882; per-site sd +/-0.40 px</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>1.47x oversampled, effective 15 cm not the 10.0 cm grid (published 1.3x, within the 12.6-13.7 cm published band given +/-0.40 px site spread - REPRODUCED). Bands equally sharp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16) plus mod-32 period confirmation, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2615 v=1.1726; z h=13.02 v=8.67; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; mod-32 profile peaks at indices 7,15,23,31; per-axis scan: h phase 7 (15/15, z=12.41), v phase 7 (15/15, z=16.98)</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag - the STRONGEST blocking signature in the archive (v-axis z=16.98). Intact JPEG 8x8 DCT grid, mod-32 confirms period 8, in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.039% at DN0, 0.018% at DN255; G: 0.003% at DN0, 0.025% at DN255; B: 0.056% at DN0, 0.011% at DN255; band sd R/G/B = 47.5/45.1/43.1</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>mean R=108.4 G=108.4 B=84.4; G-R=-0.1 DN; B-G=-24.0 DN; GRVI mean=+0.0222 sd=0.0791; frac(GRVI&gt;.02)=0.3267 (published .3463)</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift; red and green now exactly equal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.992 r_RB=0.924 r_GB=0.934; B~aR+bG+c: R2 med=0.8758 min=0.8533, resid sd=13.66 DN, a=-0.15 b=1.02 c=4.4; control fits G~(R,B) R2=0.9887, R~(G,B) R2=0.9839; normalised unexplained fraction B=0.2972 G=0.1046 R=0.1145; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.713</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band - the most independent blue in the archive (index 2.713). Note the fitted coefficients (a=-0.15, b=1.02) superficially resemble 2000's 'blue tracks green' pattern, which is exactly why raw coefficients are NOT a detector: the redundancy index separates them 2.71 vs 1.07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.33 px -&gt; EFFECTIVE 13.3 cm (oversampling 1.33x); published 1.35x; per-band rise px: R=1.33 G=1.31 B=1.26; normalised HF power rel. green: R=0.87 G=1.00 B=1.36; autocorr lag1-4 (G) = 0.9384/0.8749/0.8427/0.8141; per-site sd +/-1.21 px</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>1.33x oversampled, effective 13 cm (published 1.35x - REPRODUCED). Large per-site spread (+/-1.21 px) driven by one site's edge estimate; the median is nonetheless in exact agreement with the published value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1501 v=1.1463; z h=6.28 v=6.26; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=8.50), v phase 7 (15/15, z=9.12)</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.029% at DN0, 0.071% at DN255; G: 0.010% at DN0, 0.061% at DN255; B: 0.065% at DN0, 0.004% at DN255; band sd R/G/B = 52.4/47.9/38.8</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>mean R=112.4 G=110.5 B=90.9; G-R=-1.9 DN; B-G=-19.6 DN; GRVI mean=+0.0384 sd=0.0925; frac(GRVI&gt;.02)=0.3619 (published .2745)</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.986 r_RB=0.928 r_GB=0.908; B~aR+bG+c: R2 med=0.8631 min=0.8201, resid sd=15.38 DN, a=1.25 b=-0.28 c=-6.4; control fits G~(R,B) R2=0.9764, R~(G,B) R2=0.9787; normalised unexplained fraction B=0.2740 G=0.1288 R=0.1268; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.144</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.144). This is the UNCATALOGUED second 2017 acquisition, distinct from 2017_coe - and note its band statistics are nearly identical to 2017_coe's (index 2.106, means 117.2/113.9/85.2 vs 117.3/113.8/85.2), which is worth investigating as possible shared provenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.32 px -&gt; EFFECTIVE 13.2 cm (oversampling 1.32x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.32 G=1.31 B=1.28; normalised HF power rel. green: R=0.86 G=1.00 B=1.39; autocorr lag1-4 (G) = 0.9510/0.8926/0.8600/0.8318; per-site sd +/-0.39 px</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.32x oversampled, effective 13 cm on a 10.0 cm grid - in line with the other fine King years. Bands equally sharp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1544 v=1.1406; z h=6.46 v=4.92; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=8.52), v phase 7 (15/15, z=7.66)</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.009% at DN0, 0.096% at DN255; G: 0.005% at DN0, 0.109% at DN255; B: 0.218% at DN0, 0.004% at DN255; band sd R/G/B = 41.4/39.5/44.0</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>mean R=117.2 G=113.9 B=85.2; G-R=-3.3 DN; B-G=-28.7 DN; GRVI mean=-0.0024 sd=0.0487; frac(GRVI&gt;.02)=0.1958 (published .1877)</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>One point on the King red-brightening drift; mean GRVI has now crossed to negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.993 r_RB=0.930 r_GB=0.925; B~aR+bG+c: R2 med=0.8647 min=0.8442, resid sd=15.63 DN, a=1.25 b=-0.38 c=-3.7; control fits G~(R,B) R2=0.9881, R~(G,B) R2=0.9889; normalised unexplained fraction B=0.2714 G=0.1032 R=0.1012; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.655</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.655).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.28 px -&gt; EFFECTIVE 12.8 cm (oversampling 1.28x); published 1.35x; per-band rise px: R=1.28 G=1.27 B=1.23; normalised HF power rel. green: R=1.07 G=1.00 B=1.07; autocorr lag1-4 (G) = 0.9121/0.8072/0.7681/0.7316; per-site sd +/-0.06 px</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>1.28x oversampled, effective 13 cm (published 1.35x - REPRODUCED). The sharpest King acquisition. Bands equally sharp (max/min 1.021).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.1079 v=1.0925; z h=3.70 v=3.18; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=7.28), v phase 7 (15/15, z=6.63)</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.003% at DN0, 0.178% at DN255; G: 0.056% at DN0, 0.312% at DN255; B: 0.461% at DN0, 0.012% at DN255; band sd R/G/B = 49.8/49.1/46.5</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>mean R=124.8 G=120.8 B=92.8; G-R=-4.0 DN; B-G=-28.0 DN; GRVI mean=-0.0208 sd=0.0484; frac(GRVI&gt;.02)=0.0640 (published .1146)</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>The far end of the King drift. This is the file that reads .11 while 2019 NAIP over the same ground reads .89 - and the mechanism is visible here: red is 4.0 DN BRIGHTER than green, where in 2000 it was 14.4 DN darker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.994 r_RB=0.929 r_GB=0.929; B~aR+bG+c: R2 med=0.8652 min=0.8325, resid sd=15.53 DN, a=0.36 b=0.47 c=-9.5; control fits G~(R,B) R2=0.9892, R~(G,B) R2=0.9875; normalised unexplained fraction B=0.2578 G=0.1000 R=0.1084; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.475</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.475). Highest R-G correlation in the archive (r_RG=0.994) - red and green are nearly redundant with each other in the post-2012 King regime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.31 px -&gt; EFFECTIVE 13.2 cm (oversampling 1.31x); published 1.35x; per-band rise px: R=1.31 G=1.29 B=1.28; normalised HF power rel. green: R=0.91 G=1.00 B=1.16; autocorr lag1-4 (G) = 0.9335/0.8433/0.7906/0.7527; per-site sd +/-0.07 px</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>1.31x oversampled, effective 13 cm (published 1.35x - REPRODUCED). Bands equally sharp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2275 v=1.1008; z h=8.06 v=3.11; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=9.53), v phase 7 (15/15, z=7.06)</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.183% at DN255; G: 0.010% at DN0, 0.141% at DN255; B: 0.266% at DN0, 0.056% at DN255; band sd R/G/B = 48.1/46.4/46.0</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>mean R=135.1 G=129.1 B=99.8; G-R=-6.0 DN; B-G=-29.3 DN; GRVI mean=-0.0215 sd=0.0399; frac(GRVI&gt;.02)=0.0659 (published .1344)</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>Most negative G-R in the archive (-6.0 DN) and the largest B-G gap (-29.3). Red has now risen 34 DN above its 2000 value while green rose only 14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.991 r_RB=0.923 r_GB=0.918; B~aR+bG+c: R2 med=0.8545 min=0.8526, resid sd=16.10 DN, a=0.81 b=0.03 c=-3.2; control fits G~(R,B) R2=0.9842, R~(G,B) R2=0.9880; normalised unexplained fraction B=0.2709 G=0.1082 R=0.1052; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.538</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.538). Lowest raw B~aR+bG+c R2 in the archive (0.8545) with the largest residual (16.1 DN) - the opposite pole from 2000/2005.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 10.0 cm ground; band-1 rise=1.30 px -&gt; EFFECTIVE 13.0 cm (oversampling 1.30x); published 1.35x; per-band rise px: R=1.30 G=1.28 B=1.28; normalised HF power rel. green: R=0.88 G=1.00 B=1.01; autocorr lag1-4 (G) = 0.9230/0.8482/0.7968/0.7551; per-site sd +/-0.08 px</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>1.30x oversampled, effective 13 cm (published 1.35x - REPRODUCED). Bands equally sharp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2111 v=1.0707; z h=5.73 v=3.84; modal peak phase = 7 in both axes; per-axis scan: h phase 7 (14/15 band-site combos, z=9.42), v phase 7 (15/15, z=8.42)</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE. Vertical signature is the weakest in the King series (ratio 1.07) but the phase agreement is still 15/15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.004% at DN0, 0.141% at DN255; G: 0.002% at DN0, 0.130% at DN255; B: 0.046% at DN0, 0.326% at DN255; band sd R/G/B = 52.2/50.2/47.9</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>mean R=136.2 G=134.2 B=105.2; G-R=-2.0 DN; B-G=-29.0 DN; GRVI mean=-0.0036 sd=0.0427; frac(GRVI&gt;.02)=0.2065 (published .1541)</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>End of the King series: mean red 136.2 vs 100.9 in 2000 (+35%) against green's +16%. This pair of numbers is the whole .8027 -&gt; .1146 drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.986 r_RB=0.927 r_GB=0.907; B~aR+bG+c: R2 med=0.8607 min=0.8225, resid sd=15.23 DN, a=1.22 b=-0.25 c=-6.1; control fits G~(R,B) R2=0.9749, R~(G,B) R2=0.9789; normalised unexplained fraction B=0.2734 G=0.1303 R=0.1292; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.106</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.106). Band statistics almost identical to the uncatalogued 2017_king (index 2.144, means within 0.1 DN on all three bands) - the two nominally different 2017 acquisitions may share provenance; worth checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 5.0 cm ground; band-1 rise=1.52 px -&gt; EFFECTIVE 7.6 cm (oversampling 1.52x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.52 G=1.63 B=1.65; normalised HF power rel. green: R=0.87 G=1.00 B=1.26; autocorr lag1-4 (G) = 0.9858/0.9544/0.9198/0.8917; median over 5 sites, per-site sd +/-0.85 px - noisier than the King years, treat as indicative</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.52x oversampled, effective 7.6 cm on a 5.0 cm grid - the softest of the four CoE years. CAVEAT: per-site sd +/-0.85 px, so this is indicative rather than tightly determined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.3507 v=1.2711; z h=6.99 v=8.96; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=8.03), v phase 7 (15/15, z=11.82)</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag - the LARGEST boundary/within ratio in the archive (1.35 horizontal). Intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.002% at DN0, 0.049% at DN255; G: 0.000% at DN0, 0.080% at DN255; B: 0.113% at DN0, 0.002% at DN255; band sd R/G/B = 41.0/38.9/43.6</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (PREVIOUSLY UNMEASURED for the CoE years)</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>mean R=117.3 G=113.8 B=85.2; G-R=-3.5 DN; B-G=-28.6 DN; GRVI mean=-0.0032 sd=0.0452; frac(GRVI&gt;.02)=0.2036</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>NEW - first colour-cast measurement for a CoE year. Sits at the low-greenness end alongside 2017k/2019k, so the CoE series is NOT on a neutral balance either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.987 r_RB=0.933 r_GB=0.908; B~aR+bG+c: R2 med=0.8735 min=0.7706, resid sd=14.26 DN, a=1.09 b=-0.23 c=-5.8; control fits G~(R,B) R2=0.9737, R~(G,B) R2=0.9776; normalised unexplained fraction B=0.2721 G=0.1489 R=0.1435; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.862</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 1.862). THE LABELLED YEAR - its blue is genuinely independent, so the hand labels were drawn on true three-band imagery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 5.0 cm ground; band-1 rise=1.39 px -&gt; EFFECTIVE 7.0 cm (oversampling 1.39x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.39 G=1.39 B=1.34; normalised HF power rel. green: R=0.92 G=1.00 B=1.03; autocorr lag1-4 (G) = 0.9718/0.9090/0.8421/0.7902; median over 5 sites, per-site sd +/-0.41 px - noisier than the King years, treat as indicative</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>NEW, and the single most-wanted number in IMAGERY_FACTS: the LABELLED YEAR is 1.39x oversampled, effective 7.0 cm on a 5.0 cm grid. All three bands equally sharp (max/min 1.136), so the label year has no per-band defect. CAVEAT: per-site sd +/-0.41 px.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16) plus mod-32 period confirmation, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2187 v=1.2147; z h=7.64 v=9.25; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; mod-32 profile peaks at indices 7,15,23,31; per-axis scan: h phase 7 (15/15, z=10.42), v phase 7 (15/15, z=13.44)</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag, and this is the LABELLED YEAR: an intact JPEG 8x8 DCT block grid (mod-32 confirms period 8) sits in a file tagged lossless DEFLATE. The imagery the hand annotations were drawn on has an undisclosed lossy compression history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.002% at DN0, 0.105% at DN255; G: 0.000% at DN0, 0.057% at DN255; B: 0.058% at DN0, 0.028% at DN255; band sd R/G/B = 43.2/40.2/42.6</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (PREVIOUSLY UNMEASURED for the CoE years)</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>mean R=117.8 G=117.6 B=96.0; G-R=-0.1 DN; B-G=-21.7 DN; GRVI mean=+0.0070 sd=0.0549; frac(GRVI&gt;.02)=0.2919</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>NEW, and directly relevant to the IMAGERY_FACTS section 6 hypothesis. The labelled year sits at frac=.2919 - low, but ABOVE 2017k/2019k/2021k and well below 2022_coe (.7298) and 2024_coe (.6583) from the SAME sensor. Since a within-sensor comparison is the valid one, 2020 does read as a relatively low-greenness CoE acquisition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.983 r_RB=0.938 r_GB=0.921; B~aR+bG+c: R2 med=0.8826 min=0.8091, resid sd=13.68 DN, a=1.21 b=-0.13 c=-11.2; control fits G~(R,B) R2=0.9669, R~(G,B) R2=0.9747; normalised unexplained fraction B=0.2643 G=0.1510 R=0.1427; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.800</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 1.800).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 5.0 cm ground; band-1 rise=1.30 px -&gt; EFFECTIVE 6.5 cm (oversampling 1.30x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.30 G=1.39 B=1.38; normalised HF power rel. green: R=0.86 G=1.00 B=0.72; autocorr lag1-4 (G) = 0.9667/0.9026/0.8455/0.8119; median over 5 sites, per-site sd +/-1.17 px - noisier than the King years, treat as indicative</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.30x oversampled, effective 6.5 cm on a 5.0 cm grid - the sharpest CoE year. CAVEAT: largest per-site spread of the CoE group (+/-1.17 px); indicative only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.3572 v=1.3098; z h=7.35 v=8.36; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=7.98), v phase 7 (15/15, z=11.48)</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag - largest horizontal boundary ratio in the archive (1.357). Intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.008% at DN0, 0.000% at DN255; G: 0.000% at DN0, 0.196% at DN255; B: 0.042% at DN0, 0.008% at DN255; band sd R/G/B = 39.4/38.0/43.4</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (PREVIOUSLY UNMEASURED for the CoE years)</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>mean R=115.8 G=124.9 B=92.7; G-R=+9.1 DN; B-G=-32.1 DN; GRVI mean=+0.0461 sd=0.0573; frac(GRVI&gt;.02)=0.7298</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>NEW. The CoE series has its own large internal colour swing: .2036 (2017) -&gt; .2919 (2020) -&gt; .7298 (2022) -&gt; .6583 (2024), a 3.6x range within one sensor and 7 years. Largest B-G gap of any file (-32.1 DN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.995 r_RB=0.934 r_GB=0.927; B~aR+bG+c: R2 med=0.8741 min=0.8534, resid sd=14.17 DN, a=0.44 b=0.34 c=14.5; control fits G~(R,B) R2=0.9900, R~(G,B) R2=0.9893; normalised unexplained fraction B=0.2467 G=0.1031 R=0.1110; RELATIVE blue-redundancy index nB/mean(nG,nR)=2.305</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 2.305). Highest r_RG in the archive (0.995).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 5.0 cm ground; band-1 rise=1.35 px -&gt; EFFECTIVE 6.8 cm (oversampling 1.35x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.35 G=1.35 B=1.28; normalised HF power rel. green: R=0.99 G=1.00 B=1.07; autocorr lag1-4 (G) = 0.9641/0.9164/0.8585/0.8174; median over 5 sites, per-site sd +/-0.82 px - noisier than the King years, treat as indicative</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.35x oversampled, effective 6.8 cm on a 5.0 cm grid. Bands equally sharp. CAVEAT: per-site sd +/-0.82 px; indicative only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = DEFLATE (predictor 2); phase-7/mean-other ratio h=1.2972 v=1.2631; z h=8.79 v=6.99; modal peak phase = 7 in both axes, 15/15 site-band-axis combinations agree; per-axis scan: h phase 7 (15/15, z=10.49), v phase 7 (15/15, z=14.15)</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>CONTRADICTS the container tag: intact JPEG 8x8 DCT grid in a file tagged lossless DEFLATE. All four CoE years show the same strong signature (ratios 1.22-1.36), so this is a property of the CoE delivery chain, not one bad year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 256 distinct (DN 0-255), 0 empty bins inside range; B: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>Clean 8-bit, no comb: no post-quantisation stretch detectable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.011% at DN0, 0.000% at DN255; G: 0.000% at DN0, 0.000% at DN255; B: 0.018% at DN0, 0.001% at DN255; band sd R/G/B = 50.0/46.5/44.0</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping - the cleanest file in the archive (zero pixels at DN255 in R and G).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows (PREVIOUSLY UNMEASURED for the CoE years)</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>mean R=112.4 G=121.9 B=107.2; G-R=+9.5 DN; B-G=-14.8 DN; GRVI mean=+0.0794 sd=0.1169; frac(GRVI&gt;.02)=0.6583</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>NEW. Highest GRVI mean of the CoE years (+0.0794), essentially tied with 2000 King (+0.0784) - so a 2020-vs-2024 CoE comparison carries a colour-balance step of the same size as the one that makes 2000 the King outlier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd; plus NIR~aR+bG+cB+d (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.972 r_RB=0.927 r_GB=0.920; B~aR+bG+c: R2 med=0.8925 min=0.8365, resid sd=10.51 DN, a=0.51 b=0.10 c=38.7; control fits G~(R,B) R2=0.9495, R~(G,B) R2=0.9484; normalised unexplained fraction B=0.2520 G=0.1935 R=0.1812; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.345; NIR~aR+bG+cB+d R2=0.743 (resid 38.1 DN)</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>Blue: intermediate, not flagged as synthetic. NIR is unambiguously REAL - only 74.3% of its variance is predictable from RGB, with a 38.1 DN residual, the largest independent signal of any band in the archive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation, and sub-pixel band registration</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 15.2 cm ground; band-1 rise=2.32 px -&gt; EFFECTIVE 35.4 cm (oversampling 2.32x); PREVIOUSLY UNMEASURED; per-band rise px: R=2.32 G=2.33 B=3.22 N=3.25; normalised HF power rel. green: R=0.85 G=1.00 B=0.59 N=0.45; autocorr lag1-4 (G) = 0.9815/0.9452/0.9091/0.8755; blue-vs-green registration offset 0.224 px; per-site sd +/-0.37 px</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>NEW and consequential - this is the project's most-cited year. 2.32x oversampled: effective 35 cm, NOT the 15.2 cm the grid advertises, and 1.7x coarser than 2021_snoh on the byte-identical grid. Separately, the BLUE band is degraded on its own (rise 3.22 vs 2.32/2.33; 0.53-0.59x green's normalised HF; blue-vs-green misregistration 0.224 px, 20-200x any other file), and NIR is joint-softest (3.25 px, 0.45x green's HF) - and NIR is the band the project's NDVI reference is built from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites; plus mod-32 period scan</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = LZW (predictor 2); phase-7/mean-other ratio h=0.9951 v=1.1811; z h=-0.55 v=1.26; modal peak phase = inconsistent across sites/bands; mod-32 profile peaks scattered (top indices 26,8,25,2,6); per-axis scan: h modal phase 0 (16/20 combos, mean z=2.30), v modal phase 5 (20/20 combos, mean z=2.19)</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>No JPEG 8x8 DCT block grid - tag and evidence agree that no DCT stage is visible. Two caveats: a wavelet-based lossy history leaves no 8x8 grid and is NOT excluded by this test; and the v-axis does show a borderline consistent phase-5 period-8 (20/20 combos but only z=2.19), the weak version of what 2021_snoh shows strongly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>R: 256 distinct (DN 0-255), 0 empty bins inside range; G: 245 distinct (DN 11-255), 0 empty bins inside range; B: 223 distinct (DN 31-255), 2 empty bins inside range at [33, 35]; N: 256 distinct (DN 0-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>Negligible comb (2 isolated empty DNs in blue). But note blue's used range STARTS at DN 31 - blue never goes darker than 31 anywhere in 5 windows, a floor consistent with an additive haze/offset term, and consistent with its fitted intercept c=+38.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.000% at DN255; G: 0.000% at DN0, 0.000% at DN255; B: 0.000% at DN0, 0.000% at DN255; N: 0.000% at DN0, 0.000% at DN255; band sd R/G/B = 50.4/43.1/35.0</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>Zero clipping in all four bands - no contrast stretch was pushed to the rails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>mean R=90.0 G=99.7 B=98.3; G-R=+9.7 DN; B-G=-1.4 DN; GRVI mean=+0.1075 sd=0.1112; frac(GRVI&gt;.02)=0.6368 (published .6928)</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>Cross-sensor reference point. Its blue sits only 1.4 DN below green - close to 2000 King's anomalous +2.1 - which shows that a near-zero B-G is achievable with a real (if degraded) blue band, so B-G alone is corroborating rather than diagnostic evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd; plus NIR~aR+bG+cB+d (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.971 r_RB=0.952 r_GB=0.936; B~aR+bG+c: R2 med=0.9096 min=0.8980, resid sd=8.49 DN, a=0.56 b=0.24 c=7.9; control fits G~(R,B) R2=0.9452, R~(G,B) R2=0.9558; normalised unexplained fraction B=0.2298 G=0.1850 R=0.1734; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.283; NIR~aR+bG+cB+d R2=0.730 (resid 24.5 DN)</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>Blue: intermediate, not flagged. NIR unambiguously REAL (R2 0.730, resid 24.5 DN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 15.2 cm ground; band-1 rise=1.35 px -&gt; EFFECTIVE 20.6 cm (oversampling 1.35x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.35 G=1.34 B=1.32 N=2.30; normalised HF power rel. green: R=0.95 G=1.00 B=1.79 N=0.27; autocorr lag1-4 (G) = 0.9669/0.8960/0.8308/0.7862; per-site sd +/-0.35 px</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.35x oversampled, effective 20.6 cm - properly sampled, and 1.7x sharper than 2016_snoh on the byte-identical grid. But its NIR is the worst per-band mismatch of any NIR file: rise 2.30 px vs 1.32 for blue (1.75x blurrier) and only 0.27x green's normalised HF power. The NDVI reference for 2021 is built on a ~35 cm effective band inside a 20.6 cm effective image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites; plus mod-32 period scan</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = LZW (predictor 2); phase-7/mean-other ratio h=0.9897 v=0.9783; z h=-0.63 v=-0.36; modal peak phase = inconsistent; per-axis scan: h modal phase 3 (9/20 combos, mean z=2.18), v modal phase 5 (20/20 combos, mean z=8.03)</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>No JPEG 8x8 DCT block grid: no phase-7 excess, mod-32 peaks scattered. BUT a real non-DCT period-8 modulation IS present - v-axis phase 5, 20/20 band-site combos, z=8.03. Phase-locked but NOT at a block boundary, so not aligned JPEG; origin undetermined (scan-line or resampling periodicity). Do not read this file as artefact-free just because the DCT test is negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins inside the used range</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>R: 251 distinct (DN 3-253), 0 empty bins inside range; G: 237 distinct (DN 17-254), 1 empty bin inside range at [18]; B: 254 distinct (DN 1-254), 0 empty bins inside range; N: 233 distinct (DN 23-255), 0 empty bins inside range</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>Negligible comb (1 isolated empty DN). The reduced distinct counts are range limits, not missing interior levels - unlike NAIP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.000% at DN255; G: 0.000% at DN0, 0.000% at DN255; B: 0.000% at DN0, 0.000% at DN255; N: 0.000% at DN0, 0.000% at DN255; band sd R/G/B = 39.0/32.9/33.1</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>Zero clipping in all four bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>mean R=87.1 G=94.2 B=81.8; G-R=+7.1 DN; B-G=-12.4 DN; GRVI mean=+0.0644 sd=0.0746; frac(GRVI&gt;.02)=0.6041 (published .6157)</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>Cross-sensor reference point. Snohomish 2016 vs 2021 differ by only .03 in frac, so the Snohomish pair is far better colour-matched to each other than the King pairs are - the resolution difference (2.32x vs 1.35x), not colour, is what separates them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd; plus NIR~aR+bG+cB+d (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.979 r_RB=0.953 r_GB=0.940; B~aR+bG+c: R2 med=0.9117 min=0.8307, resid sd=8.84 DN, a=0.44 b=0.23 c=27.2; control fits G~(R,B) R2=0.9595, R~(G,B) R2=0.9650; normalised unexplained fraction B=0.2115 G=0.1560 R=0.1616; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.332; NIR~aR+bG+cB+d R2=0.734 (resid 30.5 DN)</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>Blue: intermediate, not flagged. NIR unambiguously REAL (R2 0.734, resid 30.5 DN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 60.0 cm ground; band-1 rise=1.58 px -&gt; EFFECTIVE 95.1 cm (oversampling 1.58x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.58 G=1.39 B=1.37 N=1.67; normalised HF power rel. green: R=0.88 G=1.00 B=1.25 N=0.61; autocorr lag1-4 (G) = 0.9565/0.8724/0.7910/0.7183; per-site sd +/-0.38 px</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.58x oversampled, effective 95 cm on a 60 cm grid - the coarsest effective resolution in the archive. NIR is again the softest band (1.67 px, 0.61x green's normalised HF), which matters because this is one of the two NAIP years used as an NDVI reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites; plus mod-32 period scan</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = LZW (predictor None - the only files in the archive with no predictor); phase-7/mean-other ratio h=0.9995 v=1.0238; z h=-0.04 v=1.23; modal peak phase = inconsistent; mod-32 peaks scattered (top indices 13,0,14,10,29); per-axis scan: h modal phase 5 (13/20 combos, z=1.90), v modal phase 7 (5/20 combos, z=2.07)</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>No JPEG 8x8 DCT block grid and no consistent alternative phase - the cleanest periodicity result in the archive. Tag and evidence agree that no DCT stage is visible, but a wavelet-based lossy history leaves no 8x8 grid and is NOT excluded by this test. Note T4 shows this file HAS been radiometrically altered, just not by a DCT codec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins strictly inside the used range (comb detection)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>R: 241 distinct (DN 4-254), 10 empty bins inside range at [5, 7, 244, 245, 246, 247, 249, 251, 252, 253]; G: 224 distinct (DN 24-248), 1 empty bin at [27]; B: 230 distinct (DN 24-255), 2 empty bins at [28, 254]; N: 250 distinct (DN 0-255), 6 empty bins at [243, 245, 246, 249, 253, 254]</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>COMB PRESENT - the clearest in the archive. Red has 8 of the 10 DN values in the span 244-253 unreachable, and NIR has 6 unreachable near the top. That is the signature of a per-band gain/offset stretch applied AFTER 8-bit quantisation. All 16 King/CoE files show zero interior empty bins by comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.000% at DN255; G: 0.000% at DN0, 0.000% at DN255; B: 0.000% at DN0, 0.000% at DN255; N: 0.026% at DN0, 0.000% at DN255; band sd R/G/B = 43.7/39.0/34.3</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping. Note NIR does reach DN0 (0.026%) - relevant because band 4 is mislabelled as ALPHA, so those pixels render fully transparent in any RGBA-honouring reader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>mean R=72.0 G=90.2 B=88.5; G-R=+18.2 DN; B-G=-1.7 DN; GRVI mean=+0.1562 sd=0.0981; frac(GRVI&gt;.02)=0.9036 (published .8919)</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>The other half of the decisive 2019 pair. G-R = +18.2 DN here versus -4.0 DN in 2019 King, over the same ground in the same year - a 22 DN swing in the red-green relationship that no vegetation process can produce. Mean red is 72.0 here versus 124.8 in 2019 King: red gain is the entire explanation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>T1 synthesised-band detector: Pearson band correlations; OLS B~aR+bG+c; conditional-std functional dependence normalised by band sd; plus NIR~aR+bG+cB+d (5 ground-matched 200 m windows)</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>r_RG=0.973 r_RB=0.897 r_GB=0.936; B~aR+bG+c: R2 med=0.8769 min=0.8012, resid sd=13.96 DN, a=0.23 b=0.55 c=29.2; control fits G~(R,B) R2=0.9696, R~(G,B) R2=0.9560; normalised unexplained fraction B=0.2870 G=0.1537 R=0.1541; RELATIVE blue-redundancy index nB/mean(nG,nR)=1.865; NIR~aR+bG+cB+d R2=0.780 (resid 27.0 DN)</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>REAL measured blue band (index 1.865). NIR unambiguously REAL (R2 0.780, resid 27.0 DN). Lowest r_RB in the archive (0.897).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>T2 effective resolution / oversampling: q138b.py edge-response copied verbatim, band 1, 5 native 512x512 windows; plus per-band rise, contrast-normalised HF power, lag-1..4 autocorrelation</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>grid GSD 60.0 cm ground; band-1 rise=1.38 px -&gt; EFFECTIVE 83.1 cm (oversampling 1.38x); PREVIOUSLY UNMEASURED; per-band rise px: R=1.38 G=1.36 B=1.32 N=1.39; normalised HF power rel. green: R=0.98 G=1.00 B=1.51 N=0.84; autocorr lag1-4 (G) = 0.9570/0.8723/0.7873/0.7085; per-site sd +/-0.02 px (tightest in the archive)</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>NEW: 1.38x oversampled, effective 83 cm on a 60 cm grid - 12 cm sharper than 2019 NAIP (95 cm) despite identical grid and footprint, so the two NAIP years are not resolution-matched either. NIR is mildly the softest band (1.39 px, 0.84x green's HF) - the best NIR of the four NIR-bearing files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>T3 compression forensics: phase-mod-8 profile (origin snapped to an absolute multiple of 16), boundary ratio and z, both axes, all bands, 5 sites; plus mod-32 period scan</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>GDAL COMPRESSION tag = LZW (predictor None); phase-7/mean-other ratio h=1.0070 v=0.9946; z h=0.53 v=-0.53; modal peak phase = inconsistent; per-axis scan: h modal phase 0 (7/20 combos, z=2.03), v modal phase 0 (6/20 combos, z=2.23)</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>No JPEG 8x8 DCT block grid and no consistent alternative phase. Tag and evidence agree that no DCT stage is visible, but a wavelet-based lossy history leaves no 8x8 grid and is NOT excluded by this test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>T4 bit-depth / quantisation: union histogram over 5 windows per band; distinct values out of 256 and empty bins strictly inside the used range (comb detection)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>R: 249 distinct (DN 0-255), 7 empty bins inside range at [1, 2, 3, 4, 5, 6, 9]; G: 226 distinct (DN 28-255), 2 empty bins at [29, 37]; B: 243 distinct (DN 12-255), 1 empty bin at [13]; N: 240 distinct (DN 10-255), 6 empty bins at [11, 12, 13, 15, 16, 17]</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>COMB PRESENT: red has 7 unreachable DNs in the run 1-9 and NIR has 6 in the run 11-17. Same defect as 2019 NAIP but mirrored to the dark end of the range, so the two NAIP years received DIFFERENT per-band stretches - another undocumented year-to-year processing difference within one source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>T5 saturation / clipping: fraction of valid pixels at DN 0 and DN 255 per band, 5 ground-matched windows</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>R: 0.000% at DN0, 0.023% at DN255; G: 0.000% at DN0, 0.039% at DN255; B: 0.000% at DN0, 0.050% at DN255; N: 0.000% at DN0, 0.207% at DN255; band sd R/G/B = 58.1/47.6/42.6</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>No meaningful clipping, though NIR clips 0.21% at DN255 - the highest NIR clipping of the four NIR files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>T6 greenness drift per band: per-band mean/sd and GRVI=(G-R)/(G+R) with frac&gt;0.02, same 5 fixed ground windows</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>mean R=133.6 G=139.2 B=127.5; G-R=+5.6 DN; B-G=-11.7 DN; GRVI mean=+0.0808 sd=0.0565; frac(GRVI&gt;.02)=0.6436; published value for this file's counterpart is .7822 (recorded as '2022n')</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>Cross-sensor reference point, but note the NAIP pair is itself not colour-matched: G-R falls from +18.2 DN (2019n) to +5.6 DN (this file), and mean red rises from 72.0 to 133.6 - an 86% red gain between two acquisitions from the same programme. See the separate finding on this file's year label being UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ALL 20 (band labelling audit)</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>GDAL colorinterp per band, read from the file headers of all 20 rasters</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>All four RGBI files (2016_snoh, 2021_snoh, 2019_naip, 2023_naip) declare band 4 colorinterp = 6 = ALPHA, not NIR or undefined. Band-4 data is continuous and vegetation-bright (mean 103.3-170.3 DN, 228-256 distinct values, NIR~f(R,G,B) R2 only 0.730-0.780) and is unambiguously NIR. The 16 RGB files declare 3/4/5 = red/green/blue as expected.</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>MISLABELLED in all four NIR-bearing files. rasterio band indexing is unaffected, but any RGBA-honouring path (PIL, matplotlib, gdal_translate to PNG, most web tile chains) will treat NIR as opacity - making low-NIR pixels (water, shadow, pavement) transparent or premultiplying RGB by NIR. 2019_naip band 4 contains DN 0, which such a reader renders fully transparent.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D122"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Grid GSD (cm)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Oversampling x</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Effective (cm)</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>median of 5 sites; CoE sd +/-0.41-1.17 px - indicative</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>*** THE LABELLED ANCHOR YEAR *** closes IMAGERY_FACTS' 'single biggest gap'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>*** MAJOR: the most-cited year in the project resolves at 35 cm, not the 15 cm its grid advertises. Blue band ALSO misregistered 0.224 px off green - 20-200x worse than any other file ***</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>1.7x sharper than 2016 on a BYTE-IDENTICAL grid (43893x31965, EPSG:2285). Any 2016-vs-2021 change detection sees a resolution step, not only ground change</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>NAIP</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>95.1</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>NAIP</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>was mislabelled 2022n until 2026-08-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>King County</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>33.7</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>UNCATALOGUED ORPHAN; notably softer than 2007/2009 on the identical grid (1.28/1.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>King County</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>UNCATALOGUED ORPHAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>King County</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>40.1</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>2.72 (RED) / 1.75 (green) / 1.70 (blue)</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>109 red / 70 green / 68 blue</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>REVISED</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>*** the published 2.8x / 110.8 cm is a RED-BAND-ONLY figure. Effective resolution is BAND-DEPENDENT and red - the band every greenness/NDVI index depends on - is the most degraded ***</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Document / endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Verbatim quote</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Supporting detail</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Flight window</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>ANCHOR</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE DOCUMENTED in a signed city contract</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Edmonds-Snohomish County ILA 2021 (Laserfiche id=1462454), Work Order p.14</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>"Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects and receipt of imagery by County, County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest"</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Appendix A p.18: 'EagleView Regional Aerial Imagery / 2020 Imagery Program Rates ... 3 Inch AccuPlus $300'; GIS Support Services: 'Imagery ... 22 [sq mi] ... $6,600.00'</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Flight window from county side: 2020-04-13 to 2020-07-13 (SCOPI: 'nadir images captured by Pictometry International')</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>CHAIN COMPLETE but the final link is still inferential - no EDMONDS document states a date. Best-supported year in the set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>named in the same contract clause</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>same ILA</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>same clause</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr"/>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>County window 2022-04-06 to 07-11</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>named in the same contract clause</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>same ILA</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>same clause</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>County window 2024-03-31 to 05-31</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>NO contract, NO budget line, NO flight date found</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Council minutes 2023-07-25 p.15 (weblink.edmondswa.gov/WebLink/0/edoc/1654952/)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>"In 2017 flyovers and imagery was done by the consultant who did the public engagement, PlanIt Geo, for Pierce, Snohomish and King Counties as part of a stormwater modeling project."</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>WEAK: a verbal answer in minutes; conflates collector with analysis consultant; PlanIt Geo is an analytics firm, not an imagery acquirer</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>Best narrowing is King County per-frame evidence: 2017-05-04 to 05-10, source attribution unproven</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Inferred window elsewhere is 2017-02-17 to 10-30 (8.5 months, leaf-off to leaf-on) - a real phenology hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2015 (CoE service)</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>participation CONFIRMED, flight date CONTESTED</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>consortium agreement signed 2015-06-23, $3,696.21</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>THREE candidate dates at three resolutions: Apr 8/9/17 GeoTerra 2.7 in (what Edmonds signed and paid for); Feb 15-Mar 8 King Co Pictometry; Aug 7 4.8 in per the 2019 Urban Forest Management Plan</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>UNRESOLVED. Likely explanation: canopy-assessment imagery is NOT the same dataset as the city's basemap orthophoto. Resolve before any 2015 tier decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Edmonds_Marsh_2018</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>FLIGHT TIMESTAMP CONFIRMED from the service itself</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>maps.edmondswa.gov/.../Edmonds_Marsh_2018/ImageServer/info/keyProperties</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>"acquisitionStartDate":"2018-08-01T16:22:13+00:00", "acquisitionEndDate":"2018-08-01T16:52:13+00:00"</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>4-band; a 30-minute single sortie</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>2018-08-01 16:22-16:52 UTC</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>The ONLY Edmonds layer with a machine-readable acquisition time. Consistent with a drone flight, not an aircraft survey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WHY THE METADATA IS EMPTY</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>STRUCTURAL - not an oversight to chase</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>2020_Aerial_Cached keyProperties (verified in full)</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>BAND_COUNT:4, IMAGE__FORMAT:'MrSID/MG4', IMAGE__INPUT_FORMAT:'GeoTIFF', IMAGE__MODIFICATIONS:'COMPRESSED EMBEDDED MASKED MOSAICKED' - and NO acquisition-date field at all</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>But Marsh 2018 DOES populate acquisitionStartDate - so the schema carries flight dates when the source retains them</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>Edmonds' 2020/2022 layers lost theirs when county GeoTIFF tiles were mosaicked and MrSID-compressed into a single 665 GB-input image</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>CLOSES the metadata route for 2020 definitively. The paper trail was the only way, and it worked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>*** 2026 NIR LIDAR INCOMING ***</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>FORWARD</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>purpose-built canopy dataset arriving within the year</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>2026-27 Urban Tree Canopy ILA</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>"Collection will occur during leaf on conditions in mid-June to July 2026"; NIR LiDAR at &gt;8 pulses/m2; delivery includes "a flight index ... [containing] flight line ID, acquisition date, start time and end time for each flight line"</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Edmonds share $3,300 for 8.92 sq mi</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>mid-June to July 2026, LEAF-ON</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>More than 2x the 2016 lidar density (4-5 pts/m2) and ~30x the 2005 (0.25). Leaf-on, NIR, and carries the per-flight-line dates this whole exercise has been trying to recover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BEST NEXT STEP</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>ACTION</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>one records request pins THREE years</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Records request to Snohomish County DoIT (Viggo Forde, Director) for the EagleView acquisition metadata - flight logs or photo-center index with per-frame dates - for the 2020 regional acquisition project covering Edmonds, citing City of Edmonds Contract Routing Form No. 20210127. Pins 2020, 2022 AND 2024.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tier / value</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cost / dependency</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Why it matters / caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Solar geometry from shadows</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Tier 1 - highest value</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>local, files already held</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>A nadir ortho preserves shadows. Shadow AZIMUTH -&gt; solar azimuth (+180); height/shadow LENGTH -&gt; solar elevation. Two equations, two unknowns (date, time) at 47.811N -122.377W. Heights from lidar_snoh_chm.tif, or flat-roofed commercial buildings for crisp tips at 3-inch GSD. pvlib pip-installs locally.</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>*** RUN IT PER SEAMLINE PATCH, NOT PER CITY *** - a county mosaic over 22 sq mi is stitched from multiple flight lines, plausibly multiple days. This also answers a question nobody has asked: IS 2020_coe_rgb.tif EVEN A SINGLE-DATE IMAGE? If not, 'the 2020 acquisition date' is the wrong question and that matters more for the labels than the date does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Weather elimination</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Tier 1 - cheapest, run FIRST</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>free ASOS/METAR archive</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Photogrammetric survey needs clear skies, low haze, sun above ~30 deg. Pull hourly ASOS for KPAE (Paine Field, ~10 mi N) and KBFI across 2020-04-13 to 07-13 (Iowa State archive, free).</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Puget Sound spring weather will eliminate most of the 92 candidate days outright. One afternoon. Converts the window to a shortlist that method 1 picks from, and independently sanity-checks whatever method 1 returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Tide state</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Tier 1</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>free NOAA CO-OPS API</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Puget Sound tides swing 3-4 m and Edmonds has a long tidal beach. Extract the waterline, convert to elevation against the lidar bare-earth DEM, match against NOAA CO-OPS verified 6-minute water levels (Seattle station 9447130 with an Edmonds offset).</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Each candidate date admits only ~2 times matching a given tide height. Cross-check against method 1's time - agreement is strong confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>AIS vessel matching</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Tier 1 - precision play</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>free marinecadastre.gov archive</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>The Edmonds-Kingston ferry is unmistakable at 3-inch GSD and runs continuously. NOAA/BOEM publish archived 2020 AIS position reports at ~1-minute resolution. Find a MOVING vessel (wake gives it away), measure position and heading, search the archive for a match.</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>The only method that could give the exact MINUTE. Moored marina boats are useless; a ferry mid-crossing is decisive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Construction-stage bracketing</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Laserfiche permit repository</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Identify 5-10 large construction sites visible in the 2020 mosaic, pull their DATED inspection records from PermitTrax/TRAKiT in the same repository. 'Foundation passed 2020-05-12 / framing 2020-06-20' brackets the visible stage.</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Several sites intersect to a couple of weeks. Independent of every physical method. Name searches {LF:Name="*&lt;address&gt;*"} work; full-text is unreliable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Other cities' copies of the SAME flight</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Tier 3 - 5-minute check</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>public ArcGIS endpoints</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>The 2020 EagleView project covered ALL Snohomish municipalities - costs distributed across them. Everett, Lynnwood, Mountlake Terrace, Mukilteo, Marysville each hold the same flight. Enumerate their ArcGIS REST endpoints and check keyProperties for acquisitionStartDate.</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Some will NOT have destroyed the metadata the way Edmonds did by mosaicking to MrSID - the field survived intact on Edmonds' own Marsh 2018 layer. ONE CLEAN NEIGHBOUR DATES THE FLIGHT FOR FREE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>County mosaic footprint layers</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Tier 3</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish ArcGIS</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>This is exactly what cracked King County: ORTHO_IMAGE*_AREA_* footprint features carry per-frame ShotDate. Snohomish almost certainly exposes an analogous footprint layer behind SCOPI even though the HTML page prints only a prose window.</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Enumerate their REST tree properly (two hostnames 404'd but the responding Geocortex endpoint proves a working server exists) and query the footprint over Edmonds' extent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>CONNECTExplorer - ALREADY OWNED</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Tier 3 - possibly FASTEST of all</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>internal ask, no records request</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 ILA grants Edmonds 'up to ten (10) EagleView CONNECTExplorer accounts'. That viewer displays PER-IMAGE CAPTURE DATES natively.</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Not a records request - an internal ask to Brian Tuley for a login, or a screenshot from someone who has one. It was sitting in the contract the whole time and could end the exercise today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>REFRAME: phenological state, not calendar date</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>worth taking seriously</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Sentinel-2, free</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>The date is a PROXY; what affects a canopy model is PHENOLOGICAL STATE. Place 2020 on a phenology axis empirically: compute a greenness separation over fixed deciduous vs conifer stands and compare against a Sentinel-2 time series over the same polygons for 2020 (5-day revisit, exact dates). The Sentinel-2 date whose separation best matches the aerial IS the date.</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>*** CORRECTION: the agent proposed using NDVI from the CoE service because it reports 4 bands. MEASURED FALSE - band 4 on 2020 and 2022 is constant 255 = RGBA ALPHA, not NIR. The anchor has NO NDVI. The idea survives on visible-band greenness, but weaker. *** Does double duty: a dating method AND a direct measure of whether the anchor caught deciduous stands leaf-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>CAUTION ON ALL OF THEM</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>read before starting</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Methods 1, 3 and 4 date THE FRAME YOU MEASURED, not the mosaic.</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Establish whether the Edmonds AOI is SINGLE-DATE or MULTI-DATE first - it changes what 'the 2020 acquisition date' even means for the labels.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -25,6 +25,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effective_Resolution" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance_Chain" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dating_Methods" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Independence" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retractions" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method_Provenance" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MASTER'!$A$1:$P$221</definedName>
@@ -44,6 +49,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Effective_Resolution'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Provenance_Chain'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Dating_Methods'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Reference_Independence'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Retractions'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Method_Provenance'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Contradictions'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Licensing_Risk'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +86,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B2D26"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,12 +106,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11716,6 +11734,285 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Reference product</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>UPSTREAM VENDOR</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Status in this project</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2021_hires_lc.tif (v2 'Refined')</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM / NV5</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia AI proprietary feature recognition on '30cm or better aerial imagery', PLUS a stereo-derived DSM 'used to determine vegetation heights'. Refined by NV5 with ancillary data into the 20-class C-CAP scheme.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>ECOPIA AI</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>IN USE - scores 2019, 2021k, 2022, 2023, 2024</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Lineage XML: 'Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI ... using a proprietary feature recognition technology'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2016_hires_lc_snohfull.tif</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>GEOBIA objects + Random Forest on 1 m NAIP, photo-interpreted training data, and NO HEIGHT DATA AT ALL.</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM (in-house)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>IN USE - scores 2000, 2002, 2013, 2015, 2016, 2017</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Different METHOD, different VENDOR, and no height input - not merely a different class scheme</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Statewide Ecopia Land Cover 2021-2022 (1 m)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>WA WaTech / WAGeoservices</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia AI extraction from Hexagon source imagery.</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>ECOPIA AI</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>*** WAS PLANNED AS THE 'THIRD INDEPENDENT REFERENCE' - IT IS NOT INDEPENDENT ***</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Shares its extraction VENDOR and ALGORITHM with the C-CAP v2 reference it was meant to be independent of</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>wa_2021_ccap_v2_hires_canopy.tif ('Initial' family)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia Tech Corporation proprietary feature recognition; 'a digital surface model (DSM) derived from the stereo imagery was used to determine vegetation heights'.</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>ECOPIA AI</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>WORKPLAN 1.3 proposed it as the full-coverage 2021 fix</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>ALSO Ecopia. Note: Initial != an earlier version of Refined. Initial = 3 AI-extracted feature layers (Canopy/Impervious/Water); Refined = those layers expanded by NV5 into the 20-class land cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>King County TreeCanopy2021 / Landcover2019Ecopia</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>King County GIS</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Built using Ecopia Impervious and Tree Canopy data.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>ECOPIA AI</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE - King-County-only extent, does not reach Edmonds</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Would also not have been independent had the extent worked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>NDVI + CHM reference (project-built)</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>this project</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>NDVI from the acquisition's own NIR band, thresholded, intersected with the 3DEP-derived CHM.</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>NONE - built in-house from the imagery itself</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>IN USE for NIR years</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>GENUINELY independent of Ecopia - but see the caveat: it is built on the NIR band, which pixel forensics shows is the SOFTEST band in all four NIR acquisitions (1.18-1.75x blurrier than the sharpest RGB band, varying by year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>*** THE CONSEQUENCE ***</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>THREE of the products this project treats, or planned to treat, as independent canopy references trace to ONE VENDOR AND ONE ALGORITHM (Ecopia AI). Agreement between them is NOT corroboration - it is the same instrument measured twice. The Foody-2022 latent-class work explicitly REQUIRES independent instruments; feeding it two Ecopia products would violate its central assumption and produce falsely tight agreement. The only genuinely independent pair currently available is {2016 C-CAP (NOAA GEOBIA+RF, no height)} vs {the project's own NDVI+CHM}. Verify this before any three-instrument analysis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -29871,6 +30168,962 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Claim that was confidently held</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Corrected</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Where it lived</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>What actually turned out to be true</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>The lesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1936 is an empty shell</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_FACTS / CHATLOG</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nine probe windows ALL missed the data. The content band starts 74.8% down the file; a full-extent read shows real photography over 24.4% of the study area.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Sampling that is not exhaustive can agree nine times and still be wrong. Probe placement is a hypothesis, not a control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>gsd_cm was correct in the catalog</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>phase4seg/config.py</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>gsd_cm was CRS-units x 100. EPSG:2285 is US SURVEY FEET (Snohomish overstated 3.24x); EPSG:3857 inflates 1/cos(47.8)=1.49x.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>A config value is a claim, not evidence. Units are the most common silent defect in this project - it has now happened THREE times (catalog, the CoE service grid, and the '3ft' Ecopia service that is actually 1 m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 pair isolates the sensor effect</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>WORKPLAN 2</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Resolution -&gt; tier -&gt; tiling params are entangled by design, so sensor and tiling regime cannot be separated in that pair.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>WITHDRAWN and must not be resurrected. The 2026-08-22 county inventory does NOT revive it - no same-tier same-year pair exists after true-GSD correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>King County's export plateaus at ~20 cm</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>this session</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>A controlled test (312 m box, 4096 px vs 1024 px upsampled to the same grid) gives 2.16x the HF energy for the native request; the cache reaches LOD 21 ~ 5.0 cm ground.</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>The laplacian-falloff proxy was measuring JPEG smoothing, not a resolution ceiling. A proxy metric needs its own validation before it is trusted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Class 4 IS 'Developed Impervious under Tree Canopy'</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_FACTS 9.3</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>PRESENCE is measured (480,208 px = 2.40% of valid, decimated read). MEANING is INFERRED - no RAT for the held clip has been read by anyone.</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Corrected in the authoritative facts document after cross-session review. Writing an inference as a measurement is the same error class as the defect it describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>The class-4 fix moves both precision AND recall</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>cross-session</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Precision rises. RECALL'S DIRECTION IS NOT PREDICTED - the denominator grows ~2.4 pp while the numerator grows only by class-4 pixels the model already calls canopy, so recall may FALL.</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Both outcomes are consistent with the fix being correct. State direction AND magnitude before measuring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>The 2013 re-score will move the number materially</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>loop prompt</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>It moved 0.0004 (off-recipe .7395 vs citywide .7399).</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>The long-quoted .7422 was UNDER-EVIDENCED (live=0, fallback threshold), not INACCURATE. Those are different failures. A prediction stated confidently and falsified is worth more than one never written down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>B ~ aR+bG+c with high R2 detects a synthesised band</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>this session's own spec</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>On the KNOWN-SYNTHETIC control (2000) it returns R2=0.9545 - LOWER than 2005 (.9766) and 2002 (.9628), which have real blue. The specified detector would have cleared the one file known to be fake.</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>A detector must be validated against a positive control BEFORE it is applied. The working form is relative: normalise each band's unexplained variance given the other two, then compare blue's to red's and green's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2000 has 'a false blue' (i.e. RGB with one synthesised channel)</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>this session</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Understated. The Kodak DSC460CIR received NO blue light at all, and ALL THREE filter elements pass NIR: blue = NIR only, green = green+NIR, red = red+NIR. It is a colour-infrared sensor.</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>The first framing was directionally right and materially wrong. 2000 cannot be treated as an RGB acquisition at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish 2016 and 2021 are comparable (identical grid)</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>implicit</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Byte-identical grid geometry, but effective resolution differs 1.7x: 2016 = 2.32x oversampled / 35.4 cm; 2021 = 1.35x / 20.6 cm.</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Identical grid does NOT imply identical resolution. Any 2016-vs-2021 change detection sees a resolution step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>The statewide Ecopia product is a third INDEPENDENT reference</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>CHATLOG / this session</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>It shares its extraction vendor AND algorithm (Ecopia AI) with the C-CAP v2 reference it was meant to be independent of.</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>See the Reference_Independence sheet. Agreement between two Ecopia products is not corroboration.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Headline measurement</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Scope / sample</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Validation or control</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Limits, and what would overturn it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Effective resolution (all 20 files)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Edge-response rise time, esf()/rise_px() COPIED VERBATIM from Scripts/litwatch_scratch/q138b.py - the script that produced the IMAGERY_FACTS 2.2 table</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>5 fixed land sites, each a 200 m x 200 m ground box, plus a native 512x512 box with origin snapped to an absolute multiple of 16 so in-window phase == absolute phase. Sites (WGS84): S1_forest_nw 47.8225,-122.3580 (86% forest); S2_parking 47.8060,-122.3270 (94% developed); S3_residential 47.8100,-122.3700; S4_forest_s 47.7855,-122.3545; S5_suburb_ne 47.8250,-122.3400. All confirmed LAND against C-CAP 2016. All inside the intersection of all 20 footprints.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>REPRODUCED the 10 published King oversampling values at Pearson r=0.997 (2000 2.68 vs 2.8; 2005 3.92 vs 4.0; 2007 1.28 vs 1.3).</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>5 sites is not the city. CoE per-site sd is +/-0.41-1.17 px (vs +/-0.02-0.08 for well-behaved King years) - CoE numbers are INDICATIVE, not settled. Would be overturned by: a citywide pass, or sites chosen in different land-cover mixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Class 4 = 2.40% of valid pixels</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Decimated bincount</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>4000-row decimated read of the CLIPPED ccap_2021_hires_lc.tif</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Count zero in the 2016 file by the same method.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>APPROXIMATE and scoped to that clip's extent - NOT a property of the v2 product generally. Would be overturned by a full-raster count, or by the same count over the full-coverage file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>JPEG 8x8 block grid under a DEFLATE tag</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mean |first difference| profile mod 8, both axes, per band per site; mod-32 profile to confirm period 8 not 4 or 16</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>All 16 King+CoE files; 15/15 band-site-axis combinations agree (14/15 for 2000 v-axis, 2023 h-axis); mean z from 4.32 to 16.98; boundary/within ratios 1.07-1.36</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>The 4 Snohomish/NAIP files show NO phase-7 signature - a built-in negative control.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>INFERENCE (labelled as such by the measurer): because the block grid is phase-locked to the delivered EPSG:3857 grid rather than smeared by resampling, the JPEG stage most likely happened ON this grid. Would be overturned by finding a lossless original that still shows the signature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>The greenness drift is red brightening</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Per-band means over the same 5 fixed windows, all King years</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>R 100.9 (2000) -&gt; 136.2 (2023) = +35%; G 115.3 -&gt; 134.2 = +16%; B 117.4 -&gt; 105.2 = -10%. G-R collapses +14.4 -&gt; -6.0 DN.</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>frac(GRVI&gt;.02) reproduced the published series on DIFFERENT sites (2000 .8208 vs .8027; 2013 .3267 vs .3463; 2019k .0640 vs .1146).</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Reproduction on different sites is the strongest validation available here. Would be overturned by: a site set with different land-cover balance giving a different sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2016 Snohomish blue misregistration 0.224 px</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Sub-pixel band registration</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Every other file in the archive is 0.0001-0.019 px; 2021_snoh is 0.012 px. So 2016 is 20-200x larger than any other file.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Corroborated independently by blue's edge rise (3.22 px vs 2.32 red / 2.33 green) and its HF power (0.53-0.59x green's).</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Three independent measurements agree. Strong. Would be overturned by the offset appearing at only one site - it does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>The 2020 anchor's flight window</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>DOCUMENTARY, not measured</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Signed Edmonds-SnoCo ILA names the 2020 EagleView regional project; county SCOPI gives that project's window as 2020-04-13 to 07-13</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>THE FINAL LINK IS INFERENTIAL - no Edmonds document states a date. Would be CONFIRMED by: EagleView CONNECTExplorer per-image dates (Edmonds owns up to 10 accounts), a neighbouring city's un-mosaicked copy, or a county flight index. Would be OVERTURNED by evidence the AOI is multi-date.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source A</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Source C</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2015 flight date</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Apr 8/9/17 2015 at 0.225 ft (2.7 in) - GeoTerra consortium photo centres, which is what Edmonds signed and paid for (6/23/2015, $3,696.21)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Feb 15 - Mar 8 2015 - King County Pictometry frames over Edmonds</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Aug 7 2015 at 4.8 in - per the 2019 Urban Forest Management Plan</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Most likely: canopy-assessment imagery is NOT the same dataset as the city's basemap orthophoto. Resolve before any 2015 tier decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2017 imagery source</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>PlanIt Geo did 2017 flyovers for Pierce/Snohomish/King as part of stormwater modelling (Edmonds council minutes 2023-07-25 p.15, Urban Forest Planner)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>King County per-frame evidence puts imagery over Edmonds at 2017-05-04 to 05-10</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>The inferred King window is 2017-02-17 to 2017-10-30 (8.5 months)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>MINUTES ARE WEAK</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>The minute conflates collector with analysis consultant; PlanIt Geo is an analytics firm, not an imagery acquirer. Does not override per-frame evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>NAIP is leaf-on by specification</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_PLAN A4 and several CHATLOG entries assert it</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>BOTH WA NAIP flights over Edmonds are OCTOBER: 2019-10-11 and 2023-10-07</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ASSERTION WEAKENED</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>October in western Washington is late season. The leaf-on assumption should not be carried without evidence for these specific dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2000 accuracy</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>CE90 4 m stated, 'worse in the northern third of the project area' - which is where Edmonds sits</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Orthorectified to a 10 m DEM, by far the coarsest in the King series</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>CONSISTENT but poor</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Not a contradiction - a compounding weakness. 2000 is the least reliable geometry in the archive AND the most radiometrically anomalous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>'3 ft' vs 1 m naming</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>The WA statewide Ecopia service is named '3ft' and reports pixelSizeX 3.28084</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Its CRS is EPSG:2927, US SURVEY FEET, so 3.28084 ftUS = exactly 1.000 m</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>RESOLVED - it is a 1 m product</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>A THIRD instance of the units trap. Service names are not resolutions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Product family</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Rights holder</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Verbatim restriction</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>What it means here</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Risk and action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia-derived products (C-CAP v2 hi-res, statewide Ecopia land cover, the 'Initial' canopy layer)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia Tech Corporation</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>'...otherwise leverage the product for the purposes of machine learning for a period of five years from its date of creation, except with the express written consent of Ecopia Tech Corporation.'</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>*** FLAT PROHIBITION ON ML USE *** - and one version carries NO qualifier limiting it to 'creating similar land cover data'. THIS IS A MACHINE LEARNING PROJECT.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>HIGH - resolve before these products are used for training, and check whether EVALUATION-only use is covered. The project's rule that C-CAP is EVAL-ONLY, never train, may already satisfy it - but that has never been checked against the actual licence text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>King County imagery and derived products</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>King County</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>'Any sale of this map or information on this map is prohibited except by written permission of King County.' SDC records are IsPublic=false; CIR products are 'not yet available in ArcGIS Online'.</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Redistribution restricted; access terms for CIR unknown.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - confirm terms before any King product enters a download list or any output is published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds imagery</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>No licence stated anywhere - copyrightText and licenseInfo are EMPTY on every Edmonds imagery service.</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Unknown. The imagery came to Edmonds via a county ILA, so the county's and EagleView's terms may govern.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - unstated is not the same as unrestricted. The 2021 ILA and the EagleView Authorized Subdivision Agreement (executed 2021-03-22) are the documents to read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County imagery</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>'More recent imagery may not be distributed doe [sic] to contractual terms.'</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Explicit acknowledgement that some years are restricted - but which years is not stated.</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - ask which years before re-acquiring 2016/2021 at full extent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>NAIP / NOAA Digital Coast / USGS lidar</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>USDA / NOAA / USGS</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Federal public-domain products.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>No restriction found.</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>LOW - the cleanest sources in the inventory.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -8,52 +8,54 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KingCo_SDC_Catalog" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataLake_Issues" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USGS_Scenes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata_Map" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links_Checked" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Rasters_Audit" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Audit_Verdicts" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unknowns" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Mods" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pixel_Forensics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effective_Resolution" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance_Chain" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dating_Methods" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Independence" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retractions" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method_Provenance" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pixel_Size_And_Date" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KingCo_SDC_Catalog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataLake_Issues" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USGS_Scenes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata_Map" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links_Checked" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Rasters_Audit" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lake_Audit_Verdicts" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unknowns" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processing_Mods" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pixel_Forensics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effective_Resolution" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance_Chain" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dating_Methods" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Independence" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retractions" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method_Provenance" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MASTER'!$A$1:$P$221</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scores'!$A$1:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'USGS_Scenes'!$A$1:$F$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Findings'!$A$1:$G$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metadata_Map'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Sources'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Links_Checked'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Lake_Rasters_Audit'!$A$1:$L$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Lake_Audit_Verdicts'!$A$1:$A$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Unknowns'!$A$1:$A$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Processing_Mods'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Pixel_Forensics'!$A$1:$D$122</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Effective_Resolution'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Provenance_Chain'!$A$1:$H$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Dating_Methods'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Reference_Independence'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Retractions'!$A$1:$E$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Method_Provenance'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Contradictions'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Licensing_Risk'!$A$1:$E$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Scores'!$A$1:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'USGS_Scenes'!$A$1:$F$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Findings'!$A$1:$G$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Metadata_Map'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Sources'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Links_Checked'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Lake_Rasters_Audit'!$A$1:$L$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Lake_Audit_Verdicts'!$A$1:$A$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Unknowns'!$A$1:$A$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Processing_Mods'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Pixel_Forensics'!$A$1:$D$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Effective_Resolution'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Provenance_Chain'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Dating_Methods'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Reference_Independence'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Retractions'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Method_Provenance'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Contradictions'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Licensing_Risk'!$A$1:$E$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -76,7 +78,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +95,26 @@
         <fgColor rgb="007B2D26"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -106,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -116,6 +138,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -567,12 +601,394 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pixel_Size_And_Date: true pixel size (grid / true ground / effective / native flight) + date shot per held acquisition, each with evidence grade, fetched URL and verbatim quote. Source of record = Scripts/qc/imagery_pixelsize_and_date.csv (built by scratch/imagery_pixelsize_date_build.py; this sheet is a copy).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="66" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Base URL</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Download allowed</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Request limits</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County imagery</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>ArcGIS ImageServer x23</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>exportImage (native res)</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>15000 x 4100 px/request; ExportTilesAllowed false</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Capabilities Catalog,Image,Metadata. Pixel sizes in FEET (EPSG:2285)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>King County basemaps</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>https://gismaps.kingcounty.gov/arcgis/rest/services/BaseMaps</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>cached MapServer x15 (1936-2025)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>/export works (undocumented)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>4096 x 4096 px/request</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>singleFusedMapCache, 24 LODs, format MIXED = lossy JPEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>King County data catalog</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=&lt;NAME&gt;</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>metadata pages + FTP/Open Data</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>yes - originals</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>PREFERRED for King originals incl. CIR. Downloads via gis-kingcounty.opendata.arcgis.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>WA statewide public imagery</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>https://imagery-public.watech.wa.gov/arcgis/rest/services</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>ArcGIS server; folders County/ImageServices/LandCover/Municipality/NAIP/Regional/Utilities/WSDOT</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Download capability on Ecopia</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>15000 x 4100; 2048 MB download cap</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>LandCover holds only Ecopia; ImageServices empty; County has SnohomishCo 2002 + 2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WA Geoservices hub</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>https://geo.wa.gov/datasets/</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>ArcGIS Hub</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>varies - see item licenseInfo</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Best licence metadata. Item API: arcgis.com/sharing/rest/content/items/&lt;id&gt;?f=json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>NOAA Digital Coast imagery</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Azure blob, static</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>yes - direct files</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>NAIP WA 2015/2017/2021 with tileindex + urllist + VRT + STAC. Cleanest path of all</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>NOAA C-CAP high-res bulk</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>https://ocmgeodatastor1.blob.core.windows.net/ccap/bulk_download/C-CAP_High-Resolution_Data/</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Azure blob, static</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>yes - direct files</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Refined_.../CONUS holds wa_puget_2021_ccap_v2_hires_landcover.tif (1.43 GB). Also Initial_... Water/Impervious families</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>NOAA C-CAP BETA derived</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/ccap-landcover/CCAP_bulk_download/BETA_Derived_Land_Cover/</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Azure blob, static</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Land Cover 10m / Percent Canopy 30m / Percent Impervious 30m. Too coarse for crown work</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>NOAA lidar bulk</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>https://noaa-nos-coastal-lidar-pds.s3.amazonaws.com/laz/geoid18/</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>AWS S3, static</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>yes - direct files</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>2005 PSLC = 2579; 2016 USGS West WA = 6331. COPC allows HTTP bbox reads without full download</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>NOAA InPort (metadata)</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.fisheries.noaa.gov/inport/item/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>metadata catalogue</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>50149 = 2005 PSLC; 51853 = 2016 USGS; 57099 = 10m BETA; 57108 = 30m impervious BETA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1275,7 +1691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4652,7 +5068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4740,7 +5156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5458,7 +5874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7793,7 +8209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10498,7 +10914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10954,7 +11370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11359,7 +11775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11734,7 +12150,2718 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>year_label</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>grid_px</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>grid_units</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>crs</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>true_ground_cm</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>effective_cm</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>native_flight_cm</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>date_shot</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>date_precision</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>single_or_multi_date</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>evidence_grade</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>px_evidence</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>alt_date_shot</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>alt_source_url</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>alt_verbatim_quote</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1936_king_pan.tif</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>King County GIS (IMAGE_Ortho1936KCPAN)</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>0.597164</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>40.11</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (scanned prints: 0.5 ft scan resampled to 1 ft)</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>year only</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>unknown (scanned print mosaic)</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho1936KCPAN</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>1936 aerial imagery for western King County from scanned 3 foot by 3 foot prints (boards 0.5 in pixels resampled to 1 foot).</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Content covers only 24.4% of the study area (Retractions sheet). No month/season anywhere on the page; change-history dates (2006-2007) are digitisation dates.</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED (SDC page)</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr"/>
+      <c r="T2" s="1" t="inlineStr"/>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>1998_king_pan.tif</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>WA DNR via King County GIS (IMAGE_Ortho1998WADNRPAN)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>0.597164</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>40.11</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>91.44 (3 ft product; film 1:12000, 12,000 ft AGL)</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>summer 1998</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>multi (frame dates stated unavailable)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho1998WADNRPAN</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Acquisition period was Summer, 1998. Individual frame or tile acquisition dates are not available.</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Held grid 40.1 cm is 2.3x FINER than the 3 ft native: pure oversampling.</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED (SDC page)</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr"/>
+      <c r="T3" s="1" t="inlineStr"/>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2000_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Emerge Inc. via King County GIS (IMAGE_Ortho2000EmergeNAT, natural-colour DERIVATIVE of EmergeCIR)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>0.597164</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>40.11</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>109 red / 70 green / 68 blue (band-dependent; published 110.8 is red-only)</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>60.96 (2 ft)</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>late spring to early fall 2000</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>season (~5 months)</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>multi (township-level flight-date graphic referenced by the page is a 404)</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2000EmergeNAT</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>collected in lat spring to early fall 2000 [sic]. Detailed photodate information is not available.</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Sensor Kodak DSC460CIR: no blue light recorded, all three held bands NIR-contaminated (Retractions). Wayback target for an agent: https://www5.kingcounty.gov/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg (404 live).</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED (Effective_Resolution); native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr"/>
+      <c r="T4" s="1" t="inlineStr"/>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>USGS High Resolution Orthoimagery Seattle/Tacoma 2002 (Selkirk Remote Sensing) as retiled by King County (IMAGE_Ortho2002USGSNAT)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>0.597164</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>40.11</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>33 acquired, delivered at 30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002USGSNAT</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>(no acquisition statement on the page; catalog LastUpdated 2003-01-01 is maintenance metadata)</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Over Edmonds the cache serves the USGS/NGA Seattle-Tacoma product, NOT IMAGE_Ortho2002KCNAT (which is 'acquired in July 2002' but covers the county-only project). AGENT TARGET: USGS HRO Seattle/Tacoma FGDC metadata (EarthExplorer / TNM / Wayback) carries the per-project acquisition dates.</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (REST description: 'acquired at a resolution of 0.33 meter per pixel ... resampled to 1 foot per pixel')</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>July 2002 (sibling product IMAGE_Ortho2002KCNAT — does NOT serve Edmonds)</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002KCNAT</t>
+        </is>
+      </c>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t>Natural color orthophotography acquired in July 2002</t>
+        </is>
+      </c>
+      <c r="U5" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2005_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Aerials Express via King County GIS (IMAGE_Ortho2005AerialsExpressNAT)</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>0.298582</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>July 2005</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>unknown (no per-frame index exists before 2007)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2005AerialsExpressNAT</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Year 2005 (July)</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Held grid 20.1 cm vs 1 ft native = 1.5x oversampled, and the file resolves at 80.7 cm — coarser than 2000's nominal grid.</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr"/>
+      <c r="T6" s="1" t="inlineStr"/>
+      <c r="U6" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2007_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International via King County GIS (IMAGE_Ortho2007KCNAT); per-frame index ORTHO_IMAGE07_AREA_759</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>0.298582</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>15.24 (0.5 ft west county)</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>2007-06-30 to 2007-08-13 (6 days over the city: Jun 30 n=252, Jul 7 481, Jul 8 15, Jul 10 36, Jul 11 173, Aug 13 121)</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>window of 45 days, 6 flight days</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (6 days)</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE07_AREA_759/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>SHOTDATE field, 1078 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. SDC page: 'Final version 2007 (July)' — the August frames show 'July' is a simplification.</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (SDC: 6 in west)</t>
+        </is>
+      </c>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>July 2007</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2007KCNAT</t>
+        </is>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t>Final version 2007 (July) King County Natural Color orthoimagery acquired by Pictometry</t>
+        </is>
+      </c>
+      <c r="U7" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2009_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International via King County GIS (IMAGE_Ortho2009KCNAT); per-frame index ORTHO_IMAGE09_AREA_760</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>0.298582</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>15.24 (0.5 ft west county)</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>2009-05-01 to 2009-05-16 (3 days over the city: May 1 n=179, May 9 121, May 16 172)</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>window of 16 days, 3 flight days</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (3 days)</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE09_AREA_760/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>SHOTDATE/YYYYMMDD fields, 472 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Early leaf-out. SDC page states no month ('Final version 2009'); the 11/1/2009 change-history date is delivery, not flight.</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr"/>
+      <c r="T8" s="1" t="inlineStr"/>
+      <c r="U8" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2012_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>USGS/NGA Puget Sound Urban Area ortho (Mapcon Mapping, Vexcel UltraCamX/Xp) via King County GIS (IMAGE_Ortho2012KCNAT); photo-centre index ORTHO_IMAGE12_POINT_1447</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>0.298582</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>20.05</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>33.7</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>30 (delivered 0.3 m; SP orthos at 0.25/0.50/1.00 ft resampled bilinear)</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>2012-03-23 (30 photo centres, 13:25-13:44) and 2012-04-07 (45 photo centres, 12:08-12:46)</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>2 flight days</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (2 days)</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE12_POINT_1447/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>DATE_STR/TIME_STR fields, 75 photo centres inside the city polygon (query 2026-08-23); DATACOLOR='nir' for all 75</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Leaf-off to barely budding. Countywide window PUBLISHED on the SDC page (alt). Index RESOLUTION field = 1 (Apr 7) / 2 (Mar 23), units not stated.</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>2012-03-23 to 2012-05-08 (countywide)</t>
+        </is>
+      </c>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2012KCNAT</t>
+        </is>
+      </c>
+      <c r="T9" s="1" t="inlineStr">
+        <is>
+          <t>The imagery was collected between March 23, 2012 and May 8, 2012.</t>
+        </is>
+      </c>
+      <c r="U9" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2013_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International via King County GIS (IMAGE_Ortho2013KCNAT); per-frame index ORTHO_IMAGE13_AREA_2061</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>12.6-13.7 (five z20 years measured together; IMAGERY_FACTS 2.2)</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>10.16 (4 in west county)</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>2013-06-02 to 2013-06-06 (4 days over the city: Jun 2 n=111, Jun 4 137, Jun 5 218, Jun 6 222)</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>window of 5 days, 4 flight days</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (4 days)</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE13_AREA_2061/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate/YYYYMMDD fields, 688 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Fully leaf-on. Only year whose held grid (10.0 cm) ~= native (10.16 cm).</t>
+        </is>
+      </c>
+      <c r="Q10" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr"/>
+      <c r="T10" s="1" t="inlineStr"/>
+      <c r="U10" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2015_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2015 (King)</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International via King County GIS (IMAGE_Ortho2015KCNAT); per-frame index ORTHO_IMAGE15_AREA_2499</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>12.6-13.7</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (3 in west county)</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>2015-02-15 to 2015-03-08 (6 days over the city: Feb 15 n=5, Feb 18 5, Feb 21 26, Feb 28 111, Mar 7 348, Mar 8 206)</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>window of 22 days, 6 flight days</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (6 days)</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE15_AREA_2499/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate/YYYYMMDD fields, 701 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. LEAF-OFF. This held file is the Pictometry KCNAT product; the three-way 2015 CONTEST (Apr 8/9/17 GeoTerra 2.7 in / Aug 7 4.8 in UFMP) belongs to the City of Edmonds 2015 SERVICE, a different product — see the CoE 2015 row.</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr"/>
+      <c r="T11" s="1" t="inlineStr"/>
+      <c r="U11" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2017_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2017 (King)</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry International via King County GIS (IMAGE_Ortho2017KCNAT); per-frame index ORTHO_IMAGE17_AREA_2685</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>13.2</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (3 in west county); index per-frame GSD median ~6.4 cm</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>2017-05-04 to 2017-05-10 (5 days over the city: May 4 n=16, May 6 90, May 8 48, May 9 192, May 10 364)</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>window of 7 days, 5 flight days</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (5 days)</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE17_AREA_2685/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate/YYYYMMDD fields, 710 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Resolves the May 18 discrepancy in MASTER: May 18 frames (n=215) fall inside the wider bbox -122.42,47.76,-122.32,47.87 but outside the city polygon. Countywide capture window 2017-02-17 to 2017-10-30 (PUBLISHED, SDC index change history).</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr"/>
+      <c r="T12" s="1" t="inlineStr"/>
+      <c r="U12" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2019_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2019 (King)</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry/EagleView via King County GIS (IMAGE_Ortho2019KCNAT); per-frame index ORTHO_IMAGE19_AREA_2852</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>12.6-13.7</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (3 in west county)</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>2019-04-25 to 2019-05-08 (7 days over the city: Apr 25 n=92, Apr 30 387, May 1 20, May 4 160, May 6 185, May 7 332, May 8 58)</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>window of 14 days, 7 flight days</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (7 days)</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE19_AREA_2852/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate field (date only, no time), 1234 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. 2019 index also carries CameraLat/CameraLon/Bearing/Alt/FocalLen per frame (photo-centre data).</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr"/>
+      <c r="T13" s="1" t="inlineStr"/>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2021_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>2021 (King)</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Pictometry/EagleView via King County GIS (IMAGE_Ortho2021KCNAT); per-frame index ORTHO_IMAGE21_AREA_2912</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>12.6-13.7</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (3 in west county)</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>2021-04-14 to 2021-04-17 (4 days over the city: Apr 14 n=135, Apr 15 248, Apr 16 259, Apr 17 20)</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>window of 4 days</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (4 days)</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE21_AREA_2912/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate field, 662 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. NARROWED vs earlier bbox query (Apr 12/14 - May 5): the May 5 frames are outside the city polygon.</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr"/>
+      <c r="T14" s="1" t="inlineStr"/>
+      <c r="U14" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2023_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>2023 (King)</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>EagleView Technologies via King County GIS (IMAGE_Ortho2023KCNAT); per-frame index ORTHO_IMAGE23_AREA_3073</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>0.149291</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>10.03</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>12.6-13.7</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (3 in 'Neighborhood' tier incl. SW Snohomish); index per-frame GSD median 6.41 cm</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>2023-04-19 to 2023-05-07 (7 days over the city: Apr 19 n=57, Apr 20 84, Apr 25 64, Apr 26 381, Apr 27 169, May 3 336, May 7 34)</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>window of 19 days, 7 flight days</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (7 days)</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE23_AREA_3073/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t>ShotDate field, 1125 frames intersecting the city polygon (query 2026-08-23)</t>
+        </is>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which.</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>2023-04-14 to 2023-06-28 (countywide)</t>
+        </is>
+      </c>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2023KCNAT</t>
+        </is>
+      </c>
+      <c r="T15" s="1" t="inlineStr">
+        <is>
+          <t>captured by EagleView Technologies between April 14 and June 28, 2023</t>
+        </is>
+      </c>
+      <c r="U15" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Hexagon Imagery Program (HXIP) via Snohomish County Imagery/Aerial_2016 ImageServer</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>15.24</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>35.4</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft): county mosaic-catalog LowPS=1 and item pixelSizeX=1 for every primary tile over Edmonds (MEASURED 2026-08-23); the 2016 consortium 6-in (15 cm) buy-up exists over Edmonds but is NOT what the county serves</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>2016-08-11 (16:52) and 2016-08-12 (09:05, 09:30) — WA consortium 2016 6-in footprints over Edmonds</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>window of 2 days, 3 sorties</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (2 days / 3 sorties over the city; footprint = quarter-quarter quads)</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/NAIP_2016_6in_Ortho_Dates_and_Times_83s/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>SDATE '08/11/2016 16:52' (SUNEL 31) / '08/12/2016 09:05' (SUNEL 34) / '08/12/2016 09:30' (SUNEL 37), THEMENAME hxip_m_4712213/4712214_*_10_15, 11 footprints intersecting the city bbox</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>Held file = export of the county service (window means identical to exportImage, 2026-08-23) and pixel-DISTINCT from Aerial_2015 and Aerial_2017. Why INFERRED not PUBLISHED: the dated footprints are the 15 cm consortium product; the county's 1-ft tiles are a different delivery of (presumably) the same flight — the county mosaic was built from a geodatabase literally named HXIP_2015_Snohomishv3 (service /info/metadata lineage), so the 2015-08-07 HXIP 1-ft flight was a live alternative until the pixel test excluded it. OPEN: held-file shadows in the footprint labelled 16:52 point WEST (morning), so either that SDATE is UTC (=09:52 PDT) or the county product is a different sortie. Geocortex blurb 'acquired in August 2016' is mis-titled '2017 Aerial Photos'.</t>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native MEASURED (service catalog)</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>2015-08-07 15:31 (HXIP 2015 1-ft flight; EXCLUDED by pixel comparison against Aerial_2015)</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/NAIP_2015_1ft_Ortho_Dates_and_Times_83s/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T16" s="1" t="inlineStr">
+        <is>
+          <t>SDATE '08/07/2015 15:31', THEMENAME hxip_m_4712213_ne_10_30, SUNEL 46</t>
+        </is>
+      </c>
+      <c r="U16" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>2021 (Snoh)</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>HXIP via Snohomish County Imagery/Aerial_2021 ImageServer</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>15.24</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>15.24 (0.5 ft): mosaic-catalog LowPS=0.5, item pixelSizeX=0.5 (MEASURED)</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>2021-06-25 to 2021-11-11</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>window of 140 days</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>unknown (countywide window only)</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 aerial photos are 6 inch resolution and cover mainly the urban areas. The imagery was collected between June 25, 2021 and November 11, 2021.</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>AGENT TARGET: a WA consortium 2021 flight-date footprint layer (as exists for 2015-2020) would narrow this to days. Service metadata carries no date (sweep 2026-08-23).</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native MEASURED (service catalog)</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr"/>
+      <c r="T17" s="1" t="inlineStr"/>
+      <c r="U17" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>2017 (CoE)</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds Basemap/2017_Aerial_Cached (source raster 2017_Aerial.tif, 0.25 ftUS EPSG:2285); acquirer NOT ESTABLISHED</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>0.074646</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>7.6 (indicative; per-site sd +/-0.41-1.17 px)</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ftUS source raster)</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>https://weblink.edmondswa.gov/WebLink/0/edoc/1654952/</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>In 2017 flyovers and imagery was done by the consultant who did the public engagement, PlanIt Geo, for Pierce, Snohomish and King Counties as part of a stormwater modeling project.</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>The quote (council minutes 2023-07-25 p.15) is WEAK: conflates collector with analytics consultant. Candidate: King County 2017 flight 2017-05-04..05-10 over Edmonds (MEASURED on 2017_king_rgb.tif) — attribution to the city file UNPROVEN; Snohomish Aerial_2017 is a 1-ft HXIP product (2017-08-15/21) and cannot be a 3-in source. AGENT TARGET: 2017 CoE contract/budget line, sibling products, neighbour cities.</t>
+        </is>
+      </c>
+      <c r="Q18" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (service source-raster XML)</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="1" t="inlineStr"/>
+      <c r="U18" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2020_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>2020 (ANCHOR)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds Basemap/2020_Aerial_Cached; source = Snohomish County 2020 EagleView/Pictometry regional project (WASNOH20_3in) per the 2021 ILA</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>0.074646</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ftUS; county Aerial_2020 LowCellSize 0.25, dimResol 0.250000 ftUS)</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>2020-04-13 to 2020-07-13</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>window of 92 days</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>unknown — whether the Edmonds AOI is single- or multi-date is UNRESOLVED and outranks the date</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+        </is>
+      </c>
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t>The 2020 aerial photos are 3 inch resolution in the urban areas and 9 inch resolution in the rural areas, excluding much of the unpopulated mountainous portion of eastern Snohomish County, and were taken between April 13th and July 13th, 2020.</t>
+        </is>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t>Chain: ILA 2021 (Laserfiche id 1462454) Work Order p.14 'Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ... County will provide Edmonds with orthogonal imagery'; city service keyProperties carry NO acquisition date (MrSID/MG4 mosaic lost it). The window is PUBLISHED for the county product; the link to the city file is documented by contract but inferential. DEFINITIVE PIN = EagleView flight log / photo-centre index via Snohomish County DoIT (PRR citing Contract Routing Form No. 20210127) or a CONNECTExplorer capture-date screenshot (city holds up to 10 accounts).</t>
+        </is>
+      </c>
+      <c r="Q19" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+        </is>
+      </c>
+      <c r="R19" s="1" t="inlineStr">
+        <is>
+          <t>(ILA text, for the chain)</t>
+        </is>
+      </c>
+      <c r="S19" s="1" t="inlineStr">
+        <is>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+        </is>
+      </c>
+      <c r="T19" s="1" t="inlineStr">
+        <is>
+          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects and receipt of imagery by County, County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest</t>
+        </is>
+      </c>
+      <c r="U19" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2022_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>2022 (CoE)</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds Basemap/2022_Aerial_Cached; source = Snohomish County 2022 regional project (WASNOH22_3in) per the 2021 ILA</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>0.074646</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ftUS; county Aerial_2022 LowCellSize 0.25; MrSID input GeoTIFF geokeys EPSG:2285 ftUS)</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>2022-04-06 to 2022-07-11 (urban 3 in)</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>window of 96 days</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>The 2022 3 inch resolution aerial photos in the urban areas, were captured between April 6, 2022 and July, 11 2022.</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>Same chain and same definitive pin as 2020 (one PRR covers 2020/2022/2024).</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+        </is>
+      </c>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>(ILA text)</t>
+        </is>
+      </c>
+      <c r="S20" s="1" t="inlineStr">
+        <is>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+        </is>
+      </c>
+      <c r="T20" s="1" t="inlineStr">
+        <is>
+          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ...</t>
+        </is>
+      </c>
+      <c r="U20" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2024_coe_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>2024 (CoE)</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds Basemap/2024_Aerial_Cached (Edmonds2024.sid); source = Snohomish County 2024 regional project (WASNOH24_3in) per the 2021 ILA</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>0.074646</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>5.01</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ftUS; county Aerial_2024 LowCellSize 0.25)</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>2024-03-31 to 2024-05-31 (urban 3 in)</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>window of 61 days</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+        </is>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>The 2024 3 inch resolution aerial photos in the urban areas, were captured between March 31, 2024 and May, 31 2024.</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>Same chain and same definitive pin as 2020.</t>
+        </is>
+      </c>
+      <c r="Q21" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+        </is>
+      </c>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>(ILA text)</t>
+        </is>
+      </c>
+      <c r="S21" s="1" t="inlineStr">
+        <is>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+        </is>
+      </c>
+      <c r="T21" s="1" t="inlineStr">
+        <is>
+          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ...</t>
+        </is>
+      </c>
+      <c r="U21" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>(not held) City of Edmonds Basemap/2015_Aerial_Cached</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>2015 (CoE service)</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds (source raster Ed_Aerial_2015.tif, 0.25 ftUS, LZW)</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>LOD 21 cache (0.0746 WM m)</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator)</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857 (cache); source EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>5.01 (cache) / 7.62 (source)</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ftUS source) — vs 6.86 (0.225 ft, GeoTerra consortium spec) vs 12.19 (4.8 in, UFMP)</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>CONTESTED: 2015-04-08/09/17 (GeoTerra consortium photo centres) vs 2015-02-15..03-08 (King Pictometry) vs 2015-08-07 (UFMP '4.8 in')</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>(see Contradictions sheet; three sources)</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
+          <t>Included so the contest stops contaminating the held 2015_king_rgb.tif row. Likely explanation: the UFMP canopy-assessment imagery is a different dataset from the city basemap. Edmonds signed the 2015 consortium agreement 2015-06-23 ($3,696.21).</t>
+        </is>
+      </c>
+      <c r="Q22" s="1" t="inlineStr">
+        <is>
+          <t>grid PUBLISHED (service); native PUBLISHED (source-raster XML)</t>
+        </is>
+      </c>
+      <c r="R22" s="1" t="inlineStr"/>
+      <c r="S22" s="1" t="inlineStr"/>
+      <c r="T22" s="1" t="inlineStr"/>
+      <c r="U22" s="1" t="inlineStr">
+        <is>
+          <t>context (not held)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>2019n</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA NAIP WA 2019 (DOQQ m_4712213/m_4712214; flown by Hexagon under the 2019 program)</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>95.1</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>60 (collected and delivered at 60 cm)</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>2019-10-11</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr">
+        <is>
+          <t>single (all Edmonds DOQQs carry 20191011)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_fgdc_2019/47122/m_4712214_sw_10_060_20191011.txt</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr">
+        <is>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20191011</t>
+        </is>
+      </c>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
+          <t>OCTOBER — weakens the 'NAIP is leaf-on by spec' assumption. Corroborated by the WA consortium 2019 1-ft flight-area layer IDATE '2019 -10-11'.</t>
+        </is>
+      </c>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="1" t="inlineStr"/>
+      <c r="U23" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>2023n (was mislabelled 2022n)</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>USDA FSA NAIP WA 2023 (DOQQ m_4712213/m_4712214)</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>83.1</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>60 delivered (2021/2023-era WA NAIP collected finer and rectified to 60 cm)</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>single (all 8 Edmonds QQs: m_47122{13,14}_*_10_060_20231007_20240209)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_fgdc_2023/47122/m_4712214_sw_10_060_20231007_20240209.xml</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr">
+        <is>
+          <t>m_4712214_ne_10_060_20231007.tif (date field of the DOQQ file name, ISO metadata)</t>
+        </is>
+      </c>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues).</t>
+        </is>
+      </c>
+      <c r="Q24" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr"/>
+      <c r="T24" s="1" t="inlineStr"/>
+      <c r="U24" s="1" t="inlineStr">
+        <is>
+          <t>held imagery</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>lidar_snoh_chm.tif</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>~2016 (lidar)</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>USGS 3DEP HAG via Planetary Computer, reprojected by the project</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>1.000009</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>67.16</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>n/a (bilinear-upsampled ~2 m product)</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>~200 (HAG raster); lidar 0.7 m spacing</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>2016-03-17 to 2017-06-06 (USGS/WADNR lidar collection)</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr">
+        <is>
+          <t>window of 15 months</t>
+        </is>
+      </c>
+      <c r="L25" s="1" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>https://www.fisheries.noaa.gov/inport/item/51853</t>
+        </is>
+      </c>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>(collection window per IMAGERY_FACTS 8.1, sourced from InPort 51853 — REFETCH NEEDED)</t>
+        </is>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>UNITS TRAP #4: grid is 1.0 m in EPSG:3857 = 67.2 cm true ground at 47.81N, not 1 m. Row included for completeness; excluded from the imagery count.</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R25" s="1" t="inlineStr"/>
+      <c r="S25" s="1" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
+      <c r="U25" s="1" t="inlineStr">
+        <is>
+          <t>reference raster</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2016_hires_lc_snohfull.tif</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>2016 (C-CAP ref)</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM C-CAP hi-res land cover, Snohomish County 2016 (InPort 53263)</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>n/a (thematic)</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m product)</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (source-imagery date; InPort 53263 returns 'Catalog Item Not Retrievable')</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.fisheries.noaa.gov/inport/item/53263</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>Catalog Item Not Retrievable</t>
+        </is>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t>AGENT TARGET: Wayback copy of InPort 53263 / the .img sidecar metadata (wa_snohomish_co_ccap_hr_landcover20190314.img). Reference raster, not an imagery acquisition.</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr">
+        <is>
+          <t>reference raster</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2021_hires_lc.tif</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>2020-21 (C-CAP v2 ref)</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM C-CAP hi-res v2 'Refined' (Ecopia extraction, NV5 refinement)</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>n/a (thematic)</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m extraction from &lt;=30 cm imagery)</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>2020-2021 vintage (source imagery dates not stated per pixel)</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>year range</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>multi (mosaic of vendor imagery)</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>(lineage XML cc_wa_puget_2021_ccap_v2_hires_landcover.xml — URL to be re-fetched)</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI</t>
+        </is>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>GATE: published date without fetched URL+quote -&gt; downgraded. Reference raster, not an imagery acquisition. Date of the underlying imagery is the agent question.</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R27" s="1" t="inlineStr"/>
+      <c r="S27" s="1" t="inlineStr"/>
+      <c r="T27" s="1" t="inlineStr"/>
+      <c r="U27" s="1" t="inlineStr">
+        <is>
+          <t>reference raster</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U27"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12013,7 +15140,963 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="74" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Claim that was confidently held</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Corrected</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Where it lived</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>What actually turned out to be true</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>The lesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1936 is an empty shell</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_FACTS / CHATLOG</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Nine probe windows ALL missed the data. The content band starts 74.8% down the file; a full-extent read shows real photography over 24.4% of the study area.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Sampling that is not exhaustive can agree nine times and still be wrong. Probe placement is a hypothesis, not a control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>gsd_cm was correct in the catalog</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>phase4seg/config.py</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>gsd_cm was CRS-units x 100. EPSG:2285 is US SURVEY FEET (Snohomish overstated 3.24x); EPSG:3857 inflates 1/cos(47.8)=1.49x.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>A config value is a claim, not evidence. Units are the most common silent defect in this project - it has now happened THREE times (catalog, the CoE service grid, and the '3ft' Ecopia service that is actually 1 m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 pair isolates the sensor effect</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>WORKPLAN 2</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Resolution -&gt; tier -&gt; tiling params are entangled by design, so sensor and tiling regime cannot be separated in that pair.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>WITHDRAWN and must not be resurrected. The 2026-08-22 county inventory does NOT revive it - no same-tier same-year pair exists after true-GSD correction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>King County's export plateaus at ~20 cm</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>this session</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>A controlled test (312 m box, 4096 px vs 1024 px upsampled to the same grid) gives 2.16x the HF energy for the native request; the cache reaches LOD 21 ~ 5.0 cm ground.</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>The laplacian-falloff proxy was measuring JPEG smoothing, not a resolution ceiling. A proxy metric needs its own validation before it is trusted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Class 4 IS 'Developed Impervious under Tree Canopy'</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_FACTS 9.3</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>PRESENCE is measured (480,208 px = 2.40% of valid, decimated read). MEANING is INFERRED - no RAT for the held clip has been read by anyone.</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Corrected in the authoritative facts document after cross-session review. Writing an inference as a measurement is the same error class as the defect it describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>The class-4 fix moves both precision AND recall</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>cross-session</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Precision rises. RECALL'S DIRECTION IS NOT PREDICTED - the denominator grows ~2.4 pp while the numerator grows only by class-4 pixels the model already calls canopy, so recall may FALL.</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Both outcomes are consistent with the fix being correct. State direction AND magnitude before measuring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>The 2013 re-score will move the number materially</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>loop prompt</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>It moved 0.0004 (off-recipe .7395 vs citywide .7399).</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>The long-quoted .7422 was UNDER-EVIDENCED (live=0, fallback threshold), not INACCURATE. Those are different failures. A prediction stated confidently and falsified is worth more than one never written down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>B ~ aR+bG+c with high R2 detects a synthesised band</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>this session's own spec</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>On the KNOWN-SYNTHETIC control (2000) it returns R2=0.9545 - LOWER than 2005 (.9766) and 2002 (.9628), which have real blue. The specified detector would have cleared the one file known to be fake.</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>A detector must be validated against a positive control BEFORE it is applied. The working form is relative: normalise each band's unexplained variance given the other two, then compare blue's to red's and green's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2000 has 'a false blue' (i.e. RGB with one synthesised channel)</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>this session</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Understated. The Kodak DSC460CIR received NO blue light at all, and ALL THREE filter elements pass NIR: blue = NIR only, green = green+NIR, red = red+NIR. It is a colour-infrared sensor.</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>The first framing was directionally right and materially wrong. 2000 cannot be treated as an RGB acquisition at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish 2016 and 2021 are comparable (identical grid)</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>implicit</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Byte-identical grid geometry, but effective resolution differs 1.7x: 2016 = 2.32x oversampled / 35.4 cm; 2021 = 1.35x / 20.6 cm.</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Identical grid does NOT imply identical resolution. Any 2016-vs-2021 change detection sees a resolution step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>The statewide Ecopia product is a third INDEPENDENT reference</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>CHATLOG / this session</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>It shares its extraction vendor AND algorithm (Ecopia AI) with the C-CAP v2 reference it was meant to be independent of.</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>See the Reference_Independence sheet. Agreement between two Ecopia products is not corroboration.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Headline measurement</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Scope / sample</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Validation or control</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Limits, and what would overturn it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Effective resolution (all 20 files)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Edge-response rise time, esf()/rise_px() COPIED VERBATIM from Scripts/litwatch_scratch/q138b.py - the script that produced the IMAGERY_FACTS 2.2 table</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>5 fixed land sites, each a 200 m x 200 m ground box, plus a native 512x512 box with origin snapped to an absolute multiple of 16 so in-window phase == absolute phase. Sites (WGS84): S1_forest_nw 47.8225,-122.3580 (86% forest); S2_parking 47.8060,-122.3270 (94% developed); S3_residential 47.8100,-122.3700; S4_forest_s 47.7855,-122.3545; S5_suburb_ne 47.8250,-122.3400. All confirmed LAND against C-CAP 2016. All inside the intersection of all 20 footprints.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>REPRODUCED the 10 published King oversampling values at Pearson r=0.997 (2000 2.68 vs 2.8; 2005 3.92 vs 4.0; 2007 1.28 vs 1.3).</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>5 sites is not the city. CoE per-site sd is +/-0.41-1.17 px (vs +/-0.02-0.08 for well-behaved King years) - CoE numbers are INDICATIVE, not settled. Would be overturned by: a citywide pass, or sites chosen in different land-cover mixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Class 4 = 2.40% of valid pixels</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Decimated bincount</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>4000-row decimated read of the CLIPPED ccap_2021_hires_lc.tif</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Count zero in the 2016 file by the same method.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>APPROXIMATE and scoped to that clip's extent - NOT a property of the v2 product generally. Would be overturned by a full-raster count, or by the same count over the full-coverage file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>JPEG 8x8 block grid under a DEFLATE tag</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Mean |first difference| profile mod 8, both axes, per band per site; mod-32 profile to confirm period 8 not 4 or 16</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>All 16 King+CoE files; 15/15 band-site-axis combinations agree (14/15 for 2000 v-axis, 2023 h-axis); mean z from 4.32 to 16.98; boundary/within ratios 1.07-1.36</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>The 4 Snohomish/NAIP files show NO phase-7 signature - a built-in negative control.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>INFERENCE (labelled as such by the measurer): because the block grid is phase-locked to the delivered EPSG:3857 grid rather than smeared by resampling, the JPEG stage most likely happened ON this grid. Would be overturned by finding a lossless original that still shows the signature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>The greenness drift is red brightening</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Per-band means over the same 5 fixed windows, all King years</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>R 100.9 (2000) -&gt; 136.2 (2023) = +35%; G 115.3 -&gt; 134.2 = +16%; B 117.4 -&gt; 105.2 = -10%. G-R collapses +14.4 -&gt; -6.0 DN.</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>frac(GRVI&gt;.02) reproduced the published series on DIFFERENT sites (2000 .8208 vs .8027; 2013 .3267 vs .3463; 2019k .0640 vs .1146).</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Reproduction on different sites is the strongest validation available here. Would be overturned by: a site set with different land-cover balance giving a different sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2016 Snohomish blue misregistration 0.224 px</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Sub-pixel band registration</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Every other file in the archive is 0.0001-0.019 px; 2021_snoh is 0.012 px. So 2016 is 20-200x larger than any other file.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Corroborated independently by blue's edge rise (3.22 px vs 2.32 red / 2.33 green) and its HF power (0.53-0.59x green's).</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Three independent measurements agree. Strong. Would be overturned by the offset appearing at only one site - it does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>The 2020 anchor's flight window</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>DOCUMENTARY, not measured</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Signed Edmonds-SnoCo ILA names the 2020 EagleView regional project; county SCOPI gives that project's window as 2020-04-13 to 07-13</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>THE FINAL LINK IS INFERENTIAL - no Edmonds document states a date. Would be CONFIRMED by: EagleView CONNECTExplorer per-image dates (Edmonds owns up to 10 accounts), a neighbouring city's un-mosaicked copy, or a county flight index. Would be OVERTURNED by evidence the AOI is multi-date.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Source A</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Source C</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2015 flight date</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Apr 8/9/17 2015 at 0.225 ft (2.7 in) - GeoTerra consortium photo centres, which is what Edmonds signed and paid for (6/23/2015, $3,696.21)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Feb 15 - Mar 8 2015 - King County Pictometry frames over Edmonds</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Aug 7 2015 at 4.8 in - per the 2019 Urban Forest Management Plan</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Most likely: canopy-assessment imagery is NOT the same dataset as the city's basemap orthophoto. Resolve before any 2015 tier decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2017 imagery source</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>PlanIt Geo did 2017 flyovers for Pierce/Snohomish/King as part of stormwater modelling (Edmonds council minutes 2023-07-25 p.15, Urban Forest Planner)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>King County per-frame evidence puts imagery over Edmonds at 2017-05-04 to 05-10</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>The inferred King window is 2017-02-17 to 2017-10-30 (8.5 months)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>MINUTES ARE WEAK</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>The minute conflates collector with analysis consultant; PlanIt Geo is an analytics firm, not an imagery acquirer. Does not override per-frame evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>NAIP is leaf-on by specification</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>IMAGERY_PLAN A4 and several CHATLOG entries assert it</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>BOTH WA NAIP flights over Edmonds are OCTOBER: 2019-10-11 and 2023-10-07</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>ASSERTION WEAKENED</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>October in western Washington is late season. The leaf-on assumption should not be carried without evidence for these specific dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2000 accuracy</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>CE90 4 m stated, 'worse in the northern third of the project area' - which is where Edmonds sits</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Orthorectified to a 10 m DEM, by far the coarsest in the King series</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>CONSISTENT but poor</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Not a contradiction - a compounding weakness. 2000 is the least reliable geometry in the archive AND the most radiometrically anomalous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>'3 ft' vs 1 m naming</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>The WA statewide Ecopia service is named '3ft' and reports pixelSizeX 3.28084</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Its CRS is EPSG:2927, US SURVEY FEET, so 3.28084 ftUS = exactly 1.000 m</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>RESOLVED - it is a 1 m product</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>A THIRD instance of the units trap. Service names are not resolutions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="84" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Product family</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Rights holder</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Verbatim restriction</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>What it means here</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Risk and action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia-derived products (C-CAP v2 hi-res, statewide Ecopia land cover, the 'Initial' canopy layer)</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Ecopia Tech Corporation</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>'...otherwise leverage the product for the purposes of machine learning for a period of five years from its date of creation, except with the express written consent of Ecopia Tech Corporation.'</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>*** FLAT PROHIBITION ON ML USE *** - and one version carries NO qualifier limiting it to 'creating similar land cover data'. THIS IS A MACHINE LEARNING PROJECT.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>HIGH - resolve before these products are used for training, and check whether EVALUATION-only use is covered. The project's rule that C-CAP is EVAL-ONLY, never train, may already satisfy it - but that has never been checked against the actual licence text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>King County imagery and derived products</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>King County</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>'Any sale of this map or information on this map is prohibited except by written permission of King County.' SDC records are IsPublic=false; CIR products are 'not yet available in ArcGIS Online'.</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Redistribution restricted; access terms for CIR unknown.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - confirm terms before any King product enters a download list or any output is published.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds imagery</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>City of Edmonds</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>No licence stated anywhere - copyrightText and licenseInfo are EMPTY on every Edmonds imagery service.</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Unknown. The imagery came to Edmonds via a county ILA, so the county's and EagleView's terms may govern.</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - unstated is not the same as unrestricted. The 2021 ILA and the EagleView Authorized Subdivision Agreement (executed 2021-03-22) are the documents to read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County imagery</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Snohomish County</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>'More recent imagery may not be distributed doe [sic] to contractual terms.'</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Explicit acknowledgement that some years are restricted - but which years is not stated.</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM - ask which years before re-acquiring 2016/2021 at full extent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>NAIP / NOAA Digital Coast / USGS lidar</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>USDA / NOAA / USGS</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Federal public-domain products.</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>No restriction found.</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>LOW - the cleanest sources in the inventory.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30168,963 +34251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="74" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Claim that was confidently held</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Corrected</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Where it lived</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>What actually turned out to be true</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>The lesson</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>1936 is an empty shell</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>IMAGERY_FACTS / CHATLOG</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Nine probe windows ALL missed the data. The content band starts 74.8% down the file; a full-extent read shows real photography over 24.4% of the study area.</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Sampling that is not exhaustive can agree nine times and still be wrong. Probe placement is a hypothesis, not a control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>gsd_cm was correct in the catalog</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>phase4seg/config.py</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>gsd_cm was CRS-units x 100. EPSG:2285 is US SURVEY FEET (Snohomish overstated 3.24x); EPSG:3857 inflates 1/cos(47.8)=1.49x.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>A config value is a claim, not evidence. Units are the most common silent defect in this project - it has now happened THREE times (catalog, the CoE service grid, and the '3ft' Ecopia service that is actually 1 m).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>The 2021 pair isolates the sensor effect</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>WORKPLAN 2</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Resolution -&gt; tier -&gt; tiling params are entangled by design, so sensor and tiling regime cannot be separated in that pair.</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>WITHDRAWN and must not be resurrected. The 2026-08-22 county inventory does NOT revive it - no same-tier same-year pair exists after true-GSD correction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>King County's export plateaus at ~20 cm</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>this session</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>A controlled test (312 m box, 4096 px vs 1024 px upsampled to the same grid) gives 2.16x the HF energy for the native request; the cache reaches LOD 21 ~ 5.0 cm ground.</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>The laplacian-falloff proxy was measuring JPEG smoothing, not a resolution ceiling. A proxy metric needs its own validation before it is trusted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Class 4 IS 'Developed Impervious under Tree Canopy'</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>IMAGERY_FACTS 9.3</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>PRESENCE is measured (480,208 px = 2.40% of valid, decimated read). MEANING is INFERRED - no RAT for the held clip has been read by anyone.</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Corrected in the authoritative facts document after cross-session review. Writing an inference as a measurement is the same error class as the defect it describes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>The class-4 fix moves both precision AND recall</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>cross-session</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Precision rises. RECALL'S DIRECTION IS NOT PREDICTED - the denominator grows ~2.4 pp while the numerator grows only by class-4 pixels the model already calls canopy, so recall may FALL.</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Both outcomes are consistent with the fix being correct. State direction AND magnitude before measuring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>The 2013 re-score will move the number materially</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>loop prompt</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>It moved 0.0004 (off-recipe .7395 vs citywide .7399).</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>The long-quoted .7422 was UNDER-EVIDENCED (live=0, fallback threshold), not INACCURATE. Those are different failures. A prediction stated confidently and falsified is worth more than one never written down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>B ~ aR+bG+c with high R2 detects a synthesised band</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>this session's own spec</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>On the KNOWN-SYNTHETIC control (2000) it returns R2=0.9545 - LOWER than 2005 (.9766) and 2002 (.9628), which have real blue. The specified detector would have cleared the one file known to be fake.</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>A detector must be validated against a positive control BEFORE it is applied. The working form is relative: normalise each band's unexplained variance given the other two, then compare blue's to red's and green's.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2000 has 'a false blue' (i.e. RGB with one synthesised channel)</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>this session</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Understated. The Kodak DSC460CIR received NO blue light at all, and ALL THREE filter elements pass NIR: blue = NIR only, green = green+NIR, red = red+NIR. It is a colour-infrared sensor.</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>The first framing was directionally right and materially wrong. 2000 cannot be treated as an RGB acquisition at all.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Snohomish 2016 and 2021 are comparable (identical grid)</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>implicit</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Byte-identical grid geometry, but effective resolution differs 1.7x: 2016 = 2.32x oversampled / 35.4 cm; 2021 = 1.35x / 20.6 cm.</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Identical grid does NOT imply identical resolution. Any 2016-vs-2021 change detection sees a resolution step.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>The statewide Ecopia product is a third INDEPENDENT reference</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>CHATLOG / this session</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>It shares its extraction vendor AND algorithm (Ecopia AI) with the C-CAP v2 reference it was meant to be independent of.</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>See the Reference_Independence sheet. Agreement between two Ecopia products is not corroboration.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E12"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="84" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="84" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Headline measurement</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Scope / sample</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Validation or control</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Limits, and what would overturn it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Effective resolution (all 20 files)</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Edge-response rise time, esf()/rise_px() COPIED VERBATIM from Scripts/litwatch_scratch/q138b.py - the script that produced the IMAGERY_FACTS 2.2 table</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>5 fixed land sites, each a 200 m x 200 m ground box, plus a native 512x512 box with origin snapped to an absolute multiple of 16 so in-window phase == absolute phase. Sites (WGS84): S1_forest_nw 47.8225,-122.3580 (86% forest); S2_parking 47.8060,-122.3270 (94% developed); S3_residential 47.8100,-122.3700; S4_forest_s 47.7855,-122.3545; S5_suburb_ne 47.8250,-122.3400. All confirmed LAND against C-CAP 2016. All inside the intersection of all 20 footprints.</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>REPRODUCED the 10 published King oversampling values at Pearson r=0.997 (2000 2.68 vs 2.8; 2005 3.92 vs 4.0; 2007 1.28 vs 1.3).</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>5 sites is not the city. CoE per-site sd is +/-0.41-1.17 px (vs +/-0.02-0.08 for well-behaved King years) - CoE numbers are INDICATIVE, not settled. Would be overturned by: a citywide pass, or sites chosen in different land-cover mixes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Class 4 = 2.40% of valid pixels</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Decimated bincount</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>4000-row decimated read of the CLIPPED ccap_2021_hires_lc.tif</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Count zero in the 2016 file by the same method.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>APPROXIMATE and scoped to that clip's extent - NOT a property of the v2 product generally. Would be overturned by a full-raster count, or by the same count over the full-coverage file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>JPEG 8x8 block grid under a DEFLATE tag</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Mean |first difference| profile mod 8, both axes, per band per site; mod-32 profile to confirm period 8 not 4 or 16</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>All 16 King+CoE files; 15/15 band-site-axis combinations agree (14/15 for 2000 v-axis, 2023 h-axis); mean z from 4.32 to 16.98; boundary/within ratios 1.07-1.36</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>The 4 Snohomish/NAIP files show NO phase-7 signature - a built-in negative control.</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>INFERENCE (labelled as such by the measurer): because the block grid is phase-locked to the delivered EPSG:3857 grid rather than smeared by resampling, the JPEG stage most likely happened ON this grid. Would be overturned by finding a lossless original that still shows the signature.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>The greenness drift is red brightening</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Per-band means over the same 5 fixed windows, all King years</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>R 100.9 (2000) -&gt; 136.2 (2023) = +35%; G 115.3 -&gt; 134.2 = +16%; B 117.4 -&gt; 105.2 = -10%. G-R collapses +14.4 -&gt; -6.0 DN.</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>frac(GRVI&gt;.02) reproduced the published series on DIFFERENT sites (2000 .8208 vs .8027; 2013 .3267 vs .3463; 2019k .0640 vs .1146).</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Reproduction on different sites is the strongest validation available here. Would be overturned by: a site set with different land-cover balance giving a different sign.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>2016 Snohomish blue misregistration 0.224 px</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Sub-pixel band registration</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Every other file in the archive is 0.0001-0.019 px; 2021_snoh is 0.012 px. So 2016 is 20-200x larger than any other file.</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Corroborated independently by blue's edge rise (3.22 px vs 2.32 red / 2.33 green) and its HF power (0.53-0.59x green's).</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Three independent measurements agree. Strong. Would be overturned by the offset appearing at only one site - it does not.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>The 2020 anchor's flight window</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>DOCUMENTARY, not measured</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Signed Edmonds-SnoCo ILA names the 2020 EagleView regional project; county SCOPI gives that project's window as 2020-04-13 to 07-13</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>THE FINAL LINK IS INFERENTIAL - no Edmonds document states a date. Would be CONFIRMED by: EagleView CONNECTExplorer per-image dates (Edmonds owns up to 10 accounts), a neighbouring city's un-mosaicked copy, or a county flight index. Would be OVERTURNED by evidence the AOI is multi-date.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E7"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Source A</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Source B</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Source C</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>2015 flight date</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Apr 8/9/17 2015 at 0.225 ft (2.7 in) - GeoTerra consortium photo centres, which is what Edmonds signed and paid for (6/23/2015, $3,696.21)</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Feb 15 - Mar 8 2015 - King County Pictometry frames over Edmonds</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Aug 7 2015 at 4.8 in - per the 2019 Urban Forest Management Plan</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>UNRESOLVED</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Most likely: canopy-assessment imagery is NOT the same dataset as the city's basemap orthophoto. Resolve before any 2015 tier decision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>2017 imagery source</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>PlanIt Geo did 2017 flyovers for Pierce/Snohomish/King as part of stormwater modelling (Edmonds council minutes 2023-07-25 p.15, Urban Forest Planner)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>King County per-frame evidence puts imagery over Edmonds at 2017-05-04 to 05-10</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>The inferred King window is 2017-02-17 to 2017-10-30 (8.5 months)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>MINUTES ARE WEAK</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>The minute conflates collector with analysis consultant; PlanIt Geo is an analytics firm, not an imagery acquirer. Does not override per-frame evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>NAIP is leaf-on by specification</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>IMAGERY_PLAN A4 and several CHATLOG entries assert it</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>BOTH WA NAIP flights over Edmonds are OCTOBER: 2019-10-11 and 2023-10-07</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>ASSERTION WEAKENED</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>October in western Washington is late season. The leaf-on assumption should not be carried without evidence for these specific dates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>2000 accuracy</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>CE90 4 m stated, 'worse in the northern third of the project area' - which is where Edmonds sits</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Orthorectified to a 10 m DEM, by far the coarsest in the King series</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>CONSISTENT but poor</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Not a contradiction - a compounding weakness. 2000 is the least reliable geometry in the archive AND the most radiometrically anomalous.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>'3 ft' vs 1 m naming</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>The WA statewide Ecopia service is named '3ft' and reports pixelSizeX 3.28084</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Its CRS is EPSG:2927, US SURVEY FEET, so 3.28084 ftUS = exactly 1.000 m</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>RESOLVED - it is a 1 m product</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>A THIRD instance of the units trap. Service names are not resolutions.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="84" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Product family</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Rights holder</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Verbatim restriction</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>What it means here</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Risk and action</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Ecopia-derived products (C-CAP v2 hi-res, statewide Ecopia land cover, the 'Initial' canopy layer)</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Ecopia Tech Corporation</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>'...otherwise leverage the product for the purposes of machine learning for a period of five years from its date of creation, except with the express written consent of Ecopia Tech Corporation.'</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>*** FLAT PROHIBITION ON ML USE *** - and one version carries NO qualifier limiting it to 'creating similar land cover data'. THIS IS A MACHINE LEARNING PROJECT.</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>HIGH - resolve before these products are used for training, and check whether EVALUATION-only use is covered. The project's rule that C-CAP is EVAL-ONLY, never train, may already satisfy it - but that has never been checked against the actual licence text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>King County imagery and derived products</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>King County</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>'Any sale of this map or information on this map is prohibited except by written permission of King County.' SDC records are IsPublic=false; CIR products are 'not yet available in ArcGIS Online'.</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Redistribution restricted; access terms for CIR unknown.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM - confirm terms before any King product enters a download list or any output is published.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>City of Edmonds imagery</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>City of Edmonds</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>No licence stated anywhere - copyrightText and licenseInfo are EMPTY on every Edmonds imagery service.</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Unknown. The imagery came to Edmonds via a county ILA, so the county's and EagleView's terms may govern.</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM - unstated is not the same as unrestricted. The 2021 ILA and the EagleView Authorized Subdivision Agreement (executed 2021-03-22) are the documents to read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Snohomish County imagery</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Snohomish County</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>'More recent imagery may not be distributed doe [sic] to contractual terms.'</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Explicit acknowledgement that some years are restricted - but which years is not stated.</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>MEDIUM - ask which years before re-acquiring 2016/2021 at full extent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>NAIP / NOAA Digital Coast / USGS lidar</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>USDA / NOAA / USGS</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Federal public-domain products.</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>No restriction found.</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>LOW - the cleanest sources in the inventory.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31893,7 +35020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32168,7 +35295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32881,7 +36008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36160,7 +39287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43174,7 +46301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43464,379 +46591,4 @@
   <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="74" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="66" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Base URL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Download allowed</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Request limits</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Snohomish County imagery</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>ArcGIS ImageServer x23</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>exportImage (native res)</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>15000 x 4100 px/request; ExportTilesAllowed false</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Capabilities Catalog,Image,Metadata. Pixel sizes in FEET (EPSG:2285)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>King County basemaps</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>https://gismaps.kingcounty.gov/arcgis/rest/services/BaseMaps</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>cached MapServer x15 (1936-2025)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>/export works (undocumented)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>4096 x 4096 px/request</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>singleFusedMapCache, 24 LODs, format MIXED = lossy JPEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>King County data catalog</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>https://www5.kingcounty.gov/sdc/?Layer=&lt;NAME&gt;</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>metadata pages + FTP/Open Data</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>yes - originals</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>PREFERRED for King originals incl. CIR. Downloads via gis-kingcounty.opendata.arcgis.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WA statewide public imagery</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>https://imagery-public.watech.wa.gov/arcgis/rest/services</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>ArcGIS server; folders County/ImageServices/LandCover/Municipality/NAIP/Regional/Utilities/WSDOT</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Download capability on Ecopia</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>15000 x 4100; 2048 MB download cap</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>LandCover holds only Ecopia; ImageServices empty; County has SnohomishCo 2002 + 2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WA Geoservices hub</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>https://geo.wa.gov/datasets/</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>ArcGIS Hub</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>varies - see item licenseInfo</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Best licence metadata. Item API: arcgis.com/sharing/rest/content/items/&lt;id&gt;?f=json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>NOAA Digital Coast imagery</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Azure blob, static</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>yes - direct files</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>NAIP WA 2015/2017/2021 with tileindex + urllist + VRT + STAC. Cleanest path of all</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>NOAA C-CAP high-res bulk</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>https://ocmgeodatastor1.blob.core.windows.net/ccap/bulk_download/C-CAP_High-Resolution_Data/</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Azure blob, static</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>yes - direct files</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Refined_.../CONUS holds wa_puget_2021_ccap_v2_hires_landcover.tif (1.43 GB). Also Initial_... Water/Impervious families</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>NOAA C-CAP BETA derived</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>https://coastalimagery.blob.core.windows.net/ccap-landcover/CCAP_bulk_download/BETA_Derived_Land_Cover/</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Azure blob, static</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Land Cover 10m / Percent Canopy 30m / Percent Impervious 30m. Too coarse for crown work</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>NOAA lidar bulk</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>https://noaa-nos-coastal-lidar-pds.s3.amazonaws.com/laz/geoid18/</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>AWS S3, static</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>yes - direct files</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>2005 PSLC = 2579; 2016 USGS West WA = 6331. COPC allows HTTP bbox reads without full download</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>NOAA InPort (metadata)</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.fisheries.noaa.gov/inport/item/&lt;id&gt;</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>metadata catalogue</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>50149 = 2005 PSLC; 51853 = 2016 USGS; 57099 = 10m BETA; 57108 = 30m impervious BETA</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F11"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -12156,7 +12156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>Acquisition period was Summer, 1998. Individual frame or tile acquisition dates are not available.</t>
+          <t>Acquisition period was Summer, 1998.  Individual frame or tile acquisition dates are not available.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Emerge Inc. via King County GIS (IMAGE_Ortho2000EmergeNAT, natural-colour DERIVATIVE of EmergeCIR)</t>
+          <t>Emerge Inc. (contracted via Pacific Meridian / Space Imaging) via King County GIS (IMAGE_Ortho2000EmergeNAT, natural-colour DERIVATIVE of EmergeCIR)</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -12527,17 +12527,17 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>late spring to early fall 2000</t>
+          <t>2000-06-26 (the township block containing Edmonds: T27N R3E / T27N R4E, per King County's flight-date graphic)</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>season (~5 months)</t>
+          <t>single day (township-block generalisation, NOT per-frame)</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>multi (township-level flight-date graphic referenced by the page is a 404)</t>
+          <t>single date for the Edmonds block per the graphic; project is multi-date (2000-05-24 to 09-23)</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -12547,17 +12547,17 @@
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2000EmergeNAT</t>
+          <t>https://web.archive.org/web/20081010173648if_/http://www.metrokc.gov/gis/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>collected in lat spring to early fall 2000 [sic]. Detailed photodate information is not available.</t>
+          <t>2000-06-26 (callout label on the peach block containing cells t27r03, t27r04, t27r05, t28r04, t28r05). The live SDC page: 'Detailed photodate information is not available. A general overview at the township-level for data capture dates can interpolated from https://www5.kingcounty.gov/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg'</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Sensor Kodak DSC460CIR: no blue light recorded, all three held bands NIR-contaminated (Retractions). Wayback target for an agent: https://www5.kingcounty.gov/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg (404 live).</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). The graphic 404s live; the ONLY Wayback capture (CDX domain search on metrokc.gov, capture 20081010173648) was read by the agent and re-read by the session lead (qc/imagery_date_evidence/king2000/). Edmonds township identity from BLM PLSS (T27N R03E at -122.3775,47.8107; T27N R04E at -122.3150,47.8100). Per-tile YYYYMMDD dates once existed in vendor filenames but King renamed tiles to tileXX.tif; the surviving index is emerge_nat.dbf. Sensor Kodak DSC460CIR: 'Blue light is outside the filter's bandpass, so that none of the incident blue light reaches the sensor' (archived EmergeCIR FGDC).</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
@@ -12565,9 +12565,21 @@
           <t>grid/true MEASURED; effective MEASURED (Effective_Resolution); native PUBLISHED</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
-      <c r="T4" s="1" t="inlineStr"/>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>2000-05-24 to 2000-09-23 (countywide project window, Currentness_Reference: Acquisition date)</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20040102162255if_/http://www.metrokc.gov/gis/sdc/raster/ortho/Ortho2000EmergeCIRMetadata.html</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>Time_Period_of_Content: Time_Period_Information: Range_of_Dates/Times: Beginning_Date:  20000524 Ending_Date:  20000923 Currentness_Reference:  Acquisition date</t>
+        </is>
+      </c>
       <c r="U4" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -12587,7 +12599,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>USGS High Resolution Orthoimagery Seattle/Tacoma 2002 (Selkirk Remote Sensing) as retiled by King County (IMAGE_Ortho2002USGSNAT)</t>
+          <t>USGS High Resolution Orthoimagery, Seattle/Tacoma 2002 (Homeland Security; flown by Selkirk Remote Sensing) as retiled by King County (IMAGE_Ortho2002USGSNAT)</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -12617,62 +12629,62 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>33 acquired, delivered at 30.48 (1 ft)</t>
+          <t>33 acquired; delivered grid 0.98 ft = 29.9-30.0 cm (NOT 30.48): tile names '_02n098' = 98/100 ft; WA state copy LowPS 0.9846 ftUS = 30.01 cm</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
+          <t>NOT FOUND for the Edmonds pixels. CONTESTED product-level date 2002-06-11 (two named Selkirk frames near Bellevue, ~24 km south)</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>NOT FOUND</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
-        </is>
-      </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002USGSNAT</t>
+          <t>https://web.archive.org/web/20040225060658if_/http://www.metrokc.gov/gis/sdc/raster/ortho/Ortho2002USGSNATMetadata.html</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>(no acquisition statement on the page; catalog LastUpdated 2003-01-01 is maintenance metadata)</t>
+          <t>Description_of_Geographic_Extent: WRIA 8 Bounding_Coordinates: West_Bounding_Coordinate:  -122.05233309 East_Bounding_Coordinate:  -122.03790177 North_Bounding_Coordinate:  47.60259646 South_Bounding_Coordinate:  47.58876645</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Over Edmonds the cache serves the USGS/NGA Seattle-Tacoma product, NOT IMAGE_Ortho2002KCNAT (which is 'acquired in July 2002' but covers the county-only project). AGENT TARGET: USGS HRO Seattle/Tacoma FGDC metadata (EarthExplorer / TNM / Wayback) carries the per-project acquisition dates.</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 18. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). The live SDC page for this layer returns HTTP 500 (2026-08-23, 3 attempts) - cite the archived FGDC. Over Edmonds the cache serves the USGS/NGA Seattle-Tacoma product, NOT IMAGE_Ortho2002KCNAT ('acquired in July 2002', county-only project). The archived FGDC's top-level block self-labels 'Beginning_Date: 20020611 Ending_Date: 20020611 Currentness_Reference: Publication date', while its lineage block labels the same date 'Aerial photography used in orthorectification' for frames 1192_6574_089 / 1193_6574_090 and 'Field control and ABGPS' 20020611-20020620. No per-frame or per-township index exists for 2002 (CDX sweep of both King hosts: the 2000 graphic is the only flight-date graphic ever published). HRO is retired from The National Map; ScienceBase has no project record. Remaining route: EarthExplorer HRO entity-level FGDC (M2M login).</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (REST description: 'acquired at a resolution of 0.33 meter per pixel ... resampled to 1 foot per pixel')</t>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (archived FGDC + WA state service)</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>July 2002 (sibling product IMAGE_Ortho2002KCNAT — does NOT serve Edmonds)</t>
+          <t>2002-06-11 (product-level; CONTESTED currentness - see notes)</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2002KCNAT</t>
+          <t>https://web.archive.org/web/20040225060658if_/http://www.metrokc.gov/gis/sdc/raster/ortho/Ortho2002USGSNATMetadata.html</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr">
         <is>
-          <t>Natural color orthophotography acquired in July 2002</t>
+          <t>Source_Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date:  20020611 Source_Citation_Abbreviation:  1192_6574_089 Source_Contribution:  Aerial photography used in orthorectification</t>
         </is>
       </c>
       <c r="U5" s="1" t="inlineStr">
@@ -12739,7 +12751,7 @@
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>unknown (no per-frame index exists before 2007)</t>
+          <t>unknown (no per-frame index exists before 2007; no finer date exists in King County's archive - established by CDX sweep, not assumed)</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -12749,27 +12761,39 @@
       </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
+          <t>https://web.archive.org/web/20061008084602if_/http://www.metrokc.gov/gis/sdc/raster/ortho/Ortho2005AexpNatMetadata.html</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>Time_Period_of_Content: Time_Period_Information: Range_of_Dates/Times: Beginning_Date:  200507 Ending_Date:  200507 Currentness_Reference:  Ground Condition</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Held grid 20.1 cm vs 1 ft native = 1.5x oversampled, and the file resolves at 80.7 cm - coarser than 2000's nominal grid. Delivery (Aug 2006, portable hard drive) is NOT the flight date. The record's Bounding_Coordinates (North 47.74) are JUNK and would exclude Edmonds; the published extent graphic (Ortho2005AexpNatExtent.jpg, archived) shows Edmonds inside coverage.</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>July 2005</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
           <t>https://www5.kingcounty.gov/sdc/?Layer=IMAGE_Ortho2005AerialsExpressNAT</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="T6" s="1" t="inlineStr">
         <is>
           <t>Year 2005 (July)</t>
         </is>
       </c>
-      <c r="P6" s="1" t="inlineStr">
-        <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). Held grid 20.1 cm vs 1 ft native = 1.5x oversampled, and the file resolves at 80.7 cm — coarser than 2000's nominal grid.</t>
-        </is>
-      </c>
-      <c r="Q6" s="1" t="inlineStr">
-        <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
-        </is>
-      </c>
-      <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
-      <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -12849,12 +12873,12 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>SHOTDATE field, 1078 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>SHOTDATE field, 1078 frames intersecting the city polygon (query 2026-08-23; refetch-verified: field exists, all six days non-zero countywide)</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. SDC page: 'Final version 2007 (July)' — the August frames show 'July' is a simplification.</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. SDC page: 'Final version 2007 (July)' - the August frames show 'July' is a simplification.</t>
         </is>
       </c>
       <c r="Q7" s="1" t="inlineStr">
@@ -12956,7 +12980,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>SHOTDATE/YYYYMMDD fields, 472 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>SHOTDATE/YYYYMMDD fields, 472 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -13026,7 +13050,7 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>2012-03-23 (30 photo centres, 13:25-13:44) and 2012-04-07 (45 photo centres, 12:08-12:46)</t>
+          <t>2012-03-23 (30 photo centres in the city, 13:25-13:44 local) and 2012-04-07 (45 photo centres, 12:08-12:46 local)</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
@@ -13036,7 +13060,7 @@
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>MULTI (2 days)</t>
+          <t>MULTI (2 days) - and the split is MEASURABLE per location: north Edmonds = Mar 23 geometry (6/7 sites), south Edmonds includes Apr 7 geometry (shadow solar dating, qc/imagery_date_evidence/shadow_dating_2020/ctrl_scored.csv)</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -13056,7 +13080,7 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Leaf-off to barely budding. Countywide window PUBLISHED on the SDC page (alt). Index RESOLUTION field = 1 (Apr 7) / 2 (Mar 23), units not stated.</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 19. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Leaf-off to barely budding. Index times are LOCAL (13:35 UTC would put the sun below the horizon). Over the wider bbox the windows are 13:25-13:46 (Mar 23, n=61) and 11:51-13:11 (Apr 7, n=184). Index RESOLUTION field = 1 (Apr 7) / 2 (Mar 23), units not stated. Used as the POSITIVE CONTROL for shadow-geometry dating: 8/10 sites recovered an azimuth inside a real flight window (chance 0.197, P=6.9e-5).</t>
         </is>
       </c>
       <c r="Q9" s="1" t="inlineStr">
@@ -13158,7 +13182,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 688 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate/YYYYMMDD fields, 688 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -13253,12 +13277,12 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 701 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate/YYYYMMDD fields, 701 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. LEAF-OFF. This held file is the Pictometry KCNAT product; the three-way 2015 CONTEST (Apr 8/9/17 GeoTerra 2.7 in / Aug 7 4.8 in UFMP) belongs to the City of Edmonds 2015 SERVICE, a different product — see the CoE 2015 row.</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. LEAF-OFF. This held file is the Pictometry KCNAT product and is PIXEL-DISTINCT from the City of Edmonds 2015 basemap (tile correlation r=0.04-0.56 at 5 sites vs 0.99 control) - the 2015 CONTEST belongs to the CoE service row, not here. Weather note: 2015-02-15 was flown (CLR, 10 sm all day) with a maximum solar elevation of only 29.3 deg - a 30-deg sun floor is falsified by a known flight day.</t>
         </is>
       </c>
       <c r="Q11" s="1" t="inlineStr">
@@ -13348,12 +13372,12 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 710 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate/YYYYMMDD fields, 710 frames intersecting the city polygon (query 2026-08-23; an independent re-query returned 695, all 15 missing on May 10 - residual geometry handling, same days)</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Resolves the May 18 discrepancy in MASTER: May 18 frames (n=215) fall inside the wider bbox -122.42,47.76,-122.32,47.87 but outside the city polygon. Countywide capture window 2017-02-17 to 2017-10-30 (PUBLISHED, SDC index change history).</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. Resolves the May 18 discrepancy in MASTER: May 18 frames (n=215) fall inside the wider bbox -122.42,47.76,-122.32,47.87 but outside the city polygon. Countywide capture 'from mid-February through October of 2017' (gisandyou.org, King County GIS). Frame counts track flyable hours (May 4 fog until 09:53 + afternoon thunderstorm -&gt; n=16; May 9/10 clear 08:53-16:53 -&gt; n=192/364). This file is the SAME ORTHOMOSAIC as 2017_coe_rgb.tif (see that row).</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
@@ -13443,7 +13467,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field (date only, no time), 1234 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate field (date only; the layer carries Time_UTC/Time_PDT separately), 1234 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -13538,7 +13562,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field, 662 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate field, 662 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -13633,12 +13657,12 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field, 1125 frames intersecting the city polygon (query 2026-08-23)</t>
+          <t>ShotDate field, 1125 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which.</t>
+          <t>Held pixels are an export of the KingCo_Aerial_YYYY ArcGIS tile cache (gismaps.kingcounty.gov), EPSG:3857, JPEG-quantised; grid is exactly Web-Mercator LOD 20. In-file metadata: NONE (sweep 2026-08-23: no DateTime/Software/XMP/IPTC/EXIF/GDAL_METADATA in any held raster). MEASURED 2026-08-23: King County public nadir-frame index queried with the Edmonds city POLYGON (City Boundry/Edmonds Boundry.shp, esriSpatialRelIntersects); counts are frames intersecting the city, not the mosaic's seam assignment. Which frame feeds each mosaic pixel is NOT recorded, so the mosaic over any given crown is one of these days, unknown which. A 2025 index (ORTHO_IMAGE25_AREA_3074, 'Index to 2025 Pictometry nadir images', 3 in west / 6 in east) now exists on the same org and was NOT queried over Edmonds - a follow-up would date 2025 the same way.</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
@@ -13680,7 +13704,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Hexagon Imagery Program (HXIP) via Snohomish County Imagery/Aerial_2016 ImageServer</t>
+          <t>Hexagon Imagery Program (HXIP; 'Seattle' Urban Area Coverage tier of the WA Statewide Imagery Consortium) via Snohomish County Imagery/Aerial_2016 ImageServer (mosaic gdb HXIP_2016_SNOHOMISH.gdb)</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -13710,22 +13734,22 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>30.48 (1 ft): county mosaic-catalog LowPS=1 and item pixelSizeX=1 for every primary tile over Edmonds (MEASURED 2026-08-23); the 2016 consortium 6-in (15 cm) buy-up exists over Edmonds but is NOT what the county serves</t>
+          <t>30.48 (1 ft): county mosaic-catalog LowPS=1 and item pixelSizeX=1 for every primary tile over Edmonds (MEASURED); the consortium's 15 cm (6 in) 2016 product exists over Edmonds but the county serves a 1-ft delivery</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>2016-08-11 (16:52) and 2016-08-12 (09:05, 09:30) — WA consortium 2016 6-in footprints over Edmonds</t>
+          <t>2016-08-12 morning (consortium sorties 09:05 / 09:30 PDT; a 09:50 sortie also lies within the city bbox) - CONDITIONAL on the county 1-ft product being the same flight as the dated 15 cm consortium product. The 2016-08-11 16:52 sortie is EXCLUDED for the held extent (shadows point WNW = morning sun)</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>window of 2 days, 3 sorties</t>
+          <t>window of 2 days by the consortium labels (Aug 11-12); held pixels consistent with Aug 12 only</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>MULTI (2 days / 3 sorties over the city; footprint = quarter-quarter quads)</t>
+          <t>consortium labels: MULTI (2 days, 3-4 sorties over the city); held file: shadow azimuth uniformly morning (283-295 deg over 24 windows, R=1.00) - consistent with a single morning, single date NOT proven</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -13740,12 +13764,12 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>SDATE '08/11/2016 16:52' (SUNEL 31) / '08/12/2016 09:05' (SUNEL 34) / '08/12/2016 09:30' (SUNEL 37), THEMENAME hxip_m_4712213/4712214_*_10_15, 11 footprints intersecting the city bbox</t>
+          <t>SDATE '08/11/2016 16:52' (SUNEL 31) / '08/12/2016 09:05' (SUNEL 34) / '08/12/2016 09:30' (SUNEL 37), THEMENAME hxip_m_4712213/4712214_*_10_15; city-centroid point query returns hxip_m_4712213_se2_10_15, SDATE '08/12/2016 09:30', SUNEL 37, ACCURACY '0.68m (ce 95%)'</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>Held file = export of the county service (window means identical to exportImage, 2026-08-23) and pixel-DISTINCT from Aerial_2015 and Aerial_2017. Why INFERRED not PUBLISHED: the dated footprints are the 15 cm consortium product; the county's 1-ft tiles are a different delivery of (presumably) the same flight — the county mosaic was built from a geodatabase literally named HXIP_2015_Snohomishv3 (service /info/metadata lineage), so the 2015-08-07 HXIP 1-ft flight was a live alternative until the pixel test excluded it. OPEN: held-file shadows in the footprint labelled 16:52 point WEST (morning), so either that SDATE is UTC (=09:52 PDT) or the county product is a different sortie. Geocortex blurb 'acquired in August 2016' is mis-titled '2017 Aerial Photos'.</t>
+          <t>Held file = export of the county service (window means identical to exportImage) and pixel-DISTINCT from Aerial_2015 and Aerial_2017 (MEASURED). SDATE is LOCAL clock time: a 7034-footprint fit of published SUNEL vs pvlib gives RMSE 6.9 deg for UTC-7 vs 55.6 for UTC, and 09:05 read as UTC puts the sun 26 deg below the horizon. The county gdb is HXIP_2016_SNOHOMISH.gdb (the 'HXIP_2015' tokens in the lineage are a stale parent-folder / dataset-name carry-over, not 2015 imagery); the 2015-08-07 flight is excluded three ways (pixel comparison, afternoon vs morning shadows, lineage). 6-in coverage reached Edmonds because it lies inside the Valtus/Hexagon 'Seattle' UAC polygon, not via a county buy-up. The Geocortex blurb 'acquired in August 2016 as part of a Washington Statewide Imagery consortium. Pixel size of the raster is 6 inch' sits on a layer titled '2017 Aerial Photos' and contradicts the county's 1-ft tiles - CONTESTED, month-level corroboration only. Both Aug 11 and Aug 12 2016 were flyable at all three ASOS stations (Aug 11 morning marine stratus at KPAE only). C-CAP 2016 Snohomish (InPort 53263) says its source imagery is 'NAIP ... summer 2016' but no WA NAIP 2016 exists - most plausibly this HXIP flight. Held file is a study-area CROP (lon -122.404..-122.316, lat 47.783..47.828).</t>
         </is>
       </c>
       <c r="Q16" s="1" t="inlineStr">
@@ -13755,7 +13779,7 @@
       </c>
       <c r="R16" s="1" t="inlineStr">
         <is>
-          <t>2015-08-07 15:31 (HXIP 2015 1-ft flight; EXCLUDED by pixel comparison against Aerial_2015)</t>
+          <t>2015-08-07 15:31 (HXIP 2015 1-ft flight = the NAIP 2015 delivery; EXCLUDED for this file)</t>
         </is>
       </c>
       <c r="S16" s="1" t="inlineStr">
@@ -13787,7 +13811,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>HXIP via Snohomish County Imagery/Aerial_2021 ImageServer</t>
+          <t>HXIP via Snohomish County Imagery/Aerial_2021 ImageServer (mosaic gdb HXIP_2021_SNOHOMISH.gdb - a Hexagon delivery, not EagleView)</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -13827,12 +13851,12 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>window of 140 days</t>
+          <t>window of 140 days (weather trims to 108 feasible days; 18 late days never reach 30 deg sun)</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>unknown (countywide window only)</t>
+          <t>unknown; held crop flown in the AFTERNOON (shadow azimuth 67-91 deg = sun at 247-256 deg, uniform over 24 windows) - a time-of-day constraint, not a date</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -13852,7 +13876,7 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>AGENT TARGET: a WA consortium 2021 flight-date footprint layer (as exists for 2015-2020) would narrow this to days. Service metadata carries no date (sweep 2026-08-23).</t>
+          <t>CLOSED LEADS: no WA consortium flight-date layer exists for 2021 or later (all 68 WAGeoservices services + 225 items enumerated; series ends 2020); the mosaic-catalog schema has no date field at all; WA NAIP 2021 does not cover quad 47122 (eastern WA only), so no NAIP ride-along date. Remaining route: the Hexagon flight log via Snohomish County DoIT, or the consortium contact (Joanne Markert, WA OCIO). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2021-06-25..11-11): 32 of 140 days eliminated; longest feasible blocks Jul 22-Aug 6, Jul 2-15, Aug 9-19. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
@@ -13882,7 +13906,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2017_Aerial_Cached (source raster 2017_Aerial.tif, 0.25 ftUS EPSG:2285); acquirer NOT ESTABLISHED</t>
+          <t>City of Edmonds Basemap/2017_Aerial_Cached (source raster 2017_Aerial.tif, 0.25 ftUS EPSG:2285, JPEG); CONTENT = King County IMAGE_Ortho2017KCNAT (Pictometry International, 3-in 'Neighborhood' tier covering southwestern Snohomish County) - MEASURED identity</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -13912,52 +13936,64 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS source raster)</t>
+          <t>7.62 (0.25 ftUS source raster; service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS exactly)</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
+          <t>2017-05-04 to 2017-05-10 (5 days over the city: May 4 n=16, May 6 90, May 8 48, May 9 192, May 10 364) - transferred from the King County per-frame index because the two files are the SAME ORTHOMOSAIC</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>window of 7 days, 5 flight days</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
+          <t>MULTI (5 days)</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/0/edoc/1654952/</t>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE17_AREA_2685/FeatureServer/0/query</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>In 2017 flyovers and imagery was done by the consultant who did the public engagement, PlanIt Geo, for Pierce, Snohomish and King Counties as part of a stormwater modeling project.</t>
+          <t>Identity MEASURED 2026-08-23: held 2017_coe_rgb.tif (2x boxcar-downsampled) vs 2017_king_rgb.tif over a 12x12 grid on the city polygon, 66 valid 512-px windows -&gt; r min 0.9568, p5 0.9786, median 0.9923, max 0.9966, MAE median 3.54 DN; live services 2017_Aerial_Cached vs KingCo_Aerial_2017 LOD-20 tiles at 5 sites r = 0.9876-0.9935. Identical vehicles in identical stalls and identical building relief displacement -&gt; same orthorectification, not merely the same flight.</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>The quote (council minutes 2023-07-25 p.15) is WEAK: conflates collector with analytics consultant. Candidate: King County 2017 flight 2017-05-04..05-10 over Edmonds (MEASURED on 2017_king_rgb.tif) — attribution to the city file UNPROVEN; Snohomish Aerial_2017 is a 1-ft HXIP product (2017-08-15/21) and cannot be a 3-in source. AGENT TARGET: 2017 CoE contract/budget line, sibling products, neighbour cities.</t>
+          <t>Retires the 8.5-month candidate window and the council-minutes line (2023-07-25 p.15, 'PlanIt Geo ... 2017 flyovers') as evidence - the 2019 UFMP was written by Davey Resource Group and its canopy work used Aug 2015 imagery; PlanIt Geo appears nowhere in it. No City of Edmonds document naming the 2017 vendor was found; attribution rests on measured pixel identity plus King County's published coverage statement (alt). Snohomish County's own 2017 product is a 1-ft HXIP flight (2017-08-15/21) and cannot be a 3-in source. Grid note: the held grid is exactly LOD 21, which King's tile endpoint does not serve (404 at L21) but Edmonds' does - consistent with a city-service export. Method detail: qc/imagery_date_evidence/coe2017_identity/.</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (service source-raster XML)</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
-      <c r="T18" s="1" t="inlineStr"/>
+          <t>grid/true MEASURED; effective MEASURED; native MEASURED (live service)</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>mid-February through October 2017 (countywide), with SW Snohomish at 3 in</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>https://gisandyou.org/2018/05/25/2017-aerial-imagery-in-imap/</t>
+        </is>
+      </c>
+      <c r="T18" s="1" t="inlineStr">
+        <is>
+          <t>The imagery was captured by Pictometry International Corp. from mid-February through October of 2017. The original photos have a resolution of 3 inches per pixel ("Neighborhood" scale in Pictometry terminology) over urbanized, western King County ... Also covered at the Neighborhood resolution level in the 2017 imagery are southwestern Snohomish County</t>
+        </is>
+      </c>
       <c r="U18" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -13977,7 +14013,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2020_Aerial_Cached; source = Snohomish County 2020 EagleView/Pictometry regional project (WASNOH20_3in) per the 2021 ILA</t>
+          <t>City of Edmonds Basemap/2020_Aerial_Cached (MrSID/MG4 mosaic, GeoExpress 10.0.1.5035, input GeoTIFF set 665,235,977,256 B); source = Snohomish County 2020 EagleView/Pictometry regional project WASNOH20_3in per the 2021 ILA; product identity corroborated by Everett's copy ('Aerial Photos 2020 Pictometry Mosiac 3 inch resolution urban areas', 0.25 ftUS)</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -14007,22 +14043,22 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS; county Aerial_2020 LowCellSize 0.25, dimResol 0.250000 ftUS)</t>
+          <t>7.62 (0.25 ftUS; county Aerial_2020 LowCellSize 0.25, dimResol 0.250000 ftUS; Everett Image2020jp2 pixelSizeX 0.25 in EPSG:2285)</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>2020-04-13 to 2020-07-13</t>
+          <t>2020-04-13 to 2020-07-13 (county window; the single published window is the UNION of the 3-in urban and 9-in rural sub-projects - unlike 2022/2024 the county did not publish them separately). Shadow solar geometry excludes the head: 2020-04-25 to 07-13 survive (80 of 92 days)</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>window of 92 days</t>
+          <t>window of 80-92 days</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>unknown — whether the Edmonds AOI is single- or multi-date is UNRESOLVED and outranks the date</t>
+          <t>CONSISTENT WITH ONE CONTINUOUS PASS, single date NOT PROVEN: 10 QC-passing sites of 34 on a ~850 m city-wide grid give sun azimuths 120.8-192.5 deg = local times ~10:22-13:39 PDT straddling solar noon, increasing monotonically east-to-west (az vs lon r=-0.75, p=0.013; permutation p=0.026) - the signature of successive flight lines in one pass, not of day-blocks. Not excluded: several dates each flown at the same time of day.</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -14042,12 +14078,12 @@
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>Chain: ILA 2021 (Laserfiche id 1462454) Work Order p.14 'Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ... County will provide Edmonds with orthogonal imagery'; city service keyProperties carry NO acquisition date (MrSID/MG4 mosaic lost it). The window is PUBLISHED for the county product; the link to the city file is documented by contract but inferential. DEFINITIVE PIN = EagleView flight log / photo-centre index via Snohomish County DoIT (PRR citing Contract Routing Form No. 20210127) or a CONNECTExplorer capture-date screenshot (city holds up to 10 accounts).</t>
+          <t>ILA 2021 (Laserfiche id 1462454, repo=Edmonds) Work Order p.14: 'Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ... County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest'. Contract vehicle for a records request: King County RFP 1166-18-PCR (EagleView Technology Corp) via Snohomish County Piggyback PB-19-14BC (Legistar matter 2024-1168). DEFINITIVE PIN = EagleView flight log / photo-centre index via Snohomish County DoIT (Viggo Forde), or a CONNECTExplorer capture-date screenshot (Edmonds holds up to ten accounts under the ILA). City keyProperties (correct endpoint &lt;ImageServer&gt;/keyProperties?f=json; /info/keyProperties 400s on this server, positive control Edmonds_Marsh_2018 returns acquisitionStartDate 2018-08-01T16:22:13+00:00 / End 16:52:13) carry NO date: IMAGE__MODIFICATIONS 'COMPRESSED EMBEDDED MASKED MOSAICKED' - a validated null. Everett's 2020 copy is JPEG2000 and also carries no date; no 2020 MrSID twin with a surviving date was found. A per-frame index CANNOT exist on the county service (mosaic catalog = two whole-project items WASNOH20_3in / WASNOH20_9in). HAZARD: a SECOND 2020 acquisition covers Edmonds - the WA consortium 6-in Hexagon/ADS100 flight of 2020-08-27/28 (program window 2020-08-03..09-06) - DO NOT borrow its date (see context row). Shadow dating (qc/imagery_date_evidence/shadow_dating_2020/): azimuth is reliable (2012 control 8/10 in-window), elevation reads LOW and saturates above ~45 deg, so 2020 elevations are lower bounds - hence no calendar date. 2020 ortho co-registered to 2012 within &lt;=1.5 WM m. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2020-04-13..07-13): 22 of 92 days eliminated; longest feasible blocks May 7-15 (9 d), Apr 13-17, May 26-30, Jun 1-5, Jun 22-26. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county + Everett services)</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr">
@@ -14057,7 +14093,7 @@
       </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
@@ -14084,7 +14120,7 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2022_Aerial_Cached; source = Snohomish County 2022 regional project (WASNOH22_3in) per the 2021 ILA</t>
+          <t>City of Edmonds Basemap/2022_Aerial_Cached; = Snohomish County 2022 regional project WASNOH22_3in. IDENTITY MEASURED: the Edmonds and Everett 2022 MrSIDs are the same county encode (identical input-set byte count 675,609,635,568 B, GeoExpress 10.0.1.5035, EPSG:2285 ftUS geokeys)</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -14114,12 +14150,12 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS; county Aerial_2022 LowCellSize 0.25; MrSID input GeoTIFF geokeys EPSG:2285 ftUS)</t>
+          <t>7.62 (0.25 ftUS; county Aerial_2022 LowCellSize 0.25; MrSID input GeoTIFF geokeys 'Linear_Foot_US_Survey' / 2285)</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>2022-04-06 to 2022-07-11 (urban 3 in)</t>
+          <t>2022-04-06 to 2022-07-11 (urban 3 in); the rural 9-in sub-project ran 2022-05-31 to 08-11 and does not apply to Edmonds</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
@@ -14132,9 +14168,9 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -14144,32 +14180,32 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>The 2022 3 inch resolution aerial photos in the urban areas, were captured between April 6, 2022 and July, 11 2022.</t>
+          <t>The 2022 3 inch resolution aerial photos in the urban areas, were captured between April 6, 2022 and July, 11 2022. The 2022 9 inch resolution aerial photos in the rural areas, were captured between May, 31 2022 and August, 11 2022.</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>Same chain and same definitive pin as 2020 (one PRR covers 2020/2022/2024).</t>
+          <t>Upgraded INFERRED -&gt; PUBLISHED 2026-08-23: the window is published for a product whose identity with the held file is now measured (byte-count identity of the input set with Everett's Image2022_3in_sid, 'Aerial Photos 2022 Pictometry Mosaic 3 inch resolution urban areas'), not only contractual. Same definitive pin as 2020 (one PRR covers 2020/2022/2024). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2022-04-06..07-11): 19 of 97 days eliminated (weakest of the four windows - a settled spring); longest feasible block May 16-28 (13 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county + Everett services)</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>(ILA text)</t>
+          <t>(Everett keyProperties - identity proof)</t>
         </is>
       </c>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+          <t>https://gismaps.everettwa.gov/manarcgis/rest/services/Imagery/Image2022_3in_sid/ImageServer/keyProperties?f=json</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ...</t>
+          <t>"IMAGE__ENCODING_APPLICATION":"GeoExpress 10.0.1.5035","IMAGE__FORMAT":"MrSID/MG4","IMAGE__INPUT_FILE_SIZE":"675609635568.000000","IMAGE__INPUT_FORMAT":"GeoTIFF" ... "IMAGE__MODIFICATIONS":"COMPRESSED EMBEDDED MASKED MOSAICKED"</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -14191,7 +14227,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2024_Aerial_Cached (Edmonds2024.sid); source = Snohomish County 2024 regional project (WASNOH24_3in) per the 2021 ILA</t>
+          <t>City of Edmonds Basemap/2024_Aerial_Cached (MapServer over Edmonds2024.sid - no ImageServer, so no keyProperties resource exists); source = Snohomish County 2024 regional project WASNOH24_3in per the 2021 ILA</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -14226,12 +14262,12 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>2024-03-31 to 2024-05-31 (urban 3 in)</t>
+          <t>2024-03-31 to 2024-05-31 (urban 3 in); the rural 9-in sub-project ran 2024-03-16 to 06-09</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>window of 61 days</t>
+          <t>window of 62 days</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -14251,12 +14287,12 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>The 2024 3 inch resolution aerial photos in the urban areas, were captured between March 31, 2024 and May, 31 2024.</t>
+          <t>The 2024 3 inch resolution aerial photos in the urban areas, were captured between March 31, 2024 and May, 31 2024. The 2024 9 inch resolution aerial photos in the rural areas, were captured between March, 16 2024 and June, 9 2024.</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>Same chain and same definitive pin as 2020.</t>
+          <t>Stays INFERRED: no neighbour city holds a 2024 county copy (Everett stops at 2022, Mukilteo at 2019, Lynnwood publishes none), so there is no 2024 analogue of the 2022 byte-identity proof. Same definitive pin as 2020. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2024-03-31..05-31): 18 of 62 days eliminated (29%, strongest of the four); longest feasible block Apr 16-24 (9 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q21" s="1" t="inlineStr">
@@ -14271,7 +14307,7 @@
       </c>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=EdmondsWA</t>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr">
@@ -14298,7 +14334,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds (source raster Ed_Aerial_2015.tif, 0.25 ftUS, LZW)</t>
+          <t>City of Edmonds (source raster Ed_Aerial_2015.tif, 0.25 ftUS EPSG:2285, LZW); content INFERRED = 2015 Western Washington Regional Orthophotography (King County lead, 88 participants; prime GeoTerra, Edmonds frames flown by Valley Air and GeoTerra)</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -14328,52 +14364,64 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS source) — vs 6.86 (0.225 ft, GeoTerra consortium spec) vs 12.19 (4.8 in, UFMP)</t>
+          <t>&lt;= 6.86 flown (MAX_GSD 0.225 ft 'as planned' for all 346 Edmonds frames; two cameras at two altitudes both back-compute to ~6.6-6.9 cm), delivered at the 0.25 ft = 7.62 cm tier (service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS)</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>CONTESTED: 2015-04-08/09/17 (GeoTerra consortium photo centres) vs 2015-02-15..03-08 (King Pictometry) vs 2015-08-07 (UFMP '4.8 in')</t>
+          <t>2015-04-08 (n=135 photo centres in the city polygon; Valley Air, UltraCam X, 14:13-15:04 PDT) and 2015-04-17 (n=32; GeoTerra, UltraCam Xp, 12:54-13:55 PDT). CONTEST largely resolved: the King Pictometry leg is EXCLUDED by pixel comparison, the 'Aug 7 2015' leg is a DIFFERENT dataset (NAIP/HXIP 2015-08-07), leaving the consortium dates; attribution of Ed_Aerial_2015.tif to the consortium remains INFERRED and the UFMP's '4.8 in' figure is unexplained</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 flight days (window of 10 days) for the consortium product</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
+          <t>MULTI - two days, two vendors, two cameras within the city (flightlines 16002-16011 Zone 16 / 13007-13015 Zone 13)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>(see Contradictions sheet; three sources)</t>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE15C_POINT_2574/FeatureServer/0/query</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>{"FILENAME": "13007_57226", "FRAME": 57226, ... "UTC_TIME": "19:35:08", "MAX_GSD__f": 0.225, "USED": "YES", "VENDOR": "GeoTerra", "CAMERA": "UltraCam Xp", "SSN": 10411033, ... "FLIGHTLINE": "13007", "ACQ_DATE": 1429228800000} (photo-centre layer; in-polygon N=167; 'It is a reference for the raw image scans, it is not a index for tiled ortho imagery')</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>Included so the contest stops contaminating the held 2015_king_rgb.tif row. Likely explanation: the UFMP canopy-assessment imagery is a different dataset from the city basemap. Edmonds signed the 2015 consortium agreement 2015-06-23 ($3,696.21).</t>
+          <t>Photo-centre DAYS are MEASURED; binding them to Ed_Aerial_2015.tif is INFERRED via (a) 0.25 ftUS cell size matching the consortium tier, (b) CRS NAD83 SP WA North ftUS, (c) Edmonds named in GeoTerra's participant table and the consortium agreement signed 2015-06-23 ($3,696.21), (d) leaf-off/high-sun spec matching the tiles. NOTE: no Apr 9 frames exist over Edmonds (the catalogue's 'Apr 8/9/17' was wrong); one Mar 26 frame sits just outside the polygon. King leg excluded: CoE 2015 vs KingCo_Aerial_2015 LOD-20 tiles r=0.036-0.557 at 5 sites vs r=0.988-0.994 for the CoE-2017/King-2017 control. 'Aug 7 2015 / 4.8 in' (UFMP 2019 p.26) traces to the Davey Resource Group 2018 UTC Assessment which names 'USDA, Farm Service Agency' = NAIP 2015 (2015-08-07, 1 m = the same Hexagon flight as the HXIP 1-ft consortium product); '4.8 in' matches no known 2015 product. Phenology caveat from the project's own survey report: 'the need to begin immediate image acquisition due an earlier than normal bud break' - Apr 8/17 is late in a leaf-off window. Vendor/camera cross-validated at serial-number level against the Flight Subcontractor PDF (UCX 60418665 / UCXp 10411033).</t>
         </is>
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>grid PUBLISHED (service); native PUBLISHED (source-raster XML)</t>
-        </is>
-      </c>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
+          <t>grid MEASURED (live service); native MEASURED (index MAX_GSD) + PUBLISHED (tier)</t>
+        </is>
+      </c>
+      <c r="R22" s="1" t="inlineStr">
+        <is>
+          <t>2015-08-07 15:31 (UFMP/Davey 'August 7th, 2015' imagery = NAIP/HXIP 2015, NOT the city basemap)</t>
+        </is>
+      </c>
+      <c r="S22" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2015/wa_fgdc_2015/47122/m_4712214_sw_10_1_20150807.txt</t>
+        </is>
+      </c>
+      <c r="T22" s="1" t="inlineStr">
+        <is>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20150807 Currentness_Reference: Ground Condition</t>
+        </is>
+      </c>
       <c r="U22" s="1" t="inlineStr">
         <is>
           <t>context (not held)</t>
@@ -14393,7 +14441,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>USDA FSA NAIP WA 2019 (DOQQ m_4712213/m_4712214; flown by Hexagon under the 2019 program)</t>
+          <t>USDA FSA NAIP WA 2019 (DOQQ m_4712213/m_4712214; the WA consortium 2019 1-ft flight carries the same date, i.e. the Hexagon flight)</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -14438,7 +14486,7 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>single (all Edmonds DOQQs carry 20191011)</t>
+          <t>single (all Edmonds DOQQs carry 20191011; consortium flight-area IDATE '2019 -10-11' at the city centroid)</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -14453,12 +14501,12 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20191011</t>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20191011 Currentness_Reference: Ground Condition</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER — weakens the 'NAIP is leaf-on by spec' assumption. Corroborated by the WA consortium 2019 1-ft flight-area layer IDATE '2019 -10-11'.</t>
+          <t>OCTOBER. No NAIP metadata record (2015/2017/2021 Digital Coast) contains any leaf-on/leaf-off statement - only 'peak crop growing conditions'; the 'NAIP is leaf-on by spec' assumption has no documentary basis.</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
@@ -14466,9 +14514,21 @@
           <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
         </is>
       </c>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t>2019-10-11</t>
+        </is>
+      </c>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2019_Statewide_imagery_consortium_1_foot_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T23" s="1" t="inlineStr">
+        <is>
+          <t>{"FID": 23, "IDATE": "2019 -10-11"} (stray space verbatim)</t>
+        </is>
+      </c>
       <c r="U23" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -14548,12 +14608,12 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>m_4712214_ne_10_060_20231007.tif (date field of the DOQQ file name, ISO metadata)</t>
+          <t>&lt;gmd:title&gt; m_4712214_sw_10_060_20231007.tif (date field of the DOQQ file name in the ISO metadata record)</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues).</t>
+          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues). Context: NAIP 2021 over Edmonds exists (all 8 QQs STAC datetime 2021-07-13, INFERRED from file names - the FGDC sidecars for quad 47122 are absent from the Azure mirror).</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -14578,12 +14638,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>~2016 (lidar)</t>
+          <t>2016 (lidar)</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>USGS 3DEP HAG via Planetary Computer, reprojected by the project</t>
+          <t>USGS 3DEP HAG via Planetary Computer, reprojected by the project; underlying lidar = USGS_LPC_WA_Western_North_2016 (QSI for USGS/WADNR)</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -14618,12 +14678,12 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>2016-03-17 to 2017-06-06 (USGS/WADNR lidar collection)</t>
+          <t>2016-03-17 to 2016-09-30 (Western Washington 3DEP NORTH AOI; all 46 tiles over the city are North-block)</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>window of 15 months</t>
+          <t>window of 198 days</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -14643,12 +14703,12 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>(collection window per IMAGERY_FACTS 8.1, sourced from InPort 51853 — REFETCH NEEDED)</t>
+          <t>Time Frame 2016-03-17 - 2017-06-06 / North: March 17 - Sept 30, 2016 / South: March 17, 2016 - June 6, 2017</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>UNITS TRAP #4: grid is 1.0 m in EPSG:3857 = 67.2 cm true ground at 47.81N, not 1 m. Row included for completeness; excluded from the imagery count.</t>
+          <t>UNITS TRAP #4: grid is 1.0 m in EPSG:3857 = 67.2 cm true ground at 47.81N, not 1 m. Narrowed from 15 months (whole project) to the North window by point-in-polygon on NOAA's tile index (46/46 tiles /north/). Reference raster, excluded from the imagery count.</t>
         </is>
       </c>
       <c r="Q25" s="1" t="inlineStr">
@@ -14656,9 +14716,21 @@
           <t>grid/true MEASURED; native PUBLISHED</t>
         </is>
       </c>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr"/>
+      <c r="R25" s="1" t="inlineStr">
+        <is>
+          <t>2016-03-30 (INFERRED from the tile filename prefix 20160330_USGS_LPC_WA_Western_North_2016_q47122G4405 - a FILE NAME; 3/30/16 is a flight day for all three contractors in QSI report Table 3)</t>
+        </is>
+      </c>
+      <c r="S25" s="1" t="inlineStr">
+        <is>
+          <t>https://noaa-nos-coastal-lidar-pds.s3.amazonaws.com/laz/geoid18/6331/tileindex_wa2016_west_wa_m6331.gpkg</t>
+        </is>
+      </c>
+      <c r="T25" s="1" t="inlineStr">
+        <is>
+          <t>20160330_USGS_LPC_WA_Western_North_2016_q47122G4405_LAS_2018.copc.laz</t>
+        </is>
+      </c>
       <c r="U25" s="1" t="inlineStr">
         <is>
           <t>reference raster</t>
@@ -14668,87 +14740,87 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>ccap_2016_hires_lc_snohfull.tif</t>
+          <t>PSLC_2005/ (47 laz tiles)</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>2016 (C-CAP ref)</t>
+          <t>2005 (lidar)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>NOAA OCM C-CAP hi-res land cover, Snohomish County 2016 (InPort 53263)</t>
+          <t>Puget Sound LiDAR Consortium 2005 North Puget Sound Lowlands (Terrapoint), InPort 50149</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>point cloud</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>metre</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>EPSG:26910</t>
+          <t>NAD83(HARN) UTM 10N, NAVD88 GEOID18</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.25 pts/m2 stated (~0.17 cross-checked)</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>n/a (thematic)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>100 (1 m product)</t>
+          <t>n/a (2 m nominal spacing)</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>NOT FOUND (source-imagery date; InPort 53263 returns 'Catalog Item Not Retrievable')</t>
+          <t>2005-02-27 (Edmonds sub-project, 11 sq mi)</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single day</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
+          <t>single (sub-project row)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>https://www.fisheries.noaa.gov/inport/item/53263</t>
+          <t>https://www.fisheries.noaa.gov/inport/item/50149</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>Catalog Item Not Retrievable</t>
+          <t>project, area (sq mi), date(s) collected, vert. acc (cm), horiz acc. (cm), RMSE (m) - ... - Edmonds, 11, 2/27/2005, 25, 60, 0.100 - Mt. Lake Terrace, 4, 7/15/2005-9/15/2005, 25, 60, 0.100 - Mukilteo, 16, 2/27/2005, 25, 60, 0.100</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>AGENT TARGET: Wayback copy of InPort 53263 / the .img sidecar metadata (wa_snohomish_co_ccap_hr_landcover20190314.img). Reference raster, not an imagery acquisition.</t>
+          <t>LEAF-OFF (late February). Record-internal inconsistency: Mt. Lake Terrace sub-project dates run past the record's own Time Frame end (2005-07-15). Held at D:/edmonds-pipeline/Imagery/PSLC_2005 and Full_Image/PSLC_2005 (IMAGERY_FACTS 8.2).</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; native PUBLISHED</t>
+          <t>density PUBLISHED</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -14756,24 +14828,24 @@
       <c r="T26" s="1" t="inlineStr"/>
       <c r="U26" s="1" t="inlineStr">
         <is>
-          <t>reference raster</t>
+          <t>reference lidar</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>ccap_2021_hires_lc.tif</t>
+          <t>ccap_2016_hires_lc_snohfull.tif</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>2020-21 (C-CAP v2 ref)</t>
+          <t>2016 (C-CAP ref)</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>NOAA OCM C-CAP hi-res v2 'Refined' (Ecopia extraction, NV5 refinement)</t>
+          <t>NOAA OCM C-CAP hi-res land cover, Snohomish County 2016 (InPort 53263 - record RECOVERED as an InPort XML export on coast.noaa.gov; fisheries.noaa.gov still 403)</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -14803,42 +14875,42 @@
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>100 (1 m extraction from &lt;=30 cm imagery)</t>
+          <t>100 (1 m product)</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>2020-2021 vintage (source imagery dates not stated per pixel)</t>
+          <t>summer 2016 (source imagery, stated as NAIP) - CONTESTED: no WA NAIP 2016 exists (Azure NAIP v002/wa/ holds 2011, 2013, 2015, 2017, 2019, 2021, 2023 only)</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>year range</t>
+          <t>season</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>multi (mosaic of vendor imagery)</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>(lineage XML cc_wa_puget_2021_ccap_v2_hires_landcover.xml — URL to be re-fetched)</t>
+          <t>https://chs.coast.noaa.gov/htdata/raster1/landcover/bulkdownload/hires/wa/WA_Snohomish_2016_lc.xml</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI</t>
+          <t>The timeframe for this metadata is summer 2016. These maps are developed utilizing high resolution National Agriculture Imagery Program (NAIP) imagery, and can be used to track changes in the landscape through time.</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>GATE: published date without fetched URL+quote -&gt; downgraded. Reference raster, not an imagery acquisition. Date of the underlying imagery is the agent question.</t>
+          <t>Candidate reconciliation (INFERENCE): the 'summer 2016' imagery is the HXIP Aug 11-12 2016 flight (the WA consortium product is itself branded 'NAIP_2016' on AGOL), or NOAA used NAIP 2015 (2015-08-07) and labelled the product 2016 - UNRESOLVED. Traps in the record: &lt;start-date-time&gt;2016-01-01 is a year placeholder; &lt;publish-date&gt;2019-03-14 is publication. Ancillary: NGS MLLW orthoimagery 2014 for shore classes. Reference raster.</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
@@ -14855,8 +14927,317 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ccap_2021_hires_lc.tif</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2021 (C-CAP v2 ref)</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>NOAA OCM C-CAP hi-res v2 'Refined' Puget Sound 2021 (InPort 79723; Ecopia extraction, NV5 refinement)</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>n/a (thematic)</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m extraction from '30cm or better' imagery)</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>2021 (year only; 'Acquisition date of the Aerial Imagery')</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>year only</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="inlineStr">
+        <is>
+          <t>multi (mosaic of vendor imagery)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>https://ocmgeodatastor1.blob.core.windows.net/ccap/bulk_download/C-CAP_High-Resolution_Data/Refined_C-CAP_High-Resolution_Land_Cover_Classification/CONUS/wa_puget_2021_ccap_v2_hires_landcover.xml</t>
+        </is>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>&lt;currentness-reference&gt;Acquisition date of the Aerial Imagery&lt;/currentness-reference&gt; ... &lt;time-frame-type&gt;Discrete&lt;/time-frame-type&gt; &lt;start-date-time&gt;2021&lt;/start-date-time&gt; ... Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>The record was created 2026-04-28 and may post-date the held clip (2026-07-06); best-available lineage, not proven identical. Record defects: Ohio/Houston copy-paste text, 'Never Published', 'best-available-metadata: No'. LICENSING (verbatim, for the Licensing_Risk sheet): 'Users are granted a perpetual, non-exclusive, irrevocable, worldwide license to use these data ... with the exception of creating, training, improving, modifying, validating, testing, evaluating, or otherwise leveraging machine learning algorithms in order to explicitly create similar land cover data for a period of five years from its date of creation.' The Phase-1 canopy record (InPort 70562, created 2023-09-30) carries the broader unqualified form ('may not be used for the purpose of ... testing, or evaluating machine learning algorithms ... except with the express written consent of Ecopia Tech Corporation'). This project uses the product as an EVALUATION reference - flag for Kam.</t>
+        </is>
+      </c>
+      <c r="Q28" s="1" t="inlineStr">
+        <is>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr">
+        <is>
+          <t>reference raster</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>(not held) WA Statewide Imagery Consortium 2020 6-inch (Hexagon, Leica ADS100)</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>2020 (SECOND 2020 acquisition - NOT the anchor)</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>WA OCIO/WaTech Statewide Imagery Consortium, flown by Hexagon under the 2020 NAIP Imaging Program</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>15 (6 in product), nominal flight GSD 20</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>20 (nominal)</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
+        <is>
+          <t>2020-08-28 (flight-area polygon at the city centroid; 2020-08-27 also intersects the city bbox); program window 2020-08-03 to 2020-09-06</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>day (coarse flight-area block, 911-1263 sq mi)</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="inlineStr">
+        <is>
+          <t>multi (2 blocks over the city)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.arcgis.com/sharing/rest/content/items/dd83978971d8421eb6b1a7273ba51f6e?f=json</t>
+        </is>
+      </c>
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t>Digital aerial imagery for Washington state was collected by Hexagon as part of the 2020 NAIP Imaging Program. Imagery was collected between August 3, 2020 and September 6, 2020 using Leica ADS100 digital camera systems. The project was flown at heights ranging from 8,000 ft msl to 15,500 ft msl resulting in a nominal GSD of 20cm.</t>
+        </is>
+      </c>
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>HAZARD ROW: a different vendor, camera, resolution and season from 2020_coe_rgb.tif (EagleView 3 in, Apr-Jul). Year-matched substitution would introduce a ~4.5-month error - exactly the 2015 three-way pattern. Not held; a late-August leaf-on 15 cm 4-band product if ever wanted.</t>
+        </is>
+      </c>
+      <c r="Q29" s="1" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R29" s="1" t="inlineStr">
+        <is>
+          <t>2020-08-28 / 2020-08-27</t>
+        </is>
+      </c>
+      <c r="S29" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/ArcGIS/rest/services/2020_Statewide_imagery_consortium_6_inch_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T29" s="1" t="inlineStr">
+        <is>
+          <t>{"OBJECTID":9,"IDATE":"2020-08-28","squaremile":911} ; {"OBJECTID":8,"IDATE":"2020-08-27","squaremile":1263}</t>
+        </is>
+      </c>
+      <c r="U29" s="1" t="inlineStr">
+        <is>
+          <t>context (not held)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>(not held) WA Statewide Imagery Consortium 2018 6-inch; Edmonds_Marsh_2018 drone</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>2018 (two distinct acquisitions)</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>WA consortium (Hexagon) / City of Edmonds Imagery/Edmonds_Marsh_2018 ImageServer</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>15 (consortium) / 2.5 (Marsh cache LOD)</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>n/a / 3.36 (Marsh pixelSizeX 0.0336 m)</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>2018-08-07 (consortium flight area over Edmonds) ; 2018-08-01 16:22-16:52 UTC (Marsh drone sortie) - six days apart, NOT the same acquisition</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>day / exact timestamp</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2018FlightAreas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>{"FID": 18, "OBJECTID": 18, "IDATE": "2018-08-07"}</t>
+        </is>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>Recorded to prevent conflation. The Marsh service is the project's only Edmonds layer with a machine-readable timestamp and the positive control for keyProperties queries (correct path: /gis/rest/services/.../ImageServer/keyProperties?f=json).</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t>2018-08-01T16:22:13+00:00 to 16:52:13 (Marsh)</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer/keyProperties?f=json</t>
+        </is>
+      </c>
+      <c r="T30" s="1" t="inlineStr">
+        <is>
+          <t>"acquisitionEndDate":"2018-08-01T16:52:13+00:00","acquisitionStartDate":"2018-08-01T16:22:13+00:00"</t>
+        </is>
+      </c>
+      <c r="U30" s="1" t="inlineStr">
+        <is>
+          <t>context (not held)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U27"/>
+  <autoFilter ref="A1:U30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -12552,7 +12552,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>2000-06-26 (callout label on the peach block containing cells t27r03, t27r04, t27r05, t28r04, t28r05). The live SDC page: 'Detailed photodate information is not available. A general overview at the township-level for data capture dates can interpolated from https://www5.kingcounty.gov/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg'</t>
+          <t>2000-06-26 (callout label on the graphic's peach block containing cells t27r03, t27r04, t27r05, t28r04, t28r05) ... [live SDC page, IMAGE_Ortho2000EmergeNAT:] Detailed photodate information is not available. ... A general overview at the township-level for data capture dates can interpolated from https://www5.kingcounty.gov/sdc/raster/ortho/images/ortho2000emergegeneralflightdate.jpg</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>SHOTDATE field, 1078 frames intersecting the city polygon (query 2026-08-23; refetch-verified: field exists, all six days non-zero countywide)</t>
+          <t>"IMAGENAME":"WAKING035400NeighOrtho1546_070707" ... "SHOTDATE":"2007/07/07 18:27:03" (first of 1078 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2007_ORTHO_IMAGE07_AREA_759_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>SHOTDATE/YYYYMMDD fields, 472 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"IMAGENAME":"WAKING042400NeighOrtho77930_090509" ... "SHOTDATE":"2009/05/09 20:58:13" (first of 472 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2009_ORTHO_IMAGE09_AREA_760_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>DATE_STR/TIME_STR fields, 75 photo centres inside the city polygon (query 2026-08-23); DATACOLOR='nir' for all 75</t>
+          <t>"DATACOLOR":"nir" ... "DATE_STR":"Apr.07.2012" ... "TIME_STR":"12:46:28" (first of 75 photo centres inside the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2012_ORTHO_IMAGE12_POINT_1447_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 688 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"ImageName":"WAKING042400NeighOrtho8690_130602" ... "ShotDate":"2013/06/02 18:04:31" (first of 688 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2013_ORTHO_IMAGE13_AREA_2061_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 701 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"ImageName":"WAKING041401NeighOrtho4281_150228" ... "ShotDate":"2015/02/28 14:51:01" (first of 701 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2015_ORTHO_IMAGE15_AREA_2499_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>ShotDate/YYYYMMDD fields, 710 frames intersecting the city polygon (query 2026-08-23; an independent re-query returned 695, all 15 missing on May 10 - residual geometry handling, same days)</t>
+          <t>"ImageName":"WAKING043402NeighOrtho01390_170509" ... "ShotDate":"2017/05/09 17:20:09" (first of 710 frames intersecting the city polygon - an independent re-query returned 695, all 15 missing on May 10, same days; raw response qc/imagery_date_evidence/raw_records/kc_2017_ORTHO_IMAGE17_AREA_2685_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field (date only; the layer carries Time_UTC/Time_PDT separately), 1234 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"ImageName":"WAKING042402NeighOrtho5255_190425" ... "ShotDate":"2019/04/25" (date-only field; first of 1234 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2019_ORTHO_IMAGE19_AREA_2852_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field, 662 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"ImageName":"WAKING022033NeighOrtho9795_210415" ... "ShotDate":"2021/04/15 14:54:55" (first of 662 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2021_ORTHO_IMAGE21_AREA_2912_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>ShotDate field, 1125 frames intersecting the city polygon (query 2026-08-23; refetch-verified)</t>
+          <t>"ImageName":"WAKING022033NeighOrtho8996_230503" ... "ShotDate":"2023/05/03 18:48:58" (first of 1125 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2023_ORTHO_IMAGE23_AREA_3073_citypoly_first3.json)</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>SDATE '08/11/2016 16:52' (SUNEL 31) / '08/12/2016 09:05' (SUNEL 34) / '08/12/2016 09:30' (SUNEL 37), THEMENAME hxip_m_4712213/4712214_*_10_15; city-centroid point query returns hxip_m_4712213_se2_10_15, SDATE '08/12/2016 09:30', SUNEL 37, ACCURACY '0.68m (ce 95%)'</t>
+          <t>"THEMENAME":"hxip_m_4712213_se2_10_15","SDATE":"08/12/2016 09:30","SUNEL":37,"ACCURACY":"0.68m (ce 95%)" (city-centroid point query) ... "THEMENAME":"hxip_m_4712214_sw3_10_15","SDATE":"08/12/2016 09:05","SUNEL":34 ... "THEMENAME":"hxip_m_4712214_sw2_10_15","SDATE":"08/11/2016 16:52","SUNEL":31 (city bbox, 11 footprints; raw responses qc/imagery_date_evidence/raw_records/wa_2016_6in_*.json)</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>SDATE '08/07/2015 15:31', THEMENAME hxip_m_4712213_ne_10_30, SUNEL 46</t>
+          <t>"THEMENAME":"hxip_m_4712213_se_10_30","SDATE":"08/07/2015 15:31","SUNEL":46,"ACCURACY":"0.72m (ce 95%)" (city-centroid point query; raw response qc/imagery_date_evidence/raw_records/wa_2015_1ft_citycentroid.json)</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>Identity MEASURED 2026-08-23: held 2017_coe_rgb.tif (2x boxcar-downsampled) vs 2017_king_rgb.tif over a 12x12 grid on the city polygon, 66 valid 512-px windows -&gt; r min 0.9568, p5 0.9786, median 0.9923, max 0.9966, MAE median 3.54 DN; live services 2017_Aerial_Cached vs KingCo_Aerial_2017 LOD-20 tiles at 5 sites r = 0.9876-0.9935. Identical vehicles in identical stalls and identical building relief displacement -&gt; same orthorectification, not merely the same flight.</t>
+          <t>"ImageName":"WAKING043402NeighOrtho01390_170509" ... "ShotDate":"2017/05/09 17:20:09" (King County 2017 index, first of 710 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2017_ORTHO_IMAGE17_AREA_2685_citypoly_first3.json). Dates transfer because the two files are the same orthomosaic - see notes.</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>Retires the 8.5-month candidate window and the council-minutes line (2023-07-25 p.15, 'PlanIt Geo ... 2017 flyovers') as evidence - the 2019 UFMP was written by Davey Resource Group and its canopy work used Aug 2015 imagery; PlanIt Geo appears nowhere in it. No City of Edmonds document naming the 2017 vendor was found; attribution rests on measured pixel identity plus King County's published coverage statement (alt). Snohomish County's own 2017 product is a 1-ft HXIP flight (2017-08-15/21) and cannot be a 3-in source. Grid note: the held grid is exactly LOD 21, which King's tile endpoint does not serve (404 at L21) but Edmonds' does - consistent with a city-service export. Method detail: qc/imagery_date_evidence/coe2017_identity/.</t>
+          <t>Identity MEASURED 2026-08-23: held 2017_coe_rgb.tif (2x boxcar-downsampled) vs 2017_king_rgb.tif over a 12x12 grid on the city polygon, 66 valid 512-px windows -&gt; r min 0.9568, p5 0.9786, median 0.9923, max 0.9966, MAE median 3.54 DN; live services 2017_Aerial_Cached vs KingCo_Aerial_2017 LOD-20 tiles at 5 sites r = 0.9876-0.9935. Identical vehicles in identical stalls and identical building relief displacement -&gt; same orthorectification, not merely the same flight. Retires the 8.5-month candidate window and the council-minutes line (2023-07-25 p.15, 'PlanIt Geo ... 2017 flyovers') as evidence - the 2019 UFMP was written by Davey Resource Group and its canopy work used Aug 2015 imagery; PlanIt Geo appears nowhere in it. No City of Edmonds document naming the 2017 vendor was found; attribution rests on measured pixel identity plus King County's published coverage statement (alt). Snohomish County's own 2017 product is a 1-ft HXIP flight (2017-08-15/21) and cannot be a 3-in source. Grid note: the held grid is exactly LOD 21, which King's tile endpoint does not serve (404 at L21) but Edmonds' does - consistent with a city-service export. Method detail: qc/imagery_date_evidence/coe2017_identity/.</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>{"FILENAME": "13007_57226", "FRAME": 57226, ... "UTC_TIME": "19:35:08", "MAX_GSD__f": 0.225, "USED": "YES", "VENDOR": "GeoTerra", "CAMERA": "UltraCam Xp", "SSN": 10411033, ... "FLIGHTLINE": "13007", "ACQ_DATE": 1429228800000} (photo-centre layer; in-polygon N=167; 'It is a reference for the raw image scans, it is not a index for tiled ortho imagery')</t>
+          <t>"FILENAME":"13009_57445" ... "UTC_TIME":"19:54:49","MAX_GSD__f":0.225 ... "VENDOR":"GeoTerra","CAMERA":"UltraCam Xp" ... "FLIGHTLINE":"13009","ACQ_DATE":1429228800000 (= 2015-04-17 UTC; first of the photo centres inside the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2015C_ORTHO_IMAGE15C_POINT_2574_citypoly_first3.json). Layer description: It is a reference for the raw image scans, it is not a index for tiled ortho imagery</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="T23" s="1" t="inlineStr">
         <is>
-          <t>{"FID": 23, "IDATE": "2019 -10-11"} (stray space verbatim)</t>
+          <t>"IDATE":"2019 -10-11" (stray space verbatim; city-centroid point query, raw response qc/imagery_date_evidence/raw_records/wa_2019_1ft_citycentroid.json)</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>&lt;gmd:title&gt; m_4712214_sw_10_060_20231007.tif (date field of the DOQQ file name in the ISO metadata record)</t>
+          <t>&lt;gco:CharacterString&gt;m_4712214_sw_10_060_20231007.tif&lt;/gco:CharacterString&gt; (the DOQQ file name in the ISO metadata record; 20231007 = acquisition date field)</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>Time Frame 2016-03-17 - 2017-06-06 / North: March 17 - Sept 30, 2016 / South: March 17, 2016 - June 6, 2017</t>
+          <t>North: March 17 - Sept 30, 2016 ... South: March 17, 2016 - June 6, 2017</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>point cloud</t>
+          <t>point cloud (no grid)</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>0.25 pts/m2 stated (~0.17 cross-checked)</t>
+          <t>n/a (point cloud)</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>LEAF-OFF (late February). Record-internal inconsistency: Mt. Lake Terrace sub-project dates run past the record's own Time Frame end (2005-07-15). Held at D:/edmonds-pipeline/Imagery/PSLC_2005 and Full_Image/PSLC_2005 (IMAGERY_FACTS 8.2).</t>
+          <t>Density 0.25 pts/m2 stated (~0.17 cross-checked, IMAGERY_FACTS 8.1). LEAF-OFF (late February). Record-internal inconsistency: Mt. Lake Terrace sub-project dates run past the record's own Time Frame end (2005-07-15). Held at D:/edmonds-pipeline/Imagery/PSLC_2005 and Full_Image/PSLC_2005 (IMAGERY_FACTS 8.2).</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="T29" s="1" t="inlineStr">
         <is>
-          <t>{"OBJECTID":9,"IDATE":"2020-08-28","squaremile":911} ; {"OBJECTID":8,"IDATE":"2020-08-27","squaremile":1263}</t>
+          <t>"IDATE":"2020-08-28" (city centroid) ... "IDATE":"2020-08-27" (also intersects the city bbox; raw responses qc/imagery_date_evidence/raw_records/wa_2020_6in_*.json)</t>
         </is>
       </c>
       <c r="U29" s="1" t="inlineStr">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>{"FID": 18, "OBJECTID": 18, "IDATE": "2018-08-07"}</t>
+          <t>"IDATE":"2018-08-07" (city-centroid point query; raw response qc/imagery_date_evidence/raw_records/wa_2018_6in_citycentroid.json)</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -11444,7 +11444,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>SOURCE DOCUMENTED in a signed city contract</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] Still INFERRED; consistent with ONE continuous pass (shadow geometry, 10 sites); head trimmed to 2020-04-25. Contract vehicle for the PRR: King County RFP 1166-18-PCR / Piggyback PB-19-14BC. || was: SOURCE DOCUMENTED in a signed city contract</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -11482,7 +11482,7 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>named in the same contract clause</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] IDENTITY MEASURED: same MrSID encode as Everett's Image2022_3in_sid (input set 675,609,635,568 B) -&gt; window PUBLISHED. || was: named in the same contract clause</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -11542,7 +11542,7 @@
       <c r="B5" s="1" t="inlineStr"/>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>NO contract, NO budget line, NO flight date found</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] DATED: same orthomosaic as King 2017 -&gt; 2017-05-04..05-10 MEASURED. || was: NO contract, NO budget line, NO flight date found</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>maps.edmondswa.gov/.../Edmonds_Marsh_2018/ImageServer/info/keyProperties</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] LIVE PATH: https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer/keyProperties?f=json (the /arcgis/ form 500s; /info/keyProperties 400s on every service). || was: maps.edmondswa.gov/.../Edmonds_Marsh_2018/ImageServer/info/keyProperties</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>*** RUN IT PER SEAMLINE PATCH, NOT PER CITY *** - a county mosaic over 22 sq mi is stitched from multiple flight lines, plausibly multiple days. This also answers a question nobody has asked: IS 2020_coe_rgb.tif EVEN A SINGLE-DATE IMAGE? If not, 'the 2020 acquisition date' is the wrong question and that matters more for the labels than the date does.</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] RUN 2026-08-23: azimuth reliable (2012 control 8/10), elevation saturates above ~45 deg -&gt; 2020 consistent with one pass, no calendar date. Evidence qc/imagery_date_evidence/shadow_dating_2020/. || was: *** RUN IT PER SEAMLINE PATCH, NOT PER CITY *** - a county mosaic over 22 sq mi is stitched from multiple flight lines, plausibly multiple days. This also answers a question nobody has asked: IS 2020_coe_rgb.tif EVEN A SINGLE-DATE IMAGE? If not, 'the 2020 acquisition date' is the wrong question and that matters more for the labels than the date does.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Puget Sound spring weather will eliminate most of the 92 candidate days outright. One afternoon. Converts the window to a shortlist that method 1 picks from, and independently sanity-checks whatever method 1 returns.</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] RUN 2026-08-23: the 30-deg sun floor is FALSIFIED by a known flight day (2015-02-15, max elevation 29.3 deg); calibrated rule (20-deg floor, 3-station consensus) passes 46/46 controls. Eliminates 22/92 (2020), 19/97 (2022), 18/62 (2024), 32/140 (2021s) days. || was: Puget Sound spring weather will eliminate most of the 92 candidate days outright. One afternoon. Converts the window to a shortlist that method 1 picks from, and independently sanity-checks whatever method 1 returns.</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Not a records request - an internal ask to Brian Tuley for a login, or a screenshot from someone who has one. It was sitting in the contract the whole time and could end the exercise today.</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] Contract numbers for the ask/PRR now known: King County RFP 1166-18-PCR, Snohomish Piggyback PB-19-14BC, Legistar 2024-1168. || was: Not a records request - an internal ask to Brian Tuley for a login, or a screenshot from someone who has one. It was sitting in the contract the whole time and could end the exercise today.</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -15858,6 +15858,87 @@
       <c r="E12" s="1" t="inlineStr">
         <is>
           <t>See the Reference_Independence sheet. Agreement between two Ecopia products is not corroboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2017_coe_rgb.tif spans an 8.5-month leaf-off-to-leaf-on window (2017-02-17 to 10-30)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IMAGERY_FACTS 9.2 / Provenance_Chain</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>It is the same orthomosaic as 2017_king_rgb.tif (r 0.957-0.997, 66 windows) and was flown 2017-05-04..05-10 over the city.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A coarse published window for a PARENT product was carried as the file's own window. Measuring identity against a sibling file settled in minutes what document-hunting could not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>The 2015 CoE basemap date is a three-way contest between independent acquisitions</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Contradictions sheet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The three dates belong to three DIFFERENT products (NAIP/HXIP Aug 7; King Pictometry Feb-Mar; city consortium Apr 8/17). The catalogue's 'Apr 8/9/17' also contained a day (Apr 9) with no frames over Edmonds.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Year-matched product substitution is the recurring trap (it recurred the same day: a second 2020 acquisition, Hexagon 2020-08-27/28, exists over Edmonds). Always ask WHICH product before asking WHEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>The HXIP footprint SDATE '08/11/2016 16:52' is UTC because the held file shows morning shadows</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>session lead's open note</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SDATE is LOCAL time (7034-footprint SUNEL fit; 09:05 read as UTC puts the sun 26 deg below the horizon). The held county 1-ft product simply is not that sortie.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A hypothesis stated to explain one observation was tested against the whole field and failed. State it, test it, record it.</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16231,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>UNRESOLVED</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] LARGELY RESOLVED: the three dates are three DIFFERENT products. Aug 7 2015 = NAIP/HXIP 2015 (Davey UTC Assessment names USDA FSA), Feb 15-Mar 8 = King Pictometry (the held 2015_king_rgb.tif; pixel-distinct from the CoE basemap, r 0.04-0.56 vs 0.99 control), Apr 8 + Apr 17 2015 = the city consortium photo centres (no Apr 9 over Edmonds). Residual: attribution of Ed_Aerial_2015.tif to the consortium is INFERRED; the '4.8 in' figure is unexplained. || was: UNRESOLVED</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -16182,7 +16263,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>MINUTES ARE WEAK</t>
+          <t>[SUPERSEDED 2026-08-23 -&gt; Pixel_Size_And_Date] RESOLVED: 2017_coe_rgb.tif is the SAME ORTHOMOSAIC as King County IMAGE_Ortho2017KCNAT (Pictometry), MEASURED r 0.957-0.997 over 66 citywide windows; dated 2017-05-04..05-10 from the per-frame index. The council-minutes 'PlanIt Geo' line is retired (the 2019 UFMP was by Davey Resource Group and used Aug-2015 imagery). || was: MINUTES ARE WEAK</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11361,6 +11361,37 @@
       <c r="G12" s="1" t="inlineStr">
         <is>
           <t>*** the published 2.8x / 110.8 cm is a RED-BAND-ONLY figure. Effective resolution is BAND-DEPENDENT and red - the band every greenness/NDVI index depends on - is the most degraded ***</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2016_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>median of 5 Method_Provenance sites; common-grid vs 2016_snoh_rgbi.tif: new 42.98 / held 43.2 cm, HF ratio 1.013</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -13769,7 +13800,7 @@
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
-          <t>Held file = export of the county service (window means identical to exportImage) and pixel-DISTINCT from Aerial_2015 and Aerial_2017 (MEASURED). SDATE is LOCAL clock time: a 7034-footprint fit of published SUNEL vs pvlib gives RMSE 6.9 deg for UTC-7 vs 55.6 for UTC, and 09:05 read as UTC puts the sun 26 deg below the horizon. The county gdb is HXIP_2016_SNOHOMISH.gdb (the 'HXIP_2015' tokens in the lineage are a stale parent-folder / dataset-name carry-over, not 2015 imagery); the 2015-08-07 flight is excluded three ways (pixel comparison, afternoon vs morning shadows, lineage). 6-in coverage reached Edmonds because it lies inside the Valtus/Hexagon 'Seattle' UAC polygon, not via a county buy-up. The Geocortex blurb 'acquired in August 2016 as part of a Washington Statewide Imagery consortium. Pixel size of the raster is 6 inch' sits on a layer titled '2017 Aerial Photos' and contradicts the county's 1-ft tiles - CONTESTED, month-level corroboration only. Both Aug 11 and Aug 12 2016 were flyable at all three ASOS stations (Aug 11 morning marine stratus at KPAE only). C-CAP 2016 Snohomish (InPort 53263) says its source imagery is 'NAIP ... summer 2016' but no WA NAIP 2016 exists - most plausibly this HXIP flight. Held file is a study-area CROP (lon -122.404..-122.316, lat 47.783..47.828).</t>
+          <t>*** SUPERSEDED 2026-08-23 by 2016_snoh_1ft_rgbi.tif (full study extent at the native 1-ft grid; this clipped 0.5-ft server upsample is kept for provenance) *** Held file = export of the county service (window means identical to exportImage) and pixel-DISTINCT from Aerial_2015 and Aerial_2017 (MEASURED). SDATE is LOCAL clock time: a 7034-footprint fit of published SUNEL vs pvlib gives RMSE 6.9 deg for UTC-7 vs 55.6 for UTC, and 09:05 read as UTC puts the sun 26 deg below the horizon. The county gdb is HXIP_2016_SNOHOMISH.gdb (the 'HXIP_2015' tokens in the lineage are a stale parent-folder / dataset-name carry-over, not 2015 imagery); the 2015-08-07 flight is excluded three ways (pixel comparison, afternoon vs morning shadows, lineage). 6-in coverage reached Edmonds because it lies inside the Valtus/Hexagon 'Seattle' UAC polygon, not via a county buy-up. The Geocortex blurb 'acquired in August 2016 as part of a Washington Statewide Imagery consortium. Pixel size of the raster is 6 inch' sits on a layer titled '2017 Aerial Photos' and contradicts the county's 1-ft tiles - CONTESTED, month-level corroboration only. Both Aug 11 and Aug 12 2016 were flyable at all three ASOS stations (Aug 11 morning marine stratus at KPAE only). C-CAP 2016 Snohomish (InPort 53263) says its source imagery is 'NAIP ... summer 2016' but no WA NAIP 2016 exists - most plausibly this HXIP flight. Held file is a study-area CROP (lon -122.404..-122.316, lat 47.783..47.828).</t>
         </is>
       </c>
       <c r="Q16" s="1" t="inlineStr">
@@ -13801,22 +13832,22 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2021_snoh_rgbi.tif</t>
+          <t>2016_snoh_1ft_rgbi.tif</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>2021 (Snoh)</t>
+          <t>2016 (campaign S16, REPLACES 2016_snoh_rgbi.tif)</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>HXIP via Snohomish County Imagery/Aerial_2021 ImageServer (mosaic gdb HXIP_2021_SNOHOMISH.gdb - a Hexagon delivery, not EagleView)</t>
+          <t>Hexagon Imagery Program (HXIP) via Snohomish County Imagery/Aerial_2016 ImageServer, exported 2026-08-23 by pipeline/acquire_imagery.py at the native 1-ft lattice (grid snapped to the service origin, RSP_NearestNeighbor: nearest == bilinear to 0 differing pixels in the pilot)</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -13831,62 +13862,74 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>40.6 (median of 5 Method_Provenance sites on the native 1-ft grid; 1.33x oversampled) - on a common 30.48 cm grid the old and new files resolve alike (43.0 vs 43.2 cm, HF-energy ratio 1.01): same source pixels, no server resampling</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>15.24 (0.5 ft): mosaic-catalog LowPS=0.5, item pixelSizeX=0.5 (MEASURED)</t>
+          <t>30.48 (1 ft = the county's delivered tile size; served pixelSize 0.5 ft is an upsample)</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>2021-06-25 to 2021-11-11</t>
+          <t>2016-08-12 morning (consortium sorties 09:05 / 09:30 PDT; 09:50 within the city bbox) - CONDITIONAL on the county 1-ft product being the same flight as the dated 15 cm consortium product; the 2016-08-11 16:52 sortie is EXCLUDED for the old extent by shadow azimuth</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>window of 140 days (weather trims to 108 feasible days; 18 late days never reach 30 deg sun)</t>
+          <t>window of 2 days by the consortium labels (Aug 11-12); pixels consistent with Aug 12</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
-          <t>unknown; held crop flown in the AFTERNOON (shadow azimuth 67-91 deg = sun at 247-256 deg, uniform over 24 windows) - a time-of-day constraint, not a date</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
+          <t>consortium labels MULTI (2 days, 3-4 sorties); shadows uniformly morning over the old extent - the new full extent has not been re-measured for shadow direction</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
         </is>
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/NAIP_2016_6in_Ortho_Dates_and_Times_83s/FeatureServer/0/query</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>The 2021 aerial photos are 6 inch resolution and cover mainly the urban areas. The imagery was collected between June 25, 2021 and November 11, 2021.</t>
+          <t>"THEMENAME":"hxip_m_4712213_se2_10_15","SDATE":"08/12/2016 09:30","SUNEL":37,"ACCURACY":"0.68m (ce 95%)" (city-centroid point query) ... "THEMENAME":"hxip_m_4712214_sw3_10_15","SDATE":"08/12/2016 09:05","SUNEL":34 ... "THEMENAME":"hxip_m_4712214_sw2_10_15","SDATE":"08/11/2016 16:52","SUNEL":31 (city bbox, 11 footprints; raw responses qc/imagery_date_evidence/raw_records/wa_2016_6in_*.json)</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>CLOSED LEADS: no WA consortium flight-date layer exists for 2021 or later (all 68 WAGeoservices services + 225 items enumerated; series ends 2020); the mosaic-catalog schema has no date field at all; WA NAIP 2021 does not cover quad 47122 (eastern WA only), so no NAIP ride-along date. Remaining route: the Hexagon flight log via Snohomish County DoIT, or the consortium contact (Joanne Markert, WA OCIO). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2021-06-25..11-11): 32 of 140 days eliminated; longest feasible blocks Jul 22-Aug 6, Jul 2-15, Aug 9-19. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
+          <t>MEASURED on arrival (D:/edmonds-pipeline/Imagery/SnoCo/_acq/S16/measure.json): 25,116 x 35,259 px, 4 bands uint8, EPSG:2285, 2,586,179,492 B; city-polygon coverage 100% (old file 66.7%), study-extent coverage 82.3% (the rest is Puget Sound); band 4 NIR (std 66, NDVI p90 0.73); no JPEG 8x8 block signature; blue-vs-green registration 0.075 px. Fetch: 234 chunks of 2048 px + 64 px overlap, 0 failures, 30 empty (water), 9.5 min at 5.8 MB/s; stitched BigTIFF spot-verified against 12 chunks; MANIFEST.sha256 on both planes. Decision REPLACE (wins: coverage; no losses). Date evidence is inherited from the superseded row (same flight, same service).</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native MEASURED (service catalog)</t>
-        </is>
-      </c>
-      <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
-      <c r="T17" s="1" t="inlineStr"/>
+          <t>grid/true/effective MEASURED (acquire_imagery verify 2026-08-23); native MEASURED (service catalog LowPS=1)</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t>2015-08-07 15:31 (HXIP 2015 1-ft flight; EXCLUDED for this product)</t>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/NAIP_2015_1ft_Ortho_Dates_and_Times_83s/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T17" s="1" t="inlineStr">
+        <is>
+          <t>"THEMENAME":"hxip_m_4712213_se_10_30","SDATE":"08/07/2015 15:31","SUNEL":46,"ACCURACY":"0.72m (ce 95%)" (city-centroid point query; raw response qc/imagery_date_evidence/raw_records/wa_2015_1ft_citycentroid.json)</t>
+        </is>
+      </c>
       <c r="U17" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -13896,104 +13939,92 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>2017_coe_rgb.tif</t>
+          <t>2021_snoh_rgbi.tif</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>2017 (CoE)</t>
+          <t>2021 (Snoh)</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2017_Aerial_Cached (source raster 2017_Aerial.tif, 0.25 ftUS EPSG:2285, JPEG); CONTENT = King County IMAGE_Ortho2017KCNAT (Pictometry International, 3-in 'Neighborhood' tier covering southwestern Snohomish County) - MEASURED identity</t>
+          <t>HXIP via Snohomish County Imagery/Aerial_2021 ImageServer (mosaic gdb HXIP_2021_SNOHOMISH.gdb - a Hexagon delivery, not EagleView)</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>0.074646</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+          <t>US survey foot</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>EPSG:3857</t>
+          <t>EPSG:2285</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>7.6 (indicative; per-site sd +/-0.41-1.17 px)</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS source raster; service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS exactly)</t>
+          <t>15.24 (0.5 ft): mosaic-catalog LowPS=0.5, item pixelSizeX=0.5 (MEASURED)</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>2017-05-04 to 2017-05-10 (5 days over the city: May 4 n=16, May 6 90, May 8 48, May 9 192, May 10 364) - transferred from the King County per-frame index because the two files are the SAME ORTHOMOSAIC</t>
+          <t>2021-06-25 to 2021-11-11</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>window of 7 days, 5 flight days</t>
+          <t>window of 140 days (weather trims to 108 feasible days; 18 late days never reach 30 deg sun)</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
-          <t>MULTI (5 days)</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
+          <t>unknown; held crop flown in the AFTERNOON (shadow azimuth 67-91 deg = sun at 247-256 deg, uniform over 24 windows) - a time-of-day constraint, not a date</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE17_AREA_2685/FeatureServer/0/query</t>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>"ImageName":"WAKING043402NeighOrtho01390_170509" ... "ShotDate":"2017/05/09 17:20:09" (King County 2017 index, first of 710 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2017_ORTHO_IMAGE17_AREA_2685_citypoly_first3.json). Dates transfer because the two files are the same orthomosaic - see notes.</t>
+          <t>The 2021 aerial photos are 6 inch resolution and cover mainly the urban areas. The imagery was collected between June 25, 2021 and November 11, 2021.</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>Identity MEASURED 2026-08-23: held 2017_coe_rgb.tif (2x boxcar-downsampled) vs 2017_king_rgb.tif over a 12x12 grid on the city polygon, 66 valid 512-px windows -&gt; r min 0.9568, p5 0.9786, median 0.9923, max 0.9966, MAE median 3.54 DN; live services 2017_Aerial_Cached vs KingCo_Aerial_2017 LOD-20 tiles at 5 sites r = 0.9876-0.9935. Identical vehicles in identical stalls and identical building relief displacement -&gt; same orthorectification, not merely the same flight. Retires the 8.5-month candidate window and the council-minutes line (2023-07-25 p.15, 'PlanIt Geo ... 2017 flyovers') as evidence - the 2019 UFMP was written by Davey Resource Group and its canopy work used Aug 2015 imagery; PlanIt Geo appears nowhere in it. No City of Edmonds document naming the 2017 vendor was found; attribution rests on measured pixel identity plus King County's published coverage statement (alt). Snohomish County's own 2017 product is a 1-ft HXIP flight (2017-08-15/21) and cannot be a 3-in source. Grid note: the held grid is exactly LOD 21, which King's tile endpoint does not serve (404 at L21) but Edmonds' does - consistent with a city-service export. Method detail: qc/imagery_date_evidence/coe2017_identity/.</t>
+          <t>CLOSED LEADS: no WA consortium flight-date layer exists for 2021 or later (all 68 WAGeoservices services + 225 items enumerated; series ends 2020); the mosaic-catalog schema has no date field at all; WA NAIP 2021 does not cover quad 47122 (eastern WA only), so no NAIP ride-along date. Remaining route: the Hexagon flight log via Snohomish County DoIT, or the consortium contact (Joanne Markert, WA OCIO). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2021-06-25..11-11): 32 of 140 days eliminated; longest feasible blocks Jul 22-Aug 6, Jul 2-15, Aug 9-19. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native MEASURED (live service)</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t>mid-February through October 2017 (countywide), with SW Snohomish at 3 in</t>
-        </is>
-      </c>
-      <c r="S18" s="1" t="inlineStr">
-        <is>
-          <t>https://gisandyou.org/2018/05/25/2017-aerial-imagery-in-imap/</t>
-        </is>
-      </c>
-      <c r="T18" s="1" t="inlineStr">
-        <is>
-          <t>The imagery was captured by Pictometry International Corp. from mid-February through October of 2017. The original photos have a resolution of 3 inches per pixel ("Neighborhood" scale in Pictometry terminology) over urbanized, western King County ... Also covered at the Neighborhood resolution level in the 2017 imagery are southwestern Snohomish County</t>
-        </is>
-      </c>
+          <t>grid/true MEASURED; effective MEASURED; native MEASURED (service catalog)</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -14003,17 +14034,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2020_coe_rgb.tif</t>
+          <t>2017_coe_rgb.tif</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>2020 (ANCHOR)</t>
+          <t>2017 (CoE)</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2020_Aerial_Cached (MrSID/MG4 mosaic, GeoExpress 10.0.1.5035, input GeoTIFF set 665,235,977,256 B); source = Snohomish County 2020 EagleView/Pictometry regional project WASNOH20_3in per the 2021 ILA; product identity corroborated by Everett's copy ('Aerial Photos 2020 Pictometry Mosiac 3 inch resolution urban areas', 0.25 ftUS)</t>
+          <t>City of Edmonds Basemap/2017_Aerial_Cached (source raster 2017_Aerial.tif, 0.25 ftUS EPSG:2285, JPEG); CONTENT = King County IMAGE_Ortho2017KCNAT (Pictometry International, 3-in 'Neighborhood' tier covering southwestern Snohomish County) - MEASURED identity</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -14038,67 +14069,67 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.6 (indicative; per-site sd +/-0.41-1.17 px)</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS; county Aerial_2020 LowCellSize 0.25, dimResol 0.250000 ftUS; Everett Image2020jp2 pixelSizeX 0.25 in EPSG:2285)</t>
+          <t>7.62 (0.25 ftUS source raster; service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS exactly)</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>2020-04-13 to 2020-07-13 (county window; the single published window is the UNION of the 3-in urban and 9-in rural sub-projects - unlike 2022/2024 the county did not publish them separately). Shadow solar geometry excludes the head: 2020-04-25 to 07-13 survive (80 of 92 days)</t>
+          <t>2017-05-04 to 2017-05-10 (5 days over the city: May 4 n=16, May 6 90, May 8 48, May 9 192, May 10 364) - transferred from the King County per-frame index because the two files are the SAME ORTHOMOSAIC</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>window of 80-92 days</t>
+          <t>window of 7 days, 5 flight days</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>CONSISTENT WITH ONE CONTINUOUS PASS, single date NOT PROVEN: 10 QC-passing sites of 34 on a ~850 m city-wide grid give sun azimuths 120.8-192.5 deg = local times ~10:22-13:39 PDT straddling solar noon, increasing monotonically east-to-west (az vs lon r=-0.75, p=0.013; permutation p=0.026) - the signature of successive flight lines in one pass, not of day-blocks. Not excluded: several dates each flown at the same time of day.</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
+          <t>MULTI (5 days)</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
         </is>
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE17_AREA_2685/FeatureServer/0/query</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>The 2020 aerial photos are 3 inch resolution in the urban areas and 9 inch resolution in the rural areas, excluding much of the unpopulated mountainous portion of eastern Snohomish County, and were taken between April 13th and July 13th, 2020.</t>
+          <t>"ImageName":"WAKING043402NeighOrtho01390_170509" ... "ShotDate":"2017/05/09 17:20:09" (King County 2017 index, first of 710 frames intersecting the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2017_ORTHO_IMAGE17_AREA_2685_citypoly_first3.json). Dates transfer because the two files are the same orthomosaic - see notes.</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
         <is>
-          <t>ILA 2021 (Laserfiche id 1462454, repo=Edmonds) Work Order p.14: 'Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ... County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest'. Contract vehicle for a records request: King County RFP 1166-18-PCR (EagleView Technology Corp) via Snohomish County Piggyback PB-19-14BC (Legistar matter 2024-1168). DEFINITIVE PIN = EagleView flight log / photo-centre index via Snohomish County DoIT (Viggo Forde), or a CONNECTExplorer capture-date screenshot (Edmonds holds up to ten accounts under the ILA). City keyProperties (correct endpoint &lt;ImageServer&gt;/keyProperties?f=json; /info/keyProperties 400s on this server, positive control Edmonds_Marsh_2018 returns acquisitionStartDate 2018-08-01T16:22:13+00:00 / End 16:52:13) carry NO date: IMAGE__MODIFICATIONS 'COMPRESSED EMBEDDED MASKED MOSAICKED' - a validated null. Everett's 2020 copy is JPEG2000 and also carries no date; no 2020 MrSID twin with a surviving date was found. A per-frame index CANNOT exist on the county service (mosaic catalog = two whole-project items WASNOH20_3in / WASNOH20_9in). HAZARD: a SECOND 2020 acquisition covers Edmonds - the WA consortium 6-in Hexagon/ADS100 flight of 2020-08-27/28 (program window 2020-08-03..09-06) - DO NOT borrow its date (see context row). Shadow dating (qc/imagery_date_evidence/shadow_dating_2020/): azimuth is reliable (2012 control 8/10 in-window), elevation reads LOW and saturates above ~45 deg, so 2020 elevations are lower bounds - hence no calendar date. 2020 ortho co-registered to 2012 within &lt;=1.5 WM m. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2020-04-13..07-13): 22 of 92 days eliminated; longest feasible blocks May 7-15 (9 d), Apr 13-17, May 26-30, Jun 1-5, Jun 22-26. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
+          <t>Identity MEASURED 2026-08-23: held 2017_coe_rgb.tif (2x boxcar-downsampled) vs 2017_king_rgb.tif over a 12x12 grid on the city polygon, 66 valid 512-px windows -&gt; r min 0.9568, p5 0.9786, median 0.9923, max 0.9966, MAE median 3.54 DN; live services 2017_Aerial_Cached vs KingCo_Aerial_2017 LOD-20 tiles at 5 sites r = 0.9876-0.9935. Identical vehicles in identical stalls and identical building relief displacement -&gt; same orthorectification, not merely the same flight. Retires the 8.5-month candidate window and the council-minutes line (2023-07-25 p.15, 'PlanIt Geo ... 2017 flyovers') as evidence - the 2019 UFMP was written by Davey Resource Group and its canopy work used Aug 2015 imagery; PlanIt Geo appears nowhere in it. No City of Edmonds document naming the 2017 vendor was found; attribution rests on measured pixel identity plus King County's published coverage statement (alt). Snohomish County's own 2017 product is a 1-ft HXIP flight (2017-08-15/21) and cannot be a 3-in source. Grid note: the held grid is exactly LOD 21, which King's tile endpoint does not serve (404 at L21) but Edmonds' does - consistent with a city-service export. Method detail: qc/imagery_date_evidence/coe2017_identity/.</t>
         </is>
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county + Everett services)</t>
+          <t>grid/true MEASURED; effective MEASURED; native MEASURED (live service)</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr">
         <is>
-          <t>(ILA text, for the chain)</t>
+          <t>mid-February through October 2017 (countywide), with SW Snohomish at 3 in</t>
         </is>
       </c>
       <c r="S19" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
+          <t>https://gisandyou.org/2018/05/25/2017-aerial-imagery-in-imap/</t>
         </is>
       </c>
       <c r="T19" s="1" t="inlineStr">
         <is>
-          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects and receipt of imagery by County, County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest</t>
+          <t>The imagery was captured by Pictometry International Corp. from mid-February through October of 2017. The original photos have a resolution of 3 inches per pixel ("Neighborhood" scale in Pictometry terminology) over urbanized, western King County ... Also covered at the Neighborhood resolution level in the 2017 imagery are southwestern Snohomish County</t>
         </is>
       </c>
       <c r="U19" s="1" t="inlineStr">
@@ -14110,17 +14141,17 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>2022_coe_rgb.tif</t>
+          <t>2020_coe_rgb.tif</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>2022 (CoE)</t>
+          <t>2020 (ANCHOR)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2022_Aerial_Cached; = Snohomish County 2022 regional project WASNOH22_3in. IDENTITY MEASURED: the Edmonds and Everett 2022 MrSIDs are the same county encode (identical input-set byte count 675,609,635,568 B, GeoExpress 10.0.1.5035, EPSG:2285 ftUS geokeys)</t>
+          <t>City of Edmonds Basemap/2020_Aerial_Cached (MrSID/MG4 mosaic, GeoExpress 10.0.1.5035, input GeoTIFF set 665,235,977,256 B); source = Snohomish County 2020 EagleView/Pictometry regional project WASNOH20_3in per the 2021 ILA; product identity corroborated by Everett's copy ('Aerial Photos 2020 Pictometry Mosiac 3 inch resolution urban areas', 0.25 ftUS)</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -14145,32 +14176,32 @@
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS; county Aerial_2022 LowCellSize 0.25; MrSID input GeoTIFF geokeys 'Linear_Foot_US_Survey' / 2285)</t>
+          <t>7.62 (0.25 ftUS; county Aerial_2020 LowCellSize 0.25, dimResol 0.250000 ftUS; Everett Image2020jp2 pixelSizeX 0.25 in EPSG:2285)</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>2022-04-06 to 2022-07-11 (urban 3 in); the rural 9-in sub-project ran 2022-05-31 to 08-11 and does not apply to Edmonds</t>
+          <t>2020-04-13 to 2020-07-13 (county window; the single published window is the UNION of the 3-in urban and 9-in rural sub-projects - unlike 2022/2024 the county did not publish them separately). Shadow solar geometry excludes the head: 2020-04-25 to 07-13 survive (80 of 92 days)</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>window of 96 days</t>
+          <t>window of 80-92 days</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
+          <t>CONSISTENT WITH ONE CONTINUOUS PASS, single date NOT PROVEN: 10 QC-passing sites of 34 on a ~850 m city-wide grid give sun azimuths 120.8-192.5 deg = local times ~10:22-13:39 PDT straddling solar noon, increasing monotonically east-to-west (az vs lon r=-0.75, p=0.013; permutation p=0.026) - the signature of successive flight lines in one pass, not of day-blocks. Not excluded: several dates each flown at the same time of day.</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
         </is>
       </c>
       <c r="N20" s="1" t="inlineStr">
@@ -14180,12 +14211,12 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>The 2022 3 inch resolution aerial photos in the urban areas, were captured between April 6, 2022 and July, 11 2022. The 2022 9 inch resolution aerial photos in the rural areas, were captured between May, 31 2022 and August, 11 2022.</t>
+          <t>The 2020 aerial photos are 3 inch resolution in the urban areas and 9 inch resolution in the rural areas, excluding much of the unpopulated mountainous portion of eastern Snohomish County, and were taken between April 13th and July 13th, 2020.</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
-          <t>Upgraded INFERRED -&gt; PUBLISHED 2026-08-23: the window is published for a product whose identity with the held file is now measured (byte-count identity of the input set with Everett's Image2022_3in_sid, 'Aerial Photos 2022 Pictometry Mosaic 3 inch resolution urban areas'), not only contractual. Same definitive pin as 2020 (one PRR covers 2020/2022/2024). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2022-04-06..07-11): 19 of 97 days eliminated (weakest of the four windows - a settled spring); longest feasible block May 16-28 (13 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
+          <t>ILA 2021 (Laserfiche id 1462454, repo=Edmonds) Work Order p.14: 'Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ... County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest'. Contract vehicle for a records request: King County RFP 1166-18-PCR (EagleView Technology Corp) via Snohomish County Piggyback PB-19-14BC (Legistar matter 2024-1168). DEFINITIVE PIN = EagleView flight log / photo-centre index via Snohomish County DoIT (Viggo Forde), or a CONNECTExplorer capture-date screenshot (Edmonds holds up to ten accounts under the ILA). City keyProperties (correct endpoint &lt;ImageServer&gt;/keyProperties?f=json; /info/keyProperties 400s on this server, positive control Edmonds_Marsh_2018 returns acquisitionStartDate 2018-08-01T16:22:13+00:00 / End 16:52:13) carry NO date: IMAGE__MODIFICATIONS 'COMPRESSED EMBEDDED MASKED MOSAICKED' - a validated null. Everett's 2020 copy is JPEG2000 and also carries no date; no 2020 MrSID twin with a surviving date was found. A per-frame index CANNOT exist on the county service (mosaic catalog = two whole-project items WASNOH20_3in / WASNOH20_9in). HAZARD: a SECOND 2020 acquisition covers Edmonds - the WA consortium 6-in Hexagon/ADS100 flight of 2020-08-27/28 (program window 2020-08-03..09-06) - DO NOT borrow its date (see context row). Shadow dating (qc/imagery_date_evidence/shadow_dating_2020/): azimuth is reliable (2012 control 8/10 in-window), elevation reads LOW and saturates above ~45 deg, so 2020 elevations are lower bounds - hence no calendar date. 2020 ortho co-registered to 2012 within &lt;=1.5 WM m. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2020-04-13..07-13): 22 of 92 days eliminated; longest feasible blocks May 7-15 (9 d), Apr 13-17, May 26-30, Jun 1-5, Jun 22-26. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q20" s="1" t="inlineStr">
@@ -14195,17 +14226,17 @@
       </c>
       <c r="R20" s="1" t="inlineStr">
         <is>
-          <t>(Everett keyProperties - identity proof)</t>
+          <t>(ILA text, for the chain)</t>
         </is>
       </c>
       <c r="S20" s="1" t="inlineStr">
         <is>
-          <t>https://gismaps.everettwa.gov/manarcgis/rest/services/Imagery/Image2022_3in_sid/ImageServer/keyProperties?f=json</t>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
         </is>
       </c>
       <c r="T20" s="1" t="inlineStr">
         <is>
-          <t>"IMAGE__ENCODING_APPLICATION":"GeoExpress 10.0.1.5035","IMAGE__FORMAT":"MrSID/MG4","IMAGE__INPUT_FILE_SIZE":"675609635568.000000","IMAGE__INPUT_FORMAT":"GeoTIFF" ... "IMAGE__MODIFICATIONS":"COMPRESSED EMBEDDED MASKED MOSAICKED"</t>
+          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects and receipt of imagery by County, County will provide Edmonds with orthogonal imagery for Edmonds's identified area of interest</t>
         </is>
       </c>
       <c r="U20" s="1" t="inlineStr">
@@ -14217,17 +14248,17 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>2024_coe_rgb.tif</t>
+          <t>2022_coe_rgb.tif</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>2024 (CoE)</t>
+          <t>2022 (CoE)</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds Basemap/2024_Aerial_Cached (MapServer over Edmonds2024.sid - no ImageServer, so no keyProperties resource exists); source = Snohomish County 2024 regional project WASNOH24_3in per the 2021 ILA</t>
+          <t>City of Edmonds Basemap/2022_Aerial_Cached; = Snohomish County 2022 regional project WASNOH22_3in. IDENTITY MEASURED: the Edmonds and Everett 2022 MrSIDs are the same county encode (identical input-set byte count 675,609,635,568 B, GeoExpress 10.0.1.5035, EPSG:2285 ftUS geokeys)</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -14252,22 +14283,22 @@
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>7.62 (0.25 ftUS; county Aerial_2024 LowCellSize 0.25)</t>
+          <t>7.62 (0.25 ftUS; county Aerial_2022 LowCellSize 0.25; MrSID input GeoTIFF geokeys 'Linear_Foot_US_Survey' / 2285)</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>2024-03-31 to 2024-05-31 (urban 3 in); the rural 9-in sub-project ran 2024-03-16 to 06-09</t>
+          <t>2022-04-06 to 2022-07-11 (urban 3 in); the rural 9-in sub-project ran 2022-05-31 to 08-11 and does not apply to Edmonds</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>window of 62 days</t>
+          <t>window of 96 days</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -14275,9 +14306,9 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>INFERRED</t>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N21" s="1" t="inlineStr">
@@ -14287,32 +14318,32 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>The 2024 3 inch resolution aerial photos in the urban areas, were captured between March 31, 2024 and May, 31 2024. The 2024 9 inch resolution aerial photos in the rural areas, were captured between March, 16 2024 and June, 9 2024.</t>
+          <t>The 2022 3 inch resolution aerial photos in the urban areas, were captured between April 6, 2022 and July, 11 2022. The 2022 9 inch resolution aerial photos in the rural areas, were captured between May, 31 2022 and August, 11 2022.</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
         <is>
-          <t>Stays INFERRED: no neighbour city holds a 2024 county copy (Everett stops at 2022, Mukilteo at 2019, Lynnwood publishes none), so there is no 2024 analogue of the 2022 byte-identity proof. Same definitive pin as 2020. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2024-03-31..05-31): 18 of 62 days eliminated (29%, strongest of the four); longest feasible block Apr 16-24 (9 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
+          <t>Upgraded INFERRED -&gt; PUBLISHED 2026-08-23: the window is published for a product whose identity with the held file is now measured (byte-count identity of the input set with Everett's Image2022_3in_sid, 'Aerial Photos 2022 Pictometry Mosaic 3 inch resolution urban areas'), not only contractual. Same definitive pin as 2020 (one PRR covers 2020/2022/2024). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2022-04-06..07-11): 19 of 97 days eliminated (weakest of the four windows - a settled spring); longest feasible block May 16-28 (13 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county + Everett services)</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr">
         <is>
-          <t>(ILA text)</t>
+          <t>(Everett keyProperties - identity proof)</t>
         </is>
       </c>
       <c r="S21" s="1" t="inlineStr">
         <is>
-          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
+          <t>https://gismaps.everettwa.gov/manarcgis/rest/services/Imagery/Image2022_3in_sid/ImageServer/keyProperties?f=json</t>
         </is>
       </c>
       <c r="T21" s="1" t="inlineStr">
         <is>
-          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ...</t>
+          <t>"IMAGE__ENCODING_APPLICATION":"GeoExpress 10.0.1.5035","IMAGE__FORMAT":"MrSID/MG4","IMAGE__INPUT_FILE_SIZE":"675609635568.000000","IMAGE__INPUT_FORMAT":"GeoTIFF" ... "IMAGE__MODIFICATIONS":"COMPRESSED EMBEDDED MASKED MOSAICKED"</t>
         </is>
       </c>
       <c r="U21" s="1" t="inlineStr">
@@ -14324,62 +14355,62 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>(not held) City of Edmonds Basemap/2015_Aerial_Cached</t>
+          <t>2024_coe_rgb.tif</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>2015 (CoE service)</t>
+          <t>2024 (CoE)</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>City of Edmonds (source raster Ed_Aerial_2015.tif, 0.25 ftUS EPSG:2285, LZW); content INFERRED = 2015 Western Washington Regional Orthophotography (King County lead, 88 participants; prime GeoTerra, Edmonds frames flown by Valley Air and GeoTerra)</t>
+          <t>City of Edmonds Basemap/2024_Aerial_Cached (MapServer over Edmonds2024.sid - no ImageServer, so no keyProperties resource exists); source = Snohomish County 2024 regional project WASNOH24_3in per the 2021 ILA</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>LOD 21 cache (0.0746 WM m)</t>
+          <t>0.074646</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>metre (Web Mercator)</t>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>EPSG:3857 (cache); source EPSG:2285</t>
+          <t>EPSG:3857</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>5.01 (cache) / 7.62 (source)</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>not measured</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>&lt;= 6.86 flown (MAX_GSD 0.225 ft 'as planned' for all 346 Edmonds frames; two cameras at two altitudes both back-compute to ~6.6-6.9 cm), delivered at the 0.25 ft = 7.62 cm tier (service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS)</t>
+          <t>7.62 (0.25 ftUS; county Aerial_2024 LowCellSize 0.25)</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>2015-04-08 (n=135 photo centres in the city polygon; Valley Air, UltraCam X, 14:13-15:04 PDT) and 2015-04-17 (n=32; GeoTerra, UltraCam Xp, 12:54-13:55 PDT). CONTEST largely resolved: the King Pictometry leg is EXCLUDED by pixel comparison, the 'Aug 7 2015' leg is a DIFFERENT dataset (NAIP/HXIP 2015-08-07), leaving the consortium dates; attribution of Ed_Aerial_2015.tif to the consortium remains INFERRED and the UFMP's '4.8 in' figure is unexplained</t>
+          <t>2024-03-31 to 2024-05-31 (urban 3 in); the rural 9-in sub-project ran 2024-03-16 to 06-09</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>2 flight days (window of 10 days) for the consortium product</t>
+          <t>window of 62 days</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
-          <t>MULTI - two days, two vendors, two cameras within the city (flightlines 16002-16011 Zone 16 / 13007-13015 Zone 13)</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -14389,166 +14420,166 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE15C_POINT_2574/FeatureServer/0/query</t>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>"FILENAME":"13009_57445" ... "UTC_TIME":"19:54:49","MAX_GSD__f":0.225 ... "VENDOR":"GeoTerra","CAMERA":"UltraCam Xp" ... "FLIGHTLINE":"13009","ACQ_DATE":1429228800000 (= 2015-04-17 UTC; first of the photo centres inside the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2015C_ORTHO_IMAGE15C_POINT_2574_citypoly_first3.json). Layer description: It is a reference for the raw image scans, it is not a index for tiled ortho imagery</t>
+          <t>The 2024 3 inch resolution aerial photos in the urban areas, were captured between March 31, 2024 and May, 31 2024. The 2024 9 inch resolution aerial photos in the rural areas, were captured between March, 16 2024 and June, 9 2024.</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
         <is>
-          <t>Photo-centre DAYS are MEASURED; binding them to Ed_Aerial_2015.tif is INFERRED via (a) 0.25 ftUS cell size matching the consortium tier, (b) CRS NAD83 SP WA North ftUS, (c) Edmonds named in GeoTerra's participant table and the consortium agreement signed 2015-06-23 ($3,696.21), (d) leaf-off/high-sun spec matching the tiles. NOTE: no Apr 9 frames exist over Edmonds (the catalogue's 'Apr 8/9/17' was wrong); one Mar 26 frame sits just outside the polygon. King leg excluded: CoE 2015 vs KingCo_Aerial_2015 LOD-20 tiles r=0.036-0.557 at 5 sites vs r=0.988-0.994 for the CoE-2017/King-2017 control. 'Aug 7 2015 / 4.8 in' (UFMP 2019 p.26) traces to the Davey Resource Group 2018 UTC Assessment which names 'USDA, Farm Service Agency' = NAIP 2015 (2015-08-07, 1 m = the same Hexagon flight as the HXIP 1-ft consortium product); '4.8 in' matches no known 2015 product. Phenology caveat from the project's own survey report: 'the need to begin immediate image acquisition due an earlier than normal bud break' - Apr 8/17 is late in a leaf-off window. Vendor/camera cross-validated at serial-number level against the Flight Subcontractor PDF (UCX 60418665 / UCXp 10411033).</t>
+          <t>Stays INFERRED: no neighbour city holds a 2024 county copy (Everett stops at 2022, Mukilteo at 2019, Lynnwood publishes none), so there is no 2024 analogue of the 2022 byte-identity proof. Same definitive pin as 2020. Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2024-03-31..05-31): 18 of 62 days eliminated (29%, strongest of the four); longest feasible block Apr 16-24 (9 d). ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>grid MEASURED (live service); native MEASURED (index MAX_GSD) + PUBLISHED (tier)</t>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED (county service)</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr">
         <is>
-          <t>2015-08-07 15:31 (UFMP/Davey 'August 7th, 2015' imagery = NAIP/HXIP 2015, NOT the city basemap)</t>
+          <t>(ILA text)</t>
         </is>
       </c>
       <c r="S22" s="1" t="inlineStr">
         <is>
-          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2015/wa_fgdc_2015/47122/m_4712214_sw_10_1_20150807.txt</t>
+          <t>https://weblink.edmondswa.gov/WebLink/DocView.aspx?id=1462454&amp;dbid=0&amp;repo=Edmonds</t>
         </is>
       </c>
       <c r="T22" s="1" t="inlineStr">
         <is>
-          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20150807 Currentness_Reference: Ground Condition</t>
+          <t>Upon completion of the 2020, 2022 and 2024 EagleView regional aerial imagery acquisition projects ...</t>
         </is>
       </c>
       <c r="U22" s="1" t="inlineStr">
         <is>
-          <t>context (not held)</t>
+          <t>held imagery</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>2019_naip_rgbi.tif</t>
+          <t>(not held) City of Edmonds Basemap/2015_Aerial_Cached</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>2019n</t>
+          <t>2015 (CoE service)</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>USDA FSA NAIP WA 2019 (DOQQ m_4712213/m_4712214; the WA consortium 2019 1-ft flight carries the same date, i.e. the Hexagon flight)</t>
+          <t>City of Edmonds (source raster Ed_Aerial_2015.tif, 0.25 ftUS EPSG:2285, LZW); content INFERRED = 2015 Western Washington Regional Orthophotography (King County lead, 88 participants; prime GeoTerra, Edmonds frames flown by Valley Air and GeoTerra)</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>LOD 21 cache (0.0746 WM m)</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>metre</t>
+          <t>metre (Web Mercator)</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>EPSG:26910</t>
+          <t>EPSG:3857 (cache); source EPSG:2285</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>5.01 (cache) / 7.62 (source)</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>not measured</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>60 (collected and delivered at 60 cm)</t>
+          <t>&lt;= 6.86 flown (MAX_GSD 0.225 ft 'as planned' for all 346 Edmonds frames; two cameras at two altitudes both back-compute to ~6.6-6.9 cm), delivered at the 0.25 ft = 7.62 cm tier (service pixelSizeX 0.07620015240030481 m = 0.250000 ftUS)</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>2019-10-11</t>
+          <t>2015-04-08 (n=135 photo centres in the city polygon; Valley Air, UltraCam X, 14:13-15:04 PDT) and 2015-04-17 (n=32; GeoTerra, UltraCam Xp, 12:54-13:55 PDT). CONTEST largely resolved: the King Pictometry leg is EXCLUDED by pixel comparison, the 'Aug 7 2015' leg is a DIFFERENT dataset (NAIP/HXIP 2015-08-07), leaving the consortium dates; attribution of Ed_Aerial_2015.tif to the consortium remains INFERRED and the UFMP's '4.8 in' figure is unexplained</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>single day</t>
+          <t>2 flight days (window of 10 days) for the consortium product</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>single (all Edmonds DOQQs carry 20191011; consortium flight-area IDATE '2019 -10-11' at the city centroid)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>PUBLISHED</t>
+          <t>MULTI - two days, two vendors, two cameras within the city (flightlines 16002-16011 Zone 16 / 13007-13015 Zone 13)</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
         </is>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_fgdc_2019/47122/m_4712214_sw_10_060_20191011.txt</t>
+          <t>https://services.arcgis.com/Ej0PsM5Aw677QF1W/arcgis/rest/services/ORTHO_IMAGE15C_POINT_2574/FeatureServer/0/query</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20191011 Currentness_Reference: Ground Condition</t>
+          <t>"FILENAME":"13009_57445" ... "UTC_TIME":"19:54:49","MAX_GSD__f":0.225 ... "VENDOR":"GeoTerra","CAMERA":"UltraCam Xp" ... "FLIGHTLINE":"13009","ACQ_DATE":1429228800000 (= 2015-04-17 UTC; first of the photo centres inside the city polygon; raw response qc/imagery_date_evidence/raw_records/kc_2015C_ORTHO_IMAGE15C_POINT_2574_citypoly_first3.json). Layer description: It is a reference for the raw image scans, it is not a index for tiled ortho imagery</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER. No NAIP metadata record (2015/2017/2021 Digital Coast) contains any leaf-on/leaf-off statement - only 'peak crop growing conditions'; the 'NAIP is leaf-on by spec' assumption has no documentary basis.</t>
+          <t>Photo-centre DAYS are MEASURED; binding them to Ed_Aerial_2015.tif is INFERRED via (a) 0.25 ftUS cell size matching the consortium tier, (b) CRS NAD83 SP WA North ftUS, (c) Edmonds named in GeoTerra's participant table and the consortium agreement signed 2015-06-23 ($3,696.21), (d) leaf-off/high-sun spec matching the tiles. NOTE: no Apr 9 frames exist over Edmonds (the catalogue's 'Apr 8/9/17' was wrong); one Mar 26 frame sits just outside the polygon. King leg excluded: CoE 2015 vs KingCo_Aerial_2015 LOD-20 tiles r=0.036-0.557 at 5 sites vs r=0.988-0.994 for the CoE-2017/King-2017 control. 'Aug 7 2015 / 4.8 in' (UFMP 2019 p.26) traces to the Davey Resource Group 2018 UTC Assessment which names 'USDA, Farm Service Agency' = NAIP 2015 (2015-08-07, 1 m = the same Hexagon flight as the HXIP 1-ft consortium product); '4.8 in' matches no known 2015 product. Phenology caveat from the project's own survey report: 'the need to begin immediate image acquisition due an earlier than normal bud break' - Apr 8/17 is late in a leaf-off window. Vendor/camera cross-validated at serial-number level against the Flight Subcontractor PDF (UCX 60418665 / UCXp 10411033).</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+          <t>grid MEASURED (live service); native MEASURED (index MAX_GSD) + PUBLISHED (tier)</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr">
         <is>
-          <t>2019-10-11</t>
+          <t>2015-08-07 15:31 (UFMP/Davey 'August 7th, 2015' imagery = NAIP/HXIP 2015, NOT the city basemap)</t>
         </is>
       </c>
       <c r="S23" s="1" t="inlineStr">
         <is>
-          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2019_Statewide_imagery_consortium_1_foot_flight_areas/FeatureServer/0/query</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2015/wa_fgdc_2015/47122/m_4712214_sw_10_1_20150807.txt</t>
         </is>
       </c>
       <c r="T23" s="1" t="inlineStr">
         <is>
-          <t>"IDATE":"2019 -10-11" (stray space verbatim; city-centroid point query, raw response qc/imagery_date_evidence/raw_records/wa_2019_1ft_citycentroid.json)</t>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20150807 Currentness_Reference: Ground Condition</t>
         </is>
       </c>
       <c r="U23" s="1" t="inlineStr">
         <is>
-          <t>held imagery</t>
+          <t>context (not held)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2023_naip_rgbi.tif</t>
+          <t>2019_naip_rgbi.tif</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>2023n (was mislabelled 2022n)</t>
+          <t>2019n</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>USDA FSA NAIP WA 2023 (DOQQ m_4712213/m_4712214)</t>
+          <t>USDA FSA NAIP WA 2019 (DOQQ m_4712213/m_4712214; the WA consortium 2019 1-ft flight carries the same date, i.e. the Hexagon flight)</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -14573,17 +14604,17 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>60 delivered (2021/2023-era WA NAIP collected finer and rectified to 60 cm)</t>
+          <t>60 (collected and delivered at 60 cm)</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2019-10-11</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
@@ -14593,7 +14624,7 @@
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>single (all 8 Edmonds QQs: m_47122{13,14}_*_10_060_20231007_20240209)</t>
+          <t>single (all Edmonds DOQQs carry 20191011; consortium flight-area IDATE '2019 -10-11' at the city centroid)</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -14603,17 +14634,17 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_fgdc_2023/47122/m_4712214_sw_10_060_20231007_20240209.xml</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_fgdc_2019/47122/m_4712214_sw_10_060_20191011.txt</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>&lt;gco:CharacterString&gt;m_4712214_sw_10_060_20231007.tif&lt;/gco:CharacterString&gt; (the DOQQ file name in the ISO metadata record; 20231007 = acquisition date field)</t>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20191011 Currentness_Reference: Ground Condition</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues). Context: NAIP 2021 over Edmonds exists (all 8 QQs STAC datetime 2021-07-13, INFERRED from file names - the FGDC sidecars for quad 47122 are absent from the Azure mirror).</t>
+          <t>OCTOBER. No NAIP metadata record (2015/2017/2021 Digital Coast) contains any leaf-on/leaf-off statement - only 'peak crop growing conditions'; the 'NAIP is leaf-on by spec' assumption has no documentary basis.</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -14621,9 +14652,21 @@
           <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
         </is>
       </c>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr">
+        <is>
+          <t>2019-10-11</t>
+        </is>
+      </c>
+      <c r="S24" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2019_Statewide_imagery_consortium_1_foot_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T24" s="1" t="inlineStr">
+        <is>
+          <t>"IDATE":"2019 -10-11" (stray space verbatim; city-centroid point query, raw response qc/imagery_date_evidence/raw_records/wa_2019_1ft_citycentroid.json)</t>
+        </is>
+      </c>
       <c r="U24" s="1" t="inlineStr">
         <is>
           <t>held imagery</t>
@@ -14633,62 +14676,62 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>lidar_snoh_chm.tif</t>
+          <t>2023_naip_rgbi.tif</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>2016 (lidar)</t>
+          <t>2023n (was mislabelled 2022n)</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>USGS 3DEP HAG via Planetary Computer, reprojected by the project; underlying lidar = USGS_LPC_WA_Western_North_2016 (QSI for USGS/WADNR)</t>
+          <t>USDA FSA NAIP WA 2023 (DOQQ m_4712213/m_4712214)</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>1.000009</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+          <t>metre</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>EPSG:3857</t>
+          <t>EPSG:26910</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>n/a (bilinear-upsampled ~2 m product)</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>~200 (HAG raster); lidar 0.7 m spacing</t>
+          <t>60 delivered (2021/2023-era WA NAIP collected finer and rectified to 60 cm)</t>
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>2016-03-17 to 2016-09-30 (Western Washington 3DEP NORTH AOI; all 46 tiles over the city are North-block)</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>window of 198 days</t>
+          <t>single day</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>single (all 8 Edmonds QQs: m_47122{13,14}_*_10_060_20231007_20240209)</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -14698,104 +14741,92 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>https://www.fisheries.noaa.gov/inport/item/51853</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_fgdc_2023/47122/m_4712214_sw_10_060_20231007_20240209.xml</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>North: March 17 - Sept 30, 2016 ... South: March 17, 2016 - June 6, 2017</t>
+          <t>&lt;gco:CharacterString&gt;m_4712214_sw_10_060_20231007.tif&lt;/gco:CharacterString&gt; (the DOQQ file name in the ISO metadata record; 20231007 = acquisition date field)</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>UNITS TRAP #4: grid is 1.0 m in EPSG:3857 = 67.2 cm true ground at 47.81N, not 1 m. Narrowed from 15 months (whole project) to the North window by point-in-polygon on NOAA's tile index (46/46 tiles /north/). Reference raster, excluded from the imagery count.</t>
+          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues). Context: NAIP 2021 over Edmonds exists (all 8 QQs STAC datetime 2021-07-13, INFERRED from file names - the FGDC sidecars for quad 47122 are absent from the Azure mirror).</t>
         </is>
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; native PUBLISHED</t>
-        </is>
-      </c>
-      <c r="R25" s="1" t="inlineStr">
-        <is>
-          <t>2016-03-30 (INFERRED from the tile filename prefix 20160330_USGS_LPC_WA_Western_North_2016_q47122G4405 - a FILE NAME; 3/30/16 is a flight day for all three contractors in QSI report Table 3)</t>
-        </is>
-      </c>
-      <c r="S25" s="1" t="inlineStr">
-        <is>
-          <t>https://noaa-nos-coastal-lidar-pds.s3.amazonaws.com/laz/geoid18/6331/tileindex_wa2016_west_wa_m6331.gpkg</t>
-        </is>
-      </c>
-      <c r="T25" s="1" t="inlineStr">
-        <is>
-          <t>20160330_USGS_LPC_WA_Western_North_2016_q47122G4405_LAS_2018.copc.laz</t>
-        </is>
-      </c>
+          <t>grid/true MEASURED; effective MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R25" s="1" t="inlineStr"/>
+      <c r="S25" s="1" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
       <c r="U25" s="1" t="inlineStr">
         <is>
-          <t>reference raster</t>
+          <t>held imagery</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>PSLC_2005/ (47 laz tiles)</t>
+          <t>lidar_snoh_chm.tif</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>2005 (lidar)</t>
+          <t>2016 (lidar)</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Puget Sound LiDAR Consortium 2005 North Puget Sound Lowlands (Terrapoint), InPort 50149</t>
+          <t>USGS 3DEP HAG via Planetary Computer, reprojected by the project; underlying lidar = USGS_LPC_WA_Western_North_2016 (QSI for USGS/WADNR)</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>point cloud (no grid)</t>
+          <t>1.000009</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>NAD83(HARN) UTM 10N, NAVD88 GEOID18</t>
+          <t>EPSG:3857</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>n/a (point cloud)</t>
+          <t>67.16</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>n/a (bilinear-upsampled ~2 m product)</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>n/a (2 m nominal spacing)</t>
+          <t>~200 (HAG raster); lidar 0.7 m spacing</t>
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>2005-02-27 (Edmonds sub-project, 11 sq mi)</t>
+          <t>2016-03-17 to 2016-09-30 (Western Washington 3DEP NORTH AOI; all 46 tiles over the city are North-block)</t>
         </is>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>single day</t>
+          <t>window of 198 days</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>single (sub-project row)</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -14805,92 +14836,104 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>https://www.fisheries.noaa.gov/inport/item/50149</t>
+          <t>https://www.fisheries.noaa.gov/inport/item/51853</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>project, area (sq mi), date(s) collected, vert. acc (cm), horiz acc. (cm), RMSE (m) - ... - Edmonds, 11, 2/27/2005, 25, 60, 0.100 - Mt. Lake Terrace, 4, 7/15/2005-9/15/2005, 25, 60, 0.100 - Mukilteo, 16, 2/27/2005, 25, 60, 0.100</t>
+          <t>North: March 17 - Sept 30, 2016 ... South: March 17, 2016 - June 6, 2017</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
-          <t>Density 0.25 pts/m2 stated (~0.17 cross-checked, IMAGERY_FACTS 8.1). LEAF-OFF (late February). Record-internal inconsistency: Mt. Lake Terrace sub-project dates run past the record's own Time Frame end (2005-07-15). Held at D:/edmonds-pipeline/Imagery/PSLC_2005 and Full_Image/PSLC_2005 (IMAGERY_FACTS 8.2).</t>
+          <t>UNITS TRAP #4: grid is 1.0 m in EPSG:3857 = 67.2 cm true ground at 47.81N, not 1 m. Narrowed from 15 months (whole project) to the North window by point-in-polygon on NOAA's tile index (46/46 tiles /north/). Reference raster, excluded from the imagery count.</t>
         </is>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>density PUBLISHED</t>
-        </is>
-      </c>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R26" s="1" t="inlineStr">
+        <is>
+          <t>2016-03-30 (INFERRED from the tile filename prefix 20160330_USGS_LPC_WA_Western_North_2016_q47122G4405 - a FILE NAME; 3/30/16 is a flight day for all three contractors in QSI report Table 3)</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t>https://noaa-nos-coastal-lidar-pds.s3.amazonaws.com/laz/geoid18/6331/tileindex_wa2016_west_wa_m6331.gpkg</t>
+        </is>
+      </c>
+      <c r="T26" s="1" t="inlineStr">
+        <is>
+          <t>20160330_USGS_LPC_WA_Western_North_2016_q47122G4405_LAS_2018.copc.laz</t>
+        </is>
+      </c>
       <c r="U26" s="1" t="inlineStr">
         <is>
-          <t>reference lidar</t>
+          <t>reference raster</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>ccap_2016_hires_lc_snohfull.tif</t>
+          <t>PSLC_2005/ (47 laz tiles)</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>2016 (C-CAP ref)</t>
+          <t>2005 (lidar)</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>NOAA OCM C-CAP hi-res land cover, Snohomish County 2016 (InPort 53263 - record RECOVERED as an InPort XML export on coast.noaa.gov; fisheries.noaa.gov still 403)</t>
+          <t>Puget Sound LiDAR Consortium 2005 North Puget Sound Lowlands (Terrapoint), InPort 50149</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>point cloud (no grid)</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>metre</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>EPSG:26910</t>
+          <t>NAD83(HARN) UTM 10N, NAVD88 GEOID18</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>n/a (point cloud)</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>n/a (thematic)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>100 (1 m product)</t>
+          <t>n/a (2 m nominal spacing)</t>
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>summer 2016 (source imagery, stated as NAIP) - CONTESTED: no WA NAIP 2016 exists (Azure NAIP v002/wa/ holds 2011, 2013, 2015, 2017, 2019, 2021, 2023 only)</t>
+          <t>2005-02-27 (Edmonds sub-project, 11 sq mi)</t>
         </is>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>single day</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>single (sub-project row)</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -14900,22 +14943,22 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>https://chs.coast.noaa.gov/htdata/raster1/landcover/bulkdownload/hires/wa/WA_Snohomish_2016_lc.xml</t>
+          <t>https://www.fisheries.noaa.gov/inport/item/50149</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>The timeframe for this metadata is summer 2016. These maps are developed utilizing high resolution National Agriculture Imagery Program (NAIP) imagery, and can be used to track changes in the landscape through time.</t>
+          <t>project, area (sq mi), date(s) collected, vert. acc (cm), horiz acc. (cm), RMSE (m) - ... - Edmonds, 11, 2/27/2005, 25, 60, 0.100 - Mt. Lake Terrace, 4, 7/15/2005-9/15/2005, 25, 60, 0.100 - Mukilteo, 16, 2/27/2005, 25, 60, 0.100</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
-          <t>Candidate reconciliation (INFERENCE): the 'summer 2016' imagery is the HXIP Aug 11-12 2016 flight (the WA consortium product is itself branded 'NAIP_2016' on AGOL), or NOAA used NAIP 2015 (2015-08-07) and labelled the product 2016 - UNRESOLVED. Traps in the record: &lt;start-date-time&gt;2016-01-01 is a year placeholder; &lt;publish-date&gt;2019-03-14 is publication. Ancillary: NGS MLLW orthoimagery 2014 for shore classes. Reference raster.</t>
+          <t>Density 0.25 pts/m2 stated (~0.17 cross-checked, IMAGERY_FACTS 8.1). LEAF-OFF (late February). Record-internal inconsistency: Mt. Lake Terrace sub-project dates run past the record's own Time Frame end (2005-07-15). Held at D:/edmonds-pipeline/Imagery/PSLC_2005 and Full_Image/PSLC_2005 (IMAGERY_FACTS 8.2).</t>
         </is>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>grid/true MEASURED; native PUBLISHED</t>
+          <t>density PUBLISHED</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -14923,24 +14966,24 @@
       <c r="T27" s="1" t="inlineStr"/>
       <c r="U27" s="1" t="inlineStr">
         <is>
-          <t>reference raster</t>
+          <t>reference lidar</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>ccap_2021_hires_lc.tif</t>
+          <t>ccap_2016_hires_lc_snohfull.tif</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>2021 (C-CAP v2 ref)</t>
+          <t>2016 (C-CAP ref)</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>NOAA OCM C-CAP hi-res v2 'Refined' Puget Sound 2021 (InPort 79723; Ecopia extraction, NV5 refinement)</t>
+          <t>NOAA OCM C-CAP hi-res land cover, Snohomish County 2016 (InPort 53263 - record RECOVERED as an InPort XML export on coast.noaa.gov; fisheries.noaa.gov still 403)</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -14970,22 +15013,22 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>100 (1 m extraction from '30cm or better' imagery)</t>
+          <t>100 (1 m product)</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>2021 (year only; 'Acquisition date of the Aerial Imagery')</t>
+          <t>summer 2016 (source imagery, stated as NAIP) - CONTESTED: no WA NAIP 2016 exists (Azure NAIP v002/wa/ holds 2011, 2013, 2015, 2017, 2019, 2021, 2023 only)</t>
         </is>
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>year only</t>
+          <t>season</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>multi (mosaic of vendor imagery)</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -14995,17 +15038,17 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>https://ocmgeodatastor1.blob.core.windows.net/ccap/bulk_download/C-CAP_High-Resolution_Data/Refined_C-CAP_High-Resolution_Land_Cover_Classification/CONUS/wa_puget_2021_ccap_v2_hires_landcover.xml</t>
+          <t>https://chs.coast.noaa.gov/htdata/raster1/landcover/bulkdownload/hires/wa/WA_Snohomish_2016_lc.xml</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>&lt;currentness-reference&gt;Acquisition date of the Aerial Imagery&lt;/currentness-reference&gt; ... &lt;time-frame-type&gt;Discrete&lt;/time-frame-type&gt; &lt;start-date-time&gt;2021&lt;/start-date-time&gt; ... Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI</t>
+          <t>The timeframe for this metadata is summer 2016. These maps are developed utilizing high resolution National Agriculture Imagery Program (NAIP) imagery, and can be used to track changes in the landscape through time.</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
         <is>
-          <t>The record was created 2026-04-28 and may post-date the held clip (2026-07-06); best-available lineage, not proven identical. Record defects: Ohio/Houston copy-paste text, 'Never Published', 'best-available-metadata: No'. LICENSING (verbatim, for the Licensing_Risk sheet): 'Users are granted a perpetual, non-exclusive, irrevocable, worldwide license to use these data ... with the exception of creating, training, improving, modifying, validating, testing, evaluating, or otherwise leveraging machine learning algorithms in order to explicitly create similar land cover data for a period of five years from its date of creation.' The Phase-1 canopy record (InPort 70562, created 2023-09-30) carries the broader unqualified form ('may not be used for the purpose of ... testing, or evaluating machine learning algorithms ... except with the express written consent of Ecopia Tech Corporation'). This project uses the product as an EVALUATION reference - flag for Kam.</t>
+          <t>Candidate reconciliation (INFERENCE): the 'summer 2016' imagery is the HXIP Aug 11-12 2016 flight (the WA consortium product is itself branded 'NAIP_2016' on AGOL), or NOAA used NAIP 2015 (2015-08-07) and labelled the product 2016 - UNRESOLVED. Traps in the record: &lt;start-date-time&gt;2016-01-01 is a year placeholder; &lt;publish-date&gt;2019-03-14 is publication. Ancillary: NGS MLLW orthoimagery 2014 for shore classes. Reference raster.</t>
         </is>
       </c>
       <c r="Q28" s="1" t="inlineStr">
@@ -15025,62 +15068,62 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>(not held) WA Statewide Imagery Consortium 2020 6-inch (Hexagon, Leica ADS100)</t>
+          <t>ccap_2021_hires_lc.tif</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>2020 (SECOND 2020 acquisition - NOT the anchor)</t>
+          <t>2021 (C-CAP v2 ref)</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>WA OCIO/WaTech Statewide Imagery Consortium, flown by Hexagon under the 2020 NAIP Imaging Program</t>
+          <t>NOAA OCM C-CAP hi-res v2 'Refined' Puget Sound 2021 (InPort 79723; Ecopia extraction, NV5 refinement)</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>metre</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>EPSG:26910</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>15 (6 in product), nominal flight GSD 20</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>n/a (thematic)</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>20 (nominal)</t>
+          <t>100 (1 m extraction from '30cm or better' imagery)</t>
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>2020-08-28 (flight-area polygon at the city centroid; 2020-08-27 also intersects the city bbox); program window 2020-08-03 to 2020-09-06</t>
+          <t>2021 (year only; 'Acquisition date of the Aerial Imagery')</t>
         </is>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>day (coarse flight-area block, 911-1263 sq mi)</t>
+          <t>year only</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
-          <t>multi (2 blocks over the city)</t>
+          <t>multi (mosaic of vendor imagery)</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -15090,154 +15133,249 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>https://www.arcgis.com/sharing/rest/content/items/dd83978971d8421eb6b1a7273ba51f6e?f=json</t>
+          <t>https://ocmgeodatastor1.blob.core.windows.net/ccap/bulk_download/C-CAP_High-Resolution_Data/Refined_C-CAP_High-Resolution_Land_Cover_Classification/CONUS/wa_puget_2021_ccap_v2_hires_landcover.xml</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>Digital aerial imagery for Washington state was collected by Hexagon as part of the 2020 NAIP Imaging Program. Imagery was collected between August 3, 2020 and September 6, 2020 using Leica ADS100 digital camera systems. The project was flown at heights ranging from 8,000 ft msl to 15,500 ft msl resulting in a nominal GSD of 20cm.</t>
+          <t>&lt;currentness-reference&gt;Acquisition date of the Aerial Imagery&lt;/currentness-reference&gt; ... &lt;time-frame-type&gt;Discrete&lt;/time-frame-type&gt; &lt;start-date-time&gt;2021&lt;/start-date-time&gt; ... Initial 1m spatial resolution feature extraction for Impervious, Water, and Canopy (tree and scrub/shrub) mapping was conducted by Ecopia AI</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
-          <t>HAZARD ROW: a different vendor, camera, resolution and season from 2020_coe_rgb.tif (EagleView 3 in, Apr-Jul). Year-matched substitution would introduce a ~4.5-month error - exactly the 2015 three-way pattern. Not held; a late-August leaf-on 15 cm 4-band product if ever wanted.</t>
+          <t>The record was created 2026-04-28 and may post-date the held clip (2026-07-06); best-available lineage, not proven identical. Record defects: Ohio/Houston copy-paste text, 'Never Published', 'best-available-metadata: No'. LICENSING (verbatim, for the Licensing_Risk sheet): 'Users are granted a perpetual, non-exclusive, irrevocable, worldwide license to use these data ... with the exception of creating, training, improving, modifying, validating, testing, evaluating, or otherwise leveraging machine learning algorithms in order to explicitly create similar land cover data for a period of five years from its date of creation.' The Phase-1 canopy record (InPort 70562, created 2023-09-30) carries the broader unqualified form ('may not be used for the purpose of ... testing, or evaluating machine learning algorithms ... except with the express written consent of Ecopia Tech Corporation'). This project uses the product as an EVALUATION reference - flag for Kam.</t>
         </is>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>PUBLISHED</t>
-        </is>
-      </c>
-      <c r="R29" s="1" t="inlineStr">
-        <is>
-          <t>2020-08-28 / 2020-08-27</t>
-        </is>
-      </c>
-      <c r="S29" s="1" t="inlineStr">
-        <is>
-          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/ArcGIS/rest/services/2020_Statewide_imagery_consortium_6_inch_flight_areas/FeatureServer/0/query</t>
-        </is>
-      </c>
-      <c r="T29" s="1" t="inlineStr">
-        <is>
-          <t>"IDATE":"2020-08-28" (city centroid) ... "IDATE":"2020-08-27" (also intersects the city bbox; raw responses qc/imagery_date_evidence/raw_records/wa_2020_6in_*.json)</t>
-        </is>
-      </c>
+          <t>grid/true MEASURED; native PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R29" s="1" t="inlineStr"/>
+      <c r="S29" s="1" t="inlineStr"/>
+      <c r="T29" s="1" t="inlineStr"/>
       <c r="U29" s="1" t="inlineStr">
         <is>
-          <t>context (not held)</t>
+          <t>reference raster</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
+          <t>(not held) WA Statewide Imagery Consortium 2020 6-inch (Hexagon, Leica ADS100)</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>2020 (SECOND 2020 acquisition - NOT the anchor)</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>WA OCIO/WaTech Statewide Imagery Consortium, flown by Hexagon under the 2020 NAIP Imaging Program</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>15 (6 in product), nominal flight GSD 20</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>20 (nominal)</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>2020-08-28 (flight-area polygon at the city centroid; 2020-08-27 also intersects the city bbox); program window 2020-08-03 to 2020-09-06</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>day (coarse flight-area block, 911-1263 sq mi)</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>multi (2 blocks over the city)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>https://www.arcgis.com/sharing/rest/content/items/dd83978971d8421eb6b1a7273ba51f6e?f=json</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>Digital aerial imagery for Washington state was collected by Hexagon as part of the 2020 NAIP Imaging Program. Imagery was collected between August 3, 2020 and September 6, 2020 using Leica ADS100 digital camera systems. The project was flown at heights ranging from 8,000 ft msl to 15,500 ft msl resulting in a nominal GSD of 20cm.</t>
+        </is>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>HAZARD ROW: a different vendor, camera, resolution and season from 2020_coe_rgb.tif (EagleView 3 in, Apr-Jul). Year-matched substitution would introduce a ~4.5-month error - exactly the 2015 three-way pattern. Not held; a late-August leaf-on 15 cm 4-band product if ever wanted.</t>
+        </is>
+      </c>
+      <c r="Q30" s="1" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t>2020-08-28 / 2020-08-27</t>
+        </is>
+      </c>
+      <c r="S30" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/ArcGIS/rest/services/2020_Statewide_imagery_consortium_6_inch_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="T30" s="1" t="inlineStr">
+        <is>
+          <t>"IDATE":"2020-08-28" (city centroid) ... "IDATE":"2020-08-27" (also intersects the city bbox; raw responses qc/imagery_date_evidence/raw_records/wa_2020_6in_*.json)</t>
+        </is>
+      </c>
+      <c r="U30" s="1" t="inlineStr">
+        <is>
+          <t>context (not held)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>(not held) WA Statewide Imagery Consortium 2018 6-inch; Edmonds_Marsh_2018 drone</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>2018 (two distinct acquisitions)</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>WA consortium (Hexagon) / City of Edmonds Imagery/Edmonds_Marsh_2018 ImageServer</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>15 (consortium) / 2.5 (Marsh cache LOD)</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>n/a / 3.36 (Marsh pixelSizeX 0.0336 m)</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>2018-08-07 (consortium flight area over Edmonds) ; 2018-08-01 16:22-16:52 UTC (Marsh drone sortie) - six days apart, NOT the same acquisition</t>
         </is>
       </c>
-      <c r="K30" s="1" t="inlineStr">
+      <c r="K31" s="1" t="inlineStr">
         <is>
           <t>day / exact timestamp</t>
         </is>
       </c>
-      <c r="L30" s="1" t="inlineStr">
+      <c r="L31" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
       </c>
-      <c r="N30" s="1" t="inlineStr">
+      <c r="N31" s="1" t="inlineStr">
         <is>
           <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2018FlightAreas/FeatureServer/0/query</t>
         </is>
       </c>
-      <c r="O30" s="1" t="inlineStr">
+      <c r="O31" s="1" t="inlineStr">
         <is>
           <t>"IDATE":"2018-08-07" (city-centroid point query; raw response qc/imagery_date_evidence/raw_records/wa_2018_6in_citycentroid.json)</t>
         </is>
       </c>
-      <c r="P30" s="1" t="inlineStr">
+      <c r="P31" s="1" t="inlineStr">
         <is>
           <t>Recorded to prevent conflation. The Marsh service is the project's only Edmonds layer with a machine-readable timestamp and the positive control for keyProperties queries (correct path: /gis/rest/services/.../ImageServer/keyProperties?f=json).</t>
         </is>
       </c>
-      <c r="Q30" s="1" t="inlineStr">
+      <c r="Q31" s="1" t="inlineStr">
         <is>
           <t>PUBLISHED</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr">
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>2018-08-01T16:22:13+00:00 to 16:52:13 (Marsh)</t>
         </is>
       </c>
-      <c r="S30" s="1" t="inlineStr">
+      <c r="S31" s="1" t="inlineStr">
         <is>
           <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer/keyProperties?f=json</t>
         </is>
       </c>
-      <c r="T30" s="1" t="inlineStr">
+      <c r="T31" s="1" t="inlineStr">
         <is>
           <t>"acquisitionEndDate":"2018-08-01T16:52:13+00:00","acquisitionStartDate":"2018-08-01T16:22:13+00:00"</t>
         </is>
       </c>
-      <c r="U30" s="1" t="inlineStr">
+      <c r="U31" s="1" t="inlineStr">
         <is>
           <t>context (not held)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U30"/>
+  <autoFilter ref="A1:U31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16564,7 +16702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P221"/>
+  <dimension ref="A1:P222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27149,7 +27287,7 @@
       </c>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2016_snoh_1ft_rgbi.tif (coverage 82.33 &gt; 38.0). YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr">
@@ -27231,7 +27369,7 @@
       </c>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2016_snoh_1ft_rgbi.tif (coverage 82.33 &gt; 38.0). YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr">
@@ -27313,7 +27451,7 @@
       </c>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2016_snoh_1ft_rgbi.tif (coverage 82.33 &gt; 38.0). YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr">
@@ -34704,6 +34842,83 @@
       <c r="P221" s="1" t="inlineStr">
         <is>
           <t>THIS IS THE ANSWER TO (b). The Ecopia item names the source imagery verbatim: "Imagery Used for Extraction:" / "Pixel resolution: 15 cm (6\")" / "Camera sensor: Hexagon Pushbroom (Content Mapper)" / "Date of capture: 06/25/2021 - 08/14/2022". So the source is a HEXAGON commercial capture, not a state flight. NOT PUBLICLY DOWNLOADABLE - MEASURED: GET https://services.hxgncontent.com/streaming/wms?service=WMS&amp;request=GetCapabilities&amp;version=1.3.0 returns HTTP 401 Unauthorized (720-byte Tomcat error page) with no token. Corroborating evidence chain that this is the HxGN Content Program (inference, not a verbatim quote): the service host is services.hxgncontent.com, the item description is titled "Hexagon Content Program", and WAGeoservices publishes a companion item "AGOL Hexagon Token Replace (Python toolbox)" (id 59061adf38174773baab16ceb44646cf) whose snippet is "Downloadable Python toolbox that can be used to replace the access token embedded in an AGOL or Portal Item that references the Hexagon streaming service" - i.e. token-gated. Item-level access is "public" but that governs the AGOL item record, NOT the imagery. NO statewide 2021-2022 ortho service exists anywhere on imagery-public.watech.wa.gov - MEASURED by enumerating all 8 folders / 97 services; the newest statewide imagery on that server is NAIP 2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2016 full extent, native 1 ft (HXIP 2016)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 4 bands; effective 40.56 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2016/ImageServer</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2016/ImageServer</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2016_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>this file REPLACES 2016_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>decision REPLACE: wins=['coverage 82.33 &gt; 38.0'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S16</t>
         </is>
       </c>
     </row>
@@ -35526,7 +35741,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
+          <t>RESOLVED 2026-08-23: REPLACE by 2016_snoh_1ft_rgbi.tif. YES - re-acquire full extent from Snohomish ImageServer (Tier A #1)</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11392,6 +11392,217 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>median of 5 Method_Provenance sites; common-grid vs 2016_snoh_rgbi.tif: new 42.98 / held 43.2 cm, HF ratio 1.013</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2002_usgs_30cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>USGS_HRO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E14" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>median of 5 Method_Provenance sites; common-grid vs 2002_king_rgb.tif: new 56.25 / held 90.86 cm, HF ratio 1.538</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2015_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NAIP_NOAA/2015</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>133.11</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2017_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NAIP_NOAA/2017</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E16" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NAIP_NOAA/2021</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E17" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2018_coe_marsh2cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CoE</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>median of 0 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2017_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E19" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2019_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -15374,8 +15585,673 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2015_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>2015n (campaign N15)</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2015_6208/ via pipeline/acquire_imagery.py (files)</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>133.11 (median of 5 sites; 1.33x its grid)</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>100 (delivered 1 m)</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>2015-08-07</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="inlineStr">
+        <is>
+          <t>single (all 8 Edmonds DOQQs carry 20150807)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2015/wa_fgdc_2015/47122/m_4712214_sw_10_1_20150807.txt</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date: 20150807 Currentness_Reference: Ground Condition</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_NOAA\2015\_acq\N15\measure.json): 7534x10661 px, 4 bands, EPSG:26910, 267,712,247 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 44.02, NDVI p90 0.697); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. leaf-on pair to the Feb-Mar 2015 King file</t>
+        </is>
+      </c>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>2017_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>2017n (campaign N17)</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2017_8572/ via pipeline/acquire_imagery.py (files)</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>132.41 (median of 5 sites; 1.32x its grid)</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>100 (delivered 1 m)</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
+        <is>
+          <t>2017-08-15 (m_4712214 quads) and 2017-08-21 (m_4712213 quads)</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr">
+        <is>
+          <t>2 flight days</t>
+        </is>
+      </c>
+      <c r="L33" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (2 days; Edmonds straddles the two quads)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2017_8572/urllist8572.txt</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>m_4712213_ne_10_1_20170821.tif (the DOQQ file names in the provider's own urllist, saved to qc/imagery_date_evidence/raw_records/urllist8572.txt) ... m_4712214_nw_10_1_20170815.tif</t>
+        </is>
+      </c>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_NOAA\2017\_acq\N17\measure.json): 7534x10661 px, 4 bands, EPSG:26910, 258,837,380 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 58.65, NDVI p90 0.898); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. August 4-band acquisition vs the May Pictometry mosaic held twice</t>
+        </is>
+      </c>
+      <c r="Q33" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R33" s="1" t="inlineStr"/>
+      <c r="S33" s="1" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>2021_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>2021n (campaign N21)</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2021_9586/ via pipeline/acquire_imagery.py (files)</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>81.74 (median of 5 sites; 1.36x its grid)</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>60 delivered (native 15 cm, rectified 4x)</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
+        <is>
+          <t>2021-07-13</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L34" s="1" t="inlineStr">
+        <is>
+          <t>single (all 8 Edmonds QQs 2021-07-13)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>https://chs.coast.noaa.gov/htdata/raster5/imagery/WA_NAIP_2021_9586/stac/noaa_imagery_item_collection_m9586.json</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>"id": "m_4712213_ne_10_060_20210713", "properties": {"created": "2024-04-02 ...", "license": "NLPL", "datetime": "2021-07-13T00:00:00Z"}</t>
+        </is>
+      </c>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_NOAA\2021\_acq\N21\measure.json): 12556x17768 px, 4 bands, EPSG:26910, 706,833,908 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 73.41, NDVI p90 0.951); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. STAC datetime; the per-quad FGDC sidecars for quad 47122 are absent from the Azure mirror (grade stays PUBLISHED on the provider's STAC record)</t>
+        </is>
+      </c>
+      <c r="Q34" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>2002_usgs_30cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>2002u (campaign U02)</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>https://wagda.lib.washington.edu:6080/arcgis/rest/services/Imagery_services/PugetSound_2002/ImageServer via pipeline/acquire_imagery.py (--via download: original source tiles)</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>41.41 (median of 5 sites; 1.38x its grid); common grid vs held: 56.25 vs 90.86 cm, HF ratio 1.538</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>33 acquired; delivered 0.98-ft/30 cm USGS tiles (these ARE the delivered tiles)</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND for the Edmonds pixels (CONTESTED product-level 2002-06-11 - see the 2002_king_rgb.tif row)</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20040225060658if_/http://www.metrokc.gov/gis/sdc/raster/ortho/Ortho2002USGSNATMetadata.html</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>Source_Time_Period_of_Content: Time_Period_Information: Single_Date/Time: Calendar_Date:  20020611 Source_Citation_Abbreviation:  1192_6574_089 Source_Contribution:  Aerial photography used in orthorectification</t>
+        </is>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\USGS_HRO\_acq\U02\measure.json): 25112x35535 px, 3 bands, EPSG:26910, 2,010,711,608 B; city coverage 100.0%, study-extent 80.58%; JPEG 8x8 signature absent. Decision REPLACE: wins=['effective (common grid) 56.25 vs 90.86 cm', 'HF energy ratio 1.538 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]. SAME product the King cache served (USGS HRO Seattle-Tacoma) - the date question is unchanged by the better copy</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R35" s="1" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>2018_coe_marsh2cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>2018m (campaign M18)</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>0.037323</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:3857</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>3.08 (footprint-local)</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>3.36 (source pixelSizeX 0.0336 WM m; drone)</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>2018-08-01 16:22-16:52 UTC</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr">
+        <is>
+          <t>exact timestamp (30-minute sortie)</t>
+        </is>
+      </c>
+      <c r="L36" s="1" t="inlineStr">
+        <is>
+          <t>single sortie</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer/keyProperties?f=json</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>"acquisitionEndDate":"2018-08-01T16:52:13+00:00","acquisitionStartDate":"2018-08-01T16:22:13+00:00"</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\CoE\_acq\M18\measure.json): 27090x25379 px, 3 bands, EPSG:3857, 776,564,473 B; city coverage 1.03%, study-extent 0.32%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. WAIVER: 2026-08-23: stitch-vs-direct differs by 0.002% of pixels and nearest!=bilinear on every lattice tried (service extent, WM LOD 22) - a singleFusedMapCache re-renders through its own resampler, so a byte-faithful copy is unattainable. Accepted as a DISPLAY-CACHE COPY (JPEG q75 provenance recorded); seams may carry +/-decode-noise DN steps. the only Edmonds layer with a machine-readable timestamp; marsh footprint only (~1 km^2)</t>
+        </is>
+      </c>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>2017_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>2017s (campaign S17)</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2017/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>40.24 (median of 5 sites; 1.32x its grid)</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
+        <is>
+          <t>2017-08-15 and 2017-08-21 (WA consortium 1-ft flight areas over Edmonds)</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr">
+        <is>
+          <t>2 flight days</t>
+        </is>
+      </c>
+      <c r="L37" s="1" t="inlineStr">
+        <is>
+          <t>MULTI (2 flight areas)</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/Statewide_Imagery_2017_Consortium_1_ft_Footprints_(Dates_and_Times)/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>"IDATE":"2017-08-15" (city centroid) ... "IDATE":"2017-08-21" (also intersects the city bbox; raw responses qc/imagery_date_evidence/raw_records/wa_2017_1ft_citybbox.json)</t>
+        </is>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S17\measure.json): 25116x35259 px, 4 bands, EPSG:2285, 2,907,364,608 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 51.48, NDVI p90 0.667); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. the county's own HXIP flight - a different August acquisition from the May Pictometry mosaic</t>
+        </is>
+      </c>
+      <c r="Q37" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R37" s="1" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2019_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>2019s (campaign S19)</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2019/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>42.58 (median of 5 sites; 1.4x its grid)</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
+        <is>
+          <t>2019-10-11 (WA consortium 1-ft flight area over Edmonds; same Hexagon flight as NAIP 2019)</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="inlineStr">
+        <is>
+          <t>single flight area</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2019_Statewide_imagery_consortium_1_foot_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>"IDATE":"2019 -10-11" (stray space verbatim; city-centroid point query, raw response qc/imagery_date_evidence/raw_records/wa_2019_1ft_citycentroid.json)</t>
+        </is>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S19\measure.json): 25116x35259 px, 4 bands, EPSG:2285, 2,890,831,516 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 59.29, NDVI p90 0.614); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. OCTOBER - same late-season caveat as 2019n</t>
+        </is>
+      </c>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R38" s="1" t="inlineStr"/>
+      <c r="S38" s="1" t="inlineStr"/>
+      <c r="T38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U31"/>
+  <autoFilter ref="A1:U38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16702,7 +17578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P222"/>
+  <dimension ref="A1:P229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20809,7 +21685,7 @@
       </c>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>REPLACE 2026-08-23 -&gt; 2002_usgs_30cm_rgb.tif (effective (common grid) 56.25 vs 90.86 cm; HF energy ratio 1.538 (sharper on a common grid); no JPEG block signature (held has one)). no</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
@@ -20891,7 +21767,7 @@
       </c>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>REPLACE 2026-08-23 -&gt; 2002_usgs_30cm_rgb.tif (effective (common grid) 56.25 vs 90.86 cm; HF energy ratio 1.538 (sharper on a common grid); no JPEG block signature (held has one)). no</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
@@ -21055,7 +21931,7 @@
       </c>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>REPLACE 2026-08-23 -&gt; 2002_usgs_30cm_rgb.tif (effective (common grid) 56.25 vs 90.86 cm; HF energy ratio 1.538 (sharper on a common grid); no JPEG block signature (held has one)). no</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
@@ -21137,7 +22013,7 @@
       </c>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>REPLACE 2026-08-23 -&gt; 2002_usgs_30cm_rgb.tif (effective (common grid) 56.25 vs 90.86 cm; HF energy ratio 1.538 (sharper on a common grid); no JPEG block signature (held has one)). no</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
@@ -34919,6 +35795,546 @@
       <c r="P222" t="inlineStr">
         <is>
           <t>decision REPLACE: wins=['coverage 82.33 &gt; 38.0'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S16</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>USGS HRO Seattle-Tacoma 2002 original tiles (WAGDA Download)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>true GSD 30.0 cm; 3 bands; effective 41.41 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://wagda.lib.washington.edu:6080/arcgis/rest/services/Imagery_services/PugetSound_2002/ImageServer</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>https://wagda.lib.washington.edu:6080/arcgis/rest/services/Imagery_services/PugetSound_2002/ImageServer</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2002_usgs_30cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>this file REPLACES 2002_king_rgb.tif</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>decision REPLACE: wins=['effective (common grid) 56.25 vs 90.86 cm', 'HF energy ratio 1.538 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\USGS_HRO\_acq\U02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>N15 campaign acquisition (2015_naip_1m_rgbi.tif)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>true GSD 100.0 cm; 4 bands; effective 133.11 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2015_6208/</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2015_6208/</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2015_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_NOAA\2015\_acq\N15</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>N17 campaign acquisition (2017_naip_1m_rgbi.tif)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>true GSD 100.0 cm; 4 bands; effective 132.41 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2017_8572/</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2017_8572/</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>2017_naip_1m_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_NOAA\2017\_acq\N17</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>N21 campaign acquisition (2021_naip_60cm_rgbi.tif)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>true GSD 60.0 cm; 4 bands; effective 81.74 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2021_9586/</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>https://coastalimagery.blob.core.windows.net/digitalcoast/WA_NAIP_2021_9586/</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2021_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_NOAA\2021\_acq\N21</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>M18 campaign acquisition (2018_coe_marsh2cm_rgb.tif)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>true GSD 2.507 cm; 3 bands; effective None cm; EPSG:3857; city coverage 1.03%</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>https://maps.edmondswa.gov/gis/rest/services/Basemap/Edmonds_Marsh_2018/ImageServer</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>2018_coe_marsh2cm_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\CoE\_acq\M18</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>S17 campaign acquisition (2017_snoh_1ft_rgbi.tif)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 4 bands; effective 40.24 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2017/ImageServer</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2017/ImageServer</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2017_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S17</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>S19 campaign acquisition (2019_snoh_1ft_rgbi.tif)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 4 bands; effective 42.58 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2019/ImageServer</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2019/ImageServer</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>2019_snoh_1ft_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S19</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11601,6 +11601,68 @@
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>median of 5 Method_Provenance sites; common-grid vs 2021_snoh_rgbi.tif: new 20.05 / held 21.09 cm, HF ratio 1.432</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2015_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>median of 5 sites</t>
         </is>
@@ -12398,7 +12460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14225,7 +14287,7 @@
       </c>
       <c r="P18" s="1" t="inlineStr">
         <is>
-          <t>CLOSED LEADS: no WA consortium flight-date layer exists for 2021 or later (all 68 WAGeoservices services + 225 items enumerated; series ends 2020); the mosaic-catalog schema has no date field at all; WA NAIP 2021 does not cover quad 47122 (eastern WA only), so no NAIP ride-along date. Remaining route: the Hexagon flight log via Snohomish County DoIT, or the consortium contact (Joanne Markert, WA OCIO). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2021-06-25..11-11): 32 of 140 days eliminated; longest feasible blocks Jul 22-Aug 6, Jul 2-15, Aug 9-19. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
+          <t>*** SUPERSEDED 2026-08-23 by 2021_snoh_6in_rgbi.tif (full study extent on the native 0.5-ft lattice, nearest; this 53.4% clip was served bilinear on an unsnapped grid and is kept for provenance) *** CLOSED LEADS: no WA consortium flight-date layer exists for 2021 or later (all 68 WAGeoservices services + 225 items enumerated; series ends 2020); the mosaic-catalog schema has no date field at all; WA NAIP 2021 does not cover quad 47122 (eastern WA only), so no NAIP ride-along date. Remaining route: the Hexagon flight log via Snohomish County DoIT, or the consortium contact (Joanne Markert, WA OCIO). Weather elimination (ASOS KPAE+KSEA+KBFI, criterion calibrated to 46/46 known Edmonds flight days; 2021-06-25..11-11): 32 of 140 days eliminated; longest feasible blocks Jul 22-Aug 6, Jul 2-15, Aug 9-19. ELIMINATES ONLY - no surviving day is favoured. Per-day table: qc/imagery_date_evidence/weather/flyable_days.csv.</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
@@ -16250,8 +16312,198 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2021_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>2021s (campaign S21)</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>15.24</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>20.06 (median of 5 sites; 1.32x its grid); common grid vs held: 20.05 vs 21.09 cm, HF ratio 1.432</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>15.24 (0.5 ft)</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>2021-06-25 to 2021-11-11</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr">
+        <is>
+          <t>window of 140 days</t>
+        </is>
+      </c>
+      <c r="L39" s="1" t="inlineStr">
+        <is>
+          <t>unknown; the superseded clip was flown in the AFTERNOON (shadow azimuth)</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>https://snohomishcountywa.gov/5414/Interactive-Map-SCOPI</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>The 2021 aerial photos are 6 inch resolution and cover mainly the urban areas. The imagery was collected between June 25, 2021 and November 11, 2021.</t>
+        </is>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S21\measure.json): 50232x70518 px, 4 bands, EPSG:2285, 10,764,289,402 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 58.9, NDVI p90 0.618); JPEG 8x8 signature absent. Decision REPLACE: wins=['coverage 100.0 &gt; 39.5', 'HF energy ratio 1.432 (sharper on a common grid)'] losses=[]. inherits the 2021_snoh_rgbi.tif evidence</t>
+        </is>
+      </c>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R39" s="1" t="inlineStr"/>
+      <c r="S39" s="1" t="inlineStr"/>
+      <c r="T39" s="1" t="inlineStr"/>
+      <c r="U39" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2015_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>2015s (campaign S15)</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2015/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>41.39 (median of 5 sites; 1.36x its grid)</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
+        <is>
+          <t>2015-08-07 15:31 (HXIP 2015 1-ft flight over Edmonds = the NAIP 2015 delivery)</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr">
+        <is>
+          <t>single day + minute</t>
+        </is>
+      </c>
+      <c r="L40" s="1" t="inlineStr">
+        <is>
+          <t>single sortie over the city footprints</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/NAIP_2015_1ft_Ortho_Dates_and_Times_83s/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>"THEMENAME":"hxip_m_4712213_se_10_30","SDATE":"08/07/2015 15:31","SUNEL":46,"ACCURACY":"0.72m (ce 95%)" (city-centroid point query; raw response qc/imagery_date_evidence/raw_records/wa_2015_1ft_citycentroid.json)</t>
+        </is>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S15\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,209,251,170 B; city coverage 100.0%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. band 4 = ALPHA (pilot, both rendering modes) - exported 3-band</t>
+        </is>
+      </c>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R40" s="1" t="inlineStr"/>
+      <c r="S40" s="1" t="inlineStr"/>
+      <c r="T40" s="1" t="inlineStr"/>
+      <c r="U40" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U38"/>
+  <autoFilter ref="A1:U40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17578,7 +17830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P229"/>
+  <dimension ref="A1:P231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30377,7 +30629,7 @@
       </c>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2021_snoh_6in_rgbi.tif (coverage 100.0 &gt; 39.5; HF energy ratio 1.432 (sharper on a common grid)). YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr">
@@ -30541,7 +30793,7 @@
       </c>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2021_snoh_6in_rgbi.tif (coverage 100.0 &gt; 39.5; HF energy ratio 1.432 (sharper on a common grid)). YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr">
@@ -30787,7 +31039,7 @@
       </c>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
+          <t>REPLACE 2026-08-23 -&gt; 2021_snoh_6in_rgbi.tif (coverage 100.0 &gt; 39.5; HF energy ratio 1.432 (sharper on a common grid)). YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr">
@@ -36286,7 +36538,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>true GSD 30.48 cm; 4 bands; effective 42.58 cm; EPSG:2285; city coverage 100.0%</t>
@@ -36335,6 +36586,161 @@
       <c r="P229" t="inlineStr">
         <is>
           <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S19</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2021 full extent, native 0.5 ft RGBI</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>true GSD 15.24 cm; 4 bands; effective 20.06 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2021/ImageServer</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2021_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>this file REPLACES 2021_snoh_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>decision REPLACE: wins=['coverage 100.0 &gt; 39.5', 'HF energy ratio 1.432 (sharper on a common grid)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S21</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2015 1 ft RGB (band 4 = alpha, dropped)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 41.39 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2015/ImageServer</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2015/ImageServer</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>2015_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S15</t>
         </is>
       </c>
     </row>
@@ -37174,7 +37580,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
+          <t>RESOLVED 2026-08-23: REPLACE by 2021_snoh_6in_rgbi.tif. YES - re-acquire full extent from the Snohomish ImageServer (Tier A, alongside 2016)</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11665,6 +11665,161 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2018_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1990_snoh_10ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>304.801</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E24" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>median of 3 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1998_snoh_3ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E25" t="n">
+        <v>163.09</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2001_snoh_1ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E26" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2023_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NAIP_AZURE/2023</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E27" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>median of 5 Method_Provenance sites; common-grid vs 2023_naip_rgbi.tif: new 83.49 / held 84.61 cm, HF ratio 1.406</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -15024,7 +15179,7 @@
       </c>
       <c r="P25" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues). Context: NAIP 2021 over Edmonds exists (all 8 QQs STAC datetime 2021-07-13, INFERRED from file names - the FGDC sidecars for quad 47122 are absent from the Azure mirror).</t>
+          <t>*** SUPERSEDED 2026-08-23 by 2023_naip_60cm_rgbi.tif (the 8 original Azure DOQQs mosaicked, full study extent; this 69% smoothed re-export is kept for provenance) *** OCTOBER. Held bands 1-3 byte-identical to rgb_2023, band 4 to ir_2023 (DataLake_Issues). Context: NAIP 2021 over Edmonds exists (all 8 QQs STAC datetime 2021-07-13, INFERRED from file names - the FGDC sidecars for quad 47122 are absent from the Azure mirror).</t>
         </is>
       </c>
       <c r="Q25" s="1" t="inlineStr">
@@ -16502,8 +16657,483 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>2018_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>2018s (campaign S18)</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2018/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>15.24</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>20.9 (median of 5 sites; 1.37x its grid)</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>15.24 (0.5 ft HXIP 6-in delivery)</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
+        <is>
+          <t>2018-08-07 (WA consortium 6-in flight area over Edmonds)</t>
+        </is>
+      </c>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="inlineStr">
+        <is>
+          <t>single flight area</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>https://services.arcgis.com/jsIt88o09Q0r1j8h/arcgis/rest/services/2018_Statewide_imagery_consortium_6_inch_flight_areas/FeatureServer/0/query</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>"IDATE":"2018-08-07" (city-centroid and city-bbox queries agree; raw responses qc/imagery_date_evidence/raw_records/wa_2018_6in_city*.json)</t>
+        </is>
+      </c>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S18\measure.json): 50232x70518 px, 4 bands, EPSG:2285, 11,470,030,126 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 62.34, NDVI p90 0.713); JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. the ONLY citywide 2018 imagery held; same Aug-07 day-of-month as the 2015 flight by coincidence</t>
+        </is>
+      </c>
+      <c r="Q41" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R41" s="1" t="inlineStr"/>
+      <c r="S41" s="1" t="inlineStr"/>
+      <c r="T41" s="1" t="inlineStr"/>
+      <c r="U41" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>1990_snoh_10ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>1990s (campaign S90)</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1990/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>304.8</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>367.45 (median of 3 sites; 1.21x its grid)</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>304.8 (10 ft)</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_1990 only)</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1990/ImageServer</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S90\measure.json): 2513x3527 px, 1 bands, EPSG:2285, 6,713,257 B; city coverage 98.97%, study-extent 86.59%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 10-ft b/w; SCOPI's per-year list starts at 2017; no flight-date record found for any pan year</t>
+        </is>
+      </c>
+      <c r="Q42" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R42" s="1" t="inlineStr"/>
+      <c r="S42" s="1" t="inlineStr"/>
+      <c r="T42" s="1" t="inlineStr"/>
+      <c r="U42" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>1998_snoh_3ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>1998s (campaign S98)</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1998/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>91.44</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>163.09 (median of 5 sites; 1.78x its grid)</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>91.44 (3 ft DNR scan)</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year only; the service's keyProperties name the SOURCE, not the date)</t>
+        </is>
+      </c>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1998/ImageServer/keyProperties?f=json</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>U:\\1998\\b-w\\3ft_res\\dnr\\t26nr04e.tif (keyProperties IMAGE__INPUT_NAME, JSON escaping verbatim - a WA DNR 3-ft b/w product; raw response qc/imagery_date_evidence/raw_records/snoco_1998_keyProperties.json)</t>
+        </is>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S98\measure.json): 8373x11754 px, 1 bands, EPSG:2285, 79,721,073 B; city coverage 100.0%, study-extent 99.71%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. source = WA DNR 1998 orthophoto scan; pairs with the held 1998_king_pan (different product)</t>
+        </is>
+      </c>
+      <c r="Q43" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R43" s="1" t="inlineStr"/>
+      <c r="S43" s="1" t="inlineStr"/>
+      <c r="T43" s="1" t="inlineStr"/>
+      <c r="U43" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>2001_snoh_1ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>2001s (campaign S01)</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2001/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>105.13 (median of 5 sites; 3.45x its grid)</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft scanned film)</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2001 only)</t>
+        </is>
+      </c>
+      <c r="K44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2001/ImageServer</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S01\measure.json): 25117x35260 px, 1 bands, EPSG:2285, 474,665,129 B; city coverage 99.9%, study-extent 75.13%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 1-ft scanned film (effective 105 cm); no flight-date record found</t>
+        </is>
+      </c>
+      <c r="Q44" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R44" s="1" t="inlineStr"/>
+      <c r="S44" s="1" t="inlineStr"/>
+      <c r="T44" s="1" t="inlineStr"/>
+      <c r="U44" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>2023_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>2023n (campaign N23f)</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_060cm_2023/47122/ via pipeline/acquire_imagery.py (files)</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>metre</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:26910</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>82.56 (median of 5 sites; 1.38x its grid); common grid vs held: 83.49 vs 84.61 cm, HF ratio 1.406</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>60 (delivered DOQQ)</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>single day</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>single (all 8 quads 2023-10-07)</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
+        </is>
+      </c>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip?restype=container&amp;comp=list&amp;prefix=v002/wa/2023/wa_060cm_2023/47122/m_47122&amp;maxresults=200</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>m_4712213_ne_10_060_20231007_20240209.tif ... m_4712214_sw_10_060_20231007_20240209.tif (all 8 Edmonds quads carry capture 20231007 + version 20240209; listing saved qc/imagery_date_evidence/raw_records/azure_naip_2023_47122_listing.xml)</t>
+        </is>
+      </c>
+      <c r="P45" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_AZURE\2023\_acq\N23f\measure.json): 12556x17768 px, 4 bands, EPSG:26910, 727,595,134 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 57.93, NDVI p90 0.529); JPEG 8x8 signature absent. Decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.406 (sharper on a common grid)'] losses=[]. confirms the held 2023n date independently; October leaf-state caveat as 2019n/2019s</t>
+        </is>
+      </c>
+      <c r="Q45" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R45" s="1" t="inlineStr"/>
+      <c r="S45" s="1" t="inlineStr"/>
+      <c r="T45" s="1" t="inlineStr"/>
+      <c r="U45" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U40"/>
+  <autoFilter ref="A1:U45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17830,7 +18460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P231"/>
+  <dimension ref="A1:P236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36692,7 +37322,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>true GSD 30.48 cm; 3 bands; effective 41.39 cm; EPSG:2285; city coverage 100.0%</t>
@@ -36741,6 +37370,392 @@
       <c r="P231" t="inlineStr">
         <is>
           <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S15</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2018 HXIP 6-in RGBI (2018-08-07)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>true GSD 15.24 cm; 4 bands; effective 20.9 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2018/ImageServer</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2018/ImageServer</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2018_snoh_6in_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S18</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_1990 10-ft b/w</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>true GSD 304.801 cm; 1 bands; effective 367.45 cm; EPSG:2285; city coverage 98.97%</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1990/ImageServer</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1990/ImageServer</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>1990_snoh_10ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S90</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_1998 3-ft b/w (DNR scan)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>true GSD 91.44 cm; 1 bands; effective 163.09 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1998/ImageServer</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1998/ImageServer</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>1998_snoh_3ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S98</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2001 1-ft b/w</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 1 bands; effective 105.13 cm; EPSG:2285; city coverage 99.9%</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2001/ImageServer</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2001/ImageServer</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>2001_snoh_1ft_pan.tif</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>NAIP 2023 full-extent DOQQ mosaic (2023-10-07)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>true GSD 60.0 cm; 4 bands; effective 82.56 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_060cm_2023/47122/</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_060cm_2023/47122/</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>2023_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>this file REPLACES 2023_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.406 (sharper on a common grid)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_AZURE\2023\_acq\N23f</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11820,6 +11820,99 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>median of 5 Method_Provenance sites; common-grid vs 2023_naip_rgbi.tif: new 83.49 / held 84.61 cm, HF ratio 1.406</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2002_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E28" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2003_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2007_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E30" t="n">
+        <v>38.53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -16200,12 +16293,12 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>0.037323</t>
+          <t>0.03732276770595208</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
+          <t>metre</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -16215,7 +16308,7 @@
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.507</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
@@ -17132,8 +17225,293 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>2002_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>2002s (campaign S02)</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>42.1 (median of 5 sites; 1.38x its grid)</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2002 only)</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S02\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,704,437,706 B; city coverage None%, study-extent 87.61%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. NOT the USGS HRO flight: dup test vs 2002_usgs_30cm_rgb r median 0.847 at the 5 sites (same-flight pairs run 0.98-0.997; SnoCo/_acq/S02/dup_test_vs_U02.json) - a second, distinct 2002 acquisition with its own unknown date</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R46" s="1" t="inlineStr"/>
+      <c r="S46" s="1" t="inlineStr"/>
+      <c r="T46" s="1" t="inlineStr"/>
+      <c r="U46" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>2003_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>2003s (campaign S03)</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>41.62 (median of 5 sites; 1.37x its grid)</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2003 only)</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S03\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,501,046,192 B; city coverage None%, study-extent 87.49%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 2003 = a calendar year the project previously had NO imagery for</t>
+        </is>
+      </c>
+      <c r="Q47" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R47" s="1" t="inlineStr"/>
+      <c r="S47" s="1" t="inlineStr"/>
+      <c r="T47" s="1" t="inlineStr"/>
+      <c r="U47" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>2007_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>2007s (campaign S07)</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>38.53 (median of 5 sites; 1.26x its grid); common grid vs held: 39.58 vs 39.34 cm, HF ratio 1.654</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2007 only)</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S07\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,548,181,188 B; city coverage None%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=['HF energy ratio 1.654 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]. flip test vs 2007_king FAILED (eff 38.5 vs required &lt; 22.95) - complement, King keeps the 2007 key</t>
+        </is>
+      </c>
+      <c r="Q48" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U45"/>
+  <autoFilter ref="A1:U48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18460,7 +18838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P236"/>
+  <dimension ref="A1:P239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -37707,7 +38085,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>true GSD 60.0 cm; 4 bands; effective 82.56 cm; EPSG:26910; city coverage 100.0%</t>
@@ -37756,6 +38133,238 @@
       <c r="P236" t="inlineStr">
         <is>
           <t>decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.406 (sharper on a common grid)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_AZURE\2023\_acq\N23f</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2002 1-ft RGB (NOT the USGS flight: dup r 0.847)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 42.1 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2002_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2003 1-ft RGB (new project year)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 41.62 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2003_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S03</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2007 1-ft RGB (flip test vs 2007_king failed - complement)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 38.53 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2007_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=['HF energy ratio 1.654 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S07</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11913,6 +11913,37 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2019_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NAIP_AZURE/2019</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>60</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E31" t="n">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>median of 5 Method_Provenance sites; common-grid vs 2019_naip_rgbi.tif: new 84.3 / held 87.38 cm, HF ratio 1.358</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -15165,7 +15196,7 @@
       </c>
       <c r="P24" s="1" t="inlineStr">
         <is>
-          <t>OCTOBER. No NAIP metadata record (2015/2017/2021 Digital Coast) contains any leaf-on/leaf-off statement - only 'peak crop growing conditions'; the 'NAIP is leaf-on by spec' assumption has no documentary basis.</t>
+          <t>*** SUPERSEDED 2026-08-23 by 2019_naip_60cm_rgbi.tif (the 8 original Azure DOQQs, full study extent; this 69% smoothed re-export is kept for provenance) *** OCTOBER. No NAIP metadata record (2015/2017/2021 Digital Coast) contains any leaf-on/leaf-off statement - only 'peak crop growing conditions'; the 'NAIP is leaf-on by spec' assumption has no documentary basis.</t>
         </is>
       </c>
       <c r="Q24" s="1" t="inlineStr">
@@ -16293,12 +16324,12 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>0.03732276770595208</t>
+          <t>0.037323</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>metre</t>
+          <t>metre (Web Mercator, inflated 1/cos(lat))</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -16308,7 +16339,7 @@
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>2.507</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
@@ -17133,17 +17164,17 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2023_naip_60cm_rgbi.tif</t>
+          <t>2019_naip_60cm_rgbi.tif</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>2023n (campaign N23f)</t>
+          <t>2019n (campaign N19f)</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_060cm_2023/47122/ via pipeline/acquire_imagery.py (files)</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_60cm_2019/47122/ via pipeline/acquire_imagery.py (files)</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -17168,7 +17199,7 @@
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>82.56 (median of 5 sites; 1.38x its grid); common grid vs held: 83.49 vs 84.61 cm, HF ratio 1.406</t>
+          <t>82.54 (median of 5 sites; 1.38x its grid); common grid vs held: 84.3 vs 87.38 cm, HF ratio 1.358</t>
         </is>
       </c>
       <c r="I45" s="1" t="inlineStr">
@@ -17178,7 +17209,7 @@
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2019-10-11</t>
         </is>
       </c>
       <c r="K45" s="1" t="inlineStr">
@@ -17188,7 +17219,7 @@
       </c>
       <c r="L45" s="1" t="inlineStr">
         <is>
-          <t>single (all 8 quads 2023-10-07)</t>
+          <t>single (all 8 quads 2019-10-11)</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -17198,17 +17229,17 @@
       </c>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>https://naipeuwest.blob.core.windows.net/naip?restype=container&amp;comp=list&amp;prefix=v002/wa/2023/wa_060cm_2023/47122/m_47122&amp;maxresults=200</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip?restype=container&amp;comp=list&amp;prefix=v002/wa/2019/wa_60cm_2019/47122/m_47122&amp;maxresults=200</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>m_4712213_ne_10_060_20231007_20240209.tif ... m_4712214_sw_10_060_20231007_20240209.tif (all 8 Edmonds quads carry capture 20231007 + version 20240209; listing saved qc/imagery_date_evidence/raw_records/azure_naip_2023_47122_listing.xml)</t>
+          <t>m_4712213_ne_10_060_20191011.tif ... m_4712214_sw_10_060_20191011.tif (all 8 Edmonds quads carry 20191011; listing saved qc/imagery_date_evidence/raw_records/azure_naip_2019_47122_listing.xml)</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
         <is>
-          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_AZURE\2023\_acq\N23f\measure.json): 12556x17768 px, 4 bands, EPSG:26910, 727,595,134 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 57.93, NDVI p90 0.529); JPEG 8x8 signature absent. Decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.406 (sharper on a common grid)'] losses=[]. confirms the held 2023n date independently; October leaf-state caveat as 2019n/2019s</t>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_AZURE\2019\_acq\N19f\measure.json): 12556x17768 px, 4 bands, EPSG:26910, 757,507,269 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 60.69, NDVI p90 0.56); JPEG 8x8 signature absent. Decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.358 (sharper on a common grid)'] losses=[]. = the S19/HXIP flight date (same Hexagon acquisition); replaces the smoothed 69% clip; reg-loss waived as a blur artifact of the metric (registration_blur_test.json)</t>
         </is>
       </c>
       <c r="Q45" s="1" t="inlineStr">
@@ -17228,82 +17259,82 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2002_snoh_1ft_rgb.tif</t>
+          <t>2023_naip_60cm_rgbi.tif</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>2002s (campaign S02)</t>
+          <t>2023n (campaign N23f)</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer via pipeline/acquire_imagery.py (export)</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2023/wa_060cm_2023/47122/ via pipeline/acquire_imagery.py (files)</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>US survey foot</t>
+          <t>metre</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>EPSG:2285</t>
+          <t>EPSG:26910</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>42.1 (median of 5 sites; 1.38x its grid)</t>
+          <t>82.56 (median of 5 sites; 1.38x its grid); common grid vs held: 83.49 vs 84.61 cm, HF ratio 1.406</t>
         </is>
       </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>30.48 (1 ft)</t>
+          <t>60 (delivered DOQQ)</t>
         </is>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>NOT FOUND (year from the county service name Aerial_2002 only)</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>single day</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>NOT FOUND</t>
+          <t>single (all 8 quads 2023-10-07)</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>PUBLISHED</t>
         </is>
       </c>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer</t>
+          <t>https://naipeuwest.blob.core.windows.net/naip?restype=container&amp;comp=list&amp;prefix=v002/wa/2023/wa_060cm_2023/47122/m_47122&amp;maxresults=200</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m_4712213_ne_10_060_20231007_20240209.tif ... m_4712214_sw_10_060_20231007_20240209.tif (all 8 Edmonds quads carry capture 20231007 + version 20240209; listing saved qc/imagery_date_evidence/raw_records/azure_naip_2023_47122_listing.xml)</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
         <is>
-          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S02\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,704,437,706 B; city coverage None%, study-extent 87.61%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. NOT the USGS HRO flight: dup test vs 2002_usgs_30cm_rgb r median 0.847 at the 5 sites (same-flight pairs run 0.98-0.997; SnoCo/_acq/S02/dup_test_vs_U02.json) - a second, distinct 2002 acquisition with its own unknown date</t>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\NAIP_AZURE\2023\_acq\N23f\measure.json): 12556x17768 px, 4 bands, EPSG:26910, 727,595,134 B; city coverage 100.0%, study-extent 100.0%; band 4 NIR (std 57.93, NDVI p90 0.529); JPEG 8x8 signature absent. Decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.406 (sharper on a common grid)'] losses=[]. confirms the held 2023n date independently; October leaf-state caveat as 2019n/2019s</t>
         </is>
       </c>
       <c r="Q46" s="1" t="inlineStr">
@@ -17323,17 +17354,17 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2003_snoh_1ft_rgb.tif</t>
+          <t>2002_snoh_1ft_rgb.tif</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>2003s (campaign S03)</t>
+          <t>2002s (campaign S02)</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer via pipeline/acquire_imagery.py (export)</t>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer via pipeline/acquire_imagery.py (export)</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -17358,7 +17389,7 @@
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>41.62 (median of 5 sites; 1.37x its grid)</t>
+          <t>42.1 (median of 5 sites; 1.38x its grid)</t>
         </is>
       </c>
       <c r="I47" s="1" t="inlineStr">
@@ -17368,7 +17399,7 @@
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>NOT FOUND (year from the county service name Aerial_2003 only)</t>
+          <t>NOT FOUND (year from the county service name Aerial_2002 only)</t>
         </is>
       </c>
       <c r="K47" s="1" t="inlineStr">
@@ -17388,7 +17419,7 @@
       </c>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer</t>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2002/ImageServer</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
@@ -17398,7 +17429,7 @@
       </c>
       <c r="P47" s="1" t="inlineStr">
         <is>
-          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S03\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,501,046,192 B; city coverage None%, study-extent 87.49%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 2003 = a calendar year the project previously had NO imagery for</t>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S02\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,704,437,706 B; city coverage 100.0%, study-extent 87.61%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. NOT the USGS HRO flight: dup test vs 2002_usgs_30cm_rgb r median 0.847 at the 5 sites (same-flight pairs run 0.98-0.997; SnoCo/_acq/S02/dup_test_vs_U02.json) - a second, distinct 2002 acquisition with its own unknown date</t>
         </is>
       </c>
       <c r="Q47" s="1" t="inlineStr">
@@ -17418,17 +17449,17 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2007_snoh_1ft_rgb.tif</t>
+          <t>2003_snoh_1ft_rgb.tif</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>2007s (campaign S07)</t>
+          <t>2003s (campaign S03)</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer via pipeline/acquire_imagery.py (export)</t>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer via pipeline/acquire_imagery.py (export)</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -17453,7 +17484,7 @@
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>38.53 (median of 5 sites; 1.26x its grid); common grid vs held: 39.58 vs 39.34 cm, HF ratio 1.654</t>
+          <t>41.62 (median of 5 sites; 1.37x its grid)</t>
         </is>
       </c>
       <c r="I48" s="1" t="inlineStr">
@@ -17463,7 +17494,7 @@
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>NOT FOUND (year from the county service name Aerial_2007 only)</t>
+          <t>NOT FOUND (year from the county service name Aerial_2003 only)</t>
         </is>
       </c>
       <c r="K48" s="1" t="inlineStr">
@@ -17483,7 +17514,7 @@
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer</t>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2003/ImageServer</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
@@ -17493,7 +17524,7 @@
       </c>
       <c r="P48" s="1" t="inlineStr">
         <is>
-          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S07\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,548,181,188 B; city coverage None%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=['HF energy ratio 1.654 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]. flip test vs 2007_king FAILED (eff 38.5 vs required &lt; 22.95) - complement, King keeps the 2007 key</t>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S03\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,501,046,192 B; city coverage 100.0%, study-extent 87.49%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 2003 = a calendar year the project previously had NO imagery for</t>
         </is>
       </c>
       <c r="Q48" s="1" t="inlineStr">
@@ -17510,8 +17541,103 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>2007_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>2007s (campaign S07)</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>38.53 (median of 5 sites; 1.26x its grid); common grid vs held: 39.58 vs 39.34 cm, HF ratio 1.654</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2007 only)</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2007/ImageServer</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S07\measure.json): 25116x35259 px, 3 bands, EPSG:2285, 1,548,181,188 B; city coverage 100.0%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=['HF energy ratio 1.654 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]. flip test vs 2007_king FAILED (eff 38.5 vs required &lt; 22.95) - complement, King keeps the 2007 key</t>
+        </is>
+      </c>
+      <c r="Q49" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R49" s="1" t="inlineStr"/>
+      <c r="S49" s="1" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U48"/>
+  <autoFilter ref="A1:U49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18838,7 +18964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P239"/>
+  <dimension ref="A1:P240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31063,7 +31189,7 @@
       </c>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>REPLACE 2026-08-23 -&gt; 2019_naip_60cm_rgbi.tif (coverage 100.0 &gt; 66.98; HF energy ratio 1.358 (sharper on a common grid)). no</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr">
@@ -38316,7 +38442,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>true GSD 30.48 cm; 3 bands; effective 38.53 cm; EPSG:2285; city coverage 100.0%</t>
@@ -38365,6 +38490,84 @@
       <c r="P239" t="inlineStr">
         <is>
           <t>decision COMPLEMENT: wins=['HF energy ratio 1.654 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S07</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>NAIP 2019 full-extent DOQQ mosaic (2019-10-11)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>true GSD 60.0 cm; 4 bands; effective 82.54 cm; EPSG:26910; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_60cm_2019/47122/</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://naipeuwest.blob.core.windows.net/naip/v002/wa/2019/wa_60cm_2019/47122/</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>2019_naip_60cm_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>this file REPLACES 2019_naip_rgbi.tif</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.358 (sharper on a common grid)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_AZURE\2019\_acq\N19f</t>
         </is>
       </c>
     </row>
@@ -39238,7 +39441,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>RESOLVED 2026-08-23: REPLACE by 2019_naip_60cm_rgbi.tif. no</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11944,6 +11944,192 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>median of 5 Method_Provenance sites; common-grid vs 2019_naip_rgbi.tif: new 84.3 / held 87.38 cm, HF ratio 1.358</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2009_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2011_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E33" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2012_snoh_9in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1996_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E35" t="n">
+        <v>136.19</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2006_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>100</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E36" t="n">
+        <v>145.46</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2013_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>100.021</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E37" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-23 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17636,8 +17822,578 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>2009_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>2009s (campaign S09)</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2009/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>39.74 (median of 5 sites; 1.3x its grid); common grid vs held: 40.88 vs 39.33 cm, HF ratio 1.128</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2009 only)</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2009/ImageServer</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S09\measure.json): 25117x35260 px, 3 bands, EPSG:2285, 2,348,259,187 B; city coverage 100.0%, study-extent 98.42%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=['coverage 98.42 &gt; 94.92', 'HF energy ratio 1.128 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]. Aerials Express product per the service; possibly the same flight as 2009_king - identity untested</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>2011_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>2011s (campaign S11)</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2011/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2926</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>38.12 (median of 5 sites; 1.25x its grid)</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>30.48 (1 ft)</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2011 only)</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2011/ImageServer</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S11\measure.json): 25117x35259 px, 3 bands, EPSG:2926, 1,987,295,246 B; city coverage 99.63%, study-extent 79.92%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 2011 = a calendar year the project previously had NO imagery for</t>
+        </is>
+      </c>
+      <c r="Q51" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>2012_snoh_9in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>2012s (campaign S12)</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2012/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2926</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>29.81 (median of 5 sites; 1.3x its grid); common grid vs held: 29.59 vs 38.94 cm, HF ratio 1.571</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>22.86 (0.75 ft)</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2012 only)</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2012/ImageServer</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S12\measure.json): 33489x47012 px, 3 bands, EPSG:2926, 3,237,421,325 B; city coverage 99.63%, study-extent 82.29%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=['effective (common grid) 29.59 vs 38.94 cm', 'HF energy ratio 1.571 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=['less coverage']. the year the county sells on media; free from the public service; sharper than 2012_king on a common grid but 82.3% coverage</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>1996_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>1996s (campaign S96)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1996/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>3.280833</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>136.19 (median of 5 sites; 1.36x its grid)</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m)</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_1996 only)</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1996/ImageServer</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S96\measure.json): 7656x10748 px, 3 bands, EPSG:2285, 221,226,039 B; city coverage 100.0%, study-extent 94.13%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. earliest COLOR imagery of Edmonds held; outside the 2000-2024 span, no year key</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>2006_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>2006s (campaign S06)</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2006/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>3.280833</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>145.46 (median of 5 sites; 1.45x its grid)</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m)</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2006 only)</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2006/ImageServer</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P54" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S06\measure.json): 7656x10748 px, 3 bands, EPSG:2285, 218,544,136 B; city coverage 100.0%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 2006 = a new project year; likely the NAIP 2006 republished (untested)</t>
+        </is>
+      </c>
+      <c r="Q54" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>2013_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>2013s (campaign S13)</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2013/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>3.281527</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>100.02</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>137.5 (median of 5 sites; 1.37x its grid)</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>100 (1 m)</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>NOT FOUND (year from the county service name Aerial_2013 only)</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>NOT FOUND</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2013/ImageServer</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P55" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S13\measure.json): 7655x10745 px, 3 bands, EPSG:2285, 155,772,878 B; city coverage 100.0%, study-extent 100.0%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. 1-m complement to 2013_king</t>
+        </is>
+      </c>
+      <c r="Q55" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U49"/>
+  <autoFilter ref="A1:U55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18964,7 +19720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P240"/>
+  <dimension ref="A1:P246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -38519,7 +39275,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>true GSD 60.0 cm; 4 bands; effective 82.54 cm; EPSG:26910; city coverage 100.0%</t>
@@ -38568,6 +39323,469 @@
       <c r="P240" t="inlineStr">
         <is>
           <t>decision REPLACE: wins=['coverage 100.0 &gt; 66.98', 'HF energy ratio 1.358 (sharper on a common grid)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\NAIP_AZURE\2019\_acq\N19f</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2009 1-ft RGB (Aerials Express)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 39.74 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2009/ImageServer</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2009/ImageServer</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2009_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=['coverage 98.42 &gt; 94.92', 'HF energy ratio 1.128 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S09</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2011 1-ft RGB (new project year)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>true GSD 30.48 cm; 3 bands; effective 38.12 cm; EPSG:2926; city coverage 99.63%</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2011/ImageServer</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2011/ImageServer</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>2011_snoh_1ft_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S11</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2012 9-in RGB (sharper than 2012_king, partial)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>true GSD 22.86 cm; 3 bands; effective 29.81 cm; EPSG:2926; city coverage 99.63%</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2012/ImageServer</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2012/ImageServer</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2012_snoh_9in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=['effective (common grid) 29.59 vs 38.94 cm', 'HF energy ratio 1.571 (sharper on a common grid)', 'no JPEG block signature (held has one)'] losses=['less coverage']; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S12</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_1996 1-m RGB (earliest color)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>true GSD 100.0 cm; 3 bands; effective 136.19 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1996/ImageServer</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_1996/ImageServer</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>1996_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S96</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2006 1-m RGB (new project year)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>true GSD 100.0 cm; 3 bands; effective 145.46 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2006/ImageServer</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2006/ImageServer</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2006_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Snohomish Aerial_2013 1-m RGB</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>true GSD 100.021 cm; 3 bands; effective 137.5 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2013/ImageServer</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2013/ImageServer</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>2013_snoh_1m_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S13</t>
         </is>
       </c>
     </row>

--- a/Scripts/imagery_catalog_2026-08-22.xlsx
+++ b/Scripts/imagery_catalog_2026-08-22.xlsx
@@ -33,7 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licensing_Risk" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pixel_Size_And_Date'!$A$1:$U$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MASTER'!$A$1:$P$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'KingCo_SDC_Catalog'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DataLake_Issues'!$A$1:$C$15</definedName>
@@ -10920,7 +10920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12128,6 +12128,99 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2020_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-24 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2022_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-24 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>median of 5 sites</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SnoCo</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NEW 2026-08-24 (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>median of 5 sites</t>
         </is>
@@ -12925,7 +13018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -18392,8 +18485,281 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>2020_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>2020s (campaign S20)</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2020/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>9.77 (median of 5 sites; 1.28x its grid)</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ft)</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>inherited from the 2020_coe_rgb.tif row</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr"/>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>(date evidence inherited from the 2020_coe_rgb.tif row - same flight, same service)</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S20\measure.json): 100463x141035 px, 3 bands, EPSG:2285, 31,012,508,090 B; city coverage 100.0%, study-extent 98.08%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. same county EagleView 2020 programme the anchor was cut from; ANCHOR NEVER FLIPPED; no JPEG signature (held CoE copy has one)</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr"/>
+      <c r="S56" s="1" t="inlineStr"/>
+      <c r="T56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>2022_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>2022s (campaign S22)</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2022/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>9.52 (median of 5 sites; 1.25x its grid)</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ft)</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>inherited from the 2022_coe_rgb.tif row</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr"/>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>(date evidence inherited from the 2022_coe_rgb.tif row - same flight, same service)</t>
+        </is>
+      </c>
+      <c r="P57" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S22\measure.json): 100463x141035 px, 3 bands, EPSG:2285, 30,182,395,806 B; city coverage 100.0%, study-extent 98.08%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. same county EagleView 2022 programme; no JPEG signature (held CoE copy has one)</t>
+        </is>
+      </c>
+      <c r="Q57" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>2024_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>2024s (campaign S24)</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2024/ImageServer via pipeline/acquire_imagery.py (export)</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>US survey foot</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>EPSG:2285</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>7.62</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>10.2 (median of 5 sites; 1.34x its grid)</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>7.62 (0.25 ft)</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>inherited from the 2024_coe_rgb.tif row</t>
+        </is>
+      </c>
+      <c r="K58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>INFERRED</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr"/>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>(date evidence inherited from the 2024_coe_rgb.tif row - same flight, same service)</t>
+        </is>
+      </c>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>MEASURED on arrival (D:\edmonds-pipeline\Imagery\SnoCo\_acq\S24\measure.json): 100463x141035 px, 3 bands, EPSG:2285, 29,570,524,494 B; city coverage 100.0%, study-extent 98.08%; JPEG 8x8 signature absent. Decision COMPLEMENT: wins=[] losses=[]. same county EagleView 2024 programme; no JPEG signature (held CoE copy has one)</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>grid/true/effective MEASURED (acquire_imagery verify)</t>
+        </is>
+      </c>
+      <c r="R58" s="1" t="inlineStr"/>
+      <c r="S58" s="1" t="inlineStr"/>
+      <c r="T58" s="1" t="inlineStr"/>
+      <c r="U58" s="1" t="inlineStr">
+        <is>
+          <t>held imagery (campaign)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U55"/>
+  <autoFilter ref="A1:U58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19720,7 +20086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P246"/>
+  <dimension ref="A1:P249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39737,7 +40103,6 @@
           <t>see Pixel_Size_And_Date row</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
           <t>true GSD 100.021 cm; 3 bands; effective 137.5 cm; EPSG:2285; city coverage 100.0%</t>
@@ -39786,6 +40151,238 @@
       <c r="P246" t="inlineStr">
         <is>
           <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S13</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Snohomish EagleView 3-in RGB (county serving, no cache signature)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>true GSD 7.62 cm; 3 bands; effective 9.77 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2020/ImageServer</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2020/ImageServer</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2020_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S20</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Snohomish EagleView 3-in RGB (county serving, no cache signature)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>true GSD 7.62 cm; 3 bands; effective 9.52 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2022/ImageServer</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2022/ImageServer</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2022_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S22</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>imagery</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Snohomish EagleView 3-in RGB (county serving, no cache signature)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>acquire_imagery campaign 2026-08-23</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>see Pixel_Size_And_Date row</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>true GSD 7.62 cm; 3 bands; effective 10.2 cm; EPSG:2285; city coverage 100.0%</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2024/ImageServer</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>https://gis.snoco.org/img/rest/services/Imagery/Aerial_2024/ImageServer</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2024_snoh_3in_rgb.tif</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>none known (measured on arrival)</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>n/a (already held)</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>decision COMPLEMENT: wins=[] losses=[]; measure.json under D:\edmonds-pipeline\Imagery\SnoCo\_acq\S24</t>
         </is>
       </c>
     </row>
